--- a/Bank_Loan_Quarterly_Compound_Interest_TEMPLATE.xlsx
+++ b/Bank_Loan_Quarterly_Compound_Interest_TEMPLATE.xlsx
@@ -13,25 +13,8 @@
     <sheet name="Engine" sheetId="4" state="veryHidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="BF_Date">'Loan Statement'!$H$6</definedName>
-    <definedName name="BF_Amount">'Loan Statement'!$H$7</definedName>
-    <definedName name="Day_Basis">'Loan Statement'!$H$8</definedName>
-    <definedName name="Qtr_Mode">'Loan Statement'!$H$9</definedName>
-    <definedName name="Locked_To">'Loan Statement'!$H$10</definedName>
-    <definedName name="Eff_Dates">'Loan Statement'!$O$14:$O$325</definedName>
-    <definedName name="Bal_Col">'Loan Statement'!$S$14:$S$325</definedName>
-    <definedName name="Accr_Col">'Loan Statement'!$T$14:$T$325</definedName>
-    <definedName name="Big_Date">'Engine'!$B$1</definedName>
-    <definedName name="R1_From">'Engine'!$B$2</definedName>
-    <definedName name="R1_To">'Engine'!$B$3</definedName>
-    <definedName name="R2_From">'Engine'!$B$4</definedName>
-    <definedName name="R2_To">'Engine'!$B$5</definedName>
-    <definedName name="R3_From">'Engine'!$B$6</definedName>
-    <definedName name="R3_To">'Engine'!$B$7</definedName>
-    <definedName name="Rate_1">'Engine'!$B$8</definedName>
-    <definedName name="Rate_2">'Engine'!$B$9</definedName>
-    <definedName name="Rate_3">'Engine'!$B$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Loan Statement'!$13:$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Quarter Summary'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -798,20 +781,20 @@
   <dimension ref="A1:T325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12.5" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10.5" customWidth="1" min="8" max="8"/>
-    <col width="7.5" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12.5" customWidth="1" min="14" max="14"/>
+    <col width="4.5" customWidth="1" min="1" max="1"/>
+    <col width="10.5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" min="7" max="7"/>
+    <col width="7.5" customWidth="1" min="8" max="8"/>
+    <col width="5.5" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12.5" customWidth="1" min="12" max="12"/>
+    <col width="10.5" customWidth="1" min="13" max="13"/>
+    <col width="8.5" customWidth="1" min="14" max="14"/>
     <col hidden="1" width="13" customWidth="1" min="15" max="15"/>
     <col hidden="1" width="13" customWidth="1" min="16" max="16"/>
     <col hidden="1" width="13" customWidth="1" min="17" max="17"/>
@@ -829,7 +812,7 @@
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2">
-        <f>IF(OR(Rate_1=0,BF_Date=""),"▲  START HERE :  fill the Balance B/F date &amp; amount and the original interest rate in the panel below  ▼","INTEREST RATE ON THIS FILE :   "&amp;TEXT(Rate_1,"0.00")&amp;"% p.a. w.e.f. "&amp;TEXT(R1_From,"DD-MM-YYYY")&amp;IF(Rate_2&gt;0,"      |      "&amp;TEXT(Rate_2,"0.00")&amp;"% p.a. w.e.f. "&amp;TEXT(R2_From,"DD-MM-YYYY"),"")&amp;IF(Rate_3&gt;0,"      |      "&amp;TEXT(Rate_3,"0.00")&amp;"% p.a. w.e.f. "&amp;TEXT(R3_From,"DD-MM-YYYY"),"")&amp;"            BASIS : actual days / "&amp;Day_Basis&amp;"   ·   COMPOUNDED QUARTERLY")</f>
+        <f>IF(OR('Engine'!$B$8=0,$H$6=""),"▲  START HERE :  fill the Balance B/F date &amp; amount and the original interest rate in the panel below  ▼","INTEREST RATE ON THIS FILE :   "&amp;TEXT('Engine'!$B$8,"0.00")&amp;"% p.a. w.e.f. "&amp;TEXT('Engine'!$B$2,"DD-MM-YYYY")&amp;IF('Engine'!$B$9&gt;0,"      |      "&amp;TEXT('Engine'!$B$9,"0.00")&amp;"% p.a. w.e.f. "&amp;TEXT('Engine'!$B$4,"DD-MM-YYYY"),"")&amp;IF('Engine'!$B$10&gt;0,"      |      "&amp;TEXT('Engine'!$B$10,"0.00")&amp;"% p.a. w.e.f. "&amp;TEXT('Engine'!$B$6,"DD-MM-YYYY"),"")&amp;"            BASIS : actual days / "&amp;$H$8&amp;"   ·   COMPOUNDED QUARTERLY")</f>
         <v/>
       </c>
     </row>
@@ -922,7 +905,7 @@
         </is>
       </c>
       <c r="K7" s="11">
-        <f>IF(BF_Date="",0,BF_Date)</f>
+        <f>IF($H$6="",0,$H$6)</f>
         <v/>
       </c>
       <c r="L7" s="12" t="n"/>
@@ -931,7 +914,7 @@
         <v/>
       </c>
       <c r="N7" s="14">
-        <f>IF($L$7="","(slot free)",IF(AND(Locked_To&lt;&gt;"",$K$7&lt;=Locked_To),"🔒 LOCKED","EDITABLE"))</f>
+        <f>IF($L$7="","(slot free)",IF(AND($H$10&lt;&gt;"",$K$7&lt;=$H$10),"■ LOCKED","EDITABLE"))</f>
         <v/>
       </c>
     </row>
@@ -963,7 +946,7 @@
         <v/>
       </c>
       <c r="N8" s="14">
-        <f>IF($L$8="","(slot free)",IF(AND(Locked_To&lt;&gt;"",$K$8&lt;=Locked_To),"🔒 LOCKED","EDITABLE"))</f>
+        <f>IF($L$8="","(slot free)",IF(AND($H$10&lt;&gt;"",$K$8&lt;=$H$10),"■ LOCKED","EDITABLE"))</f>
         <v/>
       </c>
     </row>
@@ -995,7 +978,7 @@
         <v/>
       </c>
       <c r="N9" s="14">
-        <f>IF($L$9="","(slot free)",IF(AND(Locked_To&lt;&gt;"",$K$9&lt;=Locked_To),"🔒 LOCKED","EDITABLE"))</f>
+        <f>IF($L$9="","(slot free)",IF(AND($H$10&lt;&gt;"",$K$9&lt;=$H$10),"■ LOCKED","EDITABLE"))</f>
         <v/>
       </c>
     </row>
@@ -1028,7 +1011,7 @@
         </is>
       </c>
       <c r="C11" s="19">
-        <f>IF(BF_Date="","– not set –",TEXT(BF_Date,"DD-MM-YYYY")&amp;"  to  "&amp;TEXT('Engine'!$F$25,"DD-MM-YYYY"))</f>
+        <f>IF($H$6="","– not set –",TEXT($H$6,"DD-MM-YYYY")&amp;"  to  "&amp;TEXT('Engine'!$F$25,"DD-MM-YYYY"))</f>
         <v/>
       </c>
       <c r="D11" s="20" t="n"/>
@@ -1131,7 +1114,7 @@
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="24">
-        <f>IF($P$14=0,"QUARTER 1          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 1          "&amp;TEXT($P$14,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$14,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$14&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$14)</f>
+        <f>IF($P$14=0,"QUARTER 1          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 1          "&amp;TEXT($P$14,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$14,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$14&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$14)</f>
         <v/>
       </c>
       <c r="O14" s="25">
@@ -1188,7 +1171,7 @@
         <v/>
       </c>
       <c r="N15" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$15&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$15&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O15" s="25">
@@ -1196,7 +1179,7 @@
         <v/>
       </c>
       <c r="S15" s="38">
-        <f>BF_Amount</f>
+        <f>$H$7</f>
         <v/>
       </c>
       <c r="T15" s="38" t="n">
@@ -1218,7 +1201,7 @@
         <v/>
       </c>
       <c r="H16" s="42">
-        <f>IF($I16&lt;=0,"",(Rate_1*MAX(0,MIN($O16,R1_To)-MAX($O15,R1_From))+Rate_2*MAX(0,MIN($O16,R2_To)-MAX($O15,R2_From))+Rate_3*MAX(0,MIN($O16,R3_To)-MAX($O15,R3_From)))/100/Day_Basis/$I16*Day_Basis*100)</f>
+        <f>IF($I16&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O16,'Engine'!$B$3)-MAX($O15,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O16,'Engine'!$B$5)-MAX($O15,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O16,'Engine'!$B$7)-MAX($O15,'Engine'!$B$6)))/100/$H$8/$I16*$H$8*100)</f>
         <v/>
       </c>
       <c r="I16" s="43">
@@ -1226,7 +1209,7 @@
         <v/>
       </c>
       <c r="J16" s="41">
-        <f>IF($I16&lt;=0,0,$S15*(Rate_1*MAX(0,MIN($O16,R1_To)-MAX($O15,R1_From))+Rate_2*MAX(0,MIN($O16,R2_To)-MAX($O15,R2_From))+Rate_3*MAX(0,MIN($O16,R3_To)-MAX($O15,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I16&lt;=0,0,$S15*('Engine'!$B$8*MAX(0,MIN($O16,'Engine'!$B$3)-MAX($O15,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O16,'Engine'!$B$5)-MAX($O15,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O16,'Engine'!$B$7)-MAX($O15,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K16" s="41">
@@ -1239,7 +1222,7 @@
         <v/>
       </c>
       <c r="N16" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O16&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O16&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O16" s="25">
@@ -1270,7 +1253,7 @@
         <v/>
       </c>
       <c r="H17" s="42">
-        <f>IF($I17&lt;=0,"",(Rate_1*MAX(0,MIN($O17,R1_To)-MAX($O16,R1_From))+Rate_2*MAX(0,MIN($O17,R2_To)-MAX($O16,R2_From))+Rate_3*MAX(0,MIN($O17,R3_To)-MAX($O16,R3_From)))/100/Day_Basis/$I17*Day_Basis*100)</f>
+        <f>IF($I17&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O17,'Engine'!$B$3)-MAX($O16,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O17,'Engine'!$B$5)-MAX($O16,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O17,'Engine'!$B$7)-MAX($O16,'Engine'!$B$6)))/100/$H$8/$I17*$H$8*100)</f>
         <v/>
       </c>
       <c r="I17" s="43">
@@ -1278,7 +1261,7 @@
         <v/>
       </c>
       <c r="J17" s="41">
-        <f>IF($I17&lt;=0,0,$S16*(Rate_1*MAX(0,MIN($O17,R1_To)-MAX($O16,R1_From))+Rate_2*MAX(0,MIN($O17,R2_To)-MAX($O16,R2_From))+Rate_3*MAX(0,MIN($O17,R3_To)-MAX($O16,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I17&lt;=0,0,$S16*('Engine'!$B$8*MAX(0,MIN($O17,'Engine'!$B$3)-MAX($O16,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O17,'Engine'!$B$5)-MAX($O16,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O17,'Engine'!$B$7)-MAX($O16,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K17" s="41">
@@ -1291,7 +1274,7 @@
         <v/>
       </c>
       <c r="N17" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O17&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O17&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O17" s="25">
@@ -1322,7 +1305,7 @@
         <v/>
       </c>
       <c r="H18" s="42">
-        <f>IF($I18&lt;=0,"",(Rate_1*MAX(0,MIN($O18,R1_To)-MAX($O17,R1_From))+Rate_2*MAX(0,MIN($O18,R2_To)-MAX($O17,R2_From))+Rate_3*MAX(0,MIN($O18,R3_To)-MAX($O17,R3_From)))/100/Day_Basis/$I18*Day_Basis*100)</f>
+        <f>IF($I18&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O18,'Engine'!$B$3)-MAX($O17,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O18,'Engine'!$B$5)-MAX($O17,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O18,'Engine'!$B$7)-MAX($O17,'Engine'!$B$6)))/100/$H$8/$I18*$H$8*100)</f>
         <v/>
       </c>
       <c r="I18" s="43">
@@ -1330,7 +1313,7 @@
         <v/>
       </c>
       <c r="J18" s="41">
-        <f>IF($I18&lt;=0,0,$S17*(Rate_1*MAX(0,MIN($O18,R1_To)-MAX($O17,R1_From))+Rate_2*MAX(0,MIN($O18,R2_To)-MAX($O17,R2_From))+Rate_3*MAX(0,MIN($O18,R3_To)-MAX($O17,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I18&lt;=0,0,$S17*('Engine'!$B$8*MAX(0,MIN($O18,'Engine'!$B$3)-MAX($O17,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O18,'Engine'!$B$5)-MAX($O17,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O18,'Engine'!$B$7)-MAX($O17,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K18" s="41">
@@ -1343,7 +1326,7 @@
         <v/>
       </c>
       <c r="N18" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O18&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O18&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O18" s="25">
@@ -1374,7 +1357,7 @@
         <v/>
       </c>
       <c r="H19" s="42">
-        <f>IF($I19&lt;=0,"",(Rate_1*MAX(0,MIN($O19,R1_To)-MAX($O18,R1_From))+Rate_2*MAX(0,MIN($O19,R2_To)-MAX($O18,R2_From))+Rate_3*MAX(0,MIN($O19,R3_To)-MAX($O18,R3_From)))/100/Day_Basis/$I19*Day_Basis*100)</f>
+        <f>IF($I19&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O19,'Engine'!$B$3)-MAX($O18,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O19,'Engine'!$B$5)-MAX($O18,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O19,'Engine'!$B$7)-MAX($O18,'Engine'!$B$6)))/100/$H$8/$I19*$H$8*100)</f>
         <v/>
       </c>
       <c r="I19" s="43">
@@ -1382,7 +1365,7 @@
         <v/>
       </c>
       <c r="J19" s="41">
-        <f>IF($I19&lt;=0,0,$S18*(Rate_1*MAX(0,MIN($O19,R1_To)-MAX($O18,R1_From))+Rate_2*MAX(0,MIN($O19,R2_To)-MAX($O18,R2_From))+Rate_3*MAX(0,MIN($O19,R3_To)-MAX($O18,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I19&lt;=0,0,$S18*('Engine'!$B$8*MAX(0,MIN($O19,'Engine'!$B$3)-MAX($O18,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O19,'Engine'!$B$5)-MAX($O18,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O19,'Engine'!$B$7)-MAX($O18,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K19" s="41">
@@ -1395,7 +1378,7 @@
         <v/>
       </c>
       <c r="N19" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O19&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O19&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O19" s="25">
@@ -1426,7 +1409,7 @@
         <v/>
       </c>
       <c r="H20" s="42">
-        <f>IF($I20&lt;=0,"",(Rate_1*MAX(0,MIN($O20,R1_To)-MAX($O19,R1_From))+Rate_2*MAX(0,MIN($O20,R2_To)-MAX($O19,R2_From))+Rate_3*MAX(0,MIN($O20,R3_To)-MAX($O19,R3_From)))/100/Day_Basis/$I20*Day_Basis*100)</f>
+        <f>IF($I20&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O20,'Engine'!$B$3)-MAX($O19,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O20,'Engine'!$B$5)-MAX($O19,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O20,'Engine'!$B$7)-MAX($O19,'Engine'!$B$6)))/100/$H$8/$I20*$H$8*100)</f>
         <v/>
       </c>
       <c r="I20" s="43">
@@ -1434,7 +1417,7 @@
         <v/>
       </c>
       <c r="J20" s="41">
-        <f>IF($I20&lt;=0,0,$S19*(Rate_1*MAX(0,MIN($O20,R1_To)-MAX($O19,R1_From))+Rate_2*MAX(0,MIN($O20,R2_To)-MAX($O19,R2_From))+Rate_3*MAX(0,MIN($O20,R3_To)-MAX($O19,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I20&lt;=0,0,$S19*('Engine'!$B$8*MAX(0,MIN($O20,'Engine'!$B$3)-MAX($O19,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O20,'Engine'!$B$5)-MAX($O19,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O20,'Engine'!$B$7)-MAX($O19,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K20" s="41">
@@ -1447,7 +1430,7 @@
         <v/>
       </c>
       <c r="N20" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O20&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O20&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O20" s="25">
@@ -1478,7 +1461,7 @@
         <v/>
       </c>
       <c r="H21" s="42">
-        <f>IF($I21&lt;=0,"",(Rate_1*MAX(0,MIN($O21,R1_To)-MAX($O20,R1_From))+Rate_2*MAX(0,MIN($O21,R2_To)-MAX($O20,R2_From))+Rate_3*MAX(0,MIN($O21,R3_To)-MAX($O20,R3_From)))/100/Day_Basis/$I21*Day_Basis*100)</f>
+        <f>IF($I21&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O21,'Engine'!$B$3)-MAX($O20,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O21,'Engine'!$B$5)-MAX($O20,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O21,'Engine'!$B$7)-MAX($O20,'Engine'!$B$6)))/100/$H$8/$I21*$H$8*100)</f>
         <v/>
       </c>
       <c r="I21" s="43">
@@ -1486,7 +1469,7 @@
         <v/>
       </c>
       <c r="J21" s="41">
-        <f>IF($I21&lt;=0,0,$S20*(Rate_1*MAX(0,MIN($O21,R1_To)-MAX($O20,R1_From))+Rate_2*MAX(0,MIN($O21,R2_To)-MAX($O20,R2_From))+Rate_3*MAX(0,MIN($O21,R3_To)-MAX($O20,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I21&lt;=0,0,$S20*('Engine'!$B$8*MAX(0,MIN($O21,'Engine'!$B$3)-MAX($O20,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O21,'Engine'!$B$5)-MAX($O20,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O21,'Engine'!$B$7)-MAX($O20,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K21" s="41">
@@ -1499,7 +1482,7 @@
         <v/>
       </c>
       <c r="N21" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O21&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O21&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O21" s="25">
@@ -1530,7 +1513,7 @@
         <v/>
       </c>
       <c r="H22" s="42">
-        <f>IF($I22&lt;=0,"",(Rate_1*MAX(0,MIN($O22,R1_To)-MAX($O21,R1_From))+Rate_2*MAX(0,MIN($O22,R2_To)-MAX($O21,R2_From))+Rate_3*MAX(0,MIN($O22,R3_To)-MAX($O21,R3_From)))/100/Day_Basis/$I22*Day_Basis*100)</f>
+        <f>IF($I22&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O22,'Engine'!$B$3)-MAX($O21,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O22,'Engine'!$B$5)-MAX($O21,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O22,'Engine'!$B$7)-MAX($O21,'Engine'!$B$6)))/100/$H$8/$I22*$H$8*100)</f>
         <v/>
       </c>
       <c r="I22" s="43">
@@ -1538,7 +1521,7 @@
         <v/>
       </c>
       <c r="J22" s="41">
-        <f>IF($I22&lt;=0,0,$S21*(Rate_1*MAX(0,MIN($O22,R1_To)-MAX($O21,R1_From))+Rate_2*MAX(0,MIN($O22,R2_To)-MAX($O21,R2_From))+Rate_3*MAX(0,MIN($O22,R3_To)-MAX($O21,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I22&lt;=0,0,$S21*('Engine'!$B$8*MAX(0,MIN($O22,'Engine'!$B$3)-MAX($O21,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O22,'Engine'!$B$5)-MAX($O21,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O22,'Engine'!$B$7)-MAX($O21,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K22" s="41">
@@ -1551,7 +1534,7 @@
         <v/>
       </c>
       <c r="N22" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O22&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O22&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O22" s="25">
@@ -1582,7 +1565,7 @@
         <v/>
       </c>
       <c r="H23" s="42">
-        <f>IF($I23&lt;=0,"",(Rate_1*MAX(0,MIN($O23,R1_To)-MAX($O22,R1_From))+Rate_2*MAX(0,MIN($O23,R2_To)-MAX($O22,R2_From))+Rate_3*MAX(0,MIN($O23,R3_To)-MAX($O22,R3_From)))/100/Day_Basis/$I23*Day_Basis*100)</f>
+        <f>IF($I23&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O23,'Engine'!$B$3)-MAX($O22,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O23,'Engine'!$B$5)-MAX($O22,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O23,'Engine'!$B$7)-MAX($O22,'Engine'!$B$6)))/100/$H$8/$I23*$H$8*100)</f>
         <v/>
       </c>
       <c r="I23" s="43">
@@ -1590,7 +1573,7 @@
         <v/>
       </c>
       <c r="J23" s="41">
-        <f>IF($I23&lt;=0,0,$S22*(Rate_1*MAX(0,MIN($O23,R1_To)-MAX($O22,R1_From))+Rate_2*MAX(0,MIN($O23,R2_To)-MAX($O22,R2_From))+Rate_3*MAX(0,MIN($O23,R3_To)-MAX($O22,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I23&lt;=0,0,$S22*('Engine'!$B$8*MAX(0,MIN($O23,'Engine'!$B$3)-MAX($O22,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O23,'Engine'!$B$5)-MAX($O22,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O23,'Engine'!$B$7)-MAX($O22,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K23" s="41">
@@ -1603,7 +1586,7 @@
         <v/>
       </c>
       <c r="N23" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O23&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O23&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O23" s="25">
@@ -1634,7 +1617,7 @@
         <v/>
       </c>
       <c r="H24" s="42">
-        <f>IF($I24&lt;=0,"",(Rate_1*MAX(0,MIN($O24,R1_To)-MAX($O23,R1_From))+Rate_2*MAX(0,MIN($O24,R2_To)-MAX($O23,R2_From))+Rate_3*MAX(0,MIN($O24,R3_To)-MAX($O23,R3_From)))/100/Day_Basis/$I24*Day_Basis*100)</f>
+        <f>IF($I24&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O24,'Engine'!$B$3)-MAX($O23,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O24,'Engine'!$B$5)-MAX($O23,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O24,'Engine'!$B$7)-MAX($O23,'Engine'!$B$6)))/100/$H$8/$I24*$H$8*100)</f>
         <v/>
       </c>
       <c r="I24" s="43">
@@ -1642,7 +1625,7 @@
         <v/>
       </c>
       <c r="J24" s="41">
-        <f>IF($I24&lt;=0,0,$S23*(Rate_1*MAX(0,MIN($O24,R1_To)-MAX($O23,R1_From))+Rate_2*MAX(0,MIN($O24,R2_To)-MAX($O23,R2_From))+Rate_3*MAX(0,MIN($O24,R3_To)-MAX($O23,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I24&lt;=0,0,$S23*('Engine'!$B$8*MAX(0,MIN($O24,'Engine'!$B$3)-MAX($O23,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O24,'Engine'!$B$5)-MAX($O23,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O24,'Engine'!$B$7)-MAX($O23,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K24" s="41">
@@ -1655,7 +1638,7 @@
         <v/>
       </c>
       <c r="N24" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O24&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O24&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O24" s="25">
@@ -1686,7 +1669,7 @@
         <v/>
       </c>
       <c r="H25" s="42">
-        <f>IF($I25&lt;=0,"",(Rate_1*MAX(0,MIN($O25,R1_To)-MAX($O24,R1_From))+Rate_2*MAX(0,MIN($O25,R2_To)-MAX($O24,R2_From))+Rate_3*MAX(0,MIN($O25,R3_To)-MAX($O24,R3_From)))/100/Day_Basis/$I25*Day_Basis*100)</f>
+        <f>IF($I25&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O25,'Engine'!$B$3)-MAX($O24,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O25,'Engine'!$B$5)-MAX($O24,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O25,'Engine'!$B$7)-MAX($O24,'Engine'!$B$6)))/100/$H$8/$I25*$H$8*100)</f>
         <v/>
       </c>
       <c r="I25" s="43">
@@ -1694,7 +1677,7 @@
         <v/>
       </c>
       <c r="J25" s="41">
-        <f>IF($I25&lt;=0,0,$S24*(Rate_1*MAX(0,MIN($O25,R1_To)-MAX($O24,R1_From))+Rate_2*MAX(0,MIN($O25,R2_To)-MAX($O24,R2_From))+Rate_3*MAX(0,MIN($O25,R3_To)-MAX($O24,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I25&lt;=0,0,$S24*('Engine'!$B$8*MAX(0,MIN($O25,'Engine'!$B$3)-MAX($O24,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O25,'Engine'!$B$5)-MAX($O24,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O25,'Engine'!$B$7)-MAX($O24,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K25" s="41">
@@ -1707,7 +1690,7 @@
         <v/>
       </c>
       <c r="N25" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O25&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O25&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O25" s="25">
@@ -1748,7 +1731,7 @@
         <v/>
       </c>
       <c r="H26" s="51">
-        <f>IF($I26&lt;=0,"",(Rate_1*MAX(0,MIN($O26,R1_To)-MAX($O25,R1_From))+Rate_2*MAX(0,MIN($O26,R2_To)-MAX($O25,R2_From))+Rate_3*MAX(0,MIN($O26,R3_To)-MAX($O25,R3_From)))/100/Day_Basis/$I26*Day_Basis*100)</f>
+        <f>IF($I26&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O26,'Engine'!$B$3)-MAX($O25,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O26,'Engine'!$B$5)-MAX($O25,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O26,'Engine'!$B$7)-MAX($O25,'Engine'!$B$6)))/100/$H$8/$I26*$H$8*100)</f>
         <v/>
       </c>
       <c r="I26" s="52">
@@ -1756,7 +1739,7 @@
         <v/>
       </c>
       <c r="J26" s="53">
-        <f>IF($I26&lt;=0,0,$S25*(Rate_1*MAX(0,MIN($O26,R1_To)-MAX($O25,R1_From))+Rate_2*MAX(0,MIN($O26,R2_To)-MAX($O25,R2_From))+Rate_3*MAX(0,MIN($O26,R3_To)-MAX($O25,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I26&lt;=0,0,$S25*('Engine'!$B$8*MAX(0,MIN($O26,'Engine'!$B$3)-MAX($O25,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O26,'Engine'!$B$5)-MAX($O25,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O26,'Engine'!$B$7)-MAX($O25,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K26" s="53" t="n">
@@ -1768,7 +1751,7 @@
         <v/>
       </c>
       <c r="N26" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O26&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O26&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O26" s="25">
@@ -1785,7 +1768,7 @@
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="24">
-        <f>IF($P$27=0,"QUARTER 2          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 2          "&amp;TEXT($P$27,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$27,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$27&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$27)</f>
+        <f>IF($P$27=0,"QUARTER 2          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 2          "&amp;TEXT($P$27,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$27,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$27&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$27)</f>
         <v/>
       </c>
       <c r="O27" s="25">
@@ -1843,7 +1826,7 @@
         <v/>
       </c>
       <c r="N28" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$28&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$28&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O28" s="25">
@@ -1873,7 +1856,7 @@
         <v/>
       </c>
       <c r="H29" s="42">
-        <f>IF($I29&lt;=0,"",(Rate_1*MAX(0,MIN($O29,R1_To)-MAX($O28,R1_From))+Rate_2*MAX(0,MIN($O29,R2_To)-MAX($O28,R2_From))+Rate_3*MAX(0,MIN($O29,R3_To)-MAX($O28,R3_From)))/100/Day_Basis/$I29*Day_Basis*100)</f>
+        <f>IF($I29&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O29,'Engine'!$B$3)-MAX($O28,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O29,'Engine'!$B$5)-MAX($O28,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O29,'Engine'!$B$7)-MAX($O28,'Engine'!$B$6)))/100/$H$8/$I29*$H$8*100)</f>
         <v/>
       </c>
       <c r="I29" s="43">
@@ -1881,7 +1864,7 @@
         <v/>
       </c>
       <c r="J29" s="41">
-        <f>IF($I29&lt;=0,0,$S28*(Rate_1*MAX(0,MIN($O29,R1_To)-MAX($O28,R1_From))+Rate_2*MAX(0,MIN($O29,R2_To)-MAX($O28,R2_From))+Rate_3*MAX(0,MIN($O29,R3_To)-MAX($O28,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I29&lt;=0,0,$S28*('Engine'!$B$8*MAX(0,MIN($O29,'Engine'!$B$3)-MAX($O28,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O29,'Engine'!$B$5)-MAX($O28,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O29,'Engine'!$B$7)-MAX($O28,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K29" s="41">
@@ -1894,7 +1877,7 @@
         <v/>
       </c>
       <c r="N29" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O29&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O29&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O29" s="25">
@@ -1925,7 +1908,7 @@
         <v/>
       </c>
       <c r="H30" s="42">
-        <f>IF($I30&lt;=0,"",(Rate_1*MAX(0,MIN($O30,R1_To)-MAX($O29,R1_From))+Rate_2*MAX(0,MIN($O30,R2_To)-MAX($O29,R2_From))+Rate_3*MAX(0,MIN($O30,R3_To)-MAX($O29,R3_From)))/100/Day_Basis/$I30*Day_Basis*100)</f>
+        <f>IF($I30&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O30,'Engine'!$B$3)-MAX($O29,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O30,'Engine'!$B$5)-MAX($O29,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O30,'Engine'!$B$7)-MAX($O29,'Engine'!$B$6)))/100/$H$8/$I30*$H$8*100)</f>
         <v/>
       </c>
       <c r="I30" s="43">
@@ -1933,7 +1916,7 @@
         <v/>
       </c>
       <c r="J30" s="41">
-        <f>IF($I30&lt;=0,0,$S29*(Rate_1*MAX(0,MIN($O30,R1_To)-MAX($O29,R1_From))+Rate_2*MAX(0,MIN($O30,R2_To)-MAX($O29,R2_From))+Rate_3*MAX(0,MIN($O30,R3_To)-MAX($O29,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I30&lt;=0,0,$S29*('Engine'!$B$8*MAX(0,MIN($O30,'Engine'!$B$3)-MAX($O29,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O30,'Engine'!$B$5)-MAX($O29,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O30,'Engine'!$B$7)-MAX($O29,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K30" s="41">
@@ -1946,7 +1929,7 @@
         <v/>
       </c>
       <c r="N30" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O30&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O30&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O30" s="25">
@@ -1977,7 +1960,7 @@
         <v/>
       </c>
       <c r="H31" s="42">
-        <f>IF($I31&lt;=0,"",(Rate_1*MAX(0,MIN($O31,R1_To)-MAX($O30,R1_From))+Rate_2*MAX(0,MIN($O31,R2_To)-MAX($O30,R2_From))+Rate_3*MAX(0,MIN($O31,R3_To)-MAX($O30,R3_From)))/100/Day_Basis/$I31*Day_Basis*100)</f>
+        <f>IF($I31&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O31,'Engine'!$B$3)-MAX($O30,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O31,'Engine'!$B$5)-MAX($O30,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O31,'Engine'!$B$7)-MAX($O30,'Engine'!$B$6)))/100/$H$8/$I31*$H$8*100)</f>
         <v/>
       </c>
       <c r="I31" s="43">
@@ -1985,7 +1968,7 @@
         <v/>
       </c>
       <c r="J31" s="41">
-        <f>IF($I31&lt;=0,0,$S30*(Rate_1*MAX(0,MIN($O31,R1_To)-MAX($O30,R1_From))+Rate_2*MAX(0,MIN($O31,R2_To)-MAX($O30,R2_From))+Rate_3*MAX(0,MIN($O31,R3_To)-MAX($O30,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I31&lt;=0,0,$S30*('Engine'!$B$8*MAX(0,MIN($O31,'Engine'!$B$3)-MAX($O30,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O31,'Engine'!$B$5)-MAX($O30,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O31,'Engine'!$B$7)-MAX($O30,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K31" s="41">
@@ -1998,7 +1981,7 @@
         <v/>
       </c>
       <c r="N31" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O31&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O31&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O31" s="25">
@@ -2029,7 +2012,7 @@
         <v/>
       </c>
       <c r="H32" s="42">
-        <f>IF($I32&lt;=0,"",(Rate_1*MAX(0,MIN($O32,R1_To)-MAX($O31,R1_From))+Rate_2*MAX(0,MIN($O32,R2_To)-MAX($O31,R2_From))+Rate_3*MAX(0,MIN($O32,R3_To)-MAX($O31,R3_From)))/100/Day_Basis/$I32*Day_Basis*100)</f>
+        <f>IF($I32&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O32,'Engine'!$B$3)-MAX($O31,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O32,'Engine'!$B$5)-MAX($O31,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O32,'Engine'!$B$7)-MAX($O31,'Engine'!$B$6)))/100/$H$8/$I32*$H$8*100)</f>
         <v/>
       </c>
       <c r="I32" s="43">
@@ -2037,7 +2020,7 @@
         <v/>
       </c>
       <c r="J32" s="41">
-        <f>IF($I32&lt;=0,0,$S31*(Rate_1*MAX(0,MIN($O32,R1_To)-MAX($O31,R1_From))+Rate_2*MAX(0,MIN($O32,R2_To)-MAX($O31,R2_From))+Rate_3*MAX(0,MIN($O32,R3_To)-MAX($O31,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I32&lt;=0,0,$S31*('Engine'!$B$8*MAX(0,MIN($O32,'Engine'!$B$3)-MAX($O31,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O32,'Engine'!$B$5)-MAX($O31,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O32,'Engine'!$B$7)-MAX($O31,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K32" s="41">
@@ -2050,7 +2033,7 @@
         <v/>
       </c>
       <c r="N32" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O32&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O32&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O32" s="25">
@@ -2081,7 +2064,7 @@
         <v/>
       </c>
       <c r="H33" s="42">
-        <f>IF($I33&lt;=0,"",(Rate_1*MAX(0,MIN($O33,R1_To)-MAX($O32,R1_From))+Rate_2*MAX(0,MIN($O33,R2_To)-MAX($O32,R2_From))+Rate_3*MAX(0,MIN($O33,R3_To)-MAX($O32,R3_From)))/100/Day_Basis/$I33*Day_Basis*100)</f>
+        <f>IF($I33&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O33,'Engine'!$B$3)-MAX($O32,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O33,'Engine'!$B$5)-MAX($O32,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O33,'Engine'!$B$7)-MAX($O32,'Engine'!$B$6)))/100/$H$8/$I33*$H$8*100)</f>
         <v/>
       </c>
       <c r="I33" s="43">
@@ -2089,7 +2072,7 @@
         <v/>
       </c>
       <c r="J33" s="41">
-        <f>IF($I33&lt;=0,0,$S32*(Rate_1*MAX(0,MIN($O33,R1_To)-MAX($O32,R1_From))+Rate_2*MAX(0,MIN($O33,R2_To)-MAX($O32,R2_From))+Rate_3*MAX(0,MIN($O33,R3_To)-MAX($O32,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I33&lt;=0,0,$S32*('Engine'!$B$8*MAX(0,MIN($O33,'Engine'!$B$3)-MAX($O32,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O33,'Engine'!$B$5)-MAX($O32,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O33,'Engine'!$B$7)-MAX($O32,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K33" s="41">
@@ -2102,7 +2085,7 @@
         <v/>
       </c>
       <c r="N33" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O33&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O33&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O33" s="25">
@@ -2133,7 +2116,7 @@
         <v/>
       </c>
       <c r="H34" s="42">
-        <f>IF($I34&lt;=0,"",(Rate_1*MAX(0,MIN($O34,R1_To)-MAX($O33,R1_From))+Rate_2*MAX(0,MIN($O34,R2_To)-MAX($O33,R2_From))+Rate_3*MAX(0,MIN($O34,R3_To)-MAX($O33,R3_From)))/100/Day_Basis/$I34*Day_Basis*100)</f>
+        <f>IF($I34&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O34,'Engine'!$B$3)-MAX($O33,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O34,'Engine'!$B$5)-MAX($O33,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O34,'Engine'!$B$7)-MAX($O33,'Engine'!$B$6)))/100/$H$8/$I34*$H$8*100)</f>
         <v/>
       </c>
       <c r="I34" s="43">
@@ -2141,7 +2124,7 @@
         <v/>
       </c>
       <c r="J34" s="41">
-        <f>IF($I34&lt;=0,0,$S33*(Rate_1*MAX(0,MIN($O34,R1_To)-MAX($O33,R1_From))+Rate_2*MAX(0,MIN($O34,R2_To)-MAX($O33,R2_From))+Rate_3*MAX(0,MIN($O34,R3_To)-MAX($O33,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I34&lt;=0,0,$S33*('Engine'!$B$8*MAX(0,MIN($O34,'Engine'!$B$3)-MAX($O33,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O34,'Engine'!$B$5)-MAX($O33,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O34,'Engine'!$B$7)-MAX($O33,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K34" s="41">
@@ -2154,7 +2137,7 @@
         <v/>
       </c>
       <c r="N34" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O34&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O34&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O34" s="25">
@@ -2185,7 +2168,7 @@
         <v/>
       </c>
       <c r="H35" s="42">
-        <f>IF($I35&lt;=0,"",(Rate_1*MAX(0,MIN($O35,R1_To)-MAX($O34,R1_From))+Rate_2*MAX(0,MIN($O35,R2_To)-MAX($O34,R2_From))+Rate_3*MAX(0,MIN($O35,R3_To)-MAX($O34,R3_From)))/100/Day_Basis/$I35*Day_Basis*100)</f>
+        <f>IF($I35&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O35,'Engine'!$B$3)-MAX($O34,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O35,'Engine'!$B$5)-MAX($O34,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O35,'Engine'!$B$7)-MAX($O34,'Engine'!$B$6)))/100/$H$8/$I35*$H$8*100)</f>
         <v/>
       </c>
       <c r="I35" s="43">
@@ -2193,7 +2176,7 @@
         <v/>
       </c>
       <c r="J35" s="41">
-        <f>IF($I35&lt;=0,0,$S34*(Rate_1*MAX(0,MIN($O35,R1_To)-MAX($O34,R1_From))+Rate_2*MAX(0,MIN($O35,R2_To)-MAX($O34,R2_From))+Rate_3*MAX(0,MIN($O35,R3_To)-MAX($O34,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I35&lt;=0,0,$S34*('Engine'!$B$8*MAX(0,MIN($O35,'Engine'!$B$3)-MAX($O34,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O35,'Engine'!$B$5)-MAX($O34,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O35,'Engine'!$B$7)-MAX($O34,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K35" s="41">
@@ -2206,7 +2189,7 @@
         <v/>
       </c>
       <c r="N35" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O35&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O35&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O35" s="25">
@@ -2237,7 +2220,7 @@
         <v/>
       </c>
       <c r="H36" s="42">
-        <f>IF($I36&lt;=0,"",(Rate_1*MAX(0,MIN($O36,R1_To)-MAX($O35,R1_From))+Rate_2*MAX(0,MIN($O36,R2_To)-MAX($O35,R2_From))+Rate_3*MAX(0,MIN($O36,R3_To)-MAX($O35,R3_From)))/100/Day_Basis/$I36*Day_Basis*100)</f>
+        <f>IF($I36&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O36,'Engine'!$B$3)-MAX($O35,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O36,'Engine'!$B$5)-MAX($O35,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O36,'Engine'!$B$7)-MAX($O35,'Engine'!$B$6)))/100/$H$8/$I36*$H$8*100)</f>
         <v/>
       </c>
       <c r="I36" s="43">
@@ -2245,7 +2228,7 @@
         <v/>
       </c>
       <c r="J36" s="41">
-        <f>IF($I36&lt;=0,0,$S35*(Rate_1*MAX(0,MIN($O36,R1_To)-MAX($O35,R1_From))+Rate_2*MAX(0,MIN($O36,R2_To)-MAX($O35,R2_From))+Rate_3*MAX(0,MIN($O36,R3_To)-MAX($O35,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I36&lt;=0,0,$S35*('Engine'!$B$8*MAX(0,MIN($O36,'Engine'!$B$3)-MAX($O35,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O36,'Engine'!$B$5)-MAX($O35,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O36,'Engine'!$B$7)-MAX($O35,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K36" s="41">
@@ -2258,7 +2241,7 @@
         <v/>
       </c>
       <c r="N36" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O36&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O36&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O36" s="25">
@@ -2289,7 +2272,7 @@
         <v/>
       </c>
       <c r="H37" s="42">
-        <f>IF($I37&lt;=0,"",(Rate_1*MAX(0,MIN($O37,R1_To)-MAX($O36,R1_From))+Rate_2*MAX(0,MIN($O37,R2_To)-MAX($O36,R2_From))+Rate_3*MAX(0,MIN($O37,R3_To)-MAX($O36,R3_From)))/100/Day_Basis/$I37*Day_Basis*100)</f>
+        <f>IF($I37&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O37,'Engine'!$B$3)-MAX($O36,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O37,'Engine'!$B$5)-MAX($O36,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O37,'Engine'!$B$7)-MAX($O36,'Engine'!$B$6)))/100/$H$8/$I37*$H$8*100)</f>
         <v/>
       </c>
       <c r="I37" s="43">
@@ -2297,7 +2280,7 @@
         <v/>
       </c>
       <c r="J37" s="41">
-        <f>IF($I37&lt;=0,0,$S36*(Rate_1*MAX(0,MIN($O37,R1_To)-MAX($O36,R1_From))+Rate_2*MAX(0,MIN($O37,R2_To)-MAX($O36,R2_From))+Rate_3*MAX(0,MIN($O37,R3_To)-MAX($O36,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I37&lt;=0,0,$S36*('Engine'!$B$8*MAX(0,MIN($O37,'Engine'!$B$3)-MAX($O36,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O37,'Engine'!$B$5)-MAX($O36,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O37,'Engine'!$B$7)-MAX($O36,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K37" s="41">
@@ -2310,7 +2293,7 @@
         <v/>
       </c>
       <c r="N37" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O37&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O37&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O37" s="25">
@@ -2341,7 +2324,7 @@
         <v/>
       </c>
       <c r="H38" s="42">
-        <f>IF($I38&lt;=0,"",(Rate_1*MAX(0,MIN($O38,R1_To)-MAX($O37,R1_From))+Rate_2*MAX(0,MIN($O38,R2_To)-MAX($O37,R2_From))+Rate_3*MAX(0,MIN($O38,R3_To)-MAX($O37,R3_From)))/100/Day_Basis/$I38*Day_Basis*100)</f>
+        <f>IF($I38&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O38,'Engine'!$B$3)-MAX($O37,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O38,'Engine'!$B$5)-MAX($O37,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O38,'Engine'!$B$7)-MAX($O37,'Engine'!$B$6)))/100/$H$8/$I38*$H$8*100)</f>
         <v/>
       </c>
       <c r="I38" s="43">
@@ -2349,7 +2332,7 @@
         <v/>
       </c>
       <c r="J38" s="41">
-        <f>IF($I38&lt;=0,0,$S37*(Rate_1*MAX(0,MIN($O38,R1_To)-MAX($O37,R1_From))+Rate_2*MAX(0,MIN($O38,R2_To)-MAX($O37,R2_From))+Rate_3*MAX(0,MIN($O38,R3_To)-MAX($O37,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I38&lt;=0,0,$S37*('Engine'!$B$8*MAX(0,MIN($O38,'Engine'!$B$3)-MAX($O37,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O38,'Engine'!$B$5)-MAX($O37,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O38,'Engine'!$B$7)-MAX($O37,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K38" s="41">
@@ -2362,7 +2345,7 @@
         <v/>
       </c>
       <c r="N38" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O38&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O38&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O38" s="25">
@@ -2403,7 +2386,7 @@
         <v/>
       </c>
       <c r="H39" s="51">
-        <f>IF($I39&lt;=0,"",(Rate_1*MAX(0,MIN($O39,R1_To)-MAX($O38,R1_From))+Rate_2*MAX(0,MIN($O39,R2_To)-MAX($O38,R2_From))+Rate_3*MAX(0,MIN($O39,R3_To)-MAX($O38,R3_From)))/100/Day_Basis/$I39*Day_Basis*100)</f>
+        <f>IF($I39&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O39,'Engine'!$B$3)-MAX($O38,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O39,'Engine'!$B$5)-MAX($O38,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O39,'Engine'!$B$7)-MAX($O38,'Engine'!$B$6)))/100/$H$8/$I39*$H$8*100)</f>
         <v/>
       </c>
       <c r="I39" s="52">
@@ -2411,7 +2394,7 @@
         <v/>
       </c>
       <c r="J39" s="53">
-        <f>IF($I39&lt;=0,0,$S38*(Rate_1*MAX(0,MIN($O39,R1_To)-MAX($O38,R1_From))+Rate_2*MAX(0,MIN($O39,R2_To)-MAX($O38,R2_From))+Rate_3*MAX(0,MIN($O39,R3_To)-MAX($O38,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I39&lt;=0,0,$S38*('Engine'!$B$8*MAX(0,MIN($O39,'Engine'!$B$3)-MAX($O38,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O39,'Engine'!$B$5)-MAX($O38,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O39,'Engine'!$B$7)-MAX($O38,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K39" s="53" t="n">
@@ -2423,7 +2406,7 @@
         <v/>
       </c>
       <c r="N39" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O39&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O39&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O39" s="25">
@@ -2440,7 +2423,7 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="24">
-        <f>IF($P$40=0,"QUARTER 3          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 3          "&amp;TEXT($P$40,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$40,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$40&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$40)</f>
+        <f>IF($P$40=0,"QUARTER 3          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 3          "&amp;TEXT($P$40,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$40,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$40&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$40)</f>
         <v/>
       </c>
       <c r="O40" s="25">
@@ -2498,7 +2481,7 @@
         <v/>
       </c>
       <c r="N41" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$41&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$41&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O41" s="25">
@@ -2528,7 +2511,7 @@
         <v/>
       </c>
       <c r="H42" s="42">
-        <f>IF($I42&lt;=0,"",(Rate_1*MAX(0,MIN($O42,R1_To)-MAX($O41,R1_From))+Rate_2*MAX(0,MIN($O42,R2_To)-MAX($O41,R2_From))+Rate_3*MAX(0,MIN($O42,R3_To)-MAX($O41,R3_From)))/100/Day_Basis/$I42*Day_Basis*100)</f>
+        <f>IF($I42&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O42,'Engine'!$B$3)-MAX($O41,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O42,'Engine'!$B$5)-MAX($O41,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O42,'Engine'!$B$7)-MAX($O41,'Engine'!$B$6)))/100/$H$8/$I42*$H$8*100)</f>
         <v/>
       </c>
       <c r="I42" s="43">
@@ -2536,7 +2519,7 @@
         <v/>
       </c>
       <c r="J42" s="41">
-        <f>IF($I42&lt;=0,0,$S41*(Rate_1*MAX(0,MIN($O42,R1_To)-MAX($O41,R1_From))+Rate_2*MAX(0,MIN($O42,R2_To)-MAX($O41,R2_From))+Rate_3*MAX(0,MIN($O42,R3_To)-MAX($O41,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I42&lt;=0,0,$S41*('Engine'!$B$8*MAX(0,MIN($O42,'Engine'!$B$3)-MAX($O41,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O42,'Engine'!$B$5)-MAX($O41,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O42,'Engine'!$B$7)-MAX($O41,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K42" s="41">
@@ -2549,7 +2532,7 @@
         <v/>
       </c>
       <c r="N42" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O42&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O42&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O42" s="25">
@@ -2580,7 +2563,7 @@
         <v/>
       </c>
       <c r="H43" s="42">
-        <f>IF($I43&lt;=0,"",(Rate_1*MAX(0,MIN($O43,R1_To)-MAX($O42,R1_From))+Rate_2*MAX(0,MIN($O43,R2_To)-MAX($O42,R2_From))+Rate_3*MAX(0,MIN($O43,R3_To)-MAX($O42,R3_From)))/100/Day_Basis/$I43*Day_Basis*100)</f>
+        <f>IF($I43&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O43,'Engine'!$B$3)-MAX($O42,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O43,'Engine'!$B$5)-MAX($O42,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O43,'Engine'!$B$7)-MAX($O42,'Engine'!$B$6)))/100/$H$8/$I43*$H$8*100)</f>
         <v/>
       </c>
       <c r="I43" s="43">
@@ -2588,7 +2571,7 @@
         <v/>
       </c>
       <c r="J43" s="41">
-        <f>IF($I43&lt;=0,0,$S42*(Rate_1*MAX(0,MIN($O43,R1_To)-MAX($O42,R1_From))+Rate_2*MAX(0,MIN($O43,R2_To)-MAX($O42,R2_From))+Rate_3*MAX(0,MIN($O43,R3_To)-MAX($O42,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I43&lt;=0,0,$S42*('Engine'!$B$8*MAX(0,MIN($O43,'Engine'!$B$3)-MAX($O42,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O43,'Engine'!$B$5)-MAX($O42,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O43,'Engine'!$B$7)-MAX($O42,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K43" s="41">
@@ -2601,7 +2584,7 @@
         <v/>
       </c>
       <c r="N43" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O43&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O43&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O43" s="25">
@@ -2632,7 +2615,7 @@
         <v/>
       </c>
       <c r="H44" s="42">
-        <f>IF($I44&lt;=0,"",(Rate_1*MAX(0,MIN($O44,R1_To)-MAX($O43,R1_From))+Rate_2*MAX(0,MIN($O44,R2_To)-MAX($O43,R2_From))+Rate_3*MAX(0,MIN($O44,R3_To)-MAX($O43,R3_From)))/100/Day_Basis/$I44*Day_Basis*100)</f>
+        <f>IF($I44&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O44,'Engine'!$B$3)-MAX($O43,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O44,'Engine'!$B$5)-MAX($O43,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O44,'Engine'!$B$7)-MAX($O43,'Engine'!$B$6)))/100/$H$8/$I44*$H$8*100)</f>
         <v/>
       </c>
       <c r="I44" s="43">
@@ -2640,7 +2623,7 @@
         <v/>
       </c>
       <c r="J44" s="41">
-        <f>IF($I44&lt;=0,0,$S43*(Rate_1*MAX(0,MIN($O44,R1_To)-MAX($O43,R1_From))+Rate_2*MAX(0,MIN($O44,R2_To)-MAX($O43,R2_From))+Rate_3*MAX(0,MIN($O44,R3_To)-MAX($O43,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I44&lt;=0,0,$S43*('Engine'!$B$8*MAX(0,MIN($O44,'Engine'!$B$3)-MAX($O43,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O44,'Engine'!$B$5)-MAX($O43,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O44,'Engine'!$B$7)-MAX($O43,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K44" s="41">
@@ -2653,7 +2636,7 @@
         <v/>
       </c>
       <c r="N44" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O44&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O44&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O44" s="25">
@@ -2684,7 +2667,7 @@
         <v/>
       </c>
       <c r="H45" s="42">
-        <f>IF($I45&lt;=0,"",(Rate_1*MAX(0,MIN($O45,R1_To)-MAX($O44,R1_From))+Rate_2*MAX(0,MIN($O45,R2_To)-MAX($O44,R2_From))+Rate_3*MAX(0,MIN($O45,R3_To)-MAX($O44,R3_From)))/100/Day_Basis/$I45*Day_Basis*100)</f>
+        <f>IF($I45&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O45,'Engine'!$B$3)-MAX($O44,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O45,'Engine'!$B$5)-MAX($O44,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O45,'Engine'!$B$7)-MAX($O44,'Engine'!$B$6)))/100/$H$8/$I45*$H$8*100)</f>
         <v/>
       </c>
       <c r="I45" s="43">
@@ -2692,7 +2675,7 @@
         <v/>
       </c>
       <c r="J45" s="41">
-        <f>IF($I45&lt;=0,0,$S44*(Rate_1*MAX(0,MIN($O45,R1_To)-MAX($O44,R1_From))+Rate_2*MAX(0,MIN($O45,R2_To)-MAX($O44,R2_From))+Rate_3*MAX(0,MIN($O45,R3_To)-MAX($O44,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I45&lt;=0,0,$S44*('Engine'!$B$8*MAX(0,MIN($O45,'Engine'!$B$3)-MAX($O44,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O45,'Engine'!$B$5)-MAX($O44,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O45,'Engine'!$B$7)-MAX($O44,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K45" s="41">
@@ -2705,7 +2688,7 @@
         <v/>
       </c>
       <c r="N45" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O45&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O45&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O45" s="25">
@@ -2736,7 +2719,7 @@
         <v/>
       </c>
       <c r="H46" s="42">
-        <f>IF($I46&lt;=0,"",(Rate_1*MAX(0,MIN($O46,R1_To)-MAX($O45,R1_From))+Rate_2*MAX(0,MIN($O46,R2_To)-MAX($O45,R2_From))+Rate_3*MAX(0,MIN($O46,R3_To)-MAX($O45,R3_From)))/100/Day_Basis/$I46*Day_Basis*100)</f>
+        <f>IF($I46&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O46,'Engine'!$B$3)-MAX($O45,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O46,'Engine'!$B$5)-MAX($O45,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O46,'Engine'!$B$7)-MAX($O45,'Engine'!$B$6)))/100/$H$8/$I46*$H$8*100)</f>
         <v/>
       </c>
       <c r="I46" s="43">
@@ -2744,7 +2727,7 @@
         <v/>
       </c>
       <c r="J46" s="41">
-        <f>IF($I46&lt;=0,0,$S45*(Rate_1*MAX(0,MIN($O46,R1_To)-MAX($O45,R1_From))+Rate_2*MAX(0,MIN($O46,R2_To)-MAX($O45,R2_From))+Rate_3*MAX(0,MIN($O46,R3_To)-MAX($O45,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I46&lt;=0,0,$S45*('Engine'!$B$8*MAX(0,MIN($O46,'Engine'!$B$3)-MAX($O45,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O46,'Engine'!$B$5)-MAX($O45,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O46,'Engine'!$B$7)-MAX($O45,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K46" s="41">
@@ -2757,7 +2740,7 @@
         <v/>
       </c>
       <c r="N46" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O46&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O46&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O46" s="25">
@@ -2788,7 +2771,7 @@
         <v/>
       </c>
       <c r="H47" s="42">
-        <f>IF($I47&lt;=0,"",(Rate_1*MAX(0,MIN($O47,R1_To)-MAX($O46,R1_From))+Rate_2*MAX(0,MIN($O47,R2_To)-MAX($O46,R2_From))+Rate_3*MAX(0,MIN($O47,R3_To)-MAX($O46,R3_From)))/100/Day_Basis/$I47*Day_Basis*100)</f>
+        <f>IF($I47&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O47,'Engine'!$B$3)-MAX($O46,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O47,'Engine'!$B$5)-MAX($O46,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O47,'Engine'!$B$7)-MAX($O46,'Engine'!$B$6)))/100/$H$8/$I47*$H$8*100)</f>
         <v/>
       </c>
       <c r="I47" s="43">
@@ -2796,7 +2779,7 @@
         <v/>
       </c>
       <c r="J47" s="41">
-        <f>IF($I47&lt;=0,0,$S46*(Rate_1*MAX(0,MIN($O47,R1_To)-MAX($O46,R1_From))+Rate_2*MAX(0,MIN($O47,R2_To)-MAX($O46,R2_From))+Rate_3*MAX(0,MIN($O47,R3_To)-MAX($O46,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I47&lt;=0,0,$S46*('Engine'!$B$8*MAX(0,MIN($O47,'Engine'!$B$3)-MAX($O46,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O47,'Engine'!$B$5)-MAX($O46,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O47,'Engine'!$B$7)-MAX($O46,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K47" s="41">
@@ -2809,7 +2792,7 @@
         <v/>
       </c>
       <c r="N47" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O47&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O47&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O47" s="25">
@@ -2840,7 +2823,7 @@
         <v/>
       </c>
       <c r="H48" s="42">
-        <f>IF($I48&lt;=0,"",(Rate_1*MAX(0,MIN($O48,R1_To)-MAX($O47,R1_From))+Rate_2*MAX(0,MIN($O48,R2_To)-MAX($O47,R2_From))+Rate_3*MAX(0,MIN($O48,R3_To)-MAX($O47,R3_From)))/100/Day_Basis/$I48*Day_Basis*100)</f>
+        <f>IF($I48&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O48,'Engine'!$B$3)-MAX($O47,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O48,'Engine'!$B$5)-MAX($O47,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O48,'Engine'!$B$7)-MAX($O47,'Engine'!$B$6)))/100/$H$8/$I48*$H$8*100)</f>
         <v/>
       </c>
       <c r="I48" s="43">
@@ -2848,7 +2831,7 @@
         <v/>
       </c>
       <c r="J48" s="41">
-        <f>IF($I48&lt;=0,0,$S47*(Rate_1*MAX(0,MIN($O48,R1_To)-MAX($O47,R1_From))+Rate_2*MAX(0,MIN($O48,R2_To)-MAX($O47,R2_From))+Rate_3*MAX(0,MIN($O48,R3_To)-MAX($O47,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I48&lt;=0,0,$S47*('Engine'!$B$8*MAX(0,MIN($O48,'Engine'!$B$3)-MAX($O47,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O48,'Engine'!$B$5)-MAX($O47,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O48,'Engine'!$B$7)-MAX($O47,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K48" s="41">
@@ -2861,7 +2844,7 @@
         <v/>
       </c>
       <c r="N48" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O48&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O48&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O48" s="25">
@@ -2892,7 +2875,7 @@
         <v/>
       </c>
       <c r="H49" s="42">
-        <f>IF($I49&lt;=0,"",(Rate_1*MAX(0,MIN($O49,R1_To)-MAX($O48,R1_From))+Rate_2*MAX(0,MIN($O49,R2_To)-MAX($O48,R2_From))+Rate_3*MAX(0,MIN($O49,R3_To)-MAX($O48,R3_From)))/100/Day_Basis/$I49*Day_Basis*100)</f>
+        <f>IF($I49&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O49,'Engine'!$B$3)-MAX($O48,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O49,'Engine'!$B$5)-MAX($O48,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O49,'Engine'!$B$7)-MAX($O48,'Engine'!$B$6)))/100/$H$8/$I49*$H$8*100)</f>
         <v/>
       </c>
       <c r="I49" s="43">
@@ -2900,7 +2883,7 @@
         <v/>
       </c>
       <c r="J49" s="41">
-        <f>IF($I49&lt;=0,0,$S48*(Rate_1*MAX(0,MIN($O49,R1_To)-MAX($O48,R1_From))+Rate_2*MAX(0,MIN($O49,R2_To)-MAX($O48,R2_From))+Rate_3*MAX(0,MIN($O49,R3_To)-MAX($O48,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I49&lt;=0,0,$S48*('Engine'!$B$8*MAX(0,MIN($O49,'Engine'!$B$3)-MAX($O48,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O49,'Engine'!$B$5)-MAX($O48,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O49,'Engine'!$B$7)-MAX($O48,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K49" s="41">
@@ -2913,7 +2896,7 @@
         <v/>
       </c>
       <c r="N49" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O49&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O49&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O49" s="25">
@@ -2944,7 +2927,7 @@
         <v/>
       </c>
       <c r="H50" s="42">
-        <f>IF($I50&lt;=0,"",(Rate_1*MAX(0,MIN($O50,R1_To)-MAX($O49,R1_From))+Rate_2*MAX(0,MIN($O50,R2_To)-MAX($O49,R2_From))+Rate_3*MAX(0,MIN($O50,R3_To)-MAX($O49,R3_From)))/100/Day_Basis/$I50*Day_Basis*100)</f>
+        <f>IF($I50&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O50,'Engine'!$B$3)-MAX($O49,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O50,'Engine'!$B$5)-MAX($O49,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O50,'Engine'!$B$7)-MAX($O49,'Engine'!$B$6)))/100/$H$8/$I50*$H$8*100)</f>
         <v/>
       </c>
       <c r="I50" s="43">
@@ -2952,7 +2935,7 @@
         <v/>
       </c>
       <c r="J50" s="41">
-        <f>IF($I50&lt;=0,0,$S49*(Rate_1*MAX(0,MIN($O50,R1_To)-MAX($O49,R1_From))+Rate_2*MAX(0,MIN($O50,R2_To)-MAX($O49,R2_From))+Rate_3*MAX(0,MIN($O50,R3_To)-MAX($O49,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I50&lt;=0,0,$S49*('Engine'!$B$8*MAX(0,MIN($O50,'Engine'!$B$3)-MAX($O49,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O50,'Engine'!$B$5)-MAX($O49,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O50,'Engine'!$B$7)-MAX($O49,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K50" s="41">
@@ -2965,7 +2948,7 @@
         <v/>
       </c>
       <c r="N50" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O50&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O50&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O50" s="25">
@@ -2996,7 +2979,7 @@
         <v/>
       </c>
       <c r="H51" s="42">
-        <f>IF($I51&lt;=0,"",(Rate_1*MAX(0,MIN($O51,R1_To)-MAX($O50,R1_From))+Rate_2*MAX(0,MIN($O51,R2_To)-MAX($O50,R2_From))+Rate_3*MAX(0,MIN($O51,R3_To)-MAX($O50,R3_From)))/100/Day_Basis/$I51*Day_Basis*100)</f>
+        <f>IF($I51&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O51,'Engine'!$B$3)-MAX($O50,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O51,'Engine'!$B$5)-MAX($O50,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O51,'Engine'!$B$7)-MAX($O50,'Engine'!$B$6)))/100/$H$8/$I51*$H$8*100)</f>
         <v/>
       </c>
       <c r="I51" s="43">
@@ -3004,7 +2987,7 @@
         <v/>
       </c>
       <c r="J51" s="41">
-        <f>IF($I51&lt;=0,0,$S50*(Rate_1*MAX(0,MIN($O51,R1_To)-MAX($O50,R1_From))+Rate_2*MAX(0,MIN($O51,R2_To)-MAX($O50,R2_From))+Rate_3*MAX(0,MIN($O51,R3_To)-MAX($O50,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I51&lt;=0,0,$S50*('Engine'!$B$8*MAX(0,MIN($O51,'Engine'!$B$3)-MAX($O50,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O51,'Engine'!$B$5)-MAX($O50,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O51,'Engine'!$B$7)-MAX($O50,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K51" s="41">
@@ -3017,7 +3000,7 @@
         <v/>
       </c>
       <c r="N51" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O51&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O51&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O51" s="25">
@@ -3058,7 +3041,7 @@
         <v/>
       </c>
       <c r="H52" s="51">
-        <f>IF($I52&lt;=0,"",(Rate_1*MAX(0,MIN($O52,R1_To)-MAX($O51,R1_From))+Rate_2*MAX(0,MIN($O52,R2_To)-MAX($O51,R2_From))+Rate_3*MAX(0,MIN($O52,R3_To)-MAX($O51,R3_From)))/100/Day_Basis/$I52*Day_Basis*100)</f>
+        <f>IF($I52&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O52,'Engine'!$B$3)-MAX($O51,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O52,'Engine'!$B$5)-MAX($O51,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O52,'Engine'!$B$7)-MAX($O51,'Engine'!$B$6)))/100/$H$8/$I52*$H$8*100)</f>
         <v/>
       </c>
       <c r="I52" s="52">
@@ -3066,7 +3049,7 @@
         <v/>
       </c>
       <c r="J52" s="53">
-        <f>IF($I52&lt;=0,0,$S51*(Rate_1*MAX(0,MIN($O52,R1_To)-MAX($O51,R1_From))+Rate_2*MAX(0,MIN($O52,R2_To)-MAX($O51,R2_From))+Rate_3*MAX(0,MIN($O52,R3_To)-MAX($O51,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I52&lt;=0,0,$S51*('Engine'!$B$8*MAX(0,MIN($O52,'Engine'!$B$3)-MAX($O51,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O52,'Engine'!$B$5)-MAX($O51,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O52,'Engine'!$B$7)-MAX($O51,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K52" s="53" t="n">
@@ -3078,7 +3061,7 @@
         <v/>
       </c>
       <c r="N52" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O52&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O52&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O52" s="25">
@@ -3095,7 +3078,7 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="24">
-        <f>IF($P$53=0,"QUARTER 4          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 4          "&amp;TEXT($P$53,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$53,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$53&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$53)</f>
+        <f>IF($P$53=0,"QUARTER 4          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 4          "&amp;TEXT($P$53,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$53,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$53&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$53)</f>
         <v/>
       </c>
       <c r="O53" s="25">
@@ -3153,7 +3136,7 @@
         <v/>
       </c>
       <c r="N54" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$54&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$54&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O54" s="25">
@@ -3183,7 +3166,7 @@
         <v/>
       </c>
       <c r="H55" s="42">
-        <f>IF($I55&lt;=0,"",(Rate_1*MAX(0,MIN($O55,R1_To)-MAX($O54,R1_From))+Rate_2*MAX(0,MIN($O55,R2_To)-MAX($O54,R2_From))+Rate_3*MAX(0,MIN($O55,R3_To)-MAX($O54,R3_From)))/100/Day_Basis/$I55*Day_Basis*100)</f>
+        <f>IF($I55&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O55,'Engine'!$B$3)-MAX($O54,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O55,'Engine'!$B$5)-MAX($O54,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O55,'Engine'!$B$7)-MAX($O54,'Engine'!$B$6)))/100/$H$8/$I55*$H$8*100)</f>
         <v/>
       </c>
       <c r="I55" s="43">
@@ -3191,7 +3174,7 @@
         <v/>
       </c>
       <c r="J55" s="41">
-        <f>IF($I55&lt;=0,0,$S54*(Rate_1*MAX(0,MIN($O55,R1_To)-MAX($O54,R1_From))+Rate_2*MAX(0,MIN($O55,R2_To)-MAX($O54,R2_From))+Rate_3*MAX(0,MIN($O55,R3_To)-MAX($O54,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I55&lt;=0,0,$S54*('Engine'!$B$8*MAX(0,MIN($O55,'Engine'!$B$3)-MAX($O54,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O55,'Engine'!$B$5)-MAX($O54,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O55,'Engine'!$B$7)-MAX($O54,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K55" s="41">
@@ -3204,7 +3187,7 @@
         <v/>
       </c>
       <c r="N55" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O55&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O55&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O55" s="25">
@@ -3235,7 +3218,7 @@
         <v/>
       </c>
       <c r="H56" s="42">
-        <f>IF($I56&lt;=0,"",(Rate_1*MAX(0,MIN($O56,R1_To)-MAX($O55,R1_From))+Rate_2*MAX(0,MIN($O56,R2_To)-MAX($O55,R2_From))+Rate_3*MAX(0,MIN($O56,R3_To)-MAX($O55,R3_From)))/100/Day_Basis/$I56*Day_Basis*100)</f>
+        <f>IF($I56&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O56,'Engine'!$B$3)-MAX($O55,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O56,'Engine'!$B$5)-MAX($O55,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O56,'Engine'!$B$7)-MAX($O55,'Engine'!$B$6)))/100/$H$8/$I56*$H$8*100)</f>
         <v/>
       </c>
       <c r="I56" s="43">
@@ -3243,7 +3226,7 @@
         <v/>
       </c>
       <c r="J56" s="41">
-        <f>IF($I56&lt;=0,0,$S55*(Rate_1*MAX(0,MIN($O56,R1_To)-MAX($O55,R1_From))+Rate_2*MAX(0,MIN($O56,R2_To)-MAX($O55,R2_From))+Rate_3*MAX(0,MIN($O56,R3_To)-MAX($O55,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I56&lt;=0,0,$S55*('Engine'!$B$8*MAX(0,MIN($O56,'Engine'!$B$3)-MAX($O55,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O56,'Engine'!$B$5)-MAX($O55,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O56,'Engine'!$B$7)-MAX($O55,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K56" s="41">
@@ -3256,7 +3239,7 @@
         <v/>
       </c>
       <c r="N56" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O56&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O56&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O56" s="25">
@@ -3287,7 +3270,7 @@
         <v/>
       </c>
       <c r="H57" s="42">
-        <f>IF($I57&lt;=0,"",(Rate_1*MAX(0,MIN($O57,R1_To)-MAX($O56,R1_From))+Rate_2*MAX(0,MIN($O57,R2_To)-MAX($O56,R2_From))+Rate_3*MAX(0,MIN($O57,R3_To)-MAX($O56,R3_From)))/100/Day_Basis/$I57*Day_Basis*100)</f>
+        <f>IF($I57&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O57,'Engine'!$B$3)-MAX($O56,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O57,'Engine'!$B$5)-MAX($O56,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O57,'Engine'!$B$7)-MAX($O56,'Engine'!$B$6)))/100/$H$8/$I57*$H$8*100)</f>
         <v/>
       </c>
       <c r="I57" s="43">
@@ -3295,7 +3278,7 @@
         <v/>
       </c>
       <c r="J57" s="41">
-        <f>IF($I57&lt;=0,0,$S56*(Rate_1*MAX(0,MIN($O57,R1_To)-MAX($O56,R1_From))+Rate_2*MAX(0,MIN($O57,R2_To)-MAX($O56,R2_From))+Rate_3*MAX(0,MIN($O57,R3_To)-MAX($O56,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I57&lt;=0,0,$S56*('Engine'!$B$8*MAX(0,MIN($O57,'Engine'!$B$3)-MAX($O56,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O57,'Engine'!$B$5)-MAX($O56,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O57,'Engine'!$B$7)-MAX($O56,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K57" s="41">
@@ -3308,7 +3291,7 @@
         <v/>
       </c>
       <c r="N57" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O57&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O57&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O57" s="25">
@@ -3339,7 +3322,7 @@
         <v/>
       </c>
       <c r="H58" s="42">
-        <f>IF($I58&lt;=0,"",(Rate_1*MAX(0,MIN($O58,R1_To)-MAX($O57,R1_From))+Rate_2*MAX(0,MIN($O58,R2_To)-MAX($O57,R2_From))+Rate_3*MAX(0,MIN($O58,R3_To)-MAX($O57,R3_From)))/100/Day_Basis/$I58*Day_Basis*100)</f>
+        <f>IF($I58&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O58,'Engine'!$B$3)-MAX($O57,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O58,'Engine'!$B$5)-MAX($O57,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O58,'Engine'!$B$7)-MAX($O57,'Engine'!$B$6)))/100/$H$8/$I58*$H$8*100)</f>
         <v/>
       </c>
       <c r="I58" s="43">
@@ -3347,7 +3330,7 @@
         <v/>
       </c>
       <c r="J58" s="41">
-        <f>IF($I58&lt;=0,0,$S57*(Rate_1*MAX(0,MIN($O58,R1_To)-MAX($O57,R1_From))+Rate_2*MAX(0,MIN($O58,R2_To)-MAX($O57,R2_From))+Rate_3*MAX(0,MIN($O58,R3_To)-MAX($O57,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I58&lt;=0,0,$S57*('Engine'!$B$8*MAX(0,MIN($O58,'Engine'!$B$3)-MAX($O57,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O58,'Engine'!$B$5)-MAX($O57,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O58,'Engine'!$B$7)-MAX($O57,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K58" s="41">
@@ -3360,7 +3343,7 @@
         <v/>
       </c>
       <c r="N58" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O58&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O58&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O58" s="25">
@@ -3391,7 +3374,7 @@
         <v/>
       </c>
       <c r="H59" s="42">
-        <f>IF($I59&lt;=0,"",(Rate_1*MAX(0,MIN($O59,R1_To)-MAX($O58,R1_From))+Rate_2*MAX(0,MIN($O59,R2_To)-MAX($O58,R2_From))+Rate_3*MAX(0,MIN($O59,R3_To)-MAX($O58,R3_From)))/100/Day_Basis/$I59*Day_Basis*100)</f>
+        <f>IF($I59&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O59,'Engine'!$B$3)-MAX($O58,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O59,'Engine'!$B$5)-MAX($O58,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O59,'Engine'!$B$7)-MAX($O58,'Engine'!$B$6)))/100/$H$8/$I59*$H$8*100)</f>
         <v/>
       </c>
       <c r="I59" s="43">
@@ -3399,7 +3382,7 @@
         <v/>
       </c>
       <c r="J59" s="41">
-        <f>IF($I59&lt;=0,0,$S58*(Rate_1*MAX(0,MIN($O59,R1_To)-MAX($O58,R1_From))+Rate_2*MAX(0,MIN($O59,R2_To)-MAX($O58,R2_From))+Rate_3*MAX(0,MIN($O59,R3_To)-MAX($O58,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I59&lt;=0,0,$S58*('Engine'!$B$8*MAX(0,MIN($O59,'Engine'!$B$3)-MAX($O58,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O59,'Engine'!$B$5)-MAX($O58,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O59,'Engine'!$B$7)-MAX($O58,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K59" s="41">
@@ -3412,7 +3395,7 @@
         <v/>
       </c>
       <c r="N59" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O59&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O59&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O59" s="25">
@@ -3443,7 +3426,7 @@
         <v/>
       </c>
       <c r="H60" s="42">
-        <f>IF($I60&lt;=0,"",(Rate_1*MAX(0,MIN($O60,R1_To)-MAX($O59,R1_From))+Rate_2*MAX(0,MIN($O60,R2_To)-MAX($O59,R2_From))+Rate_3*MAX(0,MIN($O60,R3_To)-MAX($O59,R3_From)))/100/Day_Basis/$I60*Day_Basis*100)</f>
+        <f>IF($I60&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O60,'Engine'!$B$3)-MAX($O59,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O60,'Engine'!$B$5)-MAX($O59,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O60,'Engine'!$B$7)-MAX($O59,'Engine'!$B$6)))/100/$H$8/$I60*$H$8*100)</f>
         <v/>
       </c>
       <c r="I60" s="43">
@@ -3451,7 +3434,7 @@
         <v/>
       </c>
       <c r="J60" s="41">
-        <f>IF($I60&lt;=0,0,$S59*(Rate_1*MAX(0,MIN($O60,R1_To)-MAX($O59,R1_From))+Rate_2*MAX(0,MIN($O60,R2_To)-MAX($O59,R2_From))+Rate_3*MAX(0,MIN($O60,R3_To)-MAX($O59,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I60&lt;=0,0,$S59*('Engine'!$B$8*MAX(0,MIN($O60,'Engine'!$B$3)-MAX($O59,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O60,'Engine'!$B$5)-MAX($O59,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O60,'Engine'!$B$7)-MAX($O59,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K60" s="41">
@@ -3464,7 +3447,7 @@
         <v/>
       </c>
       <c r="N60" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O60&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O60&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O60" s="25">
@@ -3495,7 +3478,7 @@
         <v/>
       </c>
       <c r="H61" s="42">
-        <f>IF($I61&lt;=0,"",(Rate_1*MAX(0,MIN($O61,R1_To)-MAX($O60,R1_From))+Rate_2*MAX(0,MIN($O61,R2_To)-MAX($O60,R2_From))+Rate_3*MAX(0,MIN($O61,R3_To)-MAX($O60,R3_From)))/100/Day_Basis/$I61*Day_Basis*100)</f>
+        <f>IF($I61&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O61,'Engine'!$B$3)-MAX($O60,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O61,'Engine'!$B$5)-MAX($O60,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O61,'Engine'!$B$7)-MAX($O60,'Engine'!$B$6)))/100/$H$8/$I61*$H$8*100)</f>
         <v/>
       </c>
       <c r="I61" s="43">
@@ -3503,7 +3486,7 @@
         <v/>
       </c>
       <c r="J61" s="41">
-        <f>IF($I61&lt;=0,0,$S60*(Rate_1*MAX(0,MIN($O61,R1_To)-MAX($O60,R1_From))+Rate_2*MAX(0,MIN($O61,R2_To)-MAX($O60,R2_From))+Rate_3*MAX(0,MIN($O61,R3_To)-MAX($O60,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I61&lt;=0,0,$S60*('Engine'!$B$8*MAX(0,MIN($O61,'Engine'!$B$3)-MAX($O60,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O61,'Engine'!$B$5)-MAX($O60,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O61,'Engine'!$B$7)-MAX($O60,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K61" s="41">
@@ -3516,7 +3499,7 @@
         <v/>
       </c>
       <c r="N61" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O61&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O61&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O61" s="25">
@@ -3547,7 +3530,7 @@
         <v/>
       </c>
       <c r="H62" s="42">
-        <f>IF($I62&lt;=0,"",(Rate_1*MAX(0,MIN($O62,R1_To)-MAX($O61,R1_From))+Rate_2*MAX(0,MIN($O62,R2_To)-MAX($O61,R2_From))+Rate_3*MAX(0,MIN($O62,R3_To)-MAX($O61,R3_From)))/100/Day_Basis/$I62*Day_Basis*100)</f>
+        <f>IF($I62&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O62,'Engine'!$B$3)-MAX($O61,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O62,'Engine'!$B$5)-MAX($O61,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O62,'Engine'!$B$7)-MAX($O61,'Engine'!$B$6)))/100/$H$8/$I62*$H$8*100)</f>
         <v/>
       </c>
       <c r="I62" s="43">
@@ -3555,7 +3538,7 @@
         <v/>
       </c>
       <c r="J62" s="41">
-        <f>IF($I62&lt;=0,0,$S61*(Rate_1*MAX(0,MIN($O62,R1_To)-MAX($O61,R1_From))+Rate_2*MAX(0,MIN($O62,R2_To)-MAX($O61,R2_From))+Rate_3*MAX(0,MIN($O62,R3_To)-MAX($O61,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I62&lt;=0,0,$S61*('Engine'!$B$8*MAX(0,MIN($O62,'Engine'!$B$3)-MAX($O61,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O62,'Engine'!$B$5)-MAX($O61,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O62,'Engine'!$B$7)-MAX($O61,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K62" s="41">
@@ -3568,7 +3551,7 @@
         <v/>
       </c>
       <c r="N62" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O62&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O62&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O62" s="25">
@@ -3599,7 +3582,7 @@
         <v/>
       </c>
       <c r="H63" s="42">
-        <f>IF($I63&lt;=0,"",(Rate_1*MAX(0,MIN($O63,R1_To)-MAX($O62,R1_From))+Rate_2*MAX(0,MIN($O63,R2_To)-MAX($O62,R2_From))+Rate_3*MAX(0,MIN($O63,R3_To)-MAX($O62,R3_From)))/100/Day_Basis/$I63*Day_Basis*100)</f>
+        <f>IF($I63&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O63,'Engine'!$B$3)-MAX($O62,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O63,'Engine'!$B$5)-MAX($O62,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O63,'Engine'!$B$7)-MAX($O62,'Engine'!$B$6)))/100/$H$8/$I63*$H$8*100)</f>
         <v/>
       </c>
       <c r="I63" s="43">
@@ -3607,7 +3590,7 @@
         <v/>
       </c>
       <c r="J63" s="41">
-        <f>IF($I63&lt;=0,0,$S62*(Rate_1*MAX(0,MIN($O63,R1_To)-MAX($O62,R1_From))+Rate_2*MAX(0,MIN($O63,R2_To)-MAX($O62,R2_From))+Rate_3*MAX(0,MIN($O63,R3_To)-MAX($O62,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I63&lt;=0,0,$S62*('Engine'!$B$8*MAX(0,MIN($O63,'Engine'!$B$3)-MAX($O62,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O63,'Engine'!$B$5)-MAX($O62,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O63,'Engine'!$B$7)-MAX($O62,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K63" s="41">
@@ -3620,7 +3603,7 @@
         <v/>
       </c>
       <c r="N63" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O63&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O63&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O63" s="25">
@@ -3651,7 +3634,7 @@
         <v/>
       </c>
       <c r="H64" s="42">
-        <f>IF($I64&lt;=0,"",(Rate_1*MAX(0,MIN($O64,R1_To)-MAX($O63,R1_From))+Rate_2*MAX(0,MIN($O64,R2_To)-MAX($O63,R2_From))+Rate_3*MAX(0,MIN($O64,R3_To)-MAX($O63,R3_From)))/100/Day_Basis/$I64*Day_Basis*100)</f>
+        <f>IF($I64&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O64,'Engine'!$B$3)-MAX($O63,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O64,'Engine'!$B$5)-MAX($O63,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O64,'Engine'!$B$7)-MAX($O63,'Engine'!$B$6)))/100/$H$8/$I64*$H$8*100)</f>
         <v/>
       </c>
       <c r="I64" s="43">
@@ -3659,7 +3642,7 @@
         <v/>
       </c>
       <c r="J64" s="41">
-        <f>IF($I64&lt;=0,0,$S63*(Rate_1*MAX(0,MIN($O64,R1_To)-MAX($O63,R1_From))+Rate_2*MAX(0,MIN($O64,R2_To)-MAX($O63,R2_From))+Rate_3*MAX(0,MIN($O64,R3_To)-MAX($O63,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I64&lt;=0,0,$S63*('Engine'!$B$8*MAX(0,MIN($O64,'Engine'!$B$3)-MAX($O63,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O64,'Engine'!$B$5)-MAX($O63,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O64,'Engine'!$B$7)-MAX($O63,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K64" s="41">
@@ -3672,7 +3655,7 @@
         <v/>
       </c>
       <c r="N64" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O64&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O64&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O64" s="25">
@@ -3713,7 +3696,7 @@
         <v/>
       </c>
       <c r="H65" s="51">
-        <f>IF($I65&lt;=0,"",(Rate_1*MAX(0,MIN($O65,R1_To)-MAX($O64,R1_From))+Rate_2*MAX(0,MIN($O65,R2_To)-MAX($O64,R2_From))+Rate_3*MAX(0,MIN($O65,R3_To)-MAX($O64,R3_From)))/100/Day_Basis/$I65*Day_Basis*100)</f>
+        <f>IF($I65&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O65,'Engine'!$B$3)-MAX($O64,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O65,'Engine'!$B$5)-MAX($O64,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O65,'Engine'!$B$7)-MAX($O64,'Engine'!$B$6)))/100/$H$8/$I65*$H$8*100)</f>
         <v/>
       </c>
       <c r="I65" s="52">
@@ -3721,7 +3704,7 @@
         <v/>
       </c>
       <c r="J65" s="53">
-        <f>IF($I65&lt;=0,0,$S64*(Rate_1*MAX(0,MIN($O65,R1_To)-MAX($O64,R1_From))+Rate_2*MAX(0,MIN($O65,R2_To)-MAX($O64,R2_From))+Rate_3*MAX(0,MIN($O65,R3_To)-MAX($O64,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I65&lt;=0,0,$S64*('Engine'!$B$8*MAX(0,MIN($O65,'Engine'!$B$3)-MAX($O64,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O65,'Engine'!$B$5)-MAX($O64,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O65,'Engine'!$B$7)-MAX($O64,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K65" s="53" t="n">
@@ -3733,7 +3716,7 @@
         <v/>
       </c>
       <c r="N65" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O65&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O65&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O65" s="25">
@@ -3750,7 +3733,7 @@
     </row>
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="24">
-        <f>IF($P$66=0,"QUARTER 5          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 5          "&amp;TEXT($P$66,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$66,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$66&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$66)</f>
+        <f>IF($P$66=0,"QUARTER 5          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 5          "&amp;TEXT($P$66,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$66,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$66&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$66)</f>
         <v/>
       </c>
       <c r="O66" s="25">
@@ -3808,7 +3791,7 @@
         <v/>
       </c>
       <c r="N67" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$67&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$67&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O67" s="25">
@@ -3838,7 +3821,7 @@
         <v/>
       </c>
       <c r="H68" s="42">
-        <f>IF($I68&lt;=0,"",(Rate_1*MAX(0,MIN($O68,R1_To)-MAX($O67,R1_From))+Rate_2*MAX(0,MIN($O68,R2_To)-MAX($O67,R2_From))+Rate_3*MAX(0,MIN($O68,R3_To)-MAX($O67,R3_From)))/100/Day_Basis/$I68*Day_Basis*100)</f>
+        <f>IF($I68&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O68,'Engine'!$B$3)-MAX($O67,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O68,'Engine'!$B$5)-MAX($O67,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O68,'Engine'!$B$7)-MAX($O67,'Engine'!$B$6)))/100/$H$8/$I68*$H$8*100)</f>
         <v/>
       </c>
       <c r="I68" s="43">
@@ -3846,7 +3829,7 @@
         <v/>
       </c>
       <c r="J68" s="41">
-        <f>IF($I68&lt;=0,0,$S67*(Rate_1*MAX(0,MIN($O68,R1_To)-MAX($O67,R1_From))+Rate_2*MAX(0,MIN($O68,R2_To)-MAX($O67,R2_From))+Rate_3*MAX(0,MIN($O68,R3_To)-MAX($O67,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I68&lt;=0,0,$S67*('Engine'!$B$8*MAX(0,MIN($O68,'Engine'!$B$3)-MAX($O67,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O68,'Engine'!$B$5)-MAX($O67,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O68,'Engine'!$B$7)-MAX($O67,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K68" s="41">
@@ -3859,7 +3842,7 @@
         <v/>
       </c>
       <c r="N68" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O68&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O68&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O68" s="25">
@@ -3890,7 +3873,7 @@
         <v/>
       </c>
       <c r="H69" s="42">
-        <f>IF($I69&lt;=0,"",(Rate_1*MAX(0,MIN($O69,R1_To)-MAX($O68,R1_From))+Rate_2*MAX(0,MIN($O69,R2_To)-MAX($O68,R2_From))+Rate_3*MAX(0,MIN($O69,R3_To)-MAX($O68,R3_From)))/100/Day_Basis/$I69*Day_Basis*100)</f>
+        <f>IF($I69&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O69,'Engine'!$B$3)-MAX($O68,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O69,'Engine'!$B$5)-MAX($O68,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O69,'Engine'!$B$7)-MAX($O68,'Engine'!$B$6)))/100/$H$8/$I69*$H$8*100)</f>
         <v/>
       </c>
       <c r="I69" s="43">
@@ -3898,7 +3881,7 @@
         <v/>
       </c>
       <c r="J69" s="41">
-        <f>IF($I69&lt;=0,0,$S68*(Rate_1*MAX(0,MIN($O69,R1_To)-MAX($O68,R1_From))+Rate_2*MAX(0,MIN($O69,R2_To)-MAX($O68,R2_From))+Rate_3*MAX(0,MIN($O69,R3_To)-MAX($O68,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I69&lt;=0,0,$S68*('Engine'!$B$8*MAX(0,MIN($O69,'Engine'!$B$3)-MAX($O68,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O69,'Engine'!$B$5)-MAX($O68,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O69,'Engine'!$B$7)-MAX($O68,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K69" s="41">
@@ -3911,7 +3894,7 @@
         <v/>
       </c>
       <c r="N69" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O69&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O69&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O69" s="25">
@@ -3942,7 +3925,7 @@
         <v/>
       </c>
       <c r="H70" s="42">
-        <f>IF($I70&lt;=0,"",(Rate_1*MAX(0,MIN($O70,R1_To)-MAX($O69,R1_From))+Rate_2*MAX(0,MIN($O70,R2_To)-MAX($O69,R2_From))+Rate_3*MAX(0,MIN($O70,R3_To)-MAX($O69,R3_From)))/100/Day_Basis/$I70*Day_Basis*100)</f>
+        <f>IF($I70&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O70,'Engine'!$B$3)-MAX($O69,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O70,'Engine'!$B$5)-MAX($O69,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O70,'Engine'!$B$7)-MAX($O69,'Engine'!$B$6)))/100/$H$8/$I70*$H$8*100)</f>
         <v/>
       </c>
       <c r="I70" s="43">
@@ -3950,7 +3933,7 @@
         <v/>
       </c>
       <c r="J70" s="41">
-        <f>IF($I70&lt;=0,0,$S69*(Rate_1*MAX(0,MIN($O70,R1_To)-MAX($O69,R1_From))+Rate_2*MAX(0,MIN($O70,R2_To)-MAX($O69,R2_From))+Rate_3*MAX(0,MIN($O70,R3_To)-MAX($O69,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I70&lt;=0,0,$S69*('Engine'!$B$8*MAX(0,MIN($O70,'Engine'!$B$3)-MAX($O69,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O70,'Engine'!$B$5)-MAX($O69,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O70,'Engine'!$B$7)-MAX($O69,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K70" s="41">
@@ -3963,7 +3946,7 @@
         <v/>
       </c>
       <c r="N70" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O70&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O70&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O70" s="25">
@@ -3994,7 +3977,7 @@
         <v/>
       </c>
       <c r="H71" s="42">
-        <f>IF($I71&lt;=0,"",(Rate_1*MAX(0,MIN($O71,R1_To)-MAX($O70,R1_From))+Rate_2*MAX(0,MIN($O71,R2_To)-MAX($O70,R2_From))+Rate_3*MAX(0,MIN($O71,R3_To)-MAX($O70,R3_From)))/100/Day_Basis/$I71*Day_Basis*100)</f>
+        <f>IF($I71&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O71,'Engine'!$B$3)-MAX($O70,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O71,'Engine'!$B$5)-MAX($O70,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O71,'Engine'!$B$7)-MAX($O70,'Engine'!$B$6)))/100/$H$8/$I71*$H$8*100)</f>
         <v/>
       </c>
       <c r="I71" s="43">
@@ -4002,7 +3985,7 @@
         <v/>
       </c>
       <c r="J71" s="41">
-        <f>IF($I71&lt;=0,0,$S70*(Rate_1*MAX(0,MIN($O71,R1_To)-MAX($O70,R1_From))+Rate_2*MAX(0,MIN($O71,R2_To)-MAX($O70,R2_From))+Rate_3*MAX(0,MIN($O71,R3_To)-MAX($O70,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I71&lt;=0,0,$S70*('Engine'!$B$8*MAX(0,MIN($O71,'Engine'!$B$3)-MAX($O70,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O71,'Engine'!$B$5)-MAX($O70,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O71,'Engine'!$B$7)-MAX($O70,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K71" s="41">
@@ -4015,7 +3998,7 @@
         <v/>
       </c>
       <c r="N71" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O71&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O71&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O71" s="25">
@@ -4046,7 +4029,7 @@
         <v/>
       </c>
       <c r="H72" s="42">
-        <f>IF($I72&lt;=0,"",(Rate_1*MAX(0,MIN($O72,R1_To)-MAX($O71,R1_From))+Rate_2*MAX(0,MIN($O72,R2_To)-MAX($O71,R2_From))+Rate_3*MAX(0,MIN($O72,R3_To)-MAX($O71,R3_From)))/100/Day_Basis/$I72*Day_Basis*100)</f>
+        <f>IF($I72&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O72,'Engine'!$B$3)-MAX($O71,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O72,'Engine'!$B$5)-MAX($O71,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O72,'Engine'!$B$7)-MAX($O71,'Engine'!$B$6)))/100/$H$8/$I72*$H$8*100)</f>
         <v/>
       </c>
       <c r="I72" s="43">
@@ -4054,7 +4037,7 @@
         <v/>
       </c>
       <c r="J72" s="41">
-        <f>IF($I72&lt;=0,0,$S71*(Rate_1*MAX(0,MIN($O72,R1_To)-MAX($O71,R1_From))+Rate_2*MAX(0,MIN($O72,R2_To)-MAX($O71,R2_From))+Rate_3*MAX(0,MIN($O72,R3_To)-MAX($O71,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I72&lt;=0,0,$S71*('Engine'!$B$8*MAX(0,MIN($O72,'Engine'!$B$3)-MAX($O71,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O72,'Engine'!$B$5)-MAX($O71,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O72,'Engine'!$B$7)-MAX($O71,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K72" s="41">
@@ -4067,7 +4050,7 @@
         <v/>
       </c>
       <c r="N72" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O72&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O72&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O72" s="25">
@@ -4098,7 +4081,7 @@
         <v/>
       </c>
       <c r="H73" s="42">
-        <f>IF($I73&lt;=0,"",(Rate_1*MAX(0,MIN($O73,R1_To)-MAX($O72,R1_From))+Rate_2*MAX(0,MIN($O73,R2_To)-MAX($O72,R2_From))+Rate_3*MAX(0,MIN($O73,R3_To)-MAX($O72,R3_From)))/100/Day_Basis/$I73*Day_Basis*100)</f>
+        <f>IF($I73&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O73,'Engine'!$B$3)-MAX($O72,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O73,'Engine'!$B$5)-MAX($O72,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O73,'Engine'!$B$7)-MAX($O72,'Engine'!$B$6)))/100/$H$8/$I73*$H$8*100)</f>
         <v/>
       </c>
       <c r="I73" s="43">
@@ -4106,7 +4089,7 @@
         <v/>
       </c>
       <c r="J73" s="41">
-        <f>IF($I73&lt;=0,0,$S72*(Rate_1*MAX(0,MIN($O73,R1_To)-MAX($O72,R1_From))+Rate_2*MAX(0,MIN($O73,R2_To)-MAX($O72,R2_From))+Rate_3*MAX(0,MIN($O73,R3_To)-MAX($O72,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I73&lt;=0,0,$S72*('Engine'!$B$8*MAX(0,MIN($O73,'Engine'!$B$3)-MAX($O72,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O73,'Engine'!$B$5)-MAX($O72,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O73,'Engine'!$B$7)-MAX($O72,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K73" s="41">
@@ -4119,7 +4102,7 @@
         <v/>
       </c>
       <c r="N73" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O73&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O73&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O73" s="25">
@@ -4150,7 +4133,7 @@
         <v/>
       </c>
       <c r="H74" s="42">
-        <f>IF($I74&lt;=0,"",(Rate_1*MAX(0,MIN($O74,R1_To)-MAX($O73,R1_From))+Rate_2*MAX(0,MIN($O74,R2_To)-MAX($O73,R2_From))+Rate_3*MAX(0,MIN($O74,R3_To)-MAX($O73,R3_From)))/100/Day_Basis/$I74*Day_Basis*100)</f>
+        <f>IF($I74&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O74,'Engine'!$B$3)-MAX($O73,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O74,'Engine'!$B$5)-MAX($O73,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O74,'Engine'!$B$7)-MAX($O73,'Engine'!$B$6)))/100/$H$8/$I74*$H$8*100)</f>
         <v/>
       </c>
       <c r="I74" s="43">
@@ -4158,7 +4141,7 @@
         <v/>
       </c>
       <c r="J74" s="41">
-        <f>IF($I74&lt;=0,0,$S73*(Rate_1*MAX(0,MIN($O74,R1_To)-MAX($O73,R1_From))+Rate_2*MAX(0,MIN($O74,R2_To)-MAX($O73,R2_From))+Rate_3*MAX(0,MIN($O74,R3_To)-MAX($O73,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I74&lt;=0,0,$S73*('Engine'!$B$8*MAX(0,MIN($O74,'Engine'!$B$3)-MAX($O73,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O74,'Engine'!$B$5)-MAX($O73,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O74,'Engine'!$B$7)-MAX($O73,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K74" s="41">
@@ -4171,7 +4154,7 @@
         <v/>
       </c>
       <c r="N74" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O74&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O74&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O74" s="25">
@@ -4202,7 +4185,7 @@
         <v/>
       </c>
       <c r="H75" s="42">
-        <f>IF($I75&lt;=0,"",(Rate_1*MAX(0,MIN($O75,R1_To)-MAX($O74,R1_From))+Rate_2*MAX(0,MIN($O75,R2_To)-MAX($O74,R2_From))+Rate_3*MAX(0,MIN($O75,R3_To)-MAX($O74,R3_From)))/100/Day_Basis/$I75*Day_Basis*100)</f>
+        <f>IF($I75&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O75,'Engine'!$B$3)-MAX($O74,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O75,'Engine'!$B$5)-MAX($O74,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O75,'Engine'!$B$7)-MAX($O74,'Engine'!$B$6)))/100/$H$8/$I75*$H$8*100)</f>
         <v/>
       </c>
       <c r="I75" s="43">
@@ -4210,7 +4193,7 @@
         <v/>
       </c>
       <c r="J75" s="41">
-        <f>IF($I75&lt;=0,0,$S74*(Rate_1*MAX(0,MIN($O75,R1_To)-MAX($O74,R1_From))+Rate_2*MAX(0,MIN($O75,R2_To)-MAX($O74,R2_From))+Rate_3*MAX(0,MIN($O75,R3_To)-MAX($O74,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I75&lt;=0,0,$S74*('Engine'!$B$8*MAX(0,MIN($O75,'Engine'!$B$3)-MAX($O74,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O75,'Engine'!$B$5)-MAX($O74,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O75,'Engine'!$B$7)-MAX($O74,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K75" s="41">
@@ -4223,7 +4206,7 @@
         <v/>
       </c>
       <c r="N75" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O75&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O75&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O75" s="25">
@@ -4254,7 +4237,7 @@
         <v/>
       </c>
       <c r="H76" s="42">
-        <f>IF($I76&lt;=0,"",(Rate_1*MAX(0,MIN($O76,R1_To)-MAX($O75,R1_From))+Rate_2*MAX(0,MIN($O76,R2_To)-MAX($O75,R2_From))+Rate_3*MAX(0,MIN($O76,R3_To)-MAX($O75,R3_From)))/100/Day_Basis/$I76*Day_Basis*100)</f>
+        <f>IF($I76&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O76,'Engine'!$B$3)-MAX($O75,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O76,'Engine'!$B$5)-MAX($O75,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O76,'Engine'!$B$7)-MAX($O75,'Engine'!$B$6)))/100/$H$8/$I76*$H$8*100)</f>
         <v/>
       </c>
       <c r="I76" s="43">
@@ -4262,7 +4245,7 @@
         <v/>
       </c>
       <c r="J76" s="41">
-        <f>IF($I76&lt;=0,0,$S75*(Rate_1*MAX(0,MIN($O76,R1_To)-MAX($O75,R1_From))+Rate_2*MAX(0,MIN($O76,R2_To)-MAX($O75,R2_From))+Rate_3*MAX(0,MIN($O76,R3_To)-MAX($O75,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I76&lt;=0,0,$S75*('Engine'!$B$8*MAX(0,MIN($O76,'Engine'!$B$3)-MAX($O75,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O76,'Engine'!$B$5)-MAX($O75,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O76,'Engine'!$B$7)-MAX($O75,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K76" s="41">
@@ -4275,7 +4258,7 @@
         <v/>
       </c>
       <c r="N76" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O76&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O76&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O76" s="25">
@@ -4306,7 +4289,7 @@
         <v/>
       </c>
       <c r="H77" s="42">
-        <f>IF($I77&lt;=0,"",(Rate_1*MAX(0,MIN($O77,R1_To)-MAX($O76,R1_From))+Rate_2*MAX(0,MIN($O77,R2_To)-MAX($O76,R2_From))+Rate_3*MAX(0,MIN($O77,R3_To)-MAX($O76,R3_From)))/100/Day_Basis/$I77*Day_Basis*100)</f>
+        <f>IF($I77&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O77,'Engine'!$B$3)-MAX($O76,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O77,'Engine'!$B$5)-MAX($O76,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O77,'Engine'!$B$7)-MAX($O76,'Engine'!$B$6)))/100/$H$8/$I77*$H$8*100)</f>
         <v/>
       </c>
       <c r="I77" s="43">
@@ -4314,7 +4297,7 @@
         <v/>
       </c>
       <c r="J77" s="41">
-        <f>IF($I77&lt;=0,0,$S76*(Rate_1*MAX(0,MIN($O77,R1_To)-MAX($O76,R1_From))+Rate_2*MAX(0,MIN($O77,R2_To)-MAX($O76,R2_From))+Rate_3*MAX(0,MIN($O77,R3_To)-MAX($O76,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I77&lt;=0,0,$S76*('Engine'!$B$8*MAX(0,MIN($O77,'Engine'!$B$3)-MAX($O76,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O77,'Engine'!$B$5)-MAX($O76,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O77,'Engine'!$B$7)-MAX($O76,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K77" s="41">
@@ -4327,7 +4310,7 @@
         <v/>
       </c>
       <c r="N77" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O77&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O77&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O77" s="25">
@@ -4368,7 +4351,7 @@
         <v/>
       </c>
       <c r="H78" s="51">
-        <f>IF($I78&lt;=0,"",(Rate_1*MAX(0,MIN($O78,R1_To)-MAX($O77,R1_From))+Rate_2*MAX(0,MIN($O78,R2_To)-MAX($O77,R2_From))+Rate_3*MAX(0,MIN($O78,R3_To)-MAX($O77,R3_From)))/100/Day_Basis/$I78*Day_Basis*100)</f>
+        <f>IF($I78&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O78,'Engine'!$B$3)-MAX($O77,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O78,'Engine'!$B$5)-MAX($O77,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O78,'Engine'!$B$7)-MAX($O77,'Engine'!$B$6)))/100/$H$8/$I78*$H$8*100)</f>
         <v/>
       </c>
       <c r="I78" s="52">
@@ -4376,7 +4359,7 @@
         <v/>
       </c>
       <c r="J78" s="53">
-        <f>IF($I78&lt;=0,0,$S77*(Rate_1*MAX(0,MIN($O78,R1_To)-MAX($O77,R1_From))+Rate_2*MAX(0,MIN($O78,R2_To)-MAX($O77,R2_From))+Rate_3*MAX(0,MIN($O78,R3_To)-MAX($O77,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I78&lt;=0,0,$S77*('Engine'!$B$8*MAX(0,MIN($O78,'Engine'!$B$3)-MAX($O77,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O78,'Engine'!$B$5)-MAX($O77,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O78,'Engine'!$B$7)-MAX($O77,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K78" s="53" t="n">
@@ -4388,7 +4371,7 @@
         <v/>
       </c>
       <c r="N78" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O78&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O78&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O78" s="25">
@@ -4405,7 +4388,7 @@
     </row>
     <row r="79" ht="18" customHeight="1">
       <c r="A79" s="24">
-        <f>IF($P$79=0,"QUARTER 6          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 6          "&amp;TEXT($P$79,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$79,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$79&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$79)</f>
+        <f>IF($P$79=0,"QUARTER 6          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 6          "&amp;TEXT($P$79,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$79,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$79&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$79)</f>
         <v/>
       </c>
       <c r="O79" s="25">
@@ -4463,7 +4446,7 @@
         <v/>
       </c>
       <c r="N80" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$80&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$80&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O80" s="25">
@@ -4493,7 +4476,7 @@
         <v/>
       </c>
       <c r="H81" s="42">
-        <f>IF($I81&lt;=0,"",(Rate_1*MAX(0,MIN($O81,R1_To)-MAX($O80,R1_From))+Rate_2*MAX(0,MIN($O81,R2_To)-MAX($O80,R2_From))+Rate_3*MAX(0,MIN($O81,R3_To)-MAX($O80,R3_From)))/100/Day_Basis/$I81*Day_Basis*100)</f>
+        <f>IF($I81&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O81,'Engine'!$B$3)-MAX($O80,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O81,'Engine'!$B$5)-MAX($O80,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O81,'Engine'!$B$7)-MAX($O80,'Engine'!$B$6)))/100/$H$8/$I81*$H$8*100)</f>
         <v/>
       </c>
       <c r="I81" s="43">
@@ -4501,7 +4484,7 @@
         <v/>
       </c>
       <c r="J81" s="41">
-        <f>IF($I81&lt;=0,0,$S80*(Rate_1*MAX(0,MIN($O81,R1_To)-MAX($O80,R1_From))+Rate_2*MAX(0,MIN($O81,R2_To)-MAX($O80,R2_From))+Rate_3*MAX(0,MIN($O81,R3_To)-MAX($O80,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I81&lt;=0,0,$S80*('Engine'!$B$8*MAX(0,MIN($O81,'Engine'!$B$3)-MAX($O80,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O81,'Engine'!$B$5)-MAX($O80,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O81,'Engine'!$B$7)-MAX($O80,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K81" s="41">
@@ -4514,7 +4497,7 @@
         <v/>
       </c>
       <c r="N81" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O81&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O81&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O81" s="25">
@@ -4545,7 +4528,7 @@
         <v/>
       </c>
       <c r="H82" s="42">
-        <f>IF($I82&lt;=0,"",(Rate_1*MAX(0,MIN($O82,R1_To)-MAX($O81,R1_From))+Rate_2*MAX(0,MIN($O82,R2_To)-MAX($O81,R2_From))+Rate_3*MAX(0,MIN($O82,R3_To)-MAX($O81,R3_From)))/100/Day_Basis/$I82*Day_Basis*100)</f>
+        <f>IF($I82&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O82,'Engine'!$B$3)-MAX($O81,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O82,'Engine'!$B$5)-MAX($O81,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O82,'Engine'!$B$7)-MAX($O81,'Engine'!$B$6)))/100/$H$8/$I82*$H$8*100)</f>
         <v/>
       </c>
       <c r="I82" s="43">
@@ -4553,7 +4536,7 @@
         <v/>
       </c>
       <c r="J82" s="41">
-        <f>IF($I82&lt;=0,0,$S81*(Rate_1*MAX(0,MIN($O82,R1_To)-MAX($O81,R1_From))+Rate_2*MAX(0,MIN($O82,R2_To)-MAX($O81,R2_From))+Rate_3*MAX(0,MIN($O82,R3_To)-MAX($O81,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I82&lt;=0,0,$S81*('Engine'!$B$8*MAX(0,MIN($O82,'Engine'!$B$3)-MAX($O81,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O82,'Engine'!$B$5)-MAX($O81,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O82,'Engine'!$B$7)-MAX($O81,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K82" s="41">
@@ -4566,7 +4549,7 @@
         <v/>
       </c>
       <c r="N82" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O82&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O82&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O82" s="25">
@@ -4597,7 +4580,7 @@
         <v/>
       </c>
       <c r="H83" s="42">
-        <f>IF($I83&lt;=0,"",(Rate_1*MAX(0,MIN($O83,R1_To)-MAX($O82,R1_From))+Rate_2*MAX(0,MIN($O83,R2_To)-MAX($O82,R2_From))+Rate_3*MAX(0,MIN($O83,R3_To)-MAX($O82,R3_From)))/100/Day_Basis/$I83*Day_Basis*100)</f>
+        <f>IF($I83&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O83,'Engine'!$B$3)-MAX($O82,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O83,'Engine'!$B$5)-MAX($O82,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O83,'Engine'!$B$7)-MAX($O82,'Engine'!$B$6)))/100/$H$8/$I83*$H$8*100)</f>
         <v/>
       </c>
       <c r="I83" s="43">
@@ -4605,7 +4588,7 @@
         <v/>
       </c>
       <c r="J83" s="41">
-        <f>IF($I83&lt;=0,0,$S82*(Rate_1*MAX(0,MIN($O83,R1_To)-MAX($O82,R1_From))+Rate_2*MAX(0,MIN($O83,R2_To)-MAX($O82,R2_From))+Rate_3*MAX(0,MIN($O83,R3_To)-MAX($O82,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I83&lt;=0,0,$S82*('Engine'!$B$8*MAX(0,MIN($O83,'Engine'!$B$3)-MAX($O82,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O83,'Engine'!$B$5)-MAX($O82,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O83,'Engine'!$B$7)-MAX($O82,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K83" s="41">
@@ -4618,7 +4601,7 @@
         <v/>
       </c>
       <c r="N83" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O83&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O83&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O83" s="25">
@@ -4649,7 +4632,7 @@
         <v/>
       </c>
       <c r="H84" s="42">
-        <f>IF($I84&lt;=0,"",(Rate_1*MAX(0,MIN($O84,R1_To)-MAX($O83,R1_From))+Rate_2*MAX(0,MIN($O84,R2_To)-MAX($O83,R2_From))+Rate_3*MAX(0,MIN($O84,R3_To)-MAX($O83,R3_From)))/100/Day_Basis/$I84*Day_Basis*100)</f>
+        <f>IF($I84&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O84,'Engine'!$B$3)-MAX($O83,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O84,'Engine'!$B$5)-MAX($O83,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O84,'Engine'!$B$7)-MAX($O83,'Engine'!$B$6)))/100/$H$8/$I84*$H$8*100)</f>
         <v/>
       </c>
       <c r="I84" s="43">
@@ -4657,7 +4640,7 @@
         <v/>
       </c>
       <c r="J84" s="41">
-        <f>IF($I84&lt;=0,0,$S83*(Rate_1*MAX(0,MIN($O84,R1_To)-MAX($O83,R1_From))+Rate_2*MAX(0,MIN($O84,R2_To)-MAX($O83,R2_From))+Rate_3*MAX(0,MIN($O84,R3_To)-MAX($O83,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I84&lt;=0,0,$S83*('Engine'!$B$8*MAX(0,MIN($O84,'Engine'!$B$3)-MAX($O83,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O84,'Engine'!$B$5)-MAX($O83,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O84,'Engine'!$B$7)-MAX($O83,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K84" s="41">
@@ -4670,7 +4653,7 @@
         <v/>
       </c>
       <c r="N84" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O84&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O84&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O84" s="25">
@@ -4701,7 +4684,7 @@
         <v/>
       </c>
       <c r="H85" s="42">
-        <f>IF($I85&lt;=0,"",(Rate_1*MAX(0,MIN($O85,R1_To)-MAX($O84,R1_From))+Rate_2*MAX(0,MIN($O85,R2_To)-MAX($O84,R2_From))+Rate_3*MAX(0,MIN($O85,R3_To)-MAX($O84,R3_From)))/100/Day_Basis/$I85*Day_Basis*100)</f>
+        <f>IF($I85&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O85,'Engine'!$B$3)-MAX($O84,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O85,'Engine'!$B$5)-MAX($O84,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O85,'Engine'!$B$7)-MAX($O84,'Engine'!$B$6)))/100/$H$8/$I85*$H$8*100)</f>
         <v/>
       </c>
       <c r="I85" s="43">
@@ -4709,7 +4692,7 @@
         <v/>
       </c>
       <c r="J85" s="41">
-        <f>IF($I85&lt;=0,0,$S84*(Rate_1*MAX(0,MIN($O85,R1_To)-MAX($O84,R1_From))+Rate_2*MAX(0,MIN($O85,R2_To)-MAX($O84,R2_From))+Rate_3*MAX(0,MIN($O85,R3_To)-MAX($O84,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I85&lt;=0,0,$S84*('Engine'!$B$8*MAX(0,MIN($O85,'Engine'!$B$3)-MAX($O84,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O85,'Engine'!$B$5)-MAX($O84,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O85,'Engine'!$B$7)-MAX($O84,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K85" s="41">
@@ -4722,7 +4705,7 @@
         <v/>
       </c>
       <c r="N85" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O85&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O85&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O85" s="25">
@@ -4753,7 +4736,7 @@
         <v/>
       </c>
       <c r="H86" s="42">
-        <f>IF($I86&lt;=0,"",(Rate_1*MAX(0,MIN($O86,R1_To)-MAX($O85,R1_From))+Rate_2*MAX(0,MIN($O86,R2_To)-MAX($O85,R2_From))+Rate_3*MAX(0,MIN($O86,R3_To)-MAX($O85,R3_From)))/100/Day_Basis/$I86*Day_Basis*100)</f>
+        <f>IF($I86&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O86,'Engine'!$B$3)-MAX($O85,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O86,'Engine'!$B$5)-MAX($O85,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O86,'Engine'!$B$7)-MAX($O85,'Engine'!$B$6)))/100/$H$8/$I86*$H$8*100)</f>
         <v/>
       </c>
       <c r="I86" s="43">
@@ -4761,7 +4744,7 @@
         <v/>
       </c>
       <c r="J86" s="41">
-        <f>IF($I86&lt;=0,0,$S85*(Rate_1*MAX(0,MIN($O86,R1_To)-MAX($O85,R1_From))+Rate_2*MAX(0,MIN($O86,R2_To)-MAX($O85,R2_From))+Rate_3*MAX(0,MIN($O86,R3_To)-MAX($O85,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I86&lt;=0,0,$S85*('Engine'!$B$8*MAX(0,MIN($O86,'Engine'!$B$3)-MAX($O85,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O86,'Engine'!$B$5)-MAX($O85,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O86,'Engine'!$B$7)-MAX($O85,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K86" s="41">
@@ -4774,7 +4757,7 @@
         <v/>
       </c>
       <c r="N86" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O86&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O86&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O86" s="25">
@@ -4805,7 +4788,7 @@
         <v/>
       </c>
       <c r="H87" s="42">
-        <f>IF($I87&lt;=0,"",(Rate_1*MAX(0,MIN($O87,R1_To)-MAX($O86,R1_From))+Rate_2*MAX(0,MIN($O87,R2_To)-MAX($O86,R2_From))+Rate_3*MAX(0,MIN($O87,R3_To)-MAX($O86,R3_From)))/100/Day_Basis/$I87*Day_Basis*100)</f>
+        <f>IF($I87&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O87,'Engine'!$B$3)-MAX($O86,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O87,'Engine'!$B$5)-MAX($O86,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O87,'Engine'!$B$7)-MAX($O86,'Engine'!$B$6)))/100/$H$8/$I87*$H$8*100)</f>
         <v/>
       </c>
       <c r="I87" s="43">
@@ -4813,7 +4796,7 @@
         <v/>
       </c>
       <c r="J87" s="41">
-        <f>IF($I87&lt;=0,0,$S86*(Rate_1*MAX(0,MIN($O87,R1_To)-MAX($O86,R1_From))+Rate_2*MAX(0,MIN($O87,R2_To)-MAX($O86,R2_From))+Rate_3*MAX(0,MIN($O87,R3_To)-MAX($O86,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I87&lt;=0,0,$S86*('Engine'!$B$8*MAX(0,MIN($O87,'Engine'!$B$3)-MAX($O86,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O87,'Engine'!$B$5)-MAX($O86,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O87,'Engine'!$B$7)-MAX($O86,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K87" s="41">
@@ -4826,7 +4809,7 @@
         <v/>
       </c>
       <c r="N87" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O87&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O87&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O87" s="25">
@@ -4857,7 +4840,7 @@
         <v/>
       </c>
       <c r="H88" s="42">
-        <f>IF($I88&lt;=0,"",(Rate_1*MAX(0,MIN($O88,R1_To)-MAX($O87,R1_From))+Rate_2*MAX(0,MIN($O88,R2_To)-MAX($O87,R2_From))+Rate_3*MAX(0,MIN($O88,R3_To)-MAX($O87,R3_From)))/100/Day_Basis/$I88*Day_Basis*100)</f>
+        <f>IF($I88&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O88,'Engine'!$B$3)-MAX($O87,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O88,'Engine'!$B$5)-MAX($O87,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O88,'Engine'!$B$7)-MAX($O87,'Engine'!$B$6)))/100/$H$8/$I88*$H$8*100)</f>
         <v/>
       </c>
       <c r="I88" s="43">
@@ -4865,7 +4848,7 @@
         <v/>
       </c>
       <c r="J88" s="41">
-        <f>IF($I88&lt;=0,0,$S87*(Rate_1*MAX(0,MIN($O88,R1_To)-MAX($O87,R1_From))+Rate_2*MAX(0,MIN($O88,R2_To)-MAX($O87,R2_From))+Rate_3*MAX(0,MIN($O88,R3_To)-MAX($O87,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I88&lt;=0,0,$S87*('Engine'!$B$8*MAX(0,MIN($O88,'Engine'!$B$3)-MAX($O87,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O88,'Engine'!$B$5)-MAX($O87,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O88,'Engine'!$B$7)-MAX($O87,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K88" s="41">
@@ -4878,7 +4861,7 @@
         <v/>
       </c>
       <c r="N88" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O88&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O88&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O88" s="25">
@@ -4909,7 +4892,7 @@
         <v/>
       </c>
       <c r="H89" s="42">
-        <f>IF($I89&lt;=0,"",(Rate_1*MAX(0,MIN($O89,R1_To)-MAX($O88,R1_From))+Rate_2*MAX(0,MIN($O89,R2_To)-MAX($O88,R2_From))+Rate_3*MAX(0,MIN($O89,R3_To)-MAX($O88,R3_From)))/100/Day_Basis/$I89*Day_Basis*100)</f>
+        <f>IF($I89&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O89,'Engine'!$B$3)-MAX($O88,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O89,'Engine'!$B$5)-MAX($O88,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O89,'Engine'!$B$7)-MAX($O88,'Engine'!$B$6)))/100/$H$8/$I89*$H$8*100)</f>
         <v/>
       </c>
       <c r="I89" s="43">
@@ -4917,7 +4900,7 @@
         <v/>
       </c>
       <c r="J89" s="41">
-        <f>IF($I89&lt;=0,0,$S88*(Rate_1*MAX(0,MIN($O89,R1_To)-MAX($O88,R1_From))+Rate_2*MAX(0,MIN($O89,R2_To)-MAX($O88,R2_From))+Rate_3*MAX(0,MIN($O89,R3_To)-MAX($O88,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I89&lt;=0,0,$S88*('Engine'!$B$8*MAX(0,MIN($O89,'Engine'!$B$3)-MAX($O88,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O89,'Engine'!$B$5)-MAX($O88,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O89,'Engine'!$B$7)-MAX($O88,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K89" s="41">
@@ -4930,7 +4913,7 @@
         <v/>
       </c>
       <c r="N89" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O89&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O89&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O89" s="25">
@@ -4961,7 +4944,7 @@
         <v/>
       </c>
       <c r="H90" s="42">
-        <f>IF($I90&lt;=0,"",(Rate_1*MAX(0,MIN($O90,R1_To)-MAX($O89,R1_From))+Rate_2*MAX(0,MIN($O90,R2_To)-MAX($O89,R2_From))+Rate_3*MAX(0,MIN($O90,R3_To)-MAX($O89,R3_From)))/100/Day_Basis/$I90*Day_Basis*100)</f>
+        <f>IF($I90&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O90,'Engine'!$B$3)-MAX($O89,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O90,'Engine'!$B$5)-MAX($O89,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O90,'Engine'!$B$7)-MAX($O89,'Engine'!$B$6)))/100/$H$8/$I90*$H$8*100)</f>
         <v/>
       </c>
       <c r="I90" s="43">
@@ -4969,7 +4952,7 @@
         <v/>
       </c>
       <c r="J90" s="41">
-        <f>IF($I90&lt;=0,0,$S89*(Rate_1*MAX(0,MIN($O90,R1_To)-MAX($O89,R1_From))+Rate_2*MAX(0,MIN($O90,R2_To)-MAX($O89,R2_From))+Rate_3*MAX(0,MIN($O90,R3_To)-MAX($O89,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I90&lt;=0,0,$S89*('Engine'!$B$8*MAX(0,MIN($O90,'Engine'!$B$3)-MAX($O89,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O90,'Engine'!$B$5)-MAX($O89,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O90,'Engine'!$B$7)-MAX($O89,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K90" s="41">
@@ -4982,7 +4965,7 @@
         <v/>
       </c>
       <c r="N90" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O90&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O90&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O90" s="25">
@@ -5023,7 +5006,7 @@
         <v/>
       </c>
       <c r="H91" s="51">
-        <f>IF($I91&lt;=0,"",(Rate_1*MAX(0,MIN($O91,R1_To)-MAX($O90,R1_From))+Rate_2*MAX(0,MIN($O91,R2_To)-MAX($O90,R2_From))+Rate_3*MAX(0,MIN($O91,R3_To)-MAX($O90,R3_From)))/100/Day_Basis/$I91*Day_Basis*100)</f>
+        <f>IF($I91&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O91,'Engine'!$B$3)-MAX($O90,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O91,'Engine'!$B$5)-MAX($O90,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O91,'Engine'!$B$7)-MAX($O90,'Engine'!$B$6)))/100/$H$8/$I91*$H$8*100)</f>
         <v/>
       </c>
       <c r="I91" s="52">
@@ -5031,7 +5014,7 @@
         <v/>
       </c>
       <c r="J91" s="53">
-        <f>IF($I91&lt;=0,0,$S90*(Rate_1*MAX(0,MIN($O91,R1_To)-MAX($O90,R1_From))+Rate_2*MAX(0,MIN($O91,R2_To)-MAX($O90,R2_From))+Rate_3*MAX(0,MIN($O91,R3_To)-MAX($O90,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I91&lt;=0,0,$S90*('Engine'!$B$8*MAX(0,MIN($O91,'Engine'!$B$3)-MAX($O90,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O91,'Engine'!$B$5)-MAX($O90,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O91,'Engine'!$B$7)-MAX($O90,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K91" s="53" t="n">
@@ -5043,7 +5026,7 @@
         <v/>
       </c>
       <c r="N91" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O91&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O91&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O91" s="25">
@@ -5060,7 +5043,7 @@
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="A92" s="24">
-        <f>IF($P$92=0,"QUARTER 7          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 7          "&amp;TEXT($P$92,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$92,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$92&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$92)</f>
+        <f>IF($P$92=0,"QUARTER 7          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 7          "&amp;TEXT($P$92,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$92,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$92&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$92)</f>
         <v/>
       </c>
       <c r="O92" s="25">
@@ -5118,7 +5101,7 @@
         <v/>
       </c>
       <c r="N93" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$93&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$93&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O93" s="25">
@@ -5148,7 +5131,7 @@
         <v/>
       </c>
       <c r="H94" s="42">
-        <f>IF($I94&lt;=0,"",(Rate_1*MAX(0,MIN($O94,R1_To)-MAX($O93,R1_From))+Rate_2*MAX(0,MIN($O94,R2_To)-MAX($O93,R2_From))+Rate_3*MAX(0,MIN($O94,R3_To)-MAX($O93,R3_From)))/100/Day_Basis/$I94*Day_Basis*100)</f>
+        <f>IF($I94&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O94,'Engine'!$B$3)-MAX($O93,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O94,'Engine'!$B$5)-MAX($O93,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O94,'Engine'!$B$7)-MAX($O93,'Engine'!$B$6)))/100/$H$8/$I94*$H$8*100)</f>
         <v/>
       </c>
       <c r="I94" s="43">
@@ -5156,7 +5139,7 @@
         <v/>
       </c>
       <c r="J94" s="41">
-        <f>IF($I94&lt;=0,0,$S93*(Rate_1*MAX(0,MIN($O94,R1_To)-MAX($O93,R1_From))+Rate_2*MAX(0,MIN($O94,R2_To)-MAX($O93,R2_From))+Rate_3*MAX(0,MIN($O94,R3_To)-MAX($O93,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I94&lt;=0,0,$S93*('Engine'!$B$8*MAX(0,MIN($O94,'Engine'!$B$3)-MAX($O93,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O94,'Engine'!$B$5)-MAX($O93,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O94,'Engine'!$B$7)-MAX($O93,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K94" s="41">
@@ -5169,7 +5152,7 @@
         <v/>
       </c>
       <c r="N94" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O94&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O94&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O94" s="25">
@@ -5200,7 +5183,7 @@
         <v/>
       </c>
       <c r="H95" s="42">
-        <f>IF($I95&lt;=0,"",(Rate_1*MAX(0,MIN($O95,R1_To)-MAX($O94,R1_From))+Rate_2*MAX(0,MIN($O95,R2_To)-MAX($O94,R2_From))+Rate_3*MAX(0,MIN($O95,R3_To)-MAX($O94,R3_From)))/100/Day_Basis/$I95*Day_Basis*100)</f>
+        <f>IF($I95&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O95,'Engine'!$B$3)-MAX($O94,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O95,'Engine'!$B$5)-MAX($O94,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O95,'Engine'!$B$7)-MAX($O94,'Engine'!$B$6)))/100/$H$8/$I95*$H$8*100)</f>
         <v/>
       </c>
       <c r="I95" s="43">
@@ -5208,7 +5191,7 @@
         <v/>
       </c>
       <c r="J95" s="41">
-        <f>IF($I95&lt;=0,0,$S94*(Rate_1*MAX(0,MIN($O95,R1_To)-MAX($O94,R1_From))+Rate_2*MAX(0,MIN($O95,R2_To)-MAX($O94,R2_From))+Rate_3*MAX(0,MIN($O95,R3_To)-MAX($O94,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I95&lt;=0,0,$S94*('Engine'!$B$8*MAX(0,MIN($O95,'Engine'!$B$3)-MAX($O94,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O95,'Engine'!$B$5)-MAX($O94,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O95,'Engine'!$B$7)-MAX($O94,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K95" s="41">
@@ -5221,7 +5204,7 @@
         <v/>
       </c>
       <c r="N95" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O95&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O95&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O95" s="25">
@@ -5252,7 +5235,7 @@
         <v/>
       </c>
       <c r="H96" s="42">
-        <f>IF($I96&lt;=0,"",(Rate_1*MAX(0,MIN($O96,R1_To)-MAX($O95,R1_From))+Rate_2*MAX(0,MIN($O96,R2_To)-MAX($O95,R2_From))+Rate_3*MAX(0,MIN($O96,R3_To)-MAX($O95,R3_From)))/100/Day_Basis/$I96*Day_Basis*100)</f>
+        <f>IF($I96&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O96,'Engine'!$B$3)-MAX($O95,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O96,'Engine'!$B$5)-MAX($O95,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O96,'Engine'!$B$7)-MAX($O95,'Engine'!$B$6)))/100/$H$8/$I96*$H$8*100)</f>
         <v/>
       </c>
       <c r="I96" s="43">
@@ -5260,7 +5243,7 @@
         <v/>
       </c>
       <c r="J96" s="41">
-        <f>IF($I96&lt;=0,0,$S95*(Rate_1*MAX(0,MIN($O96,R1_To)-MAX($O95,R1_From))+Rate_2*MAX(0,MIN($O96,R2_To)-MAX($O95,R2_From))+Rate_3*MAX(0,MIN($O96,R3_To)-MAX($O95,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I96&lt;=0,0,$S95*('Engine'!$B$8*MAX(0,MIN($O96,'Engine'!$B$3)-MAX($O95,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O96,'Engine'!$B$5)-MAX($O95,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O96,'Engine'!$B$7)-MAX($O95,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K96" s="41">
@@ -5273,7 +5256,7 @@
         <v/>
       </c>
       <c r="N96" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O96&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O96&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O96" s="25">
@@ -5304,7 +5287,7 @@
         <v/>
       </c>
       <c r="H97" s="42">
-        <f>IF($I97&lt;=0,"",(Rate_1*MAX(0,MIN($O97,R1_To)-MAX($O96,R1_From))+Rate_2*MAX(0,MIN($O97,R2_To)-MAX($O96,R2_From))+Rate_3*MAX(0,MIN($O97,R3_To)-MAX($O96,R3_From)))/100/Day_Basis/$I97*Day_Basis*100)</f>
+        <f>IF($I97&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O97,'Engine'!$B$3)-MAX($O96,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O97,'Engine'!$B$5)-MAX($O96,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O97,'Engine'!$B$7)-MAX($O96,'Engine'!$B$6)))/100/$H$8/$I97*$H$8*100)</f>
         <v/>
       </c>
       <c r="I97" s="43">
@@ -5312,7 +5295,7 @@
         <v/>
       </c>
       <c r="J97" s="41">
-        <f>IF($I97&lt;=0,0,$S96*(Rate_1*MAX(0,MIN($O97,R1_To)-MAX($O96,R1_From))+Rate_2*MAX(0,MIN($O97,R2_To)-MAX($O96,R2_From))+Rate_3*MAX(0,MIN($O97,R3_To)-MAX($O96,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I97&lt;=0,0,$S96*('Engine'!$B$8*MAX(0,MIN($O97,'Engine'!$B$3)-MAX($O96,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O97,'Engine'!$B$5)-MAX($O96,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O97,'Engine'!$B$7)-MAX($O96,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K97" s="41">
@@ -5325,7 +5308,7 @@
         <v/>
       </c>
       <c r="N97" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O97&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O97&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O97" s="25">
@@ -5356,7 +5339,7 @@
         <v/>
       </c>
       <c r="H98" s="42">
-        <f>IF($I98&lt;=0,"",(Rate_1*MAX(0,MIN($O98,R1_To)-MAX($O97,R1_From))+Rate_2*MAX(0,MIN($O98,R2_To)-MAX($O97,R2_From))+Rate_3*MAX(0,MIN($O98,R3_To)-MAX($O97,R3_From)))/100/Day_Basis/$I98*Day_Basis*100)</f>
+        <f>IF($I98&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O98,'Engine'!$B$3)-MAX($O97,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O98,'Engine'!$B$5)-MAX($O97,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O98,'Engine'!$B$7)-MAX($O97,'Engine'!$B$6)))/100/$H$8/$I98*$H$8*100)</f>
         <v/>
       </c>
       <c r="I98" s="43">
@@ -5364,7 +5347,7 @@
         <v/>
       </c>
       <c r="J98" s="41">
-        <f>IF($I98&lt;=0,0,$S97*(Rate_1*MAX(0,MIN($O98,R1_To)-MAX($O97,R1_From))+Rate_2*MAX(0,MIN($O98,R2_To)-MAX($O97,R2_From))+Rate_3*MAX(0,MIN($O98,R3_To)-MAX($O97,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I98&lt;=0,0,$S97*('Engine'!$B$8*MAX(0,MIN($O98,'Engine'!$B$3)-MAX($O97,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O98,'Engine'!$B$5)-MAX($O97,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O98,'Engine'!$B$7)-MAX($O97,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K98" s="41">
@@ -5377,7 +5360,7 @@
         <v/>
       </c>
       <c r="N98" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O98&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O98&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O98" s="25">
@@ -5408,7 +5391,7 @@
         <v/>
       </c>
       <c r="H99" s="42">
-        <f>IF($I99&lt;=0,"",(Rate_1*MAX(0,MIN($O99,R1_To)-MAX($O98,R1_From))+Rate_2*MAX(0,MIN($O99,R2_To)-MAX($O98,R2_From))+Rate_3*MAX(0,MIN($O99,R3_To)-MAX($O98,R3_From)))/100/Day_Basis/$I99*Day_Basis*100)</f>
+        <f>IF($I99&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O99,'Engine'!$B$3)-MAX($O98,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O99,'Engine'!$B$5)-MAX($O98,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O99,'Engine'!$B$7)-MAX($O98,'Engine'!$B$6)))/100/$H$8/$I99*$H$8*100)</f>
         <v/>
       </c>
       <c r="I99" s="43">
@@ -5416,7 +5399,7 @@
         <v/>
       </c>
       <c r="J99" s="41">
-        <f>IF($I99&lt;=0,0,$S98*(Rate_1*MAX(0,MIN($O99,R1_To)-MAX($O98,R1_From))+Rate_2*MAX(0,MIN($O99,R2_To)-MAX($O98,R2_From))+Rate_3*MAX(0,MIN($O99,R3_To)-MAX($O98,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I99&lt;=0,0,$S98*('Engine'!$B$8*MAX(0,MIN($O99,'Engine'!$B$3)-MAX($O98,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O99,'Engine'!$B$5)-MAX($O98,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O99,'Engine'!$B$7)-MAX($O98,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K99" s="41">
@@ -5429,7 +5412,7 @@
         <v/>
       </c>
       <c r="N99" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O99&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O99&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O99" s="25">
@@ -5460,7 +5443,7 @@
         <v/>
       </c>
       <c r="H100" s="42">
-        <f>IF($I100&lt;=0,"",(Rate_1*MAX(0,MIN($O100,R1_To)-MAX($O99,R1_From))+Rate_2*MAX(0,MIN($O100,R2_To)-MAX($O99,R2_From))+Rate_3*MAX(0,MIN($O100,R3_To)-MAX($O99,R3_From)))/100/Day_Basis/$I100*Day_Basis*100)</f>
+        <f>IF($I100&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O100,'Engine'!$B$3)-MAX($O99,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O100,'Engine'!$B$5)-MAX($O99,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O100,'Engine'!$B$7)-MAX($O99,'Engine'!$B$6)))/100/$H$8/$I100*$H$8*100)</f>
         <v/>
       </c>
       <c r="I100" s="43">
@@ -5468,7 +5451,7 @@
         <v/>
       </c>
       <c r="J100" s="41">
-        <f>IF($I100&lt;=0,0,$S99*(Rate_1*MAX(0,MIN($O100,R1_To)-MAX($O99,R1_From))+Rate_2*MAX(0,MIN($O100,R2_To)-MAX($O99,R2_From))+Rate_3*MAX(0,MIN($O100,R3_To)-MAX($O99,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I100&lt;=0,0,$S99*('Engine'!$B$8*MAX(0,MIN($O100,'Engine'!$B$3)-MAX($O99,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O100,'Engine'!$B$5)-MAX($O99,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O100,'Engine'!$B$7)-MAX($O99,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K100" s="41">
@@ -5481,7 +5464,7 @@
         <v/>
       </c>
       <c r="N100" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O100&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O100&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O100" s="25">
@@ -5512,7 +5495,7 @@
         <v/>
       </c>
       <c r="H101" s="42">
-        <f>IF($I101&lt;=0,"",(Rate_1*MAX(0,MIN($O101,R1_To)-MAX($O100,R1_From))+Rate_2*MAX(0,MIN($O101,R2_To)-MAX($O100,R2_From))+Rate_3*MAX(0,MIN($O101,R3_To)-MAX($O100,R3_From)))/100/Day_Basis/$I101*Day_Basis*100)</f>
+        <f>IF($I101&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O101,'Engine'!$B$3)-MAX($O100,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O101,'Engine'!$B$5)-MAX($O100,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O101,'Engine'!$B$7)-MAX($O100,'Engine'!$B$6)))/100/$H$8/$I101*$H$8*100)</f>
         <v/>
       </c>
       <c r="I101" s="43">
@@ -5520,7 +5503,7 @@
         <v/>
       </c>
       <c r="J101" s="41">
-        <f>IF($I101&lt;=0,0,$S100*(Rate_1*MAX(0,MIN($O101,R1_To)-MAX($O100,R1_From))+Rate_2*MAX(0,MIN($O101,R2_To)-MAX($O100,R2_From))+Rate_3*MAX(0,MIN($O101,R3_To)-MAX($O100,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I101&lt;=0,0,$S100*('Engine'!$B$8*MAX(0,MIN($O101,'Engine'!$B$3)-MAX($O100,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O101,'Engine'!$B$5)-MAX($O100,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O101,'Engine'!$B$7)-MAX($O100,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K101" s="41">
@@ -5533,7 +5516,7 @@
         <v/>
       </c>
       <c r="N101" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O101&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O101&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O101" s="25">
@@ -5564,7 +5547,7 @@
         <v/>
       </c>
       <c r="H102" s="42">
-        <f>IF($I102&lt;=0,"",(Rate_1*MAX(0,MIN($O102,R1_To)-MAX($O101,R1_From))+Rate_2*MAX(0,MIN($O102,R2_To)-MAX($O101,R2_From))+Rate_3*MAX(0,MIN($O102,R3_To)-MAX($O101,R3_From)))/100/Day_Basis/$I102*Day_Basis*100)</f>
+        <f>IF($I102&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O102,'Engine'!$B$3)-MAX($O101,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O102,'Engine'!$B$5)-MAX($O101,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O102,'Engine'!$B$7)-MAX($O101,'Engine'!$B$6)))/100/$H$8/$I102*$H$8*100)</f>
         <v/>
       </c>
       <c r="I102" s="43">
@@ -5572,7 +5555,7 @@
         <v/>
       </c>
       <c r="J102" s="41">
-        <f>IF($I102&lt;=0,0,$S101*(Rate_1*MAX(0,MIN($O102,R1_To)-MAX($O101,R1_From))+Rate_2*MAX(0,MIN($O102,R2_To)-MAX($O101,R2_From))+Rate_3*MAX(0,MIN($O102,R3_To)-MAX($O101,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I102&lt;=0,0,$S101*('Engine'!$B$8*MAX(0,MIN($O102,'Engine'!$B$3)-MAX($O101,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O102,'Engine'!$B$5)-MAX($O101,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O102,'Engine'!$B$7)-MAX($O101,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K102" s="41">
@@ -5585,7 +5568,7 @@
         <v/>
       </c>
       <c r="N102" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O102&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O102&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O102" s="25">
@@ -5616,7 +5599,7 @@
         <v/>
       </c>
       <c r="H103" s="42">
-        <f>IF($I103&lt;=0,"",(Rate_1*MAX(0,MIN($O103,R1_To)-MAX($O102,R1_From))+Rate_2*MAX(0,MIN($O103,R2_To)-MAX($O102,R2_From))+Rate_3*MAX(0,MIN($O103,R3_To)-MAX($O102,R3_From)))/100/Day_Basis/$I103*Day_Basis*100)</f>
+        <f>IF($I103&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O103,'Engine'!$B$3)-MAX($O102,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O103,'Engine'!$B$5)-MAX($O102,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O103,'Engine'!$B$7)-MAX($O102,'Engine'!$B$6)))/100/$H$8/$I103*$H$8*100)</f>
         <v/>
       </c>
       <c r="I103" s="43">
@@ -5624,7 +5607,7 @@
         <v/>
       </c>
       <c r="J103" s="41">
-        <f>IF($I103&lt;=0,0,$S102*(Rate_1*MAX(0,MIN($O103,R1_To)-MAX($O102,R1_From))+Rate_2*MAX(0,MIN($O103,R2_To)-MAX($O102,R2_From))+Rate_3*MAX(0,MIN($O103,R3_To)-MAX($O102,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I103&lt;=0,0,$S102*('Engine'!$B$8*MAX(0,MIN($O103,'Engine'!$B$3)-MAX($O102,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O103,'Engine'!$B$5)-MAX($O102,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O103,'Engine'!$B$7)-MAX($O102,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K103" s="41">
@@ -5637,7 +5620,7 @@
         <v/>
       </c>
       <c r="N103" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O103&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O103&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O103" s="25">
@@ -5678,7 +5661,7 @@
         <v/>
       </c>
       <c r="H104" s="51">
-        <f>IF($I104&lt;=0,"",(Rate_1*MAX(0,MIN($O104,R1_To)-MAX($O103,R1_From))+Rate_2*MAX(0,MIN($O104,R2_To)-MAX($O103,R2_From))+Rate_3*MAX(0,MIN($O104,R3_To)-MAX($O103,R3_From)))/100/Day_Basis/$I104*Day_Basis*100)</f>
+        <f>IF($I104&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O104,'Engine'!$B$3)-MAX($O103,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O104,'Engine'!$B$5)-MAX($O103,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O104,'Engine'!$B$7)-MAX($O103,'Engine'!$B$6)))/100/$H$8/$I104*$H$8*100)</f>
         <v/>
       </c>
       <c r="I104" s="52">
@@ -5686,7 +5669,7 @@
         <v/>
       </c>
       <c r="J104" s="53">
-        <f>IF($I104&lt;=0,0,$S103*(Rate_1*MAX(0,MIN($O104,R1_To)-MAX($O103,R1_From))+Rate_2*MAX(0,MIN($O104,R2_To)-MAX($O103,R2_From))+Rate_3*MAX(0,MIN($O104,R3_To)-MAX($O103,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I104&lt;=0,0,$S103*('Engine'!$B$8*MAX(0,MIN($O104,'Engine'!$B$3)-MAX($O103,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O104,'Engine'!$B$5)-MAX($O103,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O104,'Engine'!$B$7)-MAX($O103,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K104" s="53" t="n">
@@ -5698,7 +5681,7 @@
         <v/>
       </c>
       <c r="N104" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O104&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O104&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O104" s="25">
@@ -5715,7 +5698,7 @@
     </row>
     <row r="105" ht="18" customHeight="1">
       <c r="A105" s="24">
-        <f>IF($P$105=0,"QUARTER 8          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 8          "&amp;TEXT($P$105,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$105,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$105&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$105)</f>
+        <f>IF($P$105=0,"QUARTER 8          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 8          "&amp;TEXT($P$105,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$105,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$105&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$105)</f>
         <v/>
       </c>
       <c r="O105" s="25">
@@ -5773,7 +5756,7 @@
         <v/>
       </c>
       <c r="N106" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$106&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$106&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O106" s="25">
@@ -5803,7 +5786,7 @@
         <v/>
       </c>
       <c r="H107" s="42">
-        <f>IF($I107&lt;=0,"",(Rate_1*MAX(0,MIN($O107,R1_To)-MAX($O106,R1_From))+Rate_2*MAX(0,MIN($O107,R2_To)-MAX($O106,R2_From))+Rate_3*MAX(0,MIN($O107,R3_To)-MAX($O106,R3_From)))/100/Day_Basis/$I107*Day_Basis*100)</f>
+        <f>IF($I107&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O107,'Engine'!$B$3)-MAX($O106,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O107,'Engine'!$B$5)-MAX($O106,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O107,'Engine'!$B$7)-MAX($O106,'Engine'!$B$6)))/100/$H$8/$I107*$H$8*100)</f>
         <v/>
       </c>
       <c r="I107" s="43">
@@ -5811,7 +5794,7 @@
         <v/>
       </c>
       <c r="J107" s="41">
-        <f>IF($I107&lt;=0,0,$S106*(Rate_1*MAX(0,MIN($O107,R1_To)-MAX($O106,R1_From))+Rate_2*MAX(0,MIN($O107,R2_To)-MAX($O106,R2_From))+Rate_3*MAX(0,MIN($O107,R3_To)-MAX($O106,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I107&lt;=0,0,$S106*('Engine'!$B$8*MAX(0,MIN($O107,'Engine'!$B$3)-MAX($O106,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O107,'Engine'!$B$5)-MAX($O106,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O107,'Engine'!$B$7)-MAX($O106,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K107" s="41">
@@ -5824,7 +5807,7 @@
         <v/>
       </c>
       <c r="N107" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O107&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O107&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O107" s="25">
@@ -5855,7 +5838,7 @@
         <v/>
       </c>
       <c r="H108" s="42">
-        <f>IF($I108&lt;=0,"",(Rate_1*MAX(0,MIN($O108,R1_To)-MAX($O107,R1_From))+Rate_2*MAX(0,MIN($O108,R2_To)-MAX($O107,R2_From))+Rate_3*MAX(0,MIN($O108,R3_To)-MAX($O107,R3_From)))/100/Day_Basis/$I108*Day_Basis*100)</f>
+        <f>IF($I108&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O108,'Engine'!$B$3)-MAX($O107,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O108,'Engine'!$B$5)-MAX($O107,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O108,'Engine'!$B$7)-MAX($O107,'Engine'!$B$6)))/100/$H$8/$I108*$H$8*100)</f>
         <v/>
       </c>
       <c r="I108" s="43">
@@ -5863,7 +5846,7 @@
         <v/>
       </c>
       <c r="J108" s="41">
-        <f>IF($I108&lt;=0,0,$S107*(Rate_1*MAX(0,MIN($O108,R1_To)-MAX($O107,R1_From))+Rate_2*MAX(0,MIN($O108,R2_To)-MAX($O107,R2_From))+Rate_3*MAX(0,MIN($O108,R3_To)-MAX($O107,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I108&lt;=0,0,$S107*('Engine'!$B$8*MAX(0,MIN($O108,'Engine'!$B$3)-MAX($O107,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O108,'Engine'!$B$5)-MAX($O107,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O108,'Engine'!$B$7)-MAX($O107,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K108" s="41">
@@ -5876,7 +5859,7 @@
         <v/>
       </c>
       <c r="N108" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O108&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O108&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O108" s="25">
@@ -5907,7 +5890,7 @@
         <v/>
       </c>
       <c r="H109" s="42">
-        <f>IF($I109&lt;=0,"",(Rate_1*MAX(0,MIN($O109,R1_To)-MAX($O108,R1_From))+Rate_2*MAX(0,MIN($O109,R2_To)-MAX($O108,R2_From))+Rate_3*MAX(0,MIN($O109,R3_To)-MAX($O108,R3_From)))/100/Day_Basis/$I109*Day_Basis*100)</f>
+        <f>IF($I109&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O109,'Engine'!$B$3)-MAX($O108,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O109,'Engine'!$B$5)-MAX($O108,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O109,'Engine'!$B$7)-MAX($O108,'Engine'!$B$6)))/100/$H$8/$I109*$H$8*100)</f>
         <v/>
       </c>
       <c r="I109" s="43">
@@ -5915,7 +5898,7 @@
         <v/>
       </c>
       <c r="J109" s="41">
-        <f>IF($I109&lt;=0,0,$S108*(Rate_1*MAX(0,MIN($O109,R1_To)-MAX($O108,R1_From))+Rate_2*MAX(0,MIN($O109,R2_To)-MAX($O108,R2_From))+Rate_3*MAX(0,MIN($O109,R3_To)-MAX($O108,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I109&lt;=0,0,$S108*('Engine'!$B$8*MAX(0,MIN($O109,'Engine'!$B$3)-MAX($O108,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O109,'Engine'!$B$5)-MAX($O108,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O109,'Engine'!$B$7)-MAX($O108,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K109" s="41">
@@ -5928,7 +5911,7 @@
         <v/>
       </c>
       <c r="N109" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O109&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O109&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O109" s="25">
@@ -5959,7 +5942,7 @@
         <v/>
       </c>
       <c r="H110" s="42">
-        <f>IF($I110&lt;=0,"",(Rate_1*MAX(0,MIN($O110,R1_To)-MAX($O109,R1_From))+Rate_2*MAX(0,MIN($O110,R2_To)-MAX($O109,R2_From))+Rate_3*MAX(0,MIN($O110,R3_To)-MAX($O109,R3_From)))/100/Day_Basis/$I110*Day_Basis*100)</f>
+        <f>IF($I110&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O110,'Engine'!$B$3)-MAX($O109,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O110,'Engine'!$B$5)-MAX($O109,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O110,'Engine'!$B$7)-MAX($O109,'Engine'!$B$6)))/100/$H$8/$I110*$H$8*100)</f>
         <v/>
       </c>
       <c r="I110" s="43">
@@ -5967,7 +5950,7 @@
         <v/>
       </c>
       <c r="J110" s="41">
-        <f>IF($I110&lt;=0,0,$S109*(Rate_1*MAX(0,MIN($O110,R1_To)-MAX($O109,R1_From))+Rate_2*MAX(0,MIN($O110,R2_To)-MAX($O109,R2_From))+Rate_3*MAX(0,MIN($O110,R3_To)-MAX($O109,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I110&lt;=0,0,$S109*('Engine'!$B$8*MAX(0,MIN($O110,'Engine'!$B$3)-MAX($O109,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O110,'Engine'!$B$5)-MAX($O109,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O110,'Engine'!$B$7)-MAX($O109,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K110" s="41">
@@ -5980,7 +5963,7 @@
         <v/>
       </c>
       <c r="N110" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O110&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O110&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O110" s="25">
@@ -6011,7 +5994,7 @@
         <v/>
       </c>
       <c r="H111" s="42">
-        <f>IF($I111&lt;=0,"",(Rate_1*MAX(0,MIN($O111,R1_To)-MAX($O110,R1_From))+Rate_2*MAX(0,MIN($O111,R2_To)-MAX($O110,R2_From))+Rate_3*MAX(0,MIN($O111,R3_To)-MAX($O110,R3_From)))/100/Day_Basis/$I111*Day_Basis*100)</f>
+        <f>IF($I111&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O111,'Engine'!$B$3)-MAX($O110,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O111,'Engine'!$B$5)-MAX($O110,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O111,'Engine'!$B$7)-MAX($O110,'Engine'!$B$6)))/100/$H$8/$I111*$H$8*100)</f>
         <v/>
       </c>
       <c r="I111" s="43">
@@ -6019,7 +6002,7 @@
         <v/>
       </c>
       <c r="J111" s="41">
-        <f>IF($I111&lt;=0,0,$S110*(Rate_1*MAX(0,MIN($O111,R1_To)-MAX($O110,R1_From))+Rate_2*MAX(0,MIN($O111,R2_To)-MAX($O110,R2_From))+Rate_3*MAX(0,MIN($O111,R3_To)-MAX($O110,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I111&lt;=0,0,$S110*('Engine'!$B$8*MAX(0,MIN($O111,'Engine'!$B$3)-MAX($O110,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O111,'Engine'!$B$5)-MAX($O110,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O111,'Engine'!$B$7)-MAX($O110,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K111" s="41">
@@ -6032,7 +6015,7 @@
         <v/>
       </c>
       <c r="N111" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O111&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O111&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O111" s="25">
@@ -6063,7 +6046,7 @@
         <v/>
       </c>
       <c r="H112" s="42">
-        <f>IF($I112&lt;=0,"",(Rate_1*MAX(0,MIN($O112,R1_To)-MAX($O111,R1_From))+Rate_2*MAX(0,MIN($O112,R2_To)-MAX($O111,R2_From))+Rate_3*MAX(0,MIN($O112,R3_To)-MAX($O111,R3_From)))/100/Day_Basis/$I112*Day_Basis*100)</f>
+        <f>IF($I112&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O112,'Engine'!$B$3)-MAX($O111,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O112,'Engine'!$B$5)-MAX($O111,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O112,'Engine'!$B$7)-MAX($O111,'Engine'!$B$6)))/100/$H$8/$I112*$H$8*100)</f>
         <v/>
       </c>
       <c r="I112" s="43">
@@ -6071,7 +6054,7 @@
         <v/>
       </c>
       <c r="J112" s="41">
-        <f>IF($I112&lt;=0,0,$S111*(Rate_1*MAX(0,MIN($O112,R1_To)-MAX($O111,R1_From))+Rate_2*MAX(0,MIN($O112,R2_To)-MAX($O111,R2_From))+Rate_3*MAX(0,MIN($O112,R3_To)-MAX($O111,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I112&lt;=0,0,$S111*('Engine'!$B$8*MAX(0,MIN($O112,'Engine'!$B$3)-MAX($O111,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O112,'Engine'!$B$5)-MAX($O111,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O112,'Engine'!$B$7)-MAX($O111,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K112" s="41">
@@ -6084,7 +6067,7 @@
         <v/>
       </c>
       <c r="N112" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O112&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O112&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O112" s="25">
@@ -6115,7 +6098,7 @@
         <v/>
       </c>
       <c r="H113" s="42">
-        <f>IF($I113&lt;=0,"",(Rate_1*MAX(0,MIN($O113,R1_To)-MAX($O112,R1_From))+Rate_2*MAX(0,MIN($O113,R2_To)-MAX($O112,R2_From))+Rate_3*MAX(0,MIN($O113,R3_To)-MAX($O112,R3_From)))/100/Day_Basis/$I113*Day_Basis*100)</f>
+        <f>IF($I113&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O113,'Engine'!$B$3)-MAX($O112,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O113,'Engine'!$B$5)-MAX($O112,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O113,'Engine'!$B$7)-MAX($O112,'Engine'!$B$6)))/100/$H$8/$I113*$H$8*100)</f>
         <v/>
       </c>
       <c r="I113" s="43">
@@ -6123,7 +6106,7 @@
         <v/>
       </c>
       <c r="J113" s="41">
-        <f>IF($I113&lt;=0,0,$S112*(Rate_1*MAX(0,MIN($O113,R1_To)-MAX($O112,R1_From))+Rate_2*MAX(0,MIN($O113,R2_To)-MAX($O112,R2_From))+Rate_3*MAX(0,MIN($O113,R3_To)-MAX($O112,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I113&lt;=0,0,$S112*('Engine'!$B$8*MAX(0,MIN($O113,'Engine'!$B$3)-MAX($O112,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O113,'Engine'!$B$5)-MAX($O112,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O113,'Engine'!$B$7)-MAX($O112,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K113" s="41">
@@ -6136,7 +6119,7 @@
         <v/>
       </c>
       <c r="N113" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O113&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O113&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O113" s="25">
@@ -6167,7 +6150,7 @@
         <v/>
       </c>
       <c r="H114" s="42">
-        <f>IF($I114&lt;=0,"",(Rate_1*MAX(0,MIN($O114,R1_To)-MAX($O113,R1_From))+Rate_2*MAX(0,MIN($O114,R2_To)-MAX($O113,R2_From))+Rate_3*MAX(0,MIN($O114,R3_To)-MAX($O113,R3_From)))/100/Day_Basis/$I114*Day_Basis*100)</f>
+        <f>IF($I114&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O114,'Engine'!$B$3)-MAX($O113,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O114,'Engine'!$B$5)-MAX($O113,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O114,'Engine'!$B$7)-MAX($O113,'Engine'!$B$6)))/100/$H$8/$I114*$H$8*100)</f>
         <v/>
       </c>
       <c r="I114" s="43">
@@ -6175,7 +6158,7 @@
         <v/>
       </c>
       <c r="J114" s="41">
-        <f>IF($I114&lt;=0,0,$S113*(Rate_1*MAX(0,MIN($O114,R1_To)-MAX($O113,R1_From))+Rate_2*MAX(0,MIN($O114,R2_To)-MAX($O113,R2_From))+Rate_3*MAX(0,MIN($O114,R3_To)-MAX($O113,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I114&lt;=0,0,$S113*('Engine'!$B$8*MAX(0,MIN($O114,'Engine'!$B$3)-MAX($O113,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O114,'Engine'!$B$5)-MAX($O113,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O114,'Engine'!$B$7)-MAX($O113,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K114" s="41">
@@ -6188,7 +6171,7 @@
         <v/>
       </c>
       <c r="N114" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O114&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O114&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O114" s="25">
@@ -6219,7 +6202,7 @@
         <v/>
       </c>
       <c r="H115" s="42">
-        <f>IF($I115&lt;=0,"",(Rate_1*MAX(0,MIN($O115,R1_To)-MAX($O114,R1_From))+Rate_2*MAX(0,MIN($O115,R2_To)-MAX($O114,R2_From))+Rate_3*MAX(0,MIN($O115,R3_To)-MAX($O114,R3_From)))/100/Day_Basis/$I115*Day_Basis*100)</f>
+        <f>IF($I115&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O115,'Engine'!$B$3)-MAX($O114,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O115,'Engine'!$B$5)-MAX($O114,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O115,'Engine'!$B$7)-MAX($O114,'Engine'!$B$6)))/100/$H$8/$I115*$H$8*100)</f>
         <v/>
       </c>
       <c r="I115" s="43">
@@ -6227,7 +6210,7 @@
         <v/>
       </c>
       <c r="J115" s="41">
-        <f>IF($I115&lt;=0,0,$S114*(Rate_1*MAX(0,MIN($O115,R1_To)-MAX($O114,R1_From))+Rate_2*MAX(0,MIN($O115,R2_To)-MAX($O114,R2_From))+Rate_3*MAX(0,MIN($O115,R3_To)-MAX($O114,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I115&lt;=0,0,$S114*('Engine'!$B$8*MAX(0,MIN($O115,'Engine'!$B$3)-MAX($O114,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O115,'Engine'!$B$5)-MAX($O114,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O115,'Engine'!$B$7)-MAX($O114,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K115" s="41">
@@ -6240,7 +6223,7 @@
         <v/>
       </c>
       <c r="N115" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O115&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O115&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O115" s="25">
@@ -6271,7 +6254,7 @@
         <v/>
       </c>
       <c r="H116" s="42">
-        <f>IF($I116&lt;=0,"",(Rate_1*MAX(0,MIN($O116,R1_To)-MAX($O115,R1_From))+Rate_2*MAX(0,MIN($O116,R2_To)-MAX($O115,R2_From))+Rate_3*MAX(0,MIN($O116,R3_To)-MAX($O115,R3_From)))/100/Day_Basis/$I116*Day_Basis*100)</f>
+        <f>IF($I116&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O116,'Engine'!$B$3)-MAX($O115,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O116,'Engine'!$B$5)-MAX($O115,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O116,'Engine'!$B$7)-MAX($O115,'Engine'!$B$6)))/100/$H$8/$I116*$H$8*100)</f>
         <v/>
       </c>
       <c r="I116" s="43">
@@ -6279,7 +6262,7 @@
         <v/>
       </c>
       <c r="J116" s="41">
-        <f>IF($I116&lt;=0,0,$S115*(Rate_1*MAX(0,MIN($O116,R1_To)-MAX($O115,R1_From))+Rate_2*MAX(0,MIN($O116,R2_To)-MAX($O115,R2_From))+Rate_3*MAX(0,MIN($O116,R3_To)-MAX($O115,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I116&lt;=0,0,$S115*('Engine'!$B$8*MAX(0,MIN($O116,'Engine'!$B$3)-MAX($O115,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O116,'Engine'!$B$5)-MAX($O115,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O116,'Engine'!$B$7)-MAX($O115,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K116" s="41">
@@ -6292,7 +6275,7 @@
         <v/>
       </c>
       <c r="N116" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O116&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O116&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O116" s="25">
@@ -6333,7 +6316,7 @@
         <v/>
       </c>
       <c r="H117" s="51">
-        <f>IF($I117&lt;=0,"",(Rate_1*MAX(0,MIN($O117,R1_To)-MAX($O116,R1_From))+Rate_2*MAX(0,MIN($O117,R2_To)-MAX($O116,R2_From))+Rate_3*MAX(0,MIN($O117,R3_To)-MAX($O116,R3_From)))/100/Day_Basis/$I117*Day_Basis*100)</f>
+        <f>IF($I117&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O117,'Engine'!$B$3)-MAX($O116,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O117,'Engine'!$B$5)-MAX($O116,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O117,'Engine'!$B$7)-MAX($O116,'Engine'!$B$6)))/100/$H$8/$I117*$H$8*100)</f>
         <v/>
       </c>
       <c r="I117" s="52">
@@ -6341,7 +6324,7 @@
         <v/>
       </c>
       <c r="J117" s="53">
-        <f>IF($I117&lt;=0,0,$S116*(Rate_1*MAX(0,MIN($O117,R1_To)-MAX($O116,R1_From))+Rate_2*MAX(0,MIN($O117,R2_To)-MAX($O116,R2_From))+Rate_3*MAX(0,MIN($O117,R3_To)-MAX($O116,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I117&lt;=0,0,$S116*('Engine'!$B$8*MAX(0,MIN($O117,'Engine'!$B$3)-MAX($O116,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O117,'Engine'!$B$5)-MAX($O116,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O117,'Engine'!$B$7)-MAX($O116,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K117" s="53" t="n">
@@ -6353,7 +6336,7 @@
         <v/>
       </c>
       <c r="N117" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O117&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O117&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O117" s="25">
@@ -6370,7 +6353,7 @@
     </row>
     <row r="118" ht="18" customHeight="1">
       <c r="A118" s="24">
-        <f>IF($P$118=0,"QUARTER 9          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 9          "&amp;TEXT($P$118,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$118,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$118&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$118)</f>
+        <f>IF($P$118=0,"QUARTER 9          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 9          "&amp;TEXT($P$118,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$118,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$118&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$118)</f>
         <v/>
       </c>
       <c r="O118" s="25">
@@ -6428,7 +6411,7 @@
         <v/>
       </c>
       <c r="N119" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$119&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$119&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O119" s="25">
@@ -6458,7 +6441,7 @@
         <v/>
       </c>
       <c r="H120" s="42">
-        <f>IF($I120&lt;=0,"",(Rate_1*MAX(0,MIN($O120,R1_To)-MAX($O119,R1_From))+Rate_2*MAX(0,MIN($O120,R2_To)-MAX($O119,R2_From))+Rate_3*MAX(0,MIN($O120,R3_To)-MAX($O119,R3_From)))/100/Day_Basis/$I120*Day_Basis*100)</f>
+        <f>IF($I120&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O120,'Engine'!$B$3)-MAX($O119,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O120,'Engine'!$B$5)-MAX($O119,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O120,'Engine'!$B$7)-MAX($O119,'Engine'!$B$6)))/100/$H$8/$I120*$H$8*100)</f>
         <v/>
       </c>
       <c r="I120" s="43">
@@ -6466,7 +6449,7 @@
         <v/>
       </c>
       <c r="J120" s="41">
-        <f>IF($I120&lt;=0,0,$S119*(Rate_1*MAX(0,MIN($O120,R1_To)-MAX($O119,R1_From))+Rate_2*MAX(0,MIN($O120,R2_To)-MAX($O119,R2_From))+Rate_3*MAX(0,MIN($O120,R3_To)-MAX($O119,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I120&lt;=0,0,$S119*('Engine'!$B$8*MAX(0,MIN($O120,'Engine'!$B$3)-MAX($O119,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O120,'Engine'!$B$5)-MAX($O119,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O120,'Engine'!$B$7)-MAX($O119,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K120" s="41">
@@ -6479,7 +6462,7 @@
         <v/>
       </c>
       <c r="N120" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O120&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O120&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O120" s="25">
@@ -6510,7 +6493,7 @@
         <v/>
       </c>
       <c r="H121" s="42">
-        <f>IF($I121&lt;=0,"",(Rate_1*MAX(0,MIN($O121,R1_To)-MAX($O120,R1_From))+Rate_2*MAX(0,MIN($O121,R2_To)-MAX($O120,R2_From))+Rate_3*MAX(0,MIN($O121,R3_To)-MAX($O120,R3_From)))/100/Day_Basis/$I121*Day_Basis*100)</f>
+        <f>IF($I121&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O121,'Engine'!$B$3)-MAX($O120,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O121,'Engine'!$B$5)-MAX($O120,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O121,'Engine'!$B$7)-MAX($O120,'Engine'!$B$6)))/100/$H$8/$I121*$H$8*100)</f>
         <v/>
       </c>
       <c r="I121" s="43">
@@ -6518,7 +6501,7 @@
         <v/>
       </c>
       <c r="J121" s="41">
-        <f>IF($I121&lt;=0,0,$S120*(Rate_1*MAX(0,MIN($O121,R1_To)-MAX($O120,R1_From))+Rate_2*MAX(0,MIN($O121,R2_To)-MAX($O120,R2_From))+Rate_3*MAX(0,MIN($O121,R3_To)-MAX($O120,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I121&lt;=0,0,$S120*('Engine'!$B$8*MAX(0,MIN($O121,'Engine'!$B$3)-MAX($O120,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O121,'Engine'!$B$5)-MAX($O120,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O121,'Engine'!$B$7)-MAX($O120,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K121" s="41">
@@ -6531,7 +6514,7 @@
         <v/>
       </c>
       <c r="N121" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O121&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O121&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O121" s="25">
@@ -6562,7 +6545,7 @@
         <v/>
       </c>
       <c r="H122" s="42">
-        <f>IF($I122&lt;=0,"",(Rate_1*MAX(0,MIN($O122,R1_To)-MAX($O121,R1_From))+Rate_2*MAX(0,MIN($O122,R2_To)-MAX($O121,R2_From))+Rate_3*MAX(0,MIN($O122,R3_To)-MAX($O121,R3_From)))/100/Day_Basis/$I122*Day_Basis*100)</f>
+        <f>IF($I122&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O122,'Engine'!$B$3)-MAX($O121,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O122,'Engine'!$B$5)-MAX($O121,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O122,'Engine'!$B$7)-MAX($O121,'Engine'!$B$6)))/100/$H$8/$I122*$H$8*100)</f>
         <v/>
       </c>
       <c r="I122" s="43">
@@ -6570,7 +6553,7 @@
         <v/>
       </c>
       <c r="J122" s="41">
-        <f>IF($I122&lt;=0,0,$S121*(Rate_1*MAX(0,MIN($O122,R1_To)-MAX($O121,R1_From))+Rate_2*MAX(0,MIN($O122,R2_To)-MAX($O121,R2_From))+Rate_3*MAX(0,MIN($O122,R3_To)-MAX($O121,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I122&lt;=0,0,$S121*('Engine'!$B$8*MAX(0,MIN($O122,'Engine'!$B$3)-MAX($O121,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O122,'Engine'!$B$5)-MAX($O121,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O122,'Engine'!$B$7)-MAX($O121,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K122" s="41">
@@ -6583,7 +6566,7 @@
         <v/>
       </c>
       <c r="N122" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O122&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O122&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O122" s="25">
@@ -6614,7 +6597,7 @@
         <v/>
       </c>
       <c r="H123" s="42">
-        <f>IF($I123&lt;=0,"",(Rate_1*MAX(0,MIN($O123,R1_To)-MAX($O122,R1_From))+Rate_2*MAX(0,MIN($O123,R2_To)-MAX($O122,R2_From))+Rate_3*MAX(0,MIN($O123,R3_To)-MAX($O122,R3_From)))/100/Day_Basis/$I123*Day_Basis*100)</f>
+        <f>IF($I123&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O123,'Engine'!$B$3)-MAX($O122,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O123,'Engine'!$B$5)-MAX($O122,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O123,'Engine'!$B$7)-MAX($O122,'Engine'!$B$6)))/100/$H$8/$I123*$H$8*100)</f>
         <v/>
       </c>
       <c r="I123" s="43">
@@ -6622,7 +6605,7 @@
         <v/>
       </c>
       <c r="J123" s="41">
-        <f>IF($I123&lt;=0,0,$S122*(Rate_1*MAX(0,MIN($O123,R1_To)-MAX($O122,R1_From))+Rate_2*MAX(0,MIN($O123,R2_To)-MAX($O122,R2_From))+Rate_3*MAX(0,MIN($O123,R3_To)-MAX($O122,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I123&lt;=0,0,$S122*('Engine'!$B$8*MAX(0,MIN($O123,'Engine'!$B$3)-MAX($O122,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O123,'Engine'!$B$5)-MAX($O122,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O123,'Engine'!$B$7)-MAX($O122,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K123" s="41">
@@ -6635,7 +6618,7 @@
         <v/>
       </c>
       <c r="N123" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O123&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O123&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O123" s="25">
@@ -6666,7 +6649,7 @@
         <v/>
       </c>
       <c r="H124" s="42">
-        <f>IF($I124&lt;=0,"",(Rate_1*MAX(0,MIN($O124,R1_To)-MAX($O123,R1_From))+Rate_2*MAX(0,MIN($O124,R2_To)-MAX($O123,R2_From))+Rate_3*MAX(0,MIN($O124,R3_To)-MAX($O123,R3_From)))/100/Day_Basis/$I124*Day_Basis*100)</f>
+        <f>IF($I124&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O124,'Engine'!$B$3)-MAX($O123,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O124,'Engine'!$B$5)-MAX($O123,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O124,'Engine'!$B$7)-MAX($O123,'Engine'!$B$6)))/100/$H$8/$I124*$H$8*100)</f>
         <v/>
       </c>
       <c r="I124" s="43">
@@ -6674,7 +6657,7 @@
         <v/>
       </c>
       <c r="J124" s="41">
-        <f>IF($I124&lt;=0,0,$S123*(Rate_1*MAX(0,MIN($O124,R1_To)-MAX($O123,R1_From))+Rate_2*MAX(0,MIN($O124,R2_To)-MAX($O123,R2_From))+Rate_3*MAX(0,MIN($O124,R3_To)-MAX($O123,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I124&lt;=0,0,$S123*('Engine'!$B$8*MAX(0,MIN($O124,'Engine'!$B$3)-MAX($O123,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O124,'Engine'!$B$5)-MAX($O123,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O124,'Engine'!$B$7)-MAX($O123,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K124" s="41">
@@ -6687,7 +6670,7 @@
         <v/>
       </c>
       <c r="N124" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O124&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O124&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O124" s="25">
@@ -6718,7 +6701,7 @@
         <v/>
       </c>
       <c r="H125" s="42">
-        <f>IF($I125&lt;=0,"",(Rate_1*MAX(0,MIN($O125,R1_To)-MAX($O124,R1_From))+Rate_2*MAX(0,MIN($O125,R2_To)-MAX($O124,R2_From))+Rate_3*MAX(0,MIN($O125,R3_To)-MAX($O124,R3_From)))/100/Day_Basis/$I125*Day_Basis*100)</f>
+        <f>IF($I125&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O125,'Engine'!$B$3)-MAX($O124,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O125,'Engine'!$B$5)-MAX($O124,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O125,'Engine'!$B$7)-MAX($O124,'Engine'!$B$6)))/100/$H$8/$I125*$H$8*100)</f>
         <v/>
       </c>
       <c r="I125" s="43">
@@ -6726,7 +6709,7 @@
         <v/>
       </c>
       <c r="J125" s="41">
-        <f>IF($I125&lt;=0,0,$S124*(Rate_1*MAX(0,MIN($O125,R1_To)-MAX($O124,R1_From))+Rate_2*MAX(0,MIN($O125,R2_To)-MAX($O124,R2_From))+Rate_3*MAX(0,MIN($O125,R3_To)-MAX($O124,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I125&lt;=0,0,$S124*('Engine'!$B$8*MAX(0,MIN($O125,'Engine'!$B$3)-MAX($O124,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O125,'Engine'!$B$5)-MAX($O124,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O125,'Engine'!$B$7)-MAX($O124,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K125" s="41">
@@ -6739,7 +6722,7 @@
         <v/>
       </c>
       <c r="N125" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O125&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O125&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O125" s="25">
@@ -6770,7 +6753,7 @@
         <v/>
       </c>
       <c r="H126" s="42">
-        <f>IF($I126&lt;=0,"",(Rate_1*MAX(0,MIN($O126,R1_To)-MAX($O125,R1_From))+Rate_2*MAX(0,MIN($O126,R2_To)-MAX($O125,R2_From))+Rate_3*MAX(0,MIN($O126,R3_To)-MAX($O125,R3_From)))/100/Day_Basis/$I126*Day_Basis*100)</f>
+        <f>IF($I126&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O126,'Engine'!$B$3)-MAX($O125,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O126,'Engine'!$B$5)-MAX($O125,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O126,'Engine'!$B$7)-MAX($O125,'Engine'!$B$6)))/100/$H$8/$I126*$H$8*100)</f>
         <v/>
       </c>
       <c r="I126" s="43">
@@ -6778,7 +6761,7 @@
         <v/>
       </c>
       <c r="J126" s="41">
-        <f>IF($I126&lt;=0,0,$S125*(Rate_1*MAX(0,MIN($O126,R1_To)-MAX($O125,R1_From))+Rate_2*MAX(0,MIN($O126,R2_To)-MAX($O125,R2_From))+Rate_3*MAX(0,MIN($O126,R3_To)-MAX($O125,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I126&lt;=0,0,$S125*('Engine'!$B$8*MAX(0,MIN($O126,'Engine'!$B$3)-MAX($O125,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O126,'Engine'!$B$5)-MAX($O125,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O126,'Engine'!$B$7)-MAX($O125,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K126" s="41">
@@ -6791,7 +6774,7 @@
         <v/>
       </c>
       <c r="N126" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O126&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O126&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O126" s="25">
@@ -6822,7 +6805,7 @@
         <v/>
       </c>
       <c r="H127" s="42">
-        <f>IF($I127&lt;=0,"",(Rate_1*MAX(0,MIN($O127,R1_To)-MAX($O126,R1_From))+Rate_2*MAX(0,MIN($O127,R2_To)-MAX($O126,R2_From))+Rate_3*MAX(0,MIN($O127,R3_To)-MAX($O126,R3_From)))/100/Day_Basis/$I127*Day_Basis*100)</f>
+        <f>IF($I127&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O127,'Engine'!$B$3)-MAX($O126,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O127,'Engine'!$B$5)-MAX($O126,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O127,'Engine'!$B$7)-MAX($O126,'Engine'!$B$6)))/100/$H$8/$I127*$H$8*100)</f>
         <v/>
       </c>
       <c r="I127" s="43">
@@ -6830,7 +6813,7 @@
         <v/>
       </c>
       <c r="J127" s="41">
-        <f>IF($I127&lt;=0,0,$S126*(Rate_1*MAX(0,MIN($O127,R1_To)-MAX($O126,R1_From))+Rate_2*MAX(0,MIN($O127,R2_To)-MAX($O126,R2_From))+Rate_3*MAX(0,MIN($O127,R3_To)-MAX($O126,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I127&lt;=0,0,$S126*('Engine'!$B$8*MAX(0,MIN($O127,'Engine'!$B$3)-MAX($O126,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O127,'Engine'!$B$5)-MAX($O126,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O127,'Engine'!$B$7)-MAX($O126,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K127" s="41">
@@ -6843,7 +6826,7 @@
         <v/>
       </c>
       <c r="N127" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O127&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O127&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O127" s="25">
@@ -6874,7 +6857,7 @@
         <v/>
       </c>
       <c r="H128" s="42">
-        <f>IF($I128&lt;=0,"",(Rate_1*MAX(0,MIN($O128,R1_To)-MAX($O127,R1_From))+Rate_2*MAX(0,MIN($O128,R2_To)-MAX($O127,R2_From))+Rate_3*MAX(0,MIN($O128,R3_To)-MAX($O127,R3_From)))/100/Day_Basis/$I128*Day_Basis*100)</f>
+        <f>IF($I128&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O128,'Engine'!$B$3)-MAX($O127,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O128,'Engine'!$B$5)-MAX($O127,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O128,'Engine'!$B$7)-MAX($O127,'Engine'!$B$6)))/100/$H$8/$I128*$H$8*100)</f>
         <v/>
       </c>
       <c r="I128" s="43">
@@ -6882,7 +6865,7 @@
         <v/>
       </c>
       <c r="J128" s="41">
-        <f>IF($I128&lt;=0,0,$S127*(Rate_1*MAX(0,MIN($O128,R1_To)-MAX($O127,R1_From))+Rate_2*MAX(0,MIN($O128,R2_To)-MAX($O127,R2_From))+Rate_3*MAX(0,MIN($O128,R3_To)-MAX($O127,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I128&lt;=0,0,$S127*('Engine'!$B$8*MAX(0,MIN($O128,'Engine'!$B$3)-MAX($O127,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O128,'Engine'!$B$5)-MAX($O127,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O128,'Engine'!$B$7)-MAX($O127,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K128" s="41">
@@ -6895,7 +6878,7 @@
         <v/>
       </c>
       <c r="N128" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O128&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O128&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O128" s="25">
@@ -6926,7 +6909,7 @@
         <v/>
       </c>
       <c r="H129" s="42">
-        <f>IF($I129&lt;=0,"",(Rate_1*MAX(0,MIN($O129,R1_To)-MAX($O128,R1_From))+Rate_2*MAX(0,MIN($O129,R2_To)-MAX($O128,R2_From))+Rate_3*MAX(0,MIN($O129,R3_To)-MAX($O128,R3_From)))/100/Day_Basis/$I129*Day_Basis*100)</f>
+        <f>IF($I129&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O129,'Engine'!$B$3)-MAX($O128,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O129,'Engine'!$B$5)-MAX($O128,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O129,'Engine'!$B$7)-MAX($O128,'Engine'!$B$6)))/100/$H$8/$I129*$H$8*100)</f>
         <v/>
       </c>
       <c r="I129" s="43">
@@ -6934,7 +6917,7 @@
         <v/>
       </c>
       <c r="J129" s="41">
-        <f>IF($I129&lt;=0,0,$S128*(Rate_1*MAX(0,MIN($O129,R1_To)-MAX($O128,R1_From))+Rate_2*MAX(0,MIN($O129,R2_To)-MAX($O128,R2_From))+Rate_3*MAX(0,MIN($O129,R3_To)-MAX($O128,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I129&lt;=0,0,$S128*('Engine'!$B$8*MAX(0,MIN($O129,'Engine'!$B$3)-MAX($O128,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O129,'Engine'!$B$5)-MAX($O128,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O129,'Engine'!$B$7)-MAX($O128,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K129" s="41">
@@ -6947,7 +6930,7 @@
         <v/>
       </c>
       <c r="N129" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O129&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O129&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O129" s="25">
@@ -6988,7 +6971,7 @@
         <v/>
       </c>
       <c r="H130" s="51">
-        <f>IF($I130&lt;=0,"",(Rate_1*MAX(0,MIN($O130,R1_To)-MAX($O129,R1_From))+Rate_2*MAX(0,MIN($O130,R2_To)-MAX($O129,R2_From))+Rate_3*MAX(0,MIN($O130,R3_To)-MAX($O129,R3_From)))/100/Day_Basis/$I130*Day_Basis*100)</f>
+        <f>IF($I130&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O130,'Engine'!$B$3)-MAX($O129,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O130,'Engine'!$B$5)-MAX($O129,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O130,'Engine'!$B$7)-MAX($O129,'Engine'!$B$6)))/100/$H$8/$I130*$H$8*100)</f>
         <v/>
       </c>
       <c r="I130" s="52">
@@ -6996,7 +6979,7 @@
         <v/>
       </c>
       <c r="J130" s="53">
-        <f>IF($I130&lt;=0,0,$S129*(Rate_1*MAX(0,MIN($O130,R1_To)-MAX($O129,R1_From))+Rate_2*MAX(0,MIN($O130,R2_To)-MAX($O129,R2_From))+Rate_3*MAX(0,MIN($O130,R3_To)-MAX($O129,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I130&lt;=0,0,$S129*('Engine'!$B$8*MAX(0,MIN($O130,'Engine'!$B$3)-MAX($O129,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O130,'Engine'!$B$5)-MAX($O129,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O130,'Engine'!$B$7)-MAX($O129,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K130" s="53" t="n">
@@ -7008,7 +6991,7 @@
         <v/>
       </c>
       <c r="N130" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O130&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O130&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O130" s="25">
@@ -7025,7 +7008,7 @@
     </row>
     <row r="131" ht="18" customHeight="1">
       <c r="A131" s="24">
-        <f>IF($P$131=0,"QUARTER 10          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 10          "&amp;TEXT($P$131,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$131,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$131&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$131)</f>
+        <f>IF($P$131=0,"QUARTER 10          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 10          "&amp;TEXT($P$131,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$131,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$131&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$131)</f>
         <v/>
       </c>
       <c r="O131" s="25">
@@ -7083,7 +7066,7 @@
         <v/>
       </c>
       <c r="N132" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$132&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$132&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O132" s="25">
@@ -7113,7 +7096,7 @@
         <v/>
       </c>
       <c r="H133" s="42">
-        <f>IF($I133&lt;=0,"",(Rate_1*MAX(0,MIN($O133,R1_To)-MAX($O132,R1_From))+Rate_2*MAX(0,MIN($O133,R2_To)-MAX($O132,R2_From))+Rate_3*MAX(0,MIN($O133,R3_To)-MAX($O132,R3_From)))/100/Day_Basis/$I133*Day_Basis*100)</f>
+        <f>IF($I133&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O133,'Engine'!$B$3)-MAX($O132,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O133,'Engine'!$B$5)-MAX($O132,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O133,'Engine'!$B$7)-MAX($O132,'Engine'!$B$6)))/100/$H$8/$I133*$H$8*100)</f>
         <v/>
       </c>
       <c r="I133" s="43">
@@ -7121,7 +7104,7 @@
         <v/>
       </c>
       <c r="J133" s="41">
-        <f>IF($I133&lt;=0,0,$S132*(Rate_1*MAX(0,MIN($O133,R1_To)-MAX($O132,R1_From))+Rate_2*MAX(0,MIN($O133,R2_To)-MAX($O132,R2_From))+Rate_3*MAX(0,MIN($O133,R3_To)-MAX($O132,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I133&lt;=0,0,$S132*('Engine'!$B$8*MAX(0,MIN($O133,'Engine'!$B$3)-MAX($O132,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O133,'Engine'!$B$5)-MAX($O132,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O133,'Engine'!$B$7)-MAX($O132,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K133" s="41">
@@ -7134,7 +7117,7 @@
         <v/>
       </c>
       <c r="N133" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O133&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O133&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O133" s="25">
@@ -7165,7 +7148,7 @@
         <v/>
       </c>
       <c r="H134" s="42">
-        <f>IF($I134&lt;=0,"",(Rate_1*MAX(0,MIN($O134,R1_To)-MAX($O133,R1_From))+Rate_2*MAX(0,MIN($O134,R2_To)-MAX($O133,R2_From))+Rate_3*MAX(0,MIN($O134,R3_To)-MAX($O133,R3_From)))/100/Day_Basis/$I134*Day_Basis*100)</f>
+        <f>IF($I134&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O134,'Engine'!$B$3)-MAX($O133,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O134,'Engine'!$B$5)-MAX($O133,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O134,'Engine'!$B$7)-MAX($O133,'Engine'!$B$6)))/100/$H$8/$I134*$H$8*100)</f>
         <v/>
       </c>
       <c r="I134" s="43">
@@ -7173,7 +7156,7 @@
         <v/>
       </c>
       <c r="J134" s="41">
-        <f>IF($I134&lt;=0,0,$S133*(Rate_1*MAX(0,MIN($O134,R1_To)-MAX($O133,R1_From))+Rate_2*MAX(0,MIN($O134,R2_To)-MAX($O133,R2_From))+Rate_3*MAX(0,MIN($O134,R3_To)-MAX($O133,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I134&lt;=0,0,$S133*('Engine'!$B$8*MAX(0,MIN($O134,'Engine'!$B$3)-MAX($O133,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O134,'Engine'!$B$5)-MAX($O133,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O134,'Engine'!$B$7)-MAX($O133,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K134" s="41">
@@ -7186,7 +7169,7 @@
         <v/>
       </c>
       <c r="N134" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O134&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O134&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O134" s="25">
@@ -7217,7 +7200,7 @@
         <v/>
       </c>
       <c r="H135" s="42">
-        <f>IF($I135&lt;=0,"",(Rate_1*MAX(0,MIN($O135,R1_To)-MAX($O134,R1_From))+Rate_2*MAX(0,MIN($O135,R2_To)-MAX($O134,R2_From))+Rate_3*MAX(0,MIN($O135,R3_To)-MAX($O134,R3_From)))/100/Day_Basis/$I135*Day_Basis*100)</f>
+        <f>IF($I135&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O135,'Engine'!$B$3)-MAX($O134,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O135,'Engine'!$B$5)-MAX($O134,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O135,'Engine'!$B$7)-MAX($O134,'Engine'!$B$6)))/100/$H$8/$I135*$H$8*100)</f>
         <v/>
       </c>
       <c r="I135" s="43">
@@ -7225,7 +7208,7 @@
         <v/>
       </c>
       <c r="J135" s="41">
-        <f>IF($I135&lt;=0,0,$S134*(Rate_1*MAX(0,MIN($O135,R1_To)-MAX($O134,R1_From))+Rate_2*MAX(0,MIN($O135,R2_To)-MAX($O134,R2_From))+Rate_3*MAX(0,MIN($O135,R3_To)-MAX($O134,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I135&lt;=0,0,$S134*('Engine'!$B$8*MAX(0,MIN($O135,'Engine'!$B$3)-MAX($O134,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O135,'Engine'!$B$5)-MAX($O134,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O135,'Engine'!$B$7)-MAX($O134,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K135" s="41">
@@ -7238,7 +7221,7 @@
         <v/>
       </c>
       <c r="N135" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O135&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O135&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O135" s="25">
@@ -7269,7 +7252,7 @@
         <v/>
       </c>
       <c r="H136" s="42">
-        <f>IF($I136&lt;=0,"",(Rate_1*MAX(0,MIN($O136,R1_To)-MAX($O135,R1_From))+Rate_2*MAX(0,MIN($O136,R2_To)-MAX($O135,R2_From))+Rate_3*MAX(0,MIN($O136,R3_To)-MAX($O135,R3_From)))/100/Day_Basis/$I136*Day_Basis*100)</f>
+        <f>IF($I136&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O136,'Engine'!$B$3)-MAX($O135,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O136,'Engine'!$B$5)-MAX($O135,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O136,'Engine'!$B$7)-MAX($O135,'Engine'!$B$6)))/100/$H$8/$I136*$H$8*100)</f>
         <v/>
       </c>
       <c r="I136" s="43">
@@ -7277,7 +7260,7 @@
         <v/>
       </c>
       <c r="J136" s="41">
-        <f>IF($I136&lt;=0,0,$S135*(Rate_1*MAX(0,MIN($O136,R1_To)-MAX($O135,R1_From))+Rate_2*MAX(0,MIN($O136,R2_To)-MAX($O135,R2_From))+Rate_3*MAX(0,MIN($O136,R3_To)-MAX($O135,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I136&lt;=0,0,$S135*('Engine'!$B$8*MAX(0,MIN($O136,'Engine'!$B$3)-MAX($O135,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O136,'Engine'!$B$5)-MAX($O135,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O136,'Engine'!$B$7)-MAX($O135,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K136" s="41">
@@ -7290,7 +7273,7 @@
         <v/>
       </c>
       <c r="N136" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O136&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O136&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O136" s="25">
@@ -7321,7 +7304,7 @@
         <v/>
       </c>
       <c r="H137" s="42">
-        <f>IF($I137&lt;=0,"",(Rate_1*MAX(0,MIN($O137,R1_To)-MAX($O136,R1_From))+Rate_2*MAX(0,MIN($O137,R2_To)-MAX($O136,R2_From))+Rate_3*MAX(0,MIN($O137,R3_To)-MAX($O136,R3_From)))/100/Day_Basis/$I137*Day_Basis*100)</f>
+        <f>IF($I137&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O137,'Engine'!$B$3)-MAX($O136,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O137,'Engine'!$B$5)-MAX($O136,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O137,'Engine'!$B$7)-MAX($O136,'Engine'!$B$6)))/100/$H$8/$I137*$H$8*100)</f>
         <v/>
       </c>
       <c r="I137" s="43">
@@ -7329,7 +7312,7 @@
         <v/>
       </c>
       <c r="J137" s="41">
-        <f>IF($I137&lt;=0,0,$S136*(Rate_1*MAX(0,MIN($O137,R1_To)-MAX($O136,R1_From))+Rate_2*MAX(0,MIN($O137,R2_To)-MAX($O136,R2_From))+Rate_3*MAX(0,MIN($O137,R3_To)-MAX($O136,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I137&lt;=0,0,$S136*('Engine'!$B$8*MAX(0,MIN($O137,'Engine'!$B$3)-MAX($O136,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O137,'Engine'!$B$5)-MAX($O136,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O137,'Engine'!$B$7)-MAX($O136,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K137" s="41">
@@ -7342,7 +7325,7 @@
         <v/>
       </c>
       <c r="N137" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O137&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O137&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O137" s="25">
@@ -7373,7 +7356,7 @@
         <v/>
       </c>
       <c r="H138" s="42">
-        <f>IF($I138&lt;=0,"",(Rate_1*MAX(0,MIN($O138,R1_To)-MAX($O137,R1_From))+Rate_2*MAX(0,MIN($O138,R2_To)-MAX($O137,R2_From))+Rate_3*MAX(0,MIN($O138,R3_To)-MAX($O137,R3_From)))/100/Day_Basis/$I138*Day_Basis*100)</f>
+        <f>IF($I138&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O138,'Engine'!$B$3)-MAX($O137,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O138,'Engine'!$B$5)-MAX($O137,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O138,'Engine'!$B$7)-MAX($O137,'Engine'!$B$6)))/100/$H$8/$I138*$H$8*100)</f>
         <v/>
       </c>
       <c r="I138" s="43">
@@ -7381,7 +7364,7 @@
         <v/>
       </c>
       <c r="J138" s="41">
-        <f>IF($I138&lt;=0,0,$S137*(Rate_1*MAX(0,MIN($O138,R1_To)-MAX($O137,R1_From))+Rate_2*MAX(0,MIN($O138,R2_To)-MAX($O137,R2_From))+Rate_3*MAX(0,MIN($O138,R3_To)-MAX($O137,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I138&lt;=0,0,$S137*('Engine'!$B$8*MAX(0,MIN($O138,'Engine'!$B$3)-MAX($O137,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O138,'Engine'!$B$5)-MAX($O137,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O138,'Engine'!$B$7)-MAX($O137,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K138" s="41">
@@ -7394,7 +7377,7 @@
         <v/>
       </c>
       <c r="N138" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O138&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O138&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O138" s="25">
@@ -7425,7 +7408,7 @@
         <v/>
       </c>
       <c r="H139" s="42">
-        <f>IF($I139&lt;=0,"",(Rate_1*MAX(0,MIN($O139,R1_To)-MAX($O138,R1_From))+Rate_2*MAX(0,MIN($O139,R2_To)-MAX($O138,R2_From))+Rate_3*MAX(0,MIN($O139,R3_To)-MAX($O138,R3_From)))/100/Day_Basis/$I139*Day_Basis*100)</f>
+        <f>IF($I139&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O139,'Engine'!$B$3)-MAX($O138,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O139,'Engine'!$B$5)-MAX($O138,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O139,'Engine'!$B$7)-MAX($O138,'Engine'!$B$6)))/100/$H$8/$I139*$H$8*100)</f>
         <v/>
       </c>
       <c r="I139" s="43">
@@ -7433,7 +7416,7 @@
         <v/>
       </c>
       <c r="J139" s="41">
-        <f>IF($I139&lt;=0,0,$S138*(Rate_1*MAX(0,MIN($O139,R1_To)-MAX($O138,R1_From))+Rate_2*MAX(0,MIN($O139,R2_To)-MAX($O138,R2_From))+Rate_3*MAX(0,MIN($O139,R3_To)-MAX($O138,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I139&lt;=0,0,$S138*('Engine'!$B$8*MAX(0,MIN($O139,'Engine'!$B$3)-MAX($O138,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O139,'Engine'!$B$5)-MAX($O138,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O139,'Engine'!$B$7)-MAX($O138,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K139" s="41">
@@ -7446,7 +7429,7 @@
         <v/>
       </c>
       <c r="N139" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O139&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O139&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O139" s="25">
@@ -7477,7 +7460,7 @@
         <v/>
       </c>
       <c r="H140" s="42">
-        <f>IF($I140&lt;=0,"",(Rate_1*MAX(0,MIN($O140,R1_To)-MAX($O139,R1_From))+Rate_2*MAX(0,MIN($O140,R2_To)-MAX($O139,R2_From))+Rate_3*MAX(0,MIN($O140,R3_To)-MAX($O139,R3_From)))/100/Day_Basis/$I140*Day_Basis*100)</f>
+        <f>IF($I140&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O140,'Engine'!$B$3)-MAX($O139,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O140,'Engine'!$B$5)-MAX($O139,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O140,'Engine'!$B$7)-MAX($O139,'Engine'!$B$6)))/100/$H$8/$I140*$H$8*100)</f>
         <v/>
       </c>
       <c r="I140" s="43">
@@ -7485,7 +7468,7 @@
         <v/>
       </c>
       <c r="J140" s="41">
-        <f>IF($I140&lt;=0,0,$S139*(Rate_1*MAX(0,MIN($O140,R1_To)-MAX($O139,R1_From))+Rate_2*MAX(0,MIN($O140,R2_To)-MAX($O139,R2_From))+Rate_3*MAX(0,MIN($O140,R3_To)-MAX($O139,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I140&lt;=0,0,$S139*('Engine'!$B$8*MAX(0,MIN($O140,'Engine'!$B$3)-MAX($O139,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O140,'Engine'!$B$5)-MAX($O139,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O140,'Engine'!$B$7)-MAX($O139,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K140" s="41">
@@ -7498,7 +7481,7 @@
         <v/>
       </c>
       <c r="N140" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O140&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O140&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O140" s="25">
@@ -7529,7 +7512,7 @@
         <v/>
       </c>
       <c r="H141" s="42">
-        <f>IF($I141&lt;=0,"",(Rate_1*MAX(0,MIN($O141,R1_To)-MAX($O140,R1_From))+Rate_2*MAX(0,MIN($O141,R2_To)-MAX($O140,R2_From))+Rate_3*MAX(0,MIN($O141,R3_To)-MAX($O140,R3_From)))/100/Day_Basis/$I141*Day_Basis*100)</f>
+        <f>IF($I141&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O141,'Engine'!$B$3)-MAX($O140,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O141,'Engine'!$B$5)-MAX($O140,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O141,'Engine'!$B$7)-MAX($O140,'Engine'!$B$6)))/100/$H$8/$I141*$H$8*100)</f>
         <v/>
       </c>
       <c r="I141" s="43">
@@ -7537,7 +7520,7 @@
         <v/>
       </c>
       <c r="J141" s="41">
-        <f>IF($I141&lt;=0,0,$S140*(Rate_1*MAX(0,MIN($O141,R1_To)-MAX($O140,R1_From))+Rate_2*MAX(0,MIN($O141,R2_To)-MAX($O140,R2_From))+Rate_3*MAX(0,MIN($O141,R3_To)-MAX($O140,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I141&lt;=0,0,$S140*('Engine'!$B$8*MAX(0,MIN($O141,'Engine'!$B$3)-MAX($O140,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O141,'Engine'!$B$5)-MAX($O140,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O141,'Engine'!$B$7)-MAX($O140,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K141" s="41">
@@ -7550,7 +7533,7 @@
         <v/>
       </c>
       <c r="N141" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O141&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O141&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O141" s="25">
@@ -7581,7 +7564,7 @@
         <v/>
       </c>
       <c r="H142" s="42">
-        <f>IF($I142&lt;=0,"",(Rate_1*MAX(0,MIN($O142,R1_To)-MAX($O141,R1_From))+Rate_2*MAX(0,MIN($O142,R2_To)-MAX($O141,R2_From))+Rate_3*MAX(0,MIN($O142,R3_To)-MAX($O141,R3_From)))/100/Day_Basis/$I142*Day_Basis*100)</f>
+        <f>IF($I142&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O142,'Engine'!$B$3)-MAX($O141,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O142,'Engine'!$B$5)-MAX($O141,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O142,'Engine'!$B$7)-MAX($O141,'Engine'!$B$6)))/100/$H$8/$I142*$H$8*100)</f>
         <v/>
       </c>
       <c r="I142" s="43">
@@ -7589,7 +7572,7 @@
         <v/>
       </c>
       <c r="J142" s="41">
-        <f>IF($I142&lt;=0,0,$S141*(Rate_1*MAX(0,MIN($O142,R1_To)-MAX($O141,R1_From))+Rate_2*MAX(0,MIN($O142,R2_To)-MAX($O141,R2_From))+Rate_3*MAX(0,MIN($O142,R3_To)-MAX($O141,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I142&lt;=0,0,$S141*('Engine'!$B$8*MAX(0,MIN($O142,'Engine'!$B$3)-MAX($O141,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O142,'Engine'!$B$5)-MAX($O141,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O142,'Engine'!$B$7)-MAX($O141,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K142" s="41">
@@ -7602,7 +7585,7 @@
         <v/>
       </c>
       <c r="N142" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O142&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O142&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O142" s="25">
@@ -7643,7 +7626,7 @@
         <v/>
       </c>
       <c r="H143" s="51">
-        <f>IF($I143&lt;=0,"",(Rate_1*MAX(0,MIN($O143,R1_To)-MAX($O142,R1_From))+Rate_2*MAX(0,MIN($O143,R2_To)-MAX($O142,R2_From))+Rate_3*MAX(0,MIN($O143,R3_To)-MAX($O142,R3_From)))/100/Day_Basis/$I143*Day_Basis*100)</f>
+        <f>IF($I143&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O143,'Engine'!$B$3)-MAX($O142,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O143,'Engine'!$B$5)-MAX($O142,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O143,'Engine'!$B$7)-MAX($O142,'Engine'!$B$6)))/100/$H$8/$I143*$H$8*100)</f>
         <v/>
       </c>
       <c r="I143" s="52">
@@ -7651,7 +7634,7 @@
         <v/>
       </c>
       <c r="J143" s="53">
-        <f>IF($I143&lt;=0,0,$S142*(Rate_1*MAX(0,MIN($O143,R1_To)-MAX($O142,R1_From))+Rate_2*MAX(0,MIN($O143,R2_To)-MAX($O142,R2_From))+Rate_3*MAX(0,MIN($O143,R3_To)-MAX($O142,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I143&lt;=0,0,$S142*('Engine'!$B$8*MAX(0,MIN($O143,'Engine'!$B$3)-MAX($O142,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O143,'Engine'!$B$5)-MAX($O142,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O143,'Engine'!$B$7)-MAX($O142,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K143" s="53" t="n">
@@ -7663,7 +7646,7 @@
         <v/>
       </c>
       <c r="N143" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O143&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O143&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O143" s="25">
@@ -7680,7 +7663,7 @@
     </row>
     <row r="144" ht="18" customHeight="1">
       <c r="A144" s="24">
-        <f>IF($P$144=0,"QUARTER 11          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 11          "&amp;TEXT($P$144,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$144,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$144&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$144)</f>
+        <f>IF($P$144=0,"QUARTER 11          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 11          "&amp;TEXT($P$144,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$144,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$144&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$144)</f>
         <v/>
       </c>
       <c r="O144" s="25">
@@ -7738,7 +7721,7 @@
         <v/>
       </c>
       <c r="N145" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$145&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$145&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O145" s="25">
@@ -7768,7 +7751,7 @@
         <v/>
       </c>
       <c r="H146" s="42">
-        <f>IF($I146&lt;=0,"",(Rate_1*MAX(0,MIN($O146,R1_To)-MAX($O145,R1_From))+Rate_2*MAX(0,MIN($O146,R2_To)-MAX($O145,R2_From))+Rate_3*MAX(0,MIN($O146,R3_To)-MAX($O145,R3_From)))/100/Day_Basis/$I146*Day_Basis*100)</f>
+        <f>IF($I146&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O146,'Engine'!$B$3)-MAX($O145,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O146,'Engine'!$B$5)-MAX($O145,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O146,'Engine'!$B$7)-MAX($O145,'Engine'!$B$6)))/100/$H$8/$I146*$H$8*100)</f>
         <v/>
       </c>
       <c r="I146" s="43">
@@ -7776,7 +7759,7 @@
         <v/>
       </c>
       <c r="J146" s="41">
-        <f>IF($I146&lt;=0,0,$S145*(Rate_1*MAX(0,MIN($O146,R1_To)-MAX($O145,R1_From))+Rate_2*MAX(0,MIN($O146,R2_To)-MAX($O145,R2_From))+Rate_3*MAX(0,MIN($O146,R3_To)-MAX($O145,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I146&lt;=0,0,$S145*('Engine'!$B$8*MAX(0,MIN($O146,'Engine'!$B$3)-MAX($O145,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O146,'Engine'!$B$5)-MAX($O145,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O146,'Engine'!$B$7)-MAX($O145,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K146" s="41">
@@ -7789,7 +7772,7 @@
         <v/>
       </c>
       <c r="N146" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O146&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O146&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O146" s="25">
@@ -7820,7 +7803,7 @@
         <v/>
       </c>
       <c r="H147" s="42">
-        <f>IF($I147&lt;=0,"",(Rate_1*MAX(0,MIN($O147,R1_To)-MAX($O146,R1_From))+Rate_2*MAX(0,MIN($O147,R2_To)-MAX($O146,R2_From))+Rate_3*MAX(0,MIN($O147,R3_To)-MAX($O146,R3_From)))/100/Day_Basis/$I147*Day_Basis*100)</f>
+        <f>IF($I147&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O147,'Engine'!$B$3)-MAX($O146,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O147,'Engine'!$B$5)-MAX($O146,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O147,'Engine'!$B$7)-MAX($O146,'Engine'!$B$6)))/100/$H$8/$I147*$H$8*100)</f>
         <v/>
       </c>
       <c r="I147" s="43">
@@ -7828,7 +7811,7 @@
         <v/>
       </c>
       <c r="J147" s="41">
-        <f>IF($I147&lt;=0,0,$S146*(Rate_1*MAX(0,MIN($O147,R1_To)-MAX($O146,R1_From))+Rate_2*MAX(0,MIN($O147,R2_To)-MAX($O146,R2_From))+Rate_3*MAX(0,MIN($O147,R3_To)-MAX($O146,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I147&lt;=0,0,$S146*('Engine'!$B$8*MAX(0,MIN($O147,'Engine'!$B$3)-MAX($O146,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O147,'Engine'!$B$5)-MAX($O146,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O147,'Engine'!$B$7)-MAX($O146,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K147" s="41">
@@ -7841,7 +7824,7 @@
         <v/>
       </c>
       <c r="N147" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O147&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O147&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O147" s="25">
@@ -7872,7 +7855,7 @@
         <v/>
       </c>
       <c r="H148" s="42">
-        <f>IF($I148&lt;=0,"",(Rate_1*MAX(0,MIN($O148,R1_To)-MAX($O147,R1_From))+Rate_2*MAX(0,MIN($O148,R2_To)-MAX($O147,R2_From))+Rate_3*MAX(0,MIN($O148,R3_To)-MAX($O147,R3_From)))/100/Day_Basis/$I148*Day_Basis*100)</f>
+        <f>IF($I148&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O148,'Engine'!$B$3)-MAX($O147,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O148,'Engine'!$B$5)-MAX($O147,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O148,'Engine'!$B$7)-MAX($O147,'Engine'!$B$6)))/100/$H$8/$I148*$H$8*100)</f>
         <v/>
       </c>
       <c r="I148" s="43">
@@ -7880,7 +7863,7 @@
         <v/>
       </c>
       <c r="J148" s="41">
-        <f>IF($I148&lt;=0,0,$S147*(Rate_1*MAX(0,MIN($O148,R1_To)-MAX($O147,R1_From))+Rate_2*MAX(0,MIN($O148,R2_To)-MAX($O147,R2_From))+Rate_3*MAX(0,MIN($O148,R3_To)-MAX($O147,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I148&lt;=0,0,$S147*('Engine'!$B$8*MAX(0,MIN($O148,'Engine'!$B$3)-MAX($O147,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O148,'Engine'!$B$5)-MAX($O147,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O148,'Engine'!$B$7)-MAX($O147,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K148" s="41">
@@ -7893,7 +7876,7 @@
         <v/>
       </c>
       <c r="N148" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O148&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O148&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O148" s="25">
@@ -7924,7 +7907,7 @@
         <v/>
       </c>
       <c r="H149" s="42">
-        <f>IF($I149&lt;=0,"",(Rate_1*MAX(0,MIN($O149,R1_To)-MAX($O148,R1_From))+Rate_2*MAX(0,MIN($O149,R2_To)-MAX($O148,R2_From))+Rate_3*MAX(0,MIN($O149,R3_To)-MAX($O148,R3_From)))/100/Day_Basis/$I149*Day_Basis*100)</f>
+        <f>IF($I149&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O149,'Engine'!$B$3)-MAX($O148,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O149,'Engine'!$B$5)-MAX($O148,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O149,'Engine'!$B$7)-MAX($O148,'Engine'!$B$6)))/100/$H$8/$I149*$H$8*100)</f>
         <v/>
       </c>
       <c r="I149" s="43">
@@ -7932,7 +7915,7 @@
         <v/>
       </c>
       <c r="J149" s="41">
-        <f>IF($I149&lt;=0,0,$S148*(Rate_1*MAX(0,MIN($O149,R1_To)-MAX($O148,R1_From))+Rate_2*MAX(0,MIN($O149,R2_To)-MAX($O148,R2_From))+Rate_3*MAX(0,MIN($O149,R3_To)-MAX($O148,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I149&lt;=0,0,$S148*('Engine'!$B$8*MAX(0,MIN($O149,'Engine'!$B$3)-MAX($O148,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O149,'Engine'!$B$5)-MAX($O148,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O149,'Engine'!$B$7)-MAX($O148,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K149" s="41">
@@ -7945,7 +7928,7 @@
         <v/>
       </c>
       <c r="N149" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O149&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O149&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O149" s="25">
@@ -7976,7 +7959,7 @@
         <v/>
       </c>
       <c r="H150" s="42">
-        <f>IF($I150&lt;=0,"",(Rate_1*MAX(0,MIN($O150,R1_To)-MAX($O149,R1_From))+Rate_2*MAX(0,MIN($O150,R2_To)-MAX($O149,R2_From))+Rate_3*MAX(0,MIN($O150,R3_To)-MAX($O149,R3_From)))/100/Day_Basis/$I150*Day_Basis*100)</f>
+        <f>IF($I150&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O150,'Engine'!$B$3)-MAX($O149,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O150,'Engine'!$B$5)-MAX($O149,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O150,'Engine'!$B$7)-MAX($O149,'Engine'!$B$6)))/100/$H$8/$I150*$H$8*100)</f>
         <v/>
       </c>
       <c r="I150" s="43">
@@ -7984,7 +7967,7 @@
         <v/>
       </c>
       <c r="J150" s="41">
-        <f>IF($I150&lt;=0,0,$S149*(Rate_1*MAX(0,MIN($O150,R1_To)-MAX($O149,R1_From))+Rate_2*MAX(0,MIN($O150,R2_To)-MAX($O149,R2_From))+Rate_3*MAX(0,MIN($O150,R3_To)-MAX($O149,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I150&lt;=0,0,$S149*('Engine'!$B$8*MAX(0,MIN($O150,'Engine'!$B$3)-MAX($O149,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O150,'Engine'!$B$5)-MAX($O149,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O150,'Engine'!$B$7)-MAX($O149,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K150" s="41">
@@ -7997,7 +7980,7 @@
         <v/>
       </c>
       <c r="N150" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O150&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O150&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O150" s="25">
@@ -8028,7 +8011,7 @@
         <v/>
       </c>
       <c r="H151" s="42">
-        <f>IF($I151&lt;=0,"",(Rate_1*MAX(0,MIN($O151,R1_To)-MAX($O150,R1_From))+Rate_2*MAX(0,MIN($O151,R2_To)-MAX($O150,R2_From))+Rate_3*MAX(0,MIN($O151,R3_To)-MAX($O150,R3_From)))/100/Day_Basis/$I151*Day_Basis*100)</f>
+        <f>IF($I151&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O151,'Engine'!$B$3)-MAX($O150,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O151,'Engine'!$B$5)-MAX($O150,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O151,'Engine'!$B$7)-MAX($O150,'Engine'!$B$6)))/100/$H$8/$I151*$H$8*100)</f>
         <v/>
       </c>
       <c r="I151" s="43">
@@ -8036,7 +8019,7 @@
         <v/>
       </c>
       <c r="J151" s="41">
-        <f>IF($I151&lt;=0,0,$S150*(Rate_1*MAX(0,MIN($O151,R1_To)-MAX($O150,R1_From))+Rate_2*MAX(0,MIN($O151,R2_To)-MAX($O150,R2_From))+Rate_3*MAX(0,MIN($O151,R3_To)-MAX($O150,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I151&lt;=0,0,$S150*('Engine'!$B$8*MAX(0,MIN($O151,'Engine'!$B$3)-MAX($O150,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O151,'Engine'!$B$5)-MAX($O150,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O151,'Engine'!$B$7)-MAX($O150,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K151" s="41">
@@ -8049,7 +8032,7 @@
         <v/>
       </c>
       <c r="N151" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O151&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O151&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O151" s="25">
@@ -8080,7 +8063,7 @@
         <v/>
       </c>
       <c r="H152" s="42">
-        <f>IF($I152&lt;=0,"",(Rate_1*MAX(0,MIN($O152,R1_To)-MAX($O151,R1_From))+Rate_2*MAX(0,MIN($O152,R2_To)-MAX($O151,R2_From))+Rate_3*MAX(0,MIN($O152,R3_To)-MAX($O151,R3_From)))/100/Day_Basis/$I152*Day_Basis*100)</f>
+        <f>IF($I152&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O152,'Engine'!$B$3)-MAX($O151,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O152,'Engine'!$B$5)-MAX($O151,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O152,'Engine'!$B$7)-MAX($O151,'Engine'!$B$6)))/100/$H$8/$I152*$H$8*100)</f>
         <v/>
       </c>
       <c r="I152" s="43">
@@ -8088,7 +8071,7 @@
         <v/>
       </c>
       <c r="J152" s="41">
-        <f>IF($I152&lt;=0,0,$S151*(Rate_1*MAX(0,MIN($O152,R1_To)-MAX($O151,R1_From))+Rate_2*MAX(0,MIN($O152,R2_To)-MAX($O151,R2_From))+Rate_3*MAX(0,MIN($O152,R3_To)-MAX($O151,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I152&lt;=0,0,$S151*('Engine'!$B$8*MAX(0,MIN($O152,'Engine'!$B$3)-MAX($O151,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O152,'Engine'!$B$5)-MAX($O151,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O152,'Engine'!$B$7)-MAX($O151,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K152" s="41">
@@ -8101,7 +8084,7 @@
         <v/>
       </c>
       <c r="N152" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O152&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O152&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O152" s="25">
@@ -8132,7 +8115,7 @@
         <v/>
       </c>
       <c r="H153" s="42">
-        <f>IF($I153&lt;=0,"",(Rate_1*MAX(0,MIN($O153,R1_To)-MAX($O152,R1_From))+Rate_2*MAX(0,MIN($O153,R2_To)-MAX($O152,R2_From))+Rate_3*MAX(0,MIN($O153,R3_To)-MAX($O152,R3_From)))/100/Day_Basis/$I153*Day_Basis*100)</f>
+        <f>IF($I153&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O153,'Engine'!$B$3)-MAX($O152,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O153,'Engine'!$B$5)-MAX($O152,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O153,'Engine'!$B$7)-MAX($O152,'Engine'!$B$6)))/100/$H$8/$I153*$H$8*100)</f>
         <v/>
       </c>
       <c r="I153" s="43">
@@ -8140,7 +8123,7 @@
         <v/>
       </c>
       <c r="J153" s="41">
-        <f>IF($I153&lt;=0,0,$S152*(Rate_1*MAX(0,MIN($O153,R1_To)-MAX($O152,R1_From))+Rate_2*MAX(0,MIN($O153,R2_To)-MAX($O152,R2_From))+Rate_3*MAX(0,MIN($O153,R3_To)-MAX($O152,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I153&lt;=0,0,$S152*('Engine'!$B$8*MAX(0,MIN($O153,'Engine'!$B$3)-MAX($O152,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O153,'Engine'!$B$5)-MAX($O152,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O153,'Engine'!$B$7)-MAX($O152,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K153" s="41">
@@ -8153,7 +8136,7 @@
         <v/>
       </c>
       <c r="N153" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O153&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O153&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O153" s="25">
@@ -8184,7 +8167,7 @@
         <v/>
       </c>
       <c r="H154" s="42">
-        <f>IF($I154&lt;=0,"",(Rate_1*MAX(0,MIN($O154,R1_To)-MAX($O153,R1_From))+Rate_2*MAX(0,MIN($O154,R2_To)-MAX($O153,R2_From))+Rate_3*MAX(0,MIN($O154,R3_To)-MAX($O153,R3_From)))/100/Day_Basis/$I154*Day_Basis*100)</f>
+        <f>IF($I154&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O154,'Engine'!$B$3)-MAX($O153,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O154,'Engine'!$B$5)-MAX($O153,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O154,'Engine'!$B$7)-MAX($O153,'Engine'!$B$6)))/100/$H$8/$I154*$H$8*100)</f>
         <v/>
       </c>
       <c r="I154" s="43">
@@ -8192,7 +8175,7 @@
         <v/>
       </c>
       <c r="J154" s="41">
-        <f>IF($I154&lt;=0,0,$S153*(Rate_1*MAX(0,MIN($O154,R1_To)-MAX($O153,R1_From))+Rate_2*MAX(0,MIN($O154,R2_To)-MAX($O153,R2_From))+Rate_3*MAX(0,MIN($O154,R3_To)-MAX($O153,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I154&lt;=0,0,$S153*('Engine'!$B$8*MAX(0,MIN($O154,'Engine'!$B$3)-MAX($O153,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O154,'Engine'!$B$5)-MAX($O153,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O154,'Engine'!$B$7)-MAX($O153,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K154" s="41">
@@ -8205,7 +8188,7 @@
         <v/>
       </c>
       <c r="N154" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O154&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O154&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O154" s="25">
@@ -8236,7 +8219,7 @@
         <v/>
       </c>
       <c r="H155" s="42">
-        <f>IF($I155&lt;=0,"",(Rate_1*MAX(0,MIN($O155,R1_To)-MAX($O154,R1_From))+Rate_2*MAX(0,MIN($O155,R2_To)-MAX($O154,R2_From))+Rate_3*MAX(0,MIN($O155,R3_To)-MAX($O154,R3_From)))/100/Day_Basis/$I155*Day_Basis*100)</f>
+        <f>IF($I155&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O155,'Engine'!$B$3)-MAX($O154,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O155,'Engine'!$B$5)-MAX($O154,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O155,'Engine'!$B$7)-MAX($O154,'Engine'!$B$6)))/100/$H$8/$I155*$H$8*100)</f>
         <v/>
       </c>
       <c r="I155" s="43">
@@ -8244,7 +8227,7 @@
         <v/>
       </c>
       <c r="J155" s="41">
-        <f>IF($I155&lt;=0,0,$S154*(Rate_1*MAX(0,MIN($O155,R1_To)-MAX($O154,R1_From))+Rate_2*MAX(0,MIN($O155,R2_To)-MAX($O154,R2_From))+Rate_3*MAX(0,MIN($O155,R3_To)-MAX($O154,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I155&lt;=0,0,$S154*('Engine'!$B$8*MAX(0,MIN($O155,'Engine'!$B$3)-MAX($O154,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O155,'Engine'!$B$5)-MAX($O154,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O155,'Engine'!$B$7)-MAX($O154,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K155" s="41">
@@ -8257,7 +8240,7 @@
         <v/>
       </c>
       <c r="N155" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O155&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O155&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O155" s="25">
@@ -8298,7 +8281,7 @@
         <v/>
       </c>
       <c r="H156" s="51">
-        <f>IF($I156&lt;=0,"",(Rate_1*MAX(0,MIN($O156,R1_To)-MAX($O155,R1_From))+Rate_2*MAX(0,MIN($O156,R2_To)-MAX($O155,R2_From))+Rate_3*MAX(0,MIN($O156,R3_To)-MAX($O155,R3_From)))/100/Day_Basis/$I156*Day_Basis*100)</f>
+        <f>IF($I156&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O156,'Engine'!$B$3)-MAX($O155,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O156,'Engine'!$B$5)-MAX($O155,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O156,'Engine'!$B$7)-MAX($O155,'Engine'!$B$6)))/100/$H$8/$I156*$H$8*100)</f>
         <v/>
       </c>
       <c r="I156" s="52">
@@ -8306,7 +8289,7 @@
         <v/>
       </c>
       <c r="J156" s="53">
-        <f>IF($I156&lt;=0,0,$S155*(Rate_1*MAX(0,MIN($O156,R1_To)-MAX($O155,R1_From))+Rate_2*MAX(0,MIN($O156,R2_To)-MAX($O155,R2_From))+Rate_3*MAX(0,MIN($O156,R3_To)-MAX($O155,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I156&lt;=0,0,$S155*('Engine'!$B$8*MAX(0,MIN($O156,'Engine'!$B$3)-MAX($O155,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O156,'Engine'!$B$5)-MAX($O155,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O156,'Engine'!$B$7)-MAX($O155,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K156" s="53" t="n">
@@ -8318,7 +8301,7 @@
         <v/>
       </c>
       <c r="N156" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O156&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O156&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O156" s="25">
@@ -8335,7 +8318,7 @@
     </row>
     <row r="157" ht="18" customHeight="1">
       <c r="A157" s="24">
-        <f>IF($P$157=0,"QUARTER 12          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 12          "&amp;TEXT($P$157,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$157,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$157&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$157)</f>
+        <f>IF($P$157=0,"QUARTER 12          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 12          "&amp;TEXT($P$157,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$157,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$157&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$157)</f>
         <v/>
       </c>
       <c r="O157" s="25">
@@ -8393,7 +8376,7 @@
         <v/>
       </c>
       <c r="N158" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$158&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$158&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O158" s="25">
@@ -8423,7 +8406,7 @@
         <v/>
       </c>
       <c r="H159" s="42">
-        <f>IF($I159&lt;=0,"",(Rate_1*MAX(0,MIN($O159,R1_To)-MAX($O158,R1_From))+Rate_2*MAX(0,MIN($O159,R2_To)-MAX($O158,R2_From))+Rate_3*MAX(0,MIN($O159,R3_To)-MAX($O158,R3_From)))/100/Day_Basis/$I159*Day_Basis*100)</f>
+        <f>IF($I159&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O159,'Engine'!$B$3)-MAX($O158,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O159,'Engine'!$B$5)-MAX($O158,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O159,'Engine'!$B$7)-MAX($O158,'Engine'!$B$6)))/100/$H$8/$I159*$H$8*100)</f>
         <v/>
       </c>
       <c r="I159" s="43">
@@ -8431,7 +8414,7 @@
         <v/>
       </c>
       <c r="J159" s="41">
-        <f>IF($I159&lt;=0,0,$S158*(Rate_1*MAX(0,MIN($O159,R1_To)-MAX($O158,R1_From))+Rate_2*MAX(0,MIN($O159,R2_To)-MAX($O158,R2_From))+Rate_3*MAX(0,MIN($O159,R3_To)-MAX($O158,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I159&lt;=0,0,$S158*('Engine'!$B$8*MAX(0,MIN($O159,'Engine'!$B$3)-MAX($O158,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O159,'Engine'!$B$5)-MAX($O158,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O159,'Engine'!$B$7)-MAX($O158,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K159" s="41">
@@ -8444,7 +8427,7 @@
         <v/>
       </c>
       <c r="N159" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O159&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O159&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O159" s="25">
@@ -8475,7 +8458,7 @@
         <v/>
       </c>
       <c r="H160" s="42">
-        <f>IF($I160&lt;=0,"",(Rate_1*MAX(0,MIN($O160,R1_To)-MAX($O159,R1_From))+Rate_2*MAX(0,MIN($O160,R2_To)-MAX($O159,R2_From))+Rate_3*MAX(0,MIN($O160,R3_To)-MAX($O159,R3_From)))/100/Day_Basis/$I160*Day_Basis*100)</f>
+        <f>IF($I160&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O160,'Engine'!$B$3)-MAX($O159,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O160,'Engine'!$B$5)-MAX($O159,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O160,'Engine'!$B$7)-MAX($O159,'Engine'!$B$6)))/100/$H$8/$I160*$H$8*100)</f>
         <v/>
       </c>
       <c r="I160" s="43">
@@ -8483,7 +8466,7 @@
         <v/>
       </c>
       <c r="J160" s="41">
-        <f>IF($I160&lt;=0,0,$S159*(Rate_1*MAX(0,MIN($O160,R1_To)-MAX($O159,R1_From))+Rate_2*MAX(0,MIN($O160,R2_To)-MAX($O159,R2_From))+Rate_3*MAX(0,MIN($O160,R3_To)-MAX($O159,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I160&lt;=0,0,$S159*('Engine'!$B$8*MAX(0,MIN($O160,'Engine'!$B$3)-MAX($O159,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O160,'Engine'!$B$5)-MAX($O159,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O160,'Engine'!$B$7)-MAX($O159,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K160" s="41">
@@ -8496,7 +8479,7 @@
         <v/>
       </c>
       <c r="N160" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O160&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O160&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O160" s="25">
@@ -8527,7 +8510,7 @@
         <v/>
       </c>
       <c r="H161" s="42">
-        <f>IF($I161&lt;=0,"",(Rate_1*MAX(0,MIN($O161,R1_To)-MAX($O160,R1_From))+Rate_2*MAX(0,MIN($O161,R2_To)-MAX($O160,R2_From))+Rate_3*MAX(0,MIN($O161,R3_To)-MAX($O160,R3_From)))/100/Day_Basis/$I161*Day_Basis*100)</f>
+        <f>IF($I161&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O161,'Engine'!$B$3)-MAX($O160,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O161,'Engine'!$B$5)-MAX($O160,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O161,'Engine'!$B$7)-MAX($O160,'Engine'!$B$6)))/100/$H$8/$I161*$H$8*100)</f>
         <v/>
       </c>
       <c r="I161" s="43">
@@ -8535,7 +8518,7 @@
         <v/>
       </c>
       <c r="J161" s="41">
-        <f>IF($I161&lt;=0,0,$S160*(Rate_1*MAX(0,MIN($O161,R1_To)-MAX($O160,R1_From))+Rate_2*MAX(0,MIN($O161,R2_To)-MAX($O160,R2_From))+Rate_3*MAX(0,MIN($O161,R3_To)-MAX($O160,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I161&lt;=0,0,$S160*('Engine'!$B$8*MAX(0,MIN($O161,'Engine'!$B$3)-MAX($O160,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O161,'Engine'!$B$5)-MAX($O160,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O161,'Engine'!$B$7)-MAX($O160,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K161" s="41">
@@ -8548,7 +8531,7 @@
         <v/>
       </c>
       <c r="N161" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O161&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O161&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O161" s="25">
@@ -8579,7 +8562,7 @@
         <v/>
       </c>
       <c r="H162" s="42">
-        <f>IF($I162&lt;=0,"",(Rate_1*MAX(0,MIN($O162,R1_To)-MAX($O161,R1_From))+Rate_2*MAX(0,MIN($O162,R2_To)-MAX($O161,R2_From))+Rate_3*MAX(0,MIN($O162,R3_To)-MAX($O161,R3_From)))/100/Day_Basis/$I162*Day_Basis*100)</f>
+        <f>IF($I162&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O162,'Engine'!$B$3)-MAX($O161,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O162,'Engine'!$B$5)-MAX($O161,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O162,'Engine'!$B$7)-MAX($O161,'Engine'!$B$6)))/100/$H$8/$I162*$H$8*100)</f>
         <v/>
       </c>
       <c r="I162" s="43">
@@ -8587,7 +8570,7 @@
         <v/>
       </c>
       <c r="J162" s="41">
-        <f>IF($I162&lt;=0,0,$S161*(Rate_1*MAX(0,MIN($O162,R1_To)-MAX($O161,R1_From))+Rate_2*MAX(0,MIN($O162,R2_To)-MAX($O161,R2_From))+Rate_3*MAX(0,MIN($O162,R3_To)-MAX($O161,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I162&lt;=0,0,$S161*('Engine'!$B$8*MAX(0,MIN($O162,'Engine'!$B$3)-MAX($O161,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O162,'Engine'!$B$5)-MAX($O161,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O162,'Engine'!$B$7)-MAX($O161,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K162" s="41">
@@ -8600,7 +8583,7 @@
         <v/>
       </c>
       <c r="N162" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O162&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O162&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O162" s="25">
@@ -8631,7 +8614,7 @@
         <v/>
       </c>
       <c r="H163" s="42">
-        <f>IF($I163&lt;=0,"",(Rate_1*MAX(0,MIN($O163,R1_To)-MAX($O162,R1_From))+Rate_2*MAX(0,MIN($O163,R2_To)-MAX($O162,R2_From))+Rate_3*MAX(0,MIN($O163,R3_To)-MAX($O162,R3_From)))/100/Day_Basis/$I163*Day_Basis*100)</f>
+        <f>IF($I163&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O163,'Engine'!$B$3)-MAX($O162,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O163,'Engine'!$B$5)-MAX($O162,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O163,'Engine'!$B$7)-MAX($O162,'Engine'!$B$6)))/100/$H$8/$I163*$H$8*100)</f>
         <v/>
       </c>
       <c r="I163" s="43">
@@ -8639,7 +8622,7 @@
         <v/>
       </c>
       <c r="J163" s="41">
-        <f>IF($I163&lt;=0,0,$S162*(Rate_1*MAX(0,MIN($O163,R1_To)-MAX($O162,R1_From))+Rate_2*MAX(0,MIN($O163,R2_To)-MAX($O162,R2_From))+Rate_3*MAX(0,MIN($O163,R3_To)-MAX($O162,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I163&lt;=0,0,$S162*('Engine'!$B$8*MAX(0,MIN($O163,'Engine'!$B$3)-MAX($O162,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O163,'Engine'!$B$5)-MAX($O162,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O163,'Engine'!$B$7)-MAX($O162,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K163" s="41">
@@ -8652,7 +8635,7 @@
         <v/>
       </c>
       <c r="N163" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O163&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O163&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O163" s="25">
@@ -8683,7 +8666,7 @@
         <v/>
       </c>
       <c r="H164" s="42">
-        <f>IF($I164&lt;=0,"",(Rate_1*MAX(0,MIN($O164,R1_To)-MAX($O163,R1_From))+Rate_2*MAX(0,MIN($O164,R2_To)-MAX($O163,R2_From))+Rate_3*MAX(0,MIN($O164,R3_To)-MAX($O163,R3_From)))/100/Day_Basis/$I164*Day_Basis*100)</f>
+        <f>IF($I164&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O164,'Engine'!$B$3)-MAX($O163,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O164,'Engine'!$B$5)-MAX($O163,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O164,'Engine'!$B$7)-MAX($O163,'Engine'!$B$6)))/100/$H$8/$I164*$H$8*100)</f>
         <v/>
       </c>
       <c r="I164" s="43">
@@ -8691,7 +8674,7 @@
         <v/>
       </c>
       <c r="J164" s="41">
-        <f>IF($I164&lt;=0,0,$S163*(Rate_1*MAX(0,MIN($O164,R1_To)-MAX($O163,R1_From))+Rate_2*MAX(0,MIN($O164,R2_To)-MAX($O163,R2_From))+Rate_3*MAX(0,MIN($O164,R3_To)-MAX($O163,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I164&lt;=0,0,$S163*('Engine'!$B$8*MAX(0,MIN($O164,'Engine'!$B$3)-MAX($O163,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O164,'Engine'!$B$5)-MAX($O163,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O164,'Engine'!$B$7)-MAX($O163,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K164" s="41">
@@ -8704,7 +8687,7 @@
         <v/>
       </c>
       <c r="N164" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O164&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O164&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O164" s="25">
@@ -8735,7 +8718,7 @@
         <v/>
       </c>
       <c r="H165" s="42">
-        <f>IF($I165&lt;=0,"",(Rate_1*MAX(0,MIN($O165,R1_To)-MAX($O164,R1_From))+Rate_2*MAX(0,MIN($O165,R2_To)-MAX($O164,R2_From))+Rate_3*MAX(0,MIN($O165,R3_To)-MAX($O164,R3_From)))/100/Day_Basis/$I165*Day_Basis*100)</f>
+        <f>IF($I165&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O165,'Engine'!$B$3)-MAX($O164,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O165,'Engine'!$B$5)-MAX($O164,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O165,'Engine'!$B$7)-MAX($O164,'Engine'!$B$6)))/100/$H$8/$I165*$H$8*100)</f>
         <v/>
       </c>
       <c r="I165" s="43">
@@ -8743,7 +8726,7 @@
         <v/>
       </c>
       <c r="J165" s="41">
-        <f>IF($I165&lt;=0,0,$S164*(Rate_1*MAX(0,MIN($O165,R1_To)-MAX($O164,R1_From))+Rate_2*MAX(0,MIN($O165,R2_To)-MAX($O164,R2_From))+Rate_3*MAX(0,MIN($O165,R3_To)-MAX($O164,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I165&lt;=0,0,$S164*('Engine'!$B$8*MAX(0,MIN($O165,'Engine'!$B$3)-MAX($O164,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O165,'Engine'!$B$5)-MAX($O164,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O165,'Engine'!$B$7)-MAX($O164,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K165" s="41">
@@ -8756,7 +8739,7 @@
         <v/>
       </c>
       <c r="N165" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O165&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O165&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O165" s="25">
@@ -8787,7 +8770,7 @@
         <v/>
       </c>
       <c r="H166" s="42">
-        <f>IF($I166&lt;=0,"",(Rate_1*MAX(0,MIN($O166,R1_To)-MAX($O165,R1_From))+Rate_2*MAX(0,MIN($O166,R2_To)-MAX($O165,R2_From))+Rate_3*MAX(0,MIN($O166,R3_To)-MAX($O165,R3_From)))/100/Day_Basis/$I166*Day_Basis*100)</f>
+        <f>IF($I166&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O166,'Engine'!$B$3)-MAX($O165,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O166,'Engine'!$B$5)-MAX($O165,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O166,'Engine'!$B$7)-MAX($O165,'Engine'!$B$6)))/100/$H$8/$I166*$H$8*100)</f>
         <v/>
       </c>
       <c r="I166" s="43">
@@ -8795,7 +8778,7 @@
         <v/>
       </c>
       <c r="J166" s="41">
-        <f>IF($I166&lt;=0,0,$S165*(Rate_1*MAX(0,MIN($O166,R1_To)-MAX($O165,R1_From))+Rate_2*MAX(0,MIN($O166,R2_To)-MAX($O165,R2_From))+Rate_3*MAX(0,MIN($O166,R3_To)-MAX($O165,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I166&lt;=0,0,$S165*('Engine'!$B$8*MAX(0,MIN($O166,'Engine'!$B$3)-MAX($O165,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O166,'Engine'!$B$5)-MAX($O165,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O166,'Engine'!$B$7)-MAX($O165,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K166" s="41">
@@ -8808,7 +8791,7 @@
         <v/>
       </c>
       <c r="N166" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O166&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O166&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O166" s="25">
@@ -8839,7 +8822,7 @@
         <v/>
       </c>
       <c r="H167" s="42">
-        <f>IF($I167&lt;=0,"",(Rate_1*MAX(0,MIN($O167,R1_To)-MAX($O166,R1_From))+Rate_2*MAX(0,MIN($O167,R2_To)-MAX($O166,R2_From))+Rate_3*MAX(0,MIN($O167,R3_To)-MAX($O166,R3_From)))/100/Day_Basis/$I167*Day_Basis*100)</f>
+        <f>IF($I167&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O167,'Engine'!$B$3)-MAX($O166,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O167,'Engine'!$B$5)-MAX($O166,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O167,'Engine'!$B$7)-MAX($O166,'Engine'!$B$6)))/100/$H$8/$I167*$H$8*100)</f>
         <v/>
       </c>
       <c r="I167" s="43">
@@ -8847,7 +8830,7 @@
         <v/>
       </c>
       <c r="J167" s="41">
-        <f>IF($I167&lt;=0,0,$S166*(Rate_1*MAX(0,MIN($O167,R1_To)-MAX($O166,R1_From))+Rate_2*MAX(0,MIN($O167,R2_To)-MAX($O166,R2_From))+Rate_3*MAX(0,MIN($O167,R3_To)-MAX($O166,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I167&lt;=0,0,$S166*('Engine'!$B$8*MAX(0,MIN($O167,'Engine'!$B$3)-MAX($O166,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O167,'Engine'!$B$5)-MAX($O166,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O167,'Engine'!$B$7)-MAX($O166,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K167" s="41">
@@ -8860,7 +8843,7 @@
         <v/>
       </c>
       <c r="N167" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O167&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O167&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O167" s="25">
@@ -8891,7 +8874,7 @@
         <v/>
       </c>
       <c r="H168" s="42">
-        <f>IF($I168&lt;=0,"",(Rate_1*MAX(0,MIN($O168,R1_To)-MAX($O167,R1_From))+Rate_2*MAX(0,MIN($O168,R2_To)-MAX($O167,R2_From))+Rate_3*MAX(0,MIN($O168,R3_To)-MAX($O167,R3_From)))/100/Day_Basis/$I168*Day_Basis*100)</f>
+        <f>IF($I168&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O168,'Engine'!$B$3)-MAX($O167,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O168,'Engine'!$B$5)-MAX($O167,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O168,'Engine'!$B$7)-MAX($O167,'Engine'!$B$6)))/100/$H$8/$I168*$H$8*100)</f>
         <v/>
       </c>
       <c r="I168" s="43">
@@ -8899,7 +8882,7 @@
         <v/>
       </c>
       <c r="J168" s="41">
-        <f>IF($I168&lt;=0,0,$S167*(Rate_1*MAX(0,MIN($O168,R1_To)-MAX($O167,R1_From))+Rate_2*MAX(0,MIN($O168,R2_To)-MAX($O167,R2_From))+Rate_3*MAX(0,MIN($O168,R3_To)-MAX($O167,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I168&lt;=0,0,$S167*('Engine'!$B$8*MAX(0,MIN($O168,'Engine'!$B$3)-MAX($O167,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O168,'Engine'!$B$5)-MAX($O167,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O168,'Engine'!$B$7)-MAX($O167,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K168" s="41">
@@ -8912,7 +8895,7 @@
         <v/>
       </c>
       <c r="N168" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O168&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O168&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O168" s="25">
@@ -8953,7 +8936,7 @@
         <v/>
       </c>
       <c r="H169" s="51">
-        <f>IF($I169&lt;=0,"",(Rate_1*MAX(0,MIN($O169,R1_To)-MAX($O168,R1_From))+Rate_2*MAX(0,MIN($O169,R2_To)-MAX($O168,R2_From))+Rate_3*MAX(0,MIN($O169,R3_To)-MAX($O168,R3_From)))/100/Day_Basis/$I169*Day_Basis*100)</f>
+        <f>IF($I169&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O169,'Engine'!$B$3)-MAX($O168,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O169,'Engine'!$B$5)-MAX($O168,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O169,'Engine'!$B$7)-MAX($O168,'Engine'!$B$6)))/100/$H$8/$I169*$H$8*100)</f>
         <v/>
       </c>
       <c r="I169" s="52">
@@ -8961,7 +8944,7 @@
         <v/>
       </c>
       <c r="J169" s="53">
-        <f>IF($I169&lt;=0,0,$S168*(Rate_1*MAX(0,MIN($O169,R1_To)-MAX($O168,R1_From))+Rate_2*MAX(0,MIN($O169,R2_To)-MAX($O168,R2_From))+Rate_3*MAX(0,MIN($O169,R3_To)-MAX($O168,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I169&lt;=0,0,$S168*('Engine'!$B$8*MAX(0,MIN($O169,'Engine'!$B$3)-MAX($O168,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O169,'Engine'!$B$5)-MAX($O168,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O169,'Engine'!$B$7)-MAX($O168,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K169" s="53" t="n">
@@ -8973,7 +8956,7 @@
         <v/>
       </c>
       <c r="N169" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O169&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O169&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O169" s="25">
@@ -8990,7 +8973,7 @@
     </row>
     <row r="170" ht="18" customHeight="1">
       <c r="A170" s="24">
-        <f>IF($P$170=0,"QUARTER 13          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 13          "&amp;TEXT($P$170,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$170,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$170&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$170)</f>
+        <f>IF($P$170=0,"QUARTER 13          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 13          "&amp;TEXT($P$170,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$170,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$170&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$170)</f>
         <v/>
       </c>
       <c r="O170" s="25">
@@ -9048,7 +9031,7 @@
         <v/>
       </c>
       <c r="N171" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$171&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$171&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O171" s="25">
@@ -9078,7 +9061,7 @@
         <v/>
       </c>
       <c r="H172" s="42">
-        <f>IF($I172&lt;=0,"",(Rate_1*MAX(0,MIN($O172,R1_To)-MAX($O171,R1_From))+Rate_2*MAX(0,MIN($O172,R2_To)-MAX($O171,R2_From))+Rate_3*MAX(0,MIN($O172,R3_To)-MAX($O171,R3_From)))/100/Day_Basis/$I172*Day_Basis*100)</f>
+        <f>IF($I172&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O172,'Engine'!$B$3)-MAX($O171,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O172,'Engine'!$B$5)-MAX($O171,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O172,'Engine'!$B$7)-MAX($O171,'Engine'!$B$6)))/100/$H$8/$I172*$H$8*100)</f>
         <v/>
       </c>
       <c r="I172" s="43">
@@ -9086,7 +9069,7 @@
         <v/>
       </c>
       <c r="J172" s="41">
-        <f>IF($I172&lt;=0,0,$S171*(Rate_1*MAX(0,MIN($O172,R1_To)-MAX($O171,R1_From))+Rate_2*MAX(0,MIN($O172,R2_To)-MAX($O171,R2_From))+Rate_3*MAX(0,MIN($O172,R3_To)-MAX($O171,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I172&lt;=0,0,$S171*('Engine'!$B$8*MAX(0,MIN($O172,'Engine'!$B$3)-MAX($O171,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O172,'Engine'!$B$5)-MAX($O171,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O172,'Engine'!$B$7)-MAX($O171,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K172" s="41">
@@ -9099,7 +9082,7 @@
         <v/>
       </c>
       <c r="N172" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O172&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O172&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O172" s="25">
@@ -9130,7 +9113,7 @@
         <v/>
       </c>
       <c r="H173" s="42">
-        <f>IF($I173&lt;=0,"",(Rate_1*MAX(0,MIN($O173,R1_To)-MAX($O172,R1_From))+Rate_2*MAX(0,MIN($O173,R2_To)-MAX($O172,R2_From))+Rate_3*MAX(0,MIN($O173,R3_To)-MAX($O172,R3_From)))/100/Day_Basis/$I173*Day_Basis*100)</f>
+        <f>IF($I173&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O173,'Engine'!$B$3)-MAX($O172,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O173,'Engine'!$B$5)-MAX($O172,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O173,'Engine'!$B$7)-MAX($O172,'Engine'!$B$6)))/100/$H$8/$I173*$H$8*100)</f>
         <v/>
       </c>
       <c r="I173" s="43">
@@ -9138,7 +9121,7 @@
         <v/>
       </c>
       <c r="J173" s="41">
-        <f>IF($I173&lt;=0,0,$S172*(Rate_1*MAX(0,MIN($O173,R1_To)-MAX($O172,R1_From))+Rate_2*MAX(0,MIN($O173,R2_To)-MAX($O172,R2_From))+Rate_3*MAX(0,MIN($O173,R3_To)-MAX($O172,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I173&lt;=0,0,$S172*('Engine'!$B$8*MAX(0,MIN($O173,'Engine'!$B$3)-MAX($O172,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O173,'Engine'!$B$5)-MAX($O172,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O173,'Engine'!$B$7)-MAX($O172,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K173" s="41">
@@ -9151,7 +9134,7 @@
         <v/>
       </c>
       <c r="N173" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O173&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O173&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O173" s="25">
@@ -9182,7 +9165,7 @@
         <v/>
       </c>
       <c r="H174" s="42">
-        <f>IF($I174&lt;=0,"",(Rate_1*MAX(0,MIN($O174,R1_To)-MAX($O173,R1_From))+Rate_2*MAX(0,MIN($O174,R2_To)-MAX($O173,R2_From))+Rate_3*MAX(0,MIN($O174,R3_To)-MAX($O173,R3_From)))/100/Day_Basis/$I174*Day_Basis*100)</f>
+        <f>IF($I174&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O174,'Engine'!$B$3)-MAX($O173,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O174,'Engine'!$B$5)-MAX($O173,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O174,'Engine'!$B$7)-MAX($O173,'Engine'!$B$6)))/100/$H$8/$I174*$H$8*100)</f>
         <v/>
       </c>
       <c r="I174" s="43">
@@ -9190,7 +9173,7 @@
         <v/>
       </c>
       <c r="J174" s="41">
-        <f>IF($I174&lt;=0,0,$S173*(Rate_1*MAX(0,MIN($O174,R1_To)-MAX($O173,R1_From))+Rate_2*MAX(0,MIN($O174,R2_To)-MAX($O173,R2_From))+Rate_3*MAX(0,MIN($O174,R3_To)-MAX($O173,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I174&lt;=0,0,$S173*('Engine'!$B$8*MAX(0,MIN($O174,'Engine'!$B$3)-MAX($O173,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O174,'Engine'!$B$5)-MAX($O173,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O174,'Engine'!$B$7)-MAX($O173,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K174" s="41">
@@ -9203,7 +9186,7 @@
         <v/>
       </c>
       <c r="N174" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O174&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O174&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O174" s="25">
@@ -9234,7 +9217,7 @@
         <v/>
       </c>
       <c r="H175" s="42">
-        <f>IF($I175&lt;=0,"",(Rate_1*MAX(0,MIN($O175,R1_To)-MAX($O174,R1_From))+Rate_2*MAX(0,MIN($O175,R2_To)-MAX($O174,R2_From))+Rate_3*MAX(0,MIN($O175,R3_To)-MAX($O174,R3_From)))/100/Day_Basis/$I175*Day_Basis*100)</f>
+        <f>IF($I175&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O175,'Engine'!$B$3)-MAX($O174,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O175,'Engine'!$B$5)-MAX($O174,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O175,'Engine'!$B$7)-MAX($O174,'Engine'!$B$6)))/100/$H$8/$I175*$H$8*100)</f>
         <v/>
       </c>
       <c r="I175" s="43">
@@ -9242,7 +9225,7 @@
         <v/>
       </c>
       <c r="J175" s="41">
-        <f>IF($I175&lt;=0,0,$S174*(Rate_1*MAX(0,MIN($O175,R1_To)-MAX($O174,R1_From))+Rate_2*MAX(0,MIN($O175,R2_To)-MAX($O174,R2_From))+Rate_3*MAX(0,MIN($O175,R3_To)-MAX($O174,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I175&lt;=0,0,$S174*('Engine'!$B$8*MAX(0,MIN($O175,'Engine'!$B$3)-MAX($O174,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O175,'Engine'!$B$5)-MAX($O174,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O175,'Engine'!$B$7)-MAX($O174,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K175" s="41">
@@ -9255,7 +9238,7 @@
         <v/>
       </c>
       <c r="N175" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O175&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O175&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O175" s="25">
@@ -9286,7 +9269,7 @@
         <v/>
       </c>
       <c r="H176" s="42">
-        <f>IF($I176&lt;=0,"",(Rate_1*MAX(0,MIN($O176,R1_To)-MAX($O175,R1_From))+Rate_2*MAX(0,MIN($O176,R2_To)-MAX($O175,R2_From))+Rate_3*MAX(0,MIN($O176,R3_To)-MAX($O175,R3_From)))/100/Day_Basis/$I176*Day_Basis*100)</f>
+        <f>IF($I176&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O176,'Engine'!$B$3)-MAX($O175,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O176,'Engine'!$B$5)-MAX($O175,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O176,'Engine'!$B$7)-MAX($O175,'Engine'!$B$6)))/100/$H$8/$I176*$H$8*100)</f>
         <v/>
       </c>
       <c r="I176" s="43">
@@ -9294,7 +9277,7 @@
         <v/>
       </c>
       <c r="J176" s="41">
-        <f>IF($I176&lt;=0,0,$S175*(Rate_1*MAX(0,MIN($O176,R1_To)-MAX($O175,R1_From))+Rate_2*MAX(0,MIN($O176,R2_To)-MAX($O175,R2_From))+Rate_3*MAX(0,MIN($O176,R3_To)-MAX($O175,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I176&lt;=0,0,$S175*('Engine'!$B$8*MAX(0,MIN($O176,'Engine'!$B$3)-MAX($O175,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O176,'Engine'!$B$5)-MAX($O175,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O176,'Engine'!$B$7)-MAX($O175,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K176" s="41">
@@ -9307,7 +9290,7 @@
         <v/>
       </c>
       <c r="N176" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O176&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O176&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O176" s="25">
@@ -9338,7 +9321,7 @@
         <v/>
       </c>
       <c r="H177" s="42">
-        <f>IF($I177&lt;=0,"",(Rate_1*MAX(0,MIN($O177,R1_To)-MAX($O176,R1_From))+Rate_2*MAX(0,MIN($O177,R2_To)-MAX($O176,R2_From))+Rate_3*MAX(0,MIN($O177,R3_To)-MAX($O176,R3_From)))/100/Day_Basis/$I177*Day_Basis*100)</f>
+        <f>IF($I177&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O177,'Engine'!$B$3)-MAX($O176,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O177,'Engine'!$B$5)-MAX($O176,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O177,'Engine'!$B$7)-MAX($O176,'Engine'!$B$6)))/100/$H$8/$I177*$H$8*100)</f>
         <v/>
       </c>
       <c r="I177" s="43">
@@ -9346,7 +9329,7 @@
         <v/>
       </c>
       <c r="J177" s="41">
-        <f>IF($I177&lt;=0,0,$S176*(Rate_1*MAX(0,MIN($O177,R1_To)-MAX($O176,R1_From))+Rate_2*MAX(0,MIN($O177,R2_To)-MAX($O176,R2_From))+Rate_3*MAX(0,MIN($O177,R3_To)-MAX($O176,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I177&lt;=0,0,$S176*('Engine'!$B$8*MAX(0,MIN($O177,'Engine'!$B$3)-MAX($O176,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O177,'Engine'!$B$5)-MAX($O176,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O177,'Engine'!$B$7)-MAX($O176,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K177" s="41">
@@ -9359,7 +9342,7 @@
         <v/>
       </c>
       <c r="N177" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O177&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O177&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O177" s="25">
@@ -9390,7 +9373,7 @@
         <v/>
       </c>
       <c r="H178" s="42">
-        <f>IF($I178&lt;=0,"",(Rate_1*MAX(0,MIN($O178,R1_To)-MAX($O177,R1_From))+Rate_2*MAX(0,MIN($O178,R2_To)-MAX($O177,R2_From))+Rate_3*MAX(0,MIN($O178,R3_To)-MAX($O177,R3_From)))/100/Day_Basis/$I178*Day_Basis*100)</f>
+        <f>IF($I178&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O178,'Engine'!$B$3)-MAX($O177,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O178,'Engine'!$B$5)-MAX($O177,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O178,'Engine'!$B$7)-MAX($O177,'Engine'!$B$6)))/100/$H$8/$I178*$H$8*100)</f>
         <v/>
       </c>
       <c r="I178" s="43">
@@ -9398,7 +9381,7 @@
         <v/>
       </c>
       <c r="J178" s="41">
-        <f>IF($I178&lt;=0,0,$S177*(Rate_1*MAX(0,MIN($O178,R1_To)-MAX($O177,R1_From))+Rate_2*MAX(0,MIN($O178,R2_To)-MAX($O177,R2_From))+Rate_3*MAX(0,MIN($O178,R3_To)-MAX($O177,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I178&lt;=0,0,$S177*('Engine'!$B$8*MAX(0,MIN($O178,'Engine'!$B$3)-MAX($O177,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O178,'Engine'!$B$5)-MAX($O177,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O178,'Engine'!$B$7)-MAX($O177,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K178" s="41">
@@ -9411,7 +9394,7 @@
         <v/>
       </c>
       <c r="N178" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O178&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O178&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O178" s="25">
@@ -9442,7 +9425,7 @@
         <v/>
       </c>
       <c r="H179" s="42">
-        <f>IF($I179&lt;=0,"",(Rate_1*MAX(0,MIN($O179,R1_To)-MAX($O178,R1_From))+Rate_2*MAX(0,MIN($O179,R2_To)-MAX($O178,R2_From))+Rate_3*MAX(0,MIN($O179,R3_To)-MAX($O178,R3_From)))/100/Day_Basis/$I179*Day_Basis*100)</f>
+        <f>IF($I179&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O179,'Engine'!$B$3)-MAX($O178,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O179,'Engine'!$B$5)-MAX($O178,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O179,'Engine'!$B$7)-MAX($O178,'Engine'!$B$6)))/100/$H$8/$I179*$H$8*100)</f>
         <v/>
       </c>
       <c r="I179" s="43">
@@ -9450,7 +9433,7 @@
         <v/>
       </c>
       <c r="J179" s="41">
-        <f>IF($I179&lt;=0,0,$S178*(Rate_1*MAX(0,MIN($O179,R1_To)-MAX($O178,R1_From))+Rate_2*MAX(0,MIN($O179,R2_To)-MAX($O178,R2_From))+Rate_3*MAX(0,MIN($O179,R3_To)-MAX($O178,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I179&lt;=0,0,$S178*('Engine'!$B$8*MAX(0,MIN($O179,'Engine'!$B$3)-MAX($O178,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O179,'Engine'!$B$5)-MAX($O178,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O179,'Engine'!$B$7)-MAX($O178,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K179" s="41">
@@ -9463,7 +9446,7 @@
         <v/>
       </c>
       <c r="N179" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O179&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O179&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O179" s="25">
@@ -9494,7 +9477,7 @@
         <v/>
       </c>
       <c r="H180" s="42">
-        <f>IF($I180&lt;=0,"",(Rate_1*MAX(0,MIN($O180,R1_To)-MAX($O179,R1_From))+Rate_2*MAX(0,MIN($O180,R2_To)-MAX($O179,R2_From))+Rate_3*MAX(0,MIN($O180,R3_To)-MAX($O179,R3_From)))/100/Day_Basis/$I180*Day_Basis*100)</f>
+        <f>IF($I180&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O180,'Engine'!$B$3)-MAX($O179,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O180,'Engine'!$B$5)-MAX($O179,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O180,'Engine'!$B$7)-MAX($O179,'Engine'!$B$6)))/100/$H$8/$I180*$H$8*100)</f>
         <v/>
       </c>
       <c r="I180" s="43">
@@ -9502,7 +9485,7 @@
         <v/>
       </c>
       <c r="J180" s="41">
-        <f>IF($I180&lt;=0,0,$S179*(Rate_1*MAX(0,MIN($O180,R1_To)-MAX($O179,R1_From))+Rate_2*MAX(0,MIN($O180,R2_To)-MAX($O179,R2_From))+Rate_3*MAX(0,MIN($O180,R3_To)-MAX($O179,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I180&lt;=0,0,$S179*('Engine'!$B$8*MAX(0,MIN($O180,'Engine'!$B$3)-MAX($O179,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O180,'Engine'!$B$5)-MAX($O179,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O180,'Engine'!$B$7)-MAX($O179,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K180" s="41">
@@ -9515,7 +9498,7 @@
         <v/>
       </c>
       <c r="N180" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O180&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O180&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O180" s="25">
@@ -9546,7 +9529,7 @@
         <v/>
       </c>
       <c r="H181" s="42">
-        <f>IF($I181&lt;=0,"",(Rate_1*MAX(0,MIN($O181,R1_To)-MAX($O180,R1_From))+Rate_2*MAX(0,MIN($O181,R2_To)-MAX($O180,R2_From))+Rate_3*MAX(0,MIN($O181,R3_To)-MAX($O180,R3_From)))/100/Day_Basis/$I181*Day_Basis*100)</f>
+        <f>IF($I181&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O181,'Engine'!$B$3)-MAX($O180,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O181,'Engine'!$B$5)-MAX($O180,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O181,'Engine'!$B$7)-MAX($O180,'Engine'!$B$6)))/100/$H$8/$I181*$H$8*100)</f>
         <v/>
       </c>
       <c r="I181" s="43">
@@ -9554,7 +9537,7 @@
         <v/>
       </c>
       <c r="J181" s="41">
-        <f>IF($I181&lt;=0,0,$S180*(Rate_1*MAX(0,MIN($O181,R1_To)-MAX($O180,R1_From))+Rate_2*MAX(0,MIN($O181,R2_To)-MAX($O180,R2_From))+Rate_3*MAX(0,MIN($O181,R3_To)-MAX($O180,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I181&lt;=0,0,$S180*('Engine'!$B$8*MAX(0,MIN($O181,'Engine'!$B$3)-MAX($O180,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O181,'Engine'!$B$5)-MAX($O180,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O181,'Engine'!$B$7)-MAX($O180,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K181" s="41">
@@ -9567,7 +9550,7 @@
         <v/>
       </c>
       <c r="N181" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O181&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O181&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O181" s="25">
@@ -9608,7 +9591,7 @@
         <v/>
       </c>
       <c r="H182" s="51">
-        <f>IF($I182&lt;=0,"",(Rate_1*MAX(0,MIN($O182,R1_To)-MAX($O181,R1_From))+Rate_2*MAX(0,MIN($O182,R2_To)-MAX($O181,R2_From))+Rate_3*MAX(0,MIN($O182,R3_To)-MAX($O181,R3_From)))/100/Day_Basis/$I182*Day_Basis*100)</f>
+        <f>IF($I182&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O182,'Engine'!$B$3)-MAX($O181,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O182,'Engine'!$B$5)-MAX($O181,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O182,'Engine'!$B$7)-MAX($O181,'Engine'!$B$6)))/100/$H$8/$I182*$H$8*100)</f>
         <v/>
       </c>
       <c r="I182" s="52">
@@ -9616,7 +9599,7 @@
         <v/>
       </c>
       <c r="J182" s="53">
-        <f>IF($I182&lt;=0,0,$S181*(Rate_1*MAX(0,MIN($O182,R1_To)-MAX($O181,R1_From))+Rate_2*MAX(0,MIN($O182,R2_To)-MAX($O181,R2_From))+Rate_3*MAX(0,MIN($O182,R3_To)-MAX($O181,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I182&lt;=0,0,$S181*('Engine'!$B$8*MAX(0,MIN($O182,'Engine'!$B$3)-MAX($O181,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O182,'Engine'!$B$5)-MAX($O181,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O182,'Engine'!$B$7)-MAX($O181,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K182" s="53" t="n">
@@ -9628,7 +9611,7 @@
         <v/>
       </c>
       <c r="N182" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O182&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O182&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O182" s="25">
@@ -9645,7 +9628,7 @@
     </row>
     <row r="183" ht="18" customHeight="1">
       <c r="A183" s="24">
-        <f>IF($P$183=0,"QUARTER 14          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 14          "&amp;TEXT($P$183,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$183,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$183&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$183)</f>
+        <f>IF($P$183=0,"QUARTER 14          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 14          "&amp;TEXT($P$183,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$183,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$183&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$183)</f>
         <v/>
       </c>
       <c r="O183" s="25">
@@ -9703,7 +9686,7 @@
         <v/>
       </c>
       <c r="N184" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$184&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$184&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O184" s="25">
@@ -9733,7 +9716,7 @@
         <v/>
       </c>
       <c r="H185" s="42">
-        <f>IF($I185&lt;=0,"",(Rate_1*MAX(0,MIN($O185,R1_To)-MAX($O184,R1_From))+Rate_2*MAX(0,MIN($O185,R2_To)-MAX($O184,R2_From))+Rate_3*MAX(0,MIN($O185,R3_To)-MAX($O184,R3_From)))/100/Day_Basis/$I185*Day_Basis*100)</f>
+        <f>IF($I185&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O185,'Engine'!$B$3)-MAX($O184,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O185,'Engine'!$B$5)-MAX($O184,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O185,'Engine'!$B$7)-MAX($O184,'Engine'!$B$6)))/100/$H$8/$I185*$H$8*100)</f>
         <v/>
       </c>
       <c r="I185" s="43">
@@ -9741,7 +9724,7 @@
         <v/>
       </c>
       <c r="J185" s="41">
-        <f>IF($I185&lt;=0,0,$S184*(Rate_1*MAX(0,MIN($O185,R1_To)-MAX($O184,R1_From))+Rate_2*MAX(0,MIN($O185,R2_To)-MAX($O184,R2_From))+Rate_3*MAX(0,MIN($O185,R3_To)-MAX($O184,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I185&lt;=0,0,$S184*('Engine'!$B$8*MAX(0,MIN($O185,'Engine'!$B$3)-MAX($O184,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O185,'Engine'!$B$5)-MAX($O184,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O185,'Engine'!$B$7)-MAX($O184,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K185" s="41">
@@ -9754,7 +9737,7 @@
         <v/>
       </c>
       <c r="N185" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O185&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O185&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O185" s="25">
@@ -9785,7 +9768,7 @@
         <v/>
       </c>
       <c r="H186" s="42">
-        <f>IF($I186&lt;=0,"",(Rate_1*MAX(0,MIN($O186,R1_To)-MAX($O185,R1_From))+Rate_2*MAX(0,MIN($O186,R2_To)-MAX($O185,R2_From))+Rate_3*MAX(0,MIN($O186,R3_To)-MAX($O185,R3_From)))/100/Day_Basis/$I186*Day_Basis*100)</f>
+        <f>IF($I186&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O186,'Engine'!$B$3)-MAX($O185,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O186,'Engine'!$B$5)-MAX($O185,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O186,'Engine'!$B$7)-MAX($O185,'Engine'!$B$6)))/100/$H$8/$I186*$H$8*100)</f>
         <v/>
       </c>
       <c r="I186" s="43">
@@ -9793,7 +9776,7 @@
         <v/>
       </c>
       <c r="J186" s="41">
-        <f>IF($I186&lt;=0,0,$S185*(Rate_1*MAX(0,MIN($O186,R1_To)-MAX($O185,R1_From))+Rate_2*MAX(0,MIN($O186,R2_To)-MAX($O185,R2_From))+Rate_3*MAX(0,MIN($O186,R3_To)-MAX($O185,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I186&lt;=0,0,$S185*('Engine'!$B$8*MAX(0,MIN($O186,'Engine'!$B$3)-MAX($O185,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O186,'Engine'!$B$5)-MAX($O185,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O186,'Engine'!$B$7)-MAX($O185,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K186" s="41">
@@ -9806,7 +9789,7 @@
         <v/>
       </c>
       <c r="N186" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O186&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O186&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O186" s="25">
@@ -9837,7 +9820,7 @@
         <v/>
       </c>
       <c r="H187" s="42">
-        <f>IF($I187&lt;=0,"",(Rate_1*MAX(0,MIN($O187,R1_To)-MAX($O186,R1_From))+Rate_2*MAX(0,MIN($O187,R2_To)-MAX($O186,R2_From))+Rate_3*MAX(0,MIN($O187,R3_To)-MAX($O186,R3_From)))/100/Day_Basis/$I187*Day_Basis*100)</f>
+        <f>IF($I187&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O187,'Engine'!$B$3)-MAX($O186,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O187,'Engine'!$B$5)-MAX($O186,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O187,'Engine'!$B$7)-MAX($O186,'Engine'!$B$6)))/100/$H$8/$I187*$H$8*100)</f>
         <v/>
       </c>
       <c r="I187" s="43">
@@ -9845,7 +9828,7 @@
         <v/>
       </c>
       <c r="J187" s="41">
-        <f>IF($I187&lt;=0,0,$S186*(Rate_1*MAX(0,MIN($O187,R1_To)-MAX($O186,R1_From))+Rate_2*MAX(0,MIN($O187,R2_To)-MAX($O186,R2_From))+Rate_3*MAX(0,MIN($O187,R3_To)-MAX($O186,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I187&lt;=0,0,$S186*('Engine'!$B$8*MAX(0,MIN($O187,'Engine'!$B$3)-MAX($O186,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O187,'Engine'!$B$5)-MAX($O186,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O187,'Engine'!$B$7)-MAX($O186,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K187" s="41">
@@ -9858,7 +9841,7 @@
         <v/>
       </c>
       <c r="N187" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O187&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O187&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O187" s="25">
@@ -9889,7 +9872,7 @@
         <v/>
       </c>
       <c r="H188" s="42">
-        <f>IF($I188&lt;=0,"",(Rate_1*MAX(0,MIN($O188,R1_To)-MAX($O187,R1_From))+Rate_2*MAX(0,MIN($O188,R2_To)-MAX($O187,R2_From))+Rate_3*MAX(0,MIN($O188,R3_To)-MAX($O187,R3_From)))/100/Day_Basis/$I188*Day_Basis*100)</f>
+        <f>IF($I188&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O188,'Engine'!$B$3)-MAX($O187,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O188,'Engine'!$B$5)-MAX($O187,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O188,'Engine'!$B$7)-MAX($O187,'Engine'!$B$6)))/100/$H$8/$I188*$H$8*100)</f>
         <v/>
       </c>
       <c r="I188" s="43">
@@ -9897,7 +9880,7 @@
         <v/>
       </c>
       <c r="J188" s="41">
-        <f>IF($I188&lt;=0,0,$S187*(Rate_1*MAX(0,MIN($O188,R1_To)-MAX($O187,R1_From))+Rate_2*MAX(0,MIN($O188,R2_To)-MAX($O187,R2_From))+Rate_3*MAX(0,MIN($O188,R3_To)-MAX($O187,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I188&lt;=0,0,$S187*('Engine'!$B$8*MAX(0,MIN($O188,'Engine'!$B$3)-MAX($O187,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O188,'Engine'!$B$5)-MAX($O187,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O188,'Engine'!$B$7)-MAX($O187,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K188" s="41">
@@ -9910,7 +9893,7 @@
         <v/>
       </c>
       <c r="N188" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O188&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O188&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O188" s="25">
@@ -9941,7 +9924,7 @@
         <v/>
       </c>
       <c r="H189" s="42">
-        <f>IF($I189&lt;=0,"",(Rate_1*MAX(0,MIN($O189,R1_To)-MAX($O188,R1_From))+Rate_2*MAX(0,MIN($O189,R2_To)-MAX($O188,R2_From))+Rate_3*MAX(0,MIN($O189,R3_To)-MAX($O188,R3_From)))/100/Day_Basis/$I189*Day_Basis*100)</f>
+        <f>IF($I189&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O189,'Engine'!$B$3)-MAX($O188,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O189,'Engine'!$B$5)-MAX($O188,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O189,'Engine'!$B$7)-MAX($O188,'Engine'!$B$6)))/100/$H$8/$I189*$H$8*100)</f>
         <v/>
       </c>
       <c r="I189" s="43">
@@ -9949,7 +9932,7 @@
         <v/>
       </c>
       <c r="J189" s="41">
-        <f>IF($I189&lt;=0,0,$S188*(Rate_1*MAX(0,MIN($O189,R1_To)-MAX($O188,R1_From))+Rate_2*MAX(0,MIN($O189,R2_To)-MAX($O188,R2_From))+Rate_3*MAX(0,MIN($O189,R3_To)-MAX($O188,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I189&lt;=0,0,$S188*('Engine'!$B$8*MAX(0,MIN($O189,'Engine'!$B$3)-MAX($O188,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O189,'Engine'!$B$5)-MAX($O188,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O189,'Engine'!$B$7)-MAX($O188,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K189" s="41">
@@ -9962,7 +9945,7 @@
         <v/>
       </c>
       <c r="N189" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O189&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O189&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O189" s="25">
@@ -9993,7 +9976,7 @@
         <v/>
       </c>
       <c r="H190" s="42">
-        <f>IF($I190&lt;=0,"",(Rate_1*MAX(0,MIN($O190,R1_To)-MAX($O189,R1_From))+Rate_2*MAX(0,MIN($O190,R2_To)-MAX($O189,R2_From))+Rate_3*MAX(0,MIN($O190,R3_To)-MAX($O189,R3_From)))/100/Day_Basis/$I190*Day_Basis*100)</f>
+        <f>IF($I190&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O190,'Engine'!$B$3)-MAX($O189,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O190,'Engine'!$B$5)-MAX($O189,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O190,'Engine'!$B$7)-MAX($O189,'Engine'!$B$6)))/100/$H$8/$I190*$H$8*100)</f>
         <v/>
       </c>
       <c r="I190" s="43">
@@ -10001,7 +9984,7 @@
         <v/>
       </c>
       <c r="J190" s="41">
-        <f>IF($I190&lt;=0,0,$S189*(Rate_1*MAX(0,MIN($O190,R1_To)-MAX($O189,R1_From))+Rate_2*MAX(0,MIN($O190,R2_To)-MAX($O189,R2_From))+Rate_3*MAX(0,MIN($O190,R3_To)-MAX($O189,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I190&lt;=0,0,$S189*('Engine'!$B$8*MAX(0,MIN($O190,'Engine'!$B$3)-MAX($O189,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O190,'Engine'!$B$5)-MAX($O189,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O190,'Engine'!$B$7)-MAX($O189,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K190" s="41">
@@ -10014,7 +9997,7 @@
         <v/>
       </c>
       <c r="N190" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O190&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O190&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O190" s="25">
@@ -10045,7 +10028,7 @@
         <v/>
       </c>
       <c r="H191" s="42">
-        <f>IF($I191&lt;=0,"",(Rate_1*MAX(0,MIN($O191,R1_To)-MAX($O190,R1_From))+Rate_2*MAX(0,MIN($O191,R2_To)-MAX($O190,R2_From))+Rate_3*MAX(0,MIN($O191,R3_To)-MAX($O190,R3_From)))/100/Day_Basis/$I191*Day_Basis*100)</f>
+        <f>IF($I191&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O191,'Engine'!$B$3)-MAX($O190,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O191,'Engine'!$B$5)-MAX($O190,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O191,'Engine'!$B$7)-MAX($O190,'Engine'!$B$6)))/100/$H$8/$I191*$H$8*100)</f>
         <v/>
       </c>
       <c r="I191" s="43">
@@ -10053,7 +10036,7 @@
         <v/>
       </c>
       <c r="J191" s="41">
-        <f>IF($I191&lt;=0,0,$S190*(Rate_1*MAX(0,MIN($O191,R1_To)-MAX($O190,R1_From))+Rate_2*MAX(0,MIN($O191,R2_To)-MAX($O190,R2_From))+Rate_3*MAX(0,MIN($O191,R3_To)-MAX($O190,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I191&lt;=0,0,$S190*('Engine'!$B$8*MAX(0,MIN($O191,'Engine'!$B$3)-MAX($O190,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O191,'Engine'!$B$5)-MAX($O190,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O191,'Engine'!$B$7)-MAX($O190,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K191" s="41">
@@ -10066,7 +10049,7 @@
         <v/>
       </c>
       <c r="N191" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O191&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O191&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O191" s="25">
@@ -10097,7 +10080,7 @@
         <v/>
       </c>
       <c r="H192" s="42">
-        <f>IF($I192&lt;=0,"",(Rate_1*MAX(0,MIN($O192,R1_To)-MAX($O191,R1_From))+Rate_2*MAX(0,MIN($O192,R2_To)-MAX($O191,R2_From))+Rate_3*MAX(0,MIN($O192,R3_To)-MAX($O191,R3_From)))/100/Day_Basis/$I192*Day_Basis*100)</f>
+        <f>IF($I192&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O192,'Engine'!$B$3)-MAX($O191,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O192,'Engine'!$B$5)-MAX($O191,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O192,'Engine'!$B$7)-MAX($O191,'Engine'!$B$6)))/100/$H$8/$I192*$H$8*100)</f>
         <v/>
       </c>
       <c r="I192" s="43">
@@ -10105,7 +10088,7 @@
         <v/>
       </c>
       <c r="J192" s="41">
-        <f>IF($I192&lt;=0,0,$S191*(Rate_1*MAX(0,MIN($O192,R1_To)-MAX($O191,R1_From))+Rate_2*MAX(0,MIN($O192,R2_To)-MAX($O191,R2_From))+Rate_3*MAX(0,MIN($O192,R3_To)-MAX($O191,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I192&lt;=0,0,$S191*('Engine'!$B$8*MAX(0,MIN($O192,'Engine'!$B$3)-MAX($O191,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O192,'Engine'!$B$5)-MAX($O191,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O192,'Engine'!$B$7)-MAX($O191,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K192" s="41">
@@ -10118,7 +10101,7 @@
         <v/>
       </c>
       <c r="N192" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O192&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O192&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O192" s="25">
@@ -10149,7 +10132,7 @@
         <v/>
       </c>
       <c r="H193" s="42">
-        <f>IF($I193&lt;=0,"",(Rate_1*MAX(0,MIN($O193,R1_To)-MAX($O192,R1_From))+Rate_2*MAX(0,MIN($O193,R2_To)-MAX($O192,R2_From))+Rate_3*MAX(0,MIN($O193,R3_To)-MAX($O192,R3_From)))/100/Day_Basis/$I193*Day_Basis*100)</f>
+        <f>IF($I193&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O193,'Engine'!$B$3)-MAX($O192,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O193,'Engine'!$B$5)-MAX($O192,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O193,'Engine'!$B$7)-MAX($O192,'Engine'!$B$6)))/100/$H$8/$I193*$H$8*100)</f>
         <v/>
       </c>
       <c r="I193" s="43">
@@ -10157,7 +10140,7 @@
         <v/>
       </c>
       <c r="J193" s="41">
-        <f>IF($I193&lt;=0,0,$S192*(Rate_1*MAX(0,MIN($O193,R1_To)-MAX($O192,R1_From))+Rate_2*MAX(0,MIN($O193,R2_To)-MAX($O192,R2_From))+Rate_3*MAX(0,MIN($O193,R3_To)-MAX($O192,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I193&lt;=0,0,$S192*('Engine'!$B$8*MAX(0,MIN($O193,'Engine'!$B$3)-MAX($O192,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O193,'Engine'!$B$5)-MAX($O192,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O193,'Engine'!$B$7)-MAX($O192,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K193" s="41">
@@ -10170,7 +10153,7 @@
         <v/>
       </c>
       <c r="N193" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O193&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O193&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O193" s="25">
@@ -10201,7 +10184,7 @@
         <v/>
       </c>
       <c r="H194" s="42">
-        <f>IF($I194&lt;=0,"",(Rate_1*MAX(0,MIN($O194,R1_To)-MAX($O193,R1_From))+Rate_2*MAX(0,MIN($O194,R2_To)-MAX($O193,R2_From))+Rate_3*MAX(0,MIN($O194,R3_To)-MAX($O193,R3_From)))/100/Day_Basis/$I194*Day_Basis*100)</f>
+        <f>IF($I194&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O194,'Engine'!$B$3)-MAX($O193,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O194,'Engine'!$B$5)-MAX($O193,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O194,'Engine'!$B$7)-MAX($O193,'Engine'!$B$6)))/100/$H$8/$I194*$H$8*100)</f>
         <v/>
       </c>
       <c r="I194" s="43">
@@ -10209,7 +10192,7 @@
         <v/>
       </c>
       <c r="J194" s="41">
-        <f>IF($I194&lt;=0,0,$S193*(Rate_1*MAX(0,MIN($O194,R1_To)-MAX($O193,R1_From))+Rate_2*MAX(0,MIN($O194,R2_To)-MAX($O193,R2_From))+Rate_3*MAX(0,MIN($O194,R3_To)-MAX($O193,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I194&lt;=0,0,$S193*('Engine'!$B$8*MAX(0,MIN($O194,'Engine'!$B$3)-MAX($O193,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O194,'Engine'!$B$5)-MAX($O193,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O194,'Engine'!$B$7)-MAX($O193,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K194" s="41">
@@ -10222,7 +10205,7 @@
         <v/>
       </c>
       <c r="N194" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O194&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O194&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O194" s="25">
@@ -10263,7 +10246,7 @@
         <v/>
       </c>
       <c r="H195" s="51">
-        <f>IF($I195&lt;=0,"",(Rate_1*MAX(0,MIN($O195,R1_To)-MAX($O194,R1_From))+Rate_2*MAX(0,MIN($O195,R2_To)-MAX($O194,R2_From))+Rate_3*MAX(0,MIN($O195,R3_To)-MAX($O194,R3_From)))/100/Day_Basis/$I195*Day_Basis*100)</f>
+        <f>IF($I195&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O195,'Engine'!$B$3)-MAX($O194,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O195,'Engine'!$B$5)-MAX($O194,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O195,'Engine'!$B$7)-MAX($O194,'Engine'!$B$6)))/100/$H$8/$I195*$H$8*100)</f>
         <v/>
       </c>
       <c r="I195" s="52">
@@ -10271,7 +10254,7 @@
         <v/>
       </c>
       <c r="J195" s="53">
-        <f>IF($I195&lt;=0,0,$S194*(Rate_1*MAX(0,MIN($O195,R1_To)-MAX($O194,R1_From))+Rate_2*MAX(0,MIN($O195,R2_To)-MAX($O194,R2_From))+Rate_3*MAX(0,MIN($O195,R3_To)-MAX($O194,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I195&lt;=0,0,$S194*('Engine'!$B$8*MAX(0,MIN($O195,'Engine'!$B$3)-MAX($O194,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O195,'Engine'!$B$5)-MAX($O194,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O195,'Engine'!$B$7)-MAX($O194,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K195" s="53" t="n">
@@ -10283,7 +10266,7 @@
         <v/>
       </c>
       <c r="N195" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O195&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O195&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O195" s="25">
@@ -10300,7 +10283,7 @@
     </row>
     <row r="196" ht="18" customHeight="1">
       <c r="A196" s="24">
-        <f>IF($P$196=0,"QUARTER 15          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 15          "&amp;TEXT($P$196,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$196,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$196&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$196)</f>
+        <f>IF($P$196=0,"QUARTER 15          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 15          "&amp;TEXT($P$196,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$196,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$196&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$196)</f>
         <v/>
       </c>
       <c r="O196" s="25">
@@ -10358,7 +10341,7 @@
         <v/>
       </c>
       <c r="N197" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$197&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$197&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O197" s="25">
@@ -10388,7 +10371,7 @@
         <v/>
       </c>
       <c r="H198" s="42">
-        <f>IF($I198&lt;=0,"",(Rate_1*MAX(0,MIN($O198,R1_To)-MAX($O197,R1_From))+Rate_2*MAX(0,MIN($O198,R2_To)-MAX($O197,R2_From))+Rate_3*MAX(0,MIN($O198,R3_To)-MAX($O197,R3_From)))/100/Day_Basis/$I198*Day_Basis*100)</f>
+        <f>IF($I198&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O198,'Engine'!$B$3)-MAX($O197,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O198,'Engine'!$B$5)-MAX($O197,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O198,'Engine'!$B$7)-MAX($O197,'Engine'!$B$6)))/100/$H$8/$I198*$H$8*100)</f>
         <v/>
       </c>
       <c r="I198" s="43">
@@ -10396,7 +10379,7 @@
         <v/>
       </c>
       <c r="J198" s="41">
-        <f>IF($I198&lt;=0,0,$S197*(Rate_1*MAX(0,MIN($O198,R1_To)-MAX($O197,R1_From))+Rate_2*MAX(0,MIN($O198,R2_To)-MAX($O197,R2_From))+Rate_3*MAX(0,MIN($O198,R3_To)-MAX($O197,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I198&lt;=0,0,$S197*('Engine'!$B$8*MAX(0,MIN($O198,'Engine'!$B$3)-MAX($O197,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O198,'Engine'!$B$5)-MAX($O197,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O198,'Engine'!$B$7)-MAX($O197,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K198" s="41">
@@ -10409,7 +10392,7 @@
         <v/>
       </c>
       <c r="N198" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O198&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O198&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O198" s="25">
@@ -10440,7 +10423,7 @@
         <v/>
       </c>
       <c r="H199" s="42">
-        <f>IF($I199&lt;=0,"",(Rate_1*MAX(0,MIN($O199,R1_To)-MAX($O198,R1_From))+Rate_2*MAX(0,MIN($O199,R2_To)-MAX($O198,R2_From))+Rate_3*MAX(0,MIN($O199,R3_To)-MAX($O198,R3_From)))/100/Day_Basis/$I199*Day_Basis*100)</f>
+        <f>IF($I199&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O199,'Engine'!$B$3)-MAX($O198,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O199,'Engine'!$B$5)-MAX($O198,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O199,'Engine'!$B$7)-MAX($O198,'Engine'!$B$6)))/100/$H$8/$I199*$H$8*100)</f>
         <v/>
       </c>
       <c r="I199" s="43">
@@ -10448,7 +10431,7 @@
         <v/>
       </c>
       <c r="J199" s="41">
-        <f>IF($I199&lt;=0,0,$S198*(Rate_1*MAX(0,MIN($O199,R1_To)-MAX($O198,R1_From))+Rate_2*MAX(0,MIN($O199,R2_To)-MAX($O198,R2_From))+Rate_3*MAX(0,MIN($O199,R3_To)-MAX($O198,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I199&lt;=0,0,$S198*('Engine'!$B$8*MAX(0,MIN($O199,'Engine'!$B$3)-MAX($O198,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O199,'Engine'!$B$5)-MAX($O198,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O199,'Engine'!$B$7)-MAX($O198,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K199" s="41">
@@ -10461,7 +10444,7 @@
         <v/>
       </c>
       <c r="N199" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O199&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O199&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O199" s="25">
@@ -10492,7 +10475,7 @@
         <v/>
       </c>
       <c r="H200" s="42">
-        <f>IF($I200&lt;=0,"",(Rate_1*MAX(0,MIN($O200,R1_To)-MAX($O199,R1_From))+Rate_2*MAX(0,MIN($O200,R2_To)-MAX($O199,R2_From))+Rate_3*MAX(0,MIN($O200,R3_To)-MAX($O199,R3_From)))/100/Day_Basis/$I200*Day_Basis*100)</f>
+        <f>IF($I200&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O200,'Engine'!$B$3)-MAX($O199,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O200,'Engine'!$B$5)-MAX($O199,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O200,'Engine'!$B$7)-MAX($O199,'Engine'!$B$6)))/100/$H$8/$I200*$H$8*100)</f>
         <v/>
       </c>
       <c r="I200" s="43">
@@ -10500,7 +10483,7 @@
         <v/>
       </c>
       <c r="J200" s="41">
-        <f>IF($I200&lt;=0,0,$S199*(Rate_1*MAX(0,MIN($O200,R1_To)-MAX($O199,R1_From))+Rate_2*MAX(0,MIN($O200,R2_To)-MAX($O199,R2_From))+Rate_3*MAX(0,MIN($O200,R3_To)-MAX($O199,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I200&lt;=0,0,$S199*('Engine'!$B$8*MAX(0,MIN($O200,'Engine'!$B$3)-MAX($O199,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O200,'Engine'!$B$5)-MAX($O199,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O200,'Engine'!$B$7)-MAX($O199,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K200" s="41">
@@ -10513,7 +10496,7 @@
         <v/>
       </c>
       <c r="N200" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O200&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O200&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O200" s="25">
@@ -10544,7 +10527,7 @@
         <v/>
       </c>
       <c r="H201" s="42">
-        <f>IF($I201&lt;=0,"",(Rate_1*MAX(0,MIN($O201,R1_To)-MAX($O200,R1_From))+Rate_2*MAX(0,MIN($O201,R2_To)-MAX($O200,R2_From))+Rate_3*MAX(0,MIN($O201,R3_To)-MAX($O200,R3_From)))/100/Day_Basis/$I201*Day_Basis*100)</f>
+        <f>IF($I201&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O201,'Engine'!$B$3)-MAX($O200,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O201,'Engine'!$B$5)-MAX($O200,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O201,'Engine'!$B$7)-MAX($O200,'Engine'!$B$6)))/100/$H$8/$I201*$H$8*100)</f>
         <v/>
       </c>
       <c r="I201" s="43">
@@ -10552,7 +10535,7 @@
         <v/>
       </c>
       <c r="J201" s="41">
-        <f>IF($I201&lt;=0,0,$S200*(Rate_1*MAX(0,MIN($O201,R1_To)-MAX($O200,R1_From))+Rate_2*MAX(0,MIN($O201,R2_To)-MAX($O200,R2_From))+Rate_3*MAX(0,MIN($O201,R3_To)-MAX($O200,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I201&lt;=0,0,$S200*('Engine'!$B$8*MAX(0,MIN($O201,'Engine'!$B$3)-MAX($O200,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O201,'Engine'!$B$5)-MAX($O200,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O201,'Engine'!$B$7)-MAX($O200,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K201" s="41">
@@ -10565,7 +10548,7 @@
         <v/>
       </c>
       <c r="N201" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O201&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O201&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O201" s="25">
@@ -10596,7 +10579,7 @@
         <v/>
       </c>
       <c r="H202" s="42">
-        <f>IF($I202&lt;=0,"",(Rate_1*MAX(0,MIN($O202,R1_To)-MAX($O201,R1_From))+Rate_2*MAX(0,MIN($O202,R2_To)-MAX($O201,R2_From))+Rate_3*MAX(0,MIN($O202,R3_To)-MAX($O201,R3_From)))/100/Day_Basis/$I202*Day_Basis*100)</f>
+        <f>IF($I202&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O202,'Engine'!$B$3)-MAX($O201,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O202,'Engine'!$B$5)-MAX($O201,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O202,'Engine'!$B$7)-MAX($O201,'Engine'!$B$6)))/100/$H$8/$I202*$H$8*100)</f>
         <v/>
       </c>
       <c r="I202" s="43">
@@ -10604,7 +10587,7 @@
         <v/>
       </c>
       <c r="J202" s="41">
-        <f>IF($I202&lt;=0,0,$S201*(Rate_1*MAX(0,MIN($O202,R1_To)-MAX($O201,R1_From))+Rate_2*MAX(0,MIN($O202,R2_To)-MAX($O201,R2_From))+Rate_3*MAX(0,MIN($O202,R3_To)-MAX($O201,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I202&lt;=0,0,$S201*('Engine'!$B$8*MAX(0,MIN($O202,'Engine'!$B$3)-MAX($O201,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O202,'Engine'!$B$5)-MAX($O201,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O202,'Engine'!$B$7)-MAX($O201,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K202" s="41">
@@ -10617,7 +10600,7 @@
         <v/>
       </c>
       <c r="N202" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O202&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O202&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O202" s="25">
@@ -10648,7 +10631,7 @@
         <v/>
       </c>
       <c r="H203" s="42">
-        <f>IF($I203&lt;=0,"",(Rate_1*MAX(0,MIN($O203,R1_To)-MAX($O202,R1_From))+Rate_2*MAX(0,MIN($O203,R2_To)-MAX($O202,R2_From))+Rate_3*MAX(0,MIN($O203,R3_To)-MAX($O202,R3_From)))/100/Day_Basis/$I203*Day_Basis*100)</f>
+        <f>IF($I203&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O203,'Engine'!$B$3)-MAX($O202,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O203,'Engine'!$B$5)-MAX($O202,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O203,'Engine'!$B$7)-MAX($O202,'Engine'!$B$6)))/100/$H$8/$I203*$H$8*100)</f>
         <v/>
       </c>
       <c r="I203" s="43">
@@ -10656,7 +10639,7 @@
         <v/>
       </c>
       <c r="J203" s="41">
-        <f>IF($I203&lt;=0,0,$S202*(Rate_1*MAX(0,MIN($O203,R1_To)-MAX($O202,R1_From))+Rate_2*MAX(0,MIN($O203,R2_To)-MAX($O202,R2_From))+Rate_3*MAX(0,MIN($O203,R3_To)-MAX($O202,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I203&lt;=0,0,$S202*('Engine'!$B$8*MAX(0,MIN($O203,'Engine'!$B$3)-MAX($O202,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O203,'Engine'!$B$5)-MAX($O202,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O203,'Engine'!$B$7)-MAX($O202,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K203" s="41">
@@ -10669,7 +10652,7 @@
         <v/>
       </c>
       <c r="N203" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O203&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O203&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O203" s="25">
@@ -10700,7 +10683,7 @@
         <v/>
       </c>
       <c r="H204" s="42">
-        <f>IF($I204&lt;=0,"",(Rate_1*MAX(0,MIN($O204,R1_To)-MAX($O203,R1_From))+Rate_2*MAX(0,MIN($O204,R2_To)-MAX($O203,R2_From))+Rate_3*MAX(0,MIN($O204,R3_To)-MAX($O203,R3_From)))/100/Day_Basis/$I204*Day_Basis*100)</f>
+        <f>IF($I204&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O204,'Engine'!$B$3)-MAX($O203,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O204,'Engine'!$B$5)-MAX($O203,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O204,'Engine'!$B$7)-MAX($O203,'Engine'!$B$6)))/100/$H$8/$I204*$H$8*100)</f>
         <v/>
       </c>
       <c r="I204" s="43">
@@ -10708,7 +10691,7 @@
         <v/>
       </c>
       <c r="J204" s="41">
-        <f>IF($I204&lt;=0,0,$S203*(Rate_1*MAX(0,MIN($O204,R1_To)-MAX($O203,R1_From))+Rate_2*MAX(0,MIN($O204,R2_To)-MAX($O203,R2_From))+Rate_3*MAX(0,MIN($O204,R3_To)-MAX($O203,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I204&lt;=0,0,$S203*('Engine'!$B$8*MAX(0,MIN($O204,'Engine'!$B$3)-MAX($O203,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O204,'Engine'!$B$5)-MAX($O203,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O204,'Engine'!$B$7)-MAX($O203,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K204" s="41">
@@ -10721,7 +10704,7 @@
         <v/>
       </c>
       <c r="N204" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O204&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O204&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O204" s="25">
@@ -10752,7 +10735,7 @@
         <v/>
       </c>
       <c r="H205" s="42">
-        <f>IF($I205&lt;=0,"",(Rate_1*MAX(0,MIN($O205,R1_To)-MAX($O204,R1_From))+Rate_2*MAX(0,MIN($O205,R2_To)-MAX($O204,R2_From))+Rate_3*MAX(0,MIN($O205,R3_To)-MAX($O204,R3_From)))/100/Day_Basis/$I205*Day_Basis*100)</f>
+        <f>IF($I205&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O205,'Engine'!$B$3)-MAX($O204,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O205,'Engine'!$B$5)-MAX($O204,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O205,'Engine'!$B$7)-MAX($O204,'Engine'!$B$6)))/100/$H$8/$I205*$H$8*100)</f>
         <v/>
       </c>
       <c r="I205" s="43">
@@ -10760,7 +10743,7 @@
         <v/>
       </c>
       <c r="J205" s="41">
-        <f>IF($I205&lt;=0,0,$S204*(Rate_1*MAX(0,MIN($O205,R1_To)-MAX($O204,R1_From))+Rate_2*MAX(0,MIN($O205,R2_To)-MAX($O204,R2_From))+Rate_3*MAX(0,MIN($O205,R3_To)-MAX($O204,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I205&lt;=0,0,$S204*('Engine'!$B$8*MAX(0,MIN($O205,'Engine'!$B$3)-MAX($O204,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O205,'Engine'!$B$5)-MAX($O204,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O205,'Engine'!$B$7)-MAX($O204,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K205" s="41">
@@ -10773,7 +10756,7 @@
         <v/>
       </c>
       <c r="N205" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O205&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O205&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O205" s="25">
@@ -10804,7 +10787,7 @@
         <v/>
       </c>
       <c r="H206" s="42">
-        <f>IF($I206&lt;=0,"",(Rate_1*MAX(0,MIN($O206,R1_To)-MAX($O205,R1_From))+Rate_2*MAX(0,MIN($O206,R2_To)-MAX($O205,R2_From))+Rate_3*MAX(0,MIN($O206,R3_To)-MAX($O205,R3_From)))/100/Day_Basis/$I206*Day_Basis*100)</f>
+        <f>IF($I206&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O206,'Engine'!$B$3)-MAX($O205,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O206,'Engine'!$B$5)-MAX($O205,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O206,'Engine'!$B$7)-MAX($O205,'Engine'!$B$6)))/100/$H$8/$I206*$H$8*100)</f>
         <v/>
       </c>
       <c r="I206" s="43">
@@ -10812,7 +10795,7 @@
         <v/>
       </c>
       <c r="J206" s="41">
-        <f>IF($I206&lt;=0,0,$S205*(Rate_1*MAX(0,MIN($O206,R1_To)-MAX($O205,R1_From))+Rate_2*MAX(0,MIN($O206,R2_To)-MAX($O205,R2_From))+Rate_3*MAX(0,MIN($O206,R3_To)-MAX($O205,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I206&lt;=0,0,$S205*('Engine'!$B$8*MAX(0,MIN($O206,'Engine'!$B$3)-MAX($O205,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O206,'Engine'!$B$5)-MAX($O205,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O206,'Engine'!$B$7)-MAX($O205,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K206" s="41">
@@ -10825,7 +10808,7 @@
         <v/>
       </c>
       <c r="N206" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O206&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O206&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O206" s="25">
@@ -10856,7 +10839,7 @@
         <v/>
       </c>
       <c r="H207" s="42">
-        <f>IF($I207&lt;=0,"",(Rate_1*MAX(0,MIN($O207,R1_To)-MAX($O206,R1_From))+Rate_2*MAX(0,MIN($O207,R2_To)-MAX($O206,R2_From))+Rate_3*MAX(0,MIN($O207,R3_To)-MAX($O206,R3_From)))/100/Day_Basis/$I207*Day_Basis*100)</f>
+        <f>IF($I207&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O207,'Engine'!$B$3)-MAX($O206,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O207,'Engine'!$B$5)-MAX($O206,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O207,'Engine'!$B$7)-MAX($O206,'Engine'!$B$6)))/100/$H$8/$I207*$H$8*100)</f>
         <v/>
       </c>
       <c r="I207" s="43">
@@ -10864,7 +10847,7 @@
         <v/>
       </c>
       <c r="J207" s="41">
-        <f>IF($I207&lt;=0,0,$S206*(Rate_1*MAX(0,MIN($O207,R1_To)-MAX($O206,R1_From))+Rate_2*MAX(0,MIN($O207,R2_To)-MAX($O206,R2_From))+Rate_3*MAX(0,MIN($O207,R3_To)-MAX($O206,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I207&lt;=0,0,$S206*('Engine'!$B$8*MAX(0,MIN($O207,'Engine'!$B$3)-MAX($O206,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O207,'Engine'!$B$5)-MAX($O206,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O207,'Engine'!$B$7)-MAX($O206,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K207" s="41">
@@ -10877,7 +10860,7 @@
         <v/>
       </c>
       <c r="N207" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O207&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O207&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O207" s="25">
@@ -10918,7 +10901,7 @@
         <v/>
       </c>
       <c r="H208" s="51">
-        <f>IF($I208&lt;=0,"",(Rate_1*MAX(0,MIN($O208,R1_To)-MAX($O207,R1_From))+Rate_2*MAX(0,MIN($O208,R2_To)-MAX($O207,R2_From))+Rate_3*MAX(0,MIN($O208,R3_To)-MAX($O207,R3_From)))/100/Day_Basis/$I208*Day_Basis*100)</f>
+        <f>IF($I208&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O208,'Engine'!$B$3)-MAX($O207,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O208,'Engine'!$B$5)-MAX($O207,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O208,'Engine'!$B$7)-MAX($O207,'Engine'!$B$6)))/100/$H$8/$I208*$H$8*100)</f>
         <v/>
       </c>
       <c r="I208" s="52">
@@ -10926,7 +10909,7 @@
         <v/>
       </c>
       <c r="J208" s="53">
-        <f>IF($I208&lt;=0,0,$S207*(Rate_1*MAX(0,MIN($O208,R1_To)-MAX($O207,R1_From))+Rate_2*MAX(0,MIN($O208,R2_To)-MAX($O207,R2_From))+Rate_3*MAX(0,MIN($O208,R3_To)-MAX($O207,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I208&lt;=0,0,$S207*('Engine'!$B$8*MAX(0,MIN($O208,'Engine'!$B$3)-MAX($O207,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O208,'Engine'!$B$5)-MAX($O207,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O208,'Engine'!$B$7)-MAX($O207,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K208" s="53" t="n">
@@ -10938,7 +10921,7 @@
         <v/>
       </c>
       <c r="N208" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O208&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O208&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O208" s="25">
@@ -10955,7 +10938,7 @@
     </row>
     <row r="209" ht="18" customHeight="1">
       <c r="A209" s="24">
-        <f>IF($P$209=0,"QUARTER 16          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 16          "&amp;TEXT($P$209,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$209,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$209&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$209)</f>
+        <f>IF($P$209=0,"QUARTER 16          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 16          "&amp;TEXT($P$209,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$209,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$209&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$209)</f>
         <v/>
       </c>
       <c r="O209" s="25">
@@ -11013,7 +10996,7 @@
         <v/>
       </c>
       <c r="N210" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$210&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$210&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O210" s="25">
@@ -11043,7 +11026,7 @@
         <v/>
       </c>
       <c r="H211" s="42">
-        <f>IF($I211&lt;=0,"",(Rate_1*MAX(0,MIN($O211,R1_To)-MAX($O210,R1_From))+Rate_2*MAX(0,MIN($O211,R2_To)-MAX($O210,R2_From))+Rate_3*MAX(0,MIN($O211,R3_To)-MAX($O210,R3_From)))/100/Day_Basis/$I211*Day_Basis*100)</f>
+        <f>IF($I211&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O211,'Engine'!$B$3)-MAX($O210,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O211,'Engine'!$B$5)-MAX($O210,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O211,'Engine'!$B$7)-MAX($O210,'Engine'!$B$6)))/100/$H$8/$I211*$H$8*100)</f>
         <v/>
       </c>
       <c r="I211" s="43">
@@ -11051,7 +11034,7 @@
         <v/>
       </c>
       <c r="J211" s="41">
-        <f>IF($I211&lt;=0,0,$S210*(Rate_1*MAX(0,MIN($O211,R1_To)-MAX($O210,R1_From))+Rate_2*MAX(0,MIN($O211,R2_To)-MAX($O210,R2_From))+Rate_3*MAX(0,MIN($O211,R3_To)-MAX($O210,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I211&lt;=0,0,$S210*('Engine'!$B$8*MAX(0,MIN($O211,'Engine'!$B$3)-MAX($O210,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O211,'Engine'!$B$5)-MAX($O210,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O211,'Engine'!$B$7)-MAX($O210,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K211" s="41">
@@ -11064,7 +11047,7 @@
         <v/>
       </c>
       <c r="N211" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O211&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O211&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O211" s="25">
@@ -11095,7 +11078,7 @@
         <v/>
       </c>
       <c r="H212" s="42">
-        <f>IF($I212&lt;=0,"",(Rate_1*MAX(0,MIN($O212,R1_To)-MAX($O211,R1_From))+Rate_2*MAX(0,MIN($O212,R2_To)-MAX($O211,R2_From))+Rate_3*MAX(0,MIN($O212,R3_To)-MAX($O211,R3_From)))/100/Day_Basis/$I212*Day_Basis*100)</f>
+        <f>IF($I212&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O212,'Engine'!$B$3)-MAX($O211,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O212,'Engine'!$B$5)-MAX($O211,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O212,'Engine'!$B$7)-MAX($O211,'Engine'!$B$6)))/100/$H$8/$I212*$H$8*100)</f>
         <v/>
       </c>
       <c r="I212" s="43">
@@ -11103,7 +11086,7 @@
         <v/>
       </c>
       <c r="J212" s="41">
-        <f>IF($I212&lt;=0,0,$S211*(Rate_1*MAX(0,MIN($O212,R1_To)-MAX($O211,R1_From))+Rate_2*MAX(0,MIN($O212,R2_To)-MAX($O211,R2_From))+Rate_3*MAX(0,MIN($O212,R3_To)-MAX($O211,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I212&lt;=0,0,$S211*('Engine'!$B$8*MAX(0,MIN($O212,'Engine'!$B$3)-MAX($O211,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O212,'Engine'!$B$5)-MAX($O211,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O212,'Engine'!$B$7)-MAX($O211,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K212" s="41">
@@ -11116,7 +11099,7 @@
         <v/>
       </c>
       <c r="N212" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O212&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O212&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O212" s="25">
@@ -11147,7 +11130,7 @@
         <v/>
       </c>
       <c r="H213" s="42">
-        <f>IF($I213&lt;=0,"",(Rate_1*MAX(0,MIN($O213,R1_To)-MAX($O212,R1_From))+Rate_2*MAX(0,MIN($O213,R2_To)-MAX($O212,R2_From))+Rate_3*MAX(0,MIN($O213,R3_To)-MAX($O212,R3_From)))/100/Day_Basis/$I213*Day_Basis*100)</f>
+        <f>IF($I213&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O213,'Engine'!$B$3)-MAX($O212,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O213,'Engine'!$B$5)-MAX($O212,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O213,'Engine'!$B$7)-MAX($O212,'Engine'!$B$6)))/100/$H$8/$I213*$H$8*100)</f>
         <v/>
       </c>
       <c r="I213" s="43">
@@ -11155,7 +11138,7 @@
         <v/>
       </c>
       <c r="J213" s="41">
-        <f>IF($I213&lt;=0,0,$S212*(Rate_1*MAX(0,MIN($O213,R1_To)-MAX($O212,R1_From))+Rate_2*MAX(0,MIN($O213,R2_To)-MAX($O212,R2_From))+Rate_3*MAX(0,MIN($O213,R3_To)-MAX($O212,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I213&lt;=0,0,$S212*('Engine'!$B$8*MAX(0,MIN($O213,'Engine'!$B$3)-MAX($O212,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O213,'Engine'!$B$5)-MAX($O212,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O213,'Engine'!$B$7)-MAX($O212,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K213" s="41">
@@ -11168,7 +11151,7 @@
         <v/>
       </c>
       <c r="N213" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O213&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O213&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O213" s="25">
@@ -11199,7 +11182,7 @@
         <v/>
       </c>
       <c r="H214" s="42">
-        <f>IF($I214&lt;=0,"",(Rate_1*MAX(0,MIN($O214,R1_To)-MAX($O213,R1_From))+Rate_2*MAX(0,MIN($O214,R2_To)-MAX($O213,R2_From))+Rate_3*MAX(0,MIN($O214,R3_To)-MAX($O213,R3_From)))/100/Day_Basis/$I214*Day_Basis*100)</f>
+        <f>IF($I214&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O214,'Engine'!$B$3)-MAX($O213,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O214,'Engine'!$B$5)-MAX($O213,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O214,'Engine'!$B$7)-MAX($O213,'Engine'!$B$6)))/100/$H$8/$I214*$H$8*100)</f>
         <v/>
       </c>
       <c r="I214" s="43">
@@ -11207,7 +11190,7 @@
         <v/>
       </c>
       <c r="J214" s="41">
-        <f>IF($I214&lt;=0,0,$S213*(Rate_1*MAX(0,MIN($O214,R1_To)-MAX($O213,R1_From))+Rate_2*MAX(0,MIN($O214,R2_To)-MAX($O213,R2_From))+Rate_3*MAX(0,MIN($O214,R3_To)-MAX($O213,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I214&lt;=0,0,$S213*('Engine'!$B$8*MAX(0,MIN($O214,'Engine'!$B$3)-MAX($O213,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O214,'Engine'!$B$5)-MAX($O213,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O214,'Engine'!$B$7)-MAX($O213,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K214" s="41">
@@ -11220,7 +11203,7 @@
         <v/>
       </c>
       <c r="N214" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O214&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O214&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O214" s="25">
@@ -11251,7 +11234,7 @@
         <v/>
       </c>
       <c r="H215" s="42">
-        <f>IF($I215&lt;=0,"",(Rate_1*MAX(0,MIN($O215,R1_To)-MAX($O214,R1_From))+Rate_2*MAX(0,MIN($O215,R2_To)-MAX($O214,R2_From))+Rate_3*MAX(0,MIN($O215,R3_To)-MAX($O214,R3_From)))/100/Day_Basis/$I215*Day_Basis*100)</f>
+        <f>IF($I215&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O215,'Engine'!$B$3)-MAX($O214,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O215,'Engine'!$B$5)-MAX($O214,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O215,'Engine'!$B$7)-MAX($O214,'Engine'!$B$6)))/100/$H$8/$I215*$H$8*100)</f>
         <v/>
       </c>
       <c r="I215" s="43">
@@ -11259,7 +11242,7 @@
         <v/>
       </c>
       <c r="J215" s="41">
-        <f>IF($I215&lt;=0,0,$S214*(Rate_1*MAX(0,MIN($O215,R1_To)-MAX($O214,R1_From))+Rate_2*MAX(0,MIN($O215,R2_To)-MAX($O214,R2_From))+Rate_3*MAX(0,MIN($O215,R3_To)-MAX($O214,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I215&lt;=0,0,$S214*('Engine'!$B$8*MAX(0,MIN($O215,'Engine'!$B$3)-MAX($O214,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O215,'Engine'!$B$5)-MAX($O214,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O215,'Engine'!$B$7)-MAX($O214,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K215" s="41">
@@ -11272,7 +11255,7 @@
         <v/>
       </c>
       <c r="N215" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O215&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O215&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O215" s="25">
@@ -11303,7 +11286,7 @@
         <v/>
       </c>
       <c r="H216" s="42">
-        <f>IF($I216&lt;=0,"",(Rate_1*MAX(0,MIN($O216,R1_To)-MAX($O215,R1_From))+Rate_2*MAX(0,MIN($O216,R2_To)-MAX($O215,R2_From))+Rate_3*MAX(0,MIN($O216,R3_To)-MAX($O215,R3_From)))/100/Day_Basis/$I216*Day_Basis*100)</f>
+        <f>IF($I216&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O216,'Engine'!$B$3)-MAX($O215,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O216,'Engine'!$B$5)-MAX($O215,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O216,'Engine'!$B$7)-MAX($O215,'Engine'!$B$6)))/100/$H$8/$I216*$H$8*100)</f>
         <v/>
       </c>
       <c r="I216" s="43">
@@ -11311,7 +11294,7 @@
         <v/>
       </c>
       <c r="J216" s="41">
-        <f>IF($I216&lt;=0,0,$S215*(Rate_1*MAX(0,MIN($O216,R1_To)-MAX($O215,R1_From))+Rate_2*MAX(0,MIN($O216,R2_To)-MAX($O215,R2_From))+Rate_3*MAX(0,MIN($O216,R3_To)-MAX($O215,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I216&lt;=0,0,$S215*('Engine'!$B$8*MAX(0,MIN($O216,'Engine'!$B$3)-MAX($O215,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O216,'Engine'!$B$5)-MAX($O215,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O216,'Engine'!$B$7)-MAX($O215,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K216" s="41">
@@ -11324,7 +11307,7 @@
         <v/>
       </c>
       <c r="N216" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O216&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O216&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O216" s="25">
@@ -11355,7 +11338,7 @@
         <v/>
       </c>
       <c r="H217" s="42">
-        <f>IF($I217&lt;=0,"",(Rate_1*MAX(0,MIN($O217,R1_To)-MAX($O216,R1_From))+Rate_2*MAX(0,MIN($O217,R2_To)-MAX($O216,R2_From))+Rate_3*MAX(0,MIN($O217,R3_To)-MAX($O216,R3_From)))/100/Day_Basis/$I217*Day_Basis*100)</f>
+        <f>IF($I217&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O217,'Engine'!$B$3)-MAX($O216,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O217,'Engine'!$B$5)-MAX($O216,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O217,'Engine'!$B$7)-MAX($O216,'Engine'!$B$6)))/100/$H$8/$I217*$H$8*100)</f>
         <v/>
       </c>
       <c r="I217" s="43">
@@ -11363,7 +11346,7 @@
         <v/>
       </c>
       <c r="J217" s="41">
-        <f>IF($I217&lt;=0,0,$S216*(Rate_1*MAX(0,MIN($O217,R1_To)-MAX($O216,R1_From))+Rate_2*MAX(0,MIN($O217,R2_To)-MAX($O216,R2_From))+Rate_3*MAX(0,MIN($O217,R3_To)-MAX($O216,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I217&lt;=0,0,$S216*('Engine'!$B$8*MAX(0,MIN($O217,'Engine'!$B$3)-MAX($O216,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O217,'Engine'!$B$5)-MAX($O216,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O217,'Engine'!$B$7)-MAX($O216,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K217" s="41">
@@ -11376,7 +11359,7 @@
         <v/>
       </c>
       <c r="N217" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O217&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O217&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O217" s="25">
@@ -11407,7 +11390,7 @@
         <v/>
       </c>
       <c r="H218" s="42">
-        <f>IF($I218&lt;=0,"",(Rate_1*MAX(0,MIN($O218,R1_To)-MAX($O217,R1_From))+Rate_2*MAX(0,MIN($O218,R2_To)-MAX($O217,R2_From))+Rate_3*MAX(0,MIN($O218,R3_To)-MAX($O217,R3_From)))/100/Day_Basis/$I218*Day_Basis*100)</f>
+        <f>IF($I218&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O218,'Engine'!$B$3)-MAX($O217,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O218,'Engine'!$B$5)-MAX($O217,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O218,'Engine'!$B$7)-MAX($O217,'Engine'!$B$6)))/100/$H$8/$I218*$H$8*100)</f>
         <v/>
       </c>
       <c r="I218" s="43">
@@ -11415,7 +11398,7 @@
         <v/>
       </c>
       <c r="J218" s="41">
-        <f>IF($I218&lt;=0,0,$S217*(Rate_1*MAX(0,MIN($O218,R1_To)-MAX($O217,R1_From))+Rate_2*MAX(0,MIN($O218,R2_To)-MAX($O217,R2_From))+Rate_3*MAX(0,MIN($O218,R3_To)-MAX($O217,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I218&lt;=0,0,$S217*('Engine'!$B$8*MAX(0,MIN($O218,'Engine'!$B$3)-MAX($O217,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O218,'Engine'!$B$5)-MAX($O217,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O218,'Engine'!$B$7)-MAX($O217,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K218" s="41">
@@ -11428,7 +11411,7 @@
         <v/>
       </c>
       <c r="N218" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O218&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O218&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O218" s="25">
@@ -11459,7 +11442,7 @@
         <v/>
       </c>
       <c r="H219" s="42">
-        <f>IF($I219&lt;=0,"",(Rate_1*MAX(0,MIN($O219,R1_To)-MAX($O218,R1_From))+Rate_2*MAX(0,MIN($O219,R2_To)-MAX($O218,R2_From))+Rate_3*MAX(0,MIN($O219,R3_To)-MAX($O218,R3_From)))/100/Day_Basis/$I219*Day_Basis*100)</f>
+        <f>IF($I219&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O219,'Engine'!$B$3)-MAX($O218,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O219,'Engine'!$B$5)-MAX($O218,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O219,'Engine'!$B$7)-MAX($O218,'Engine'!$B$6)))/100/$H$8/$I219*$H$8*100)</f>
         <v/>
       </c>
       <c r="I219" s="43">
@@ -11467,7 +11450,7 @@
         <v/>
       </c>
       <c r="J219" s="41">
-        <f>IF($I219&lt;=0,0,$S218*(Rate_1*MAX(0,MIN($O219,R1_To)-MAX($O218,R1_From))+Rate_2*MAX(0,MIN($O219,R2_To)-MAX($O218,R2_From))+Rate_3*MAX(0,MIN($O219,R3_To)-MAX($O218,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I219&lt;=0,0,$S218*('Engine'!$B$8*MAX(0,MIN($O219,'Engine'!$B$3)-MAX($O218,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O219,'Engine'!$B$5)-MAX($O218,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O219,'Engine'!$B$7)-MAX($O218,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K219" s="41">
@@ -11480,7 +11463,7 @@
         <v/>
       </c>
       <c r="N219" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O219&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O219&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O219" s="25">
@@ -11511,7 +11494,7 @@
         <v/>
       </c>
       <c r="H220" s="42">
-        <f>IF($I220&lt;=0,"",(Rate_1*MAX(0,MIN($O220,R1_To)-MAX($O219,R1_From))+Rate_2*MAX(0,MIN($O220,R2_To)-MAX($O219,R2_From))+Rate_3*MAX(0,MIN($O220,R3_To)-MAX($O219,R3_From)))/100/Day_Basis/$I220*Day_Basis*100)</f>
+        <f>IF($I220&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O220,'Engine'!$B$3)-MAX($O219,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O220,'Engine'!$B$5)-MAX($O219,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O220,'Engine'!$B$7)-MAX($O219,'Engine'!$B$6)))/100/$H$8/$I220*$H$8*100)</f>
         <v/>
       </c>
       <c r="I220" s="43">
@@ -11519,7 +11502,7 @@
         <v/>
       </c>
       <c r="J220" s="41">
-        <f>IF($I220&lt;=0,0,$S219*(Rate_1*MAX(0,MIN($O220,R1_To)-MAX($O219,R1_From))+Rate_2*MAX(0,MIN($O220,R2_To)-MAX($O219,R2_From))+Rate_3*MAX(0,MIN($O220,R3_To)-MAX($O219,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I220&lt;=0,0,$S219*('Engine'!$B$8*MAX(0,MIN($O220,'Engine'!$B$3)-MAX($O219,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O220,'Engine'!$B$5)-MAX($O219,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O220,'Engine'!$B$7)-MAX($O219,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K220" s="41">
@@ -11532,7 +11515,7 @@
         <v/>
       </c>
       <c r="N220" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O220&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O220&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O220" s="25">
@@ -11573,7 +11556,7 @@
         <v/>
       </c>
       <c r="H221" s="51">
-        <f>IF($I221&lt;=0,"",(Rate_1*MAX(0,MIN($O221,R1_To)-MAX($O220,R1_From))+Rate_2*MAX(0,MIN($O221,R2_To)-MAX($O220,R2_From))+Rate_3*MAX(0,MIN($O221,R3_To)-MAX($O220,R3_From)))/100/Day_Basis/$I221*Day_Basis*100)</f>
+        <f>IF($I221&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O221,'Engine'!$B$3)-MAX($O220,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O221,'Engine'!$B$5)-MAX($O220,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O221,'Engine'!$B$7)-MAX($O220,'Engine'!$B$6)))/100/$H$8/$I221*$H$8*100)</f>
         <v/>
       </c>
       <c r="I221" s="52">
@@ -11581,7 +11564,7 @@
         <v/>
       </c>
       <c r="J221" s="53">
-        <f>IF($I221&lt;=0,0,$S220*(Rate_1*MAX(0,MIN($O221,R1_To)-MAX($O220,R1_From))+Rate_2*MAX(0,MIN($O221,R2_To)-MAX($O220,R2_From))+Rate_3*MAX(0,MIN($O221,R3_To)-MAX($O220,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I221&lt;=0,0,$S220*('Engine'!$B$8*MAX(0,MIN($O221,'Engine'!$B$3)-MAX($O220,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O221,'Engine'!$B$5)-MAX($O220,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O221,'Engine'!$B$7)-MAX($O220,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K221" s="53" t="n">
@@ -11593,7 +11576,7 @@
         <v/>
       </c>
       <c r="N221" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O221&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O221&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O221" s="25">
@@ -11610,7 +11593,7 @@
     </row>
     <row r="222" ht="18" customHeight="1">
       <c r="A222" s="24">
-        <f>IF($P$222=0,"QUARTER 17          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 17          "&amp;TEXT($P$222,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$222,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$222&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$222)</f>
+        <f>IF($P$222=0,"QUARTER 17          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 17          "&amp;TEXT($P$222,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$222,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$222&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$222)</f>
         <v/>
       </c>
       <c r="O222" s="25">
@@ -11668,7 +11651,7 @@
         <v/>
       </c>
       <c r="N223" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$223&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$223&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O223" s="25">
@@ -11698,7 +11681,7 @@
         <v/>
       </c>
       <c r="H224" s="42">
-        <f>IF($I224&lt;=0,"",(Rate_1*MAX(0,MIN($O224,R1_To)-MAX($O223,R1_From))+Rate_2*MAX(0,MIN($O224,R2_To)-MAX($O223,R2_From))+Rate_3*MAX(0,MIN($O224,R3_To)-MAX($O223,R3_From)))/100/Day_Basis/$I224*Day_Basis*100)</f>
+        <f>IF($I224&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O224,'Engine'!$B$3)-MAX($O223,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O224,'Engine'!$B$5)-MAX($O223,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O224,'Engine'!$B$7)-MAX($O223,'Engine'!$B$6)))/100/$H$8/$I224*$H$8*100)</f>
         <v/>
       </c>
       <c r="I224" s="43">
@@ -11706,7 +11689,7 @@
         <v/>
       </c>
       <c r="J224" s="41">
-        <f>IF($I224&lt;=0,0,$S223*(Rate_1*MAX(0,MIN($O224,R1_To)-MAX($O223,R1_From))+Rate_2*MAX(0,MIN($O224,R2_To)-MAX($O223,R2_From))+Rate_3*MAX(0,MIN($O224,R3_To)-MAX($O223,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I224&lt;=0,0,$S223*('Engine'!$B$8*MAX(0,MIN($O224,'Engine'!$B$3)-MAX($O223,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O224,'Engine'!$B$5)-MAX($O223,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O224,'Engine'!$B$7)-MAX($O223,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K224" s="41">
@@ -11719,7 +11702,7 @@
         <v/>
       </c>
       <c r="N224" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O224&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O224&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O224" s="25">
@@ -11750,7 +11733,7 @@
         <v/>
       </c>
       <c r="H225" s="42">
-        <f>IF($I225&lt;=0,"",(Rate_1*MAX(0,MIN($O225,R1_To)-MAX($O224,R1_From))+Rate_2*MAX(0,MIN($O225,R2_To)-MAX($O224,R2_From))+Rate_3*MAX(0,MIN($O225,R3_To)-MAX($O224,R3_From)))/100/Day_Basis/$I225*Day_Basis*100)</f>
+        <f>IF($I225&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O225,'Engine'!$B$3)-MAX($O224,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O225,'Engine'!$B$5)-MAX($O224,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O225,'Engine'!$B$7)-MAX($O224,'Engine'!$B$6)))/100/$H$8/$I225*$H$8*100)</f>
         <v/>
       </c>
       <c r="I225" s="43">
@@ -11758,7 +11741,7 @@
         <v/>
       </c>
       <c r="J225" s="41">
-        <f>IF($I225&lt;=0,0,$S224*(Rate_1*MAX(0,MIN($O225,R1_To)-MAX($O224,R1_From))+Rate_2*MAX(0,MIN($O225,R2_To)-MAX($O224,R2_From))+Rate_3*MAX(0,MIN($O225,R3_To)-MAX($O224,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I225&lt;=0,0,$S224*('Engine'!$B$8*MAX(0,MIN($O225,'Engine'!$B$3)-MAX($O224,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O225,'Engine'!$B$5)-MAX($O224,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O225,'Engine'!$B$7)-MAX($O224,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K225" s="41">
@@ -11771,7 +11754,7 @@
         <v/>
       </c>
       <c r="N225" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O225&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O225&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O225" s="25">
@@ -11802,7 +11785,7 @@
         <v/>
       </c>
       <c r="H226" s="42">
-        <f>IF($I226&lt;=0,"",(Rate_1*MAX(0,MIN($O226,R1_To)-MAX($O225,R1_From))+Rate_2*MAX(0,MIN($O226,R2_To)-MAX($O225,R2_From))+Rate_3*MAX(0,MIN($O226,R3_To)-MAX($O225,R3_From)))/100/Day_Basis/$I226*Day_Basis*100)</f>
+        <f>IF($I226&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O226,'Engine'!$B$3)-MAX($O225,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O226,'Engine'!$B$5)-MAX($O225,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O226,'Engine'!$B$7)-MAX($O225,'Engine'!$B$6)))/100/$H$8/$I226*$H$8*100)</f>
         <v/>
       </c>
       <c r="I226" s="43">
@@ -11810,7 +11793,7 @@
         <v/>
       </c>
       <c r="J226" s="41">
-        <f>IF($I226&lt;=0,0,$S225*(Rate_1*MAX(0,MIN($O226,R1_To)-MAX($O225,R1_From))+Rate_2*MAX(0,MIN($O226,R2_To)-MAX($O225,R2_From))+Rate_3*MAX(0,MIN($O226,R3_To)-MAX($O225,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I226&lt;=0,0,$S225*('Engine'!$B$8*MAX(0,MIN($O226,'Engine'!$B$3)-MAX($O225,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O226,'Engine'!$B$5)-MAX($O225,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O226,'Engine'!$B$7)-MAX($O225,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K226" s="41">
@@ -11823,7 +11806,7 @@
         <v/>
       </c>
       <c r="N226" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O226&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O226&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O226" s="25">
@@ -11854,7 +11837,7 @@
         <v/>
       </c>
       <c r="H227" s="42">
-        <f>IF($I227&lt;=0,"",(Rate_1*MAX(0,MIN($O227,R1_To)-MAX($O226,R1_From))+Rate_2*MAX(0,MIN($O227,R2_To)-MAX($O226,R2_From))+Rate_3*MAX(0,MIN($O227,R3_To)-MAX($O226,R3_From)))/100/Day_Basis/$I227*Day_Basis*100)</f>
+        <f>IF($I227&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O227,'Engine'!$B$3)-MAX($O226,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O227,'Engine'!$B$5)-MAX($O226,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O227,'Engine'!$B$7)-MAX($O226,'Engine'!$B$6)))/100/$H$8/$I227*$H$8*100)</f>
         <v/>
       </c>
       <c r="I227" s="43">
@@ -11862,7 +11845,7 @@
         <v/>
       </c>
       <c r="J227" s="41">
-        <f>IF($I227&lt;=0,0,$S226*(Rate_1*MAX(0,MIN($O227,R1_To)-MAX($O226,R1_From))+Rate_2*MAX(0,MIN($O227,R2_To)-MAX($O226,R2_From))+Rate_3*MAX(0,MIN($O227,R3_To)-MAX($O226,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I227&lt;=0,0,$S226*('Engine'!$B$8*MAX(0,MIN($O227,'Engine'!$B$3)-MAX($O226,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O227,'Engine'!$B$5)-MAX($O226,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O227,'Engine'!$B$7)-MAX($O226,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K227" s="41">
@@ -11875,7 +11858,7 @@
         <v/>
       </c>
       <c r="N227" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O227&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O227&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O227" s="25">
@@ -11906,7 +11889,7 @@
         <v/>
       </c>
       <c r="H228" s="42">
-        <f>IF($I228&lt;=0,"",(Rate_1*MAX(0,MIN($O228,R1_To)-MAX($O227,R1_From))+Rate_2*MAX(0,MIN($O228,R2_To)-MAX($O227,R2_From))+Rate_3*MAX(0,MIN($O228,R3_To)-MAX($O227,R3_From)))/100/Day_Basis/$I228*Day_Basis*100)</f>
+        <f>IF($I228&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O228,'Engine'!$B$3)-MAX($O227,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O228,'Engine'!$B$5)-MAX($O227,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O228,'Engine'!$B$7)-MAX($O227,'Engine'!$B$6)))/100/$H$8/$I228*$H$8*100)</f>
         <v/>
       </c>
       <c r="I228" s="43">
@@ -11914,7 +11897,7 @@
         <v/>
       </c>
       <c r="J228" s="41">
-        <f>IF($I228&lt;=0,0,$S227*(Rate_1*MAX(0,MIN($O228,R1_To)-MAX($O227,R1_From))+Rate_2*MAX(0,MIN($O228,R2_To)-MAX($O227,R2_From))+Rate_3*MAX(0,MIN($O228,R3_To)-MAX($O227,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I228&lt;=0,0,$S227*('Engine'!$B$8*MAX(0,MIN($O228,'Engine'!$B$3)-MAX($O227,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O228,'Engine'!$B$5)-MAX($O227,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O228,'Engine'!$B$7)-MAX($O227,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K228" s="41">
@@ -11927,7 +11910,7 @@
         <v/>
       </c>
       <c r="N228" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O228&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O228&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O228" s="25">
@@ -11958,7 +11941,7 @@
         <v/>
       </c>
       <c r="H229" s="42">
-        <f>IF($I229&lt;=0,"",(Rate_1*MAX(0,MIN($O229,R1_To)-MAX($O228,R1_From))+Rate_2*MAX(0,MIN($O229,R2_To)-MAX($O228,R2_From))+Rate_3*MAX(0,MIN($O229,R3_To)-MAX($O228,R3_From)))/100/Day_Basis/$I229*Day_Basis*100)</f>
+        <f>IF($I229&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O229,'Engine'!$B$3)-MAX($O228,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O229,'Engine'!$B$5)-MAX($O228,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O229,'Engine'!$B$7)-MAX($O228,'Engine'!$B$6)))/100/$H$8/$I229*$H$8*100)</f>
         <v/>
       </c>
       <c r="I229" s="43">
@@ -11966,7 +11949,7 @@
         <v/>
       </c>
       <c r="J229" s="41">
-        <f>IF($I229&lt;=0,0,$S228*(Rate_1*MAX(0,MIN($O229,R1_To)-MAX($O228,R1_From))+Rate_2*MAX(0,MIN($O229,R2_To)-MAX($O228,R2_From))+Rate_3*MAX(0,MIN($O229,R3_To)-MAX($O228,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I229&lt;=0,0,$S228*('Engine'!$B$8*MAX(0,MIN($O229,'Engine'!$B$3)-MAX($O228,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O229,'Engine'!$B$5)-MAX($O228,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O229,'Engine'!$B$7)-MAX($O228,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K229" s="41">
@@ -11979,7 +11962,7 @@
         <v/>
       </c>
       <c r="N229" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O229&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O229&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O229" s="25">
@@ -12010,7 +11993,7 @@
         <v/>
       </c>
       <c r="H230" s="42">
-        <f>IF($I230&lt;=0,"",(Rate_1*MAX(0,MIN($O230,R1_To)-MAX($O229,R1_From))+Rate_2*MAX(0,MIN($O230,R2_To)-MAX($O229,R2_From))+Rate_3*MAX(0,MIN($O230,R3_To)-MAX($O229,R3_From)))/100/Day_Basis/$I230*Day_Basis*100)</f>
+        <f>IF($I230&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O230,'Engine'!$B$3)-MAX($O229,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O230,'Engine'!$B$5)-MAX($O229,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O230,'Engine'!$B$7)-MAX($O229,'Engine'!$B$6)))/100/$H$8/$I230*$H$8*100)</f>
         <v/>
       </c>
       <c r="I230" s="43">
@@ -12018,7 +12001,7 @@
         <v/>
       </c>
       <c r="J230" s="41">
-        <f>IF($I230&lt;=0,0,$S229*(Rate_1*MAX(0,MIN($O230,R1_To)-MAX($O229,R1_From))+Rate_2*MAX(0,MIN($O230,R2_To)-MAX($O229,R2_From))+Rate_3*MAX(0,MIN($O230,R3_To)-MAX($O229,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I230&lt;=0,0,$S229*('Engine'!$B$8*MAX(0,MIN($O230,'Engine'!$B$3)-MAX($O229,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O230,'Engine'!$B$5)-MAX($O229,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O230,'Engine'!$B$7)-MAX($O229,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K230" s="41">
@@ -12031,7 +12014,7 @@
         <v/>
       </c>
       <c r="N230" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O230&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O230&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O230" s="25">
@@ -12062,7 +12045,7 @@
         <v/>
       </c>
       <c r="H231" s="42">
-        <f>IF($I231&lt;=0,"",(Rate_1*MAX(0,MIN($O231,R1_To)-MAX($O230,R1_From))+Rate_2*MAX(0,MIN($O231,R2_To)-MAX($O230,R2_From))+Rate_3*MAX(0,MIN($O231,R3_To)-MAX($O230,R3_From)))/100/Day_Basis/$I231*Day_Basis*100)</f>
+        <f>IF($I231&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O231,'Engine'!$B$3)-MAX($O230,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O231,'Engine'!$B$5)-MAX($O230,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O231,'Engine'!$B$7)-MAX($O230,'Engine'!$B$6)))/100/$H$8/$I231*$H$8*100)</f>
         <v/>
       </c>
       <c r="I231" s="43">
@@ -12070,7 +12053,7 @@
         <v/>
       </c>
       <c r="J231" s="41">
-        <f>IF($I231&lt;=0,0,$S230*(Rate_1*MAX(0,MIN($O231,R1_To)-MAX($O230,R1_From))+Rate_2*MAX(0,MIN($O231,R2_To)-MAX($O230,R2_From))+Rate_3*MAX(0,MIN($O231,R3_To)-MAX($O230,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I231&lt;=0,0,$S230*('Engine'!$B$8*MAX(0,MIN($O231,'Engine'!$B$3)-MAX($O230,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O231,'Engine'!$B$5)-MAX($O230,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O231,'Engine'!$B$7)-MAX($O230,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K231" s="41">
@@ -12083,7 +12066,7 @@
         <v/>
       </c>
       <c r="N231" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O231&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O231&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O231" s="25">
@@ -12114,7 +12097,7 @@
         <v/>
       </c>
       <c r="H232" s="42">
-        <f>IF($I232&lt;=0,"",(Rate_1*MAX(0,MIN($O232,R1_To)-MAX($O231,R1_From))+Rate_2*MAX(0,MIN($O232,R2_To)-MAX($O231,R2_From))+Rate_3*MAX(0,MIN($O232,R3_To)-MAX($O231,R3_From)))/100/Day_Basis/$I232*Day_Basis*100)</f>
+        <f>IF($I232&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O232,'Engine'!$B$3)-MAX($O231,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O232,'Engine'!$B$5)-MAX($O231,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O232,'Engine'!$B$7)-MAX($O231,'Engine'!$B$6)))/100/$H$8/$I232*$H$8*100)</f>
         <v/>
       </c>
       <c r="I232" s="43">
@@ -12122,7 +12105,7 @@
         <v/>
       </c>
       <c r="J232" s="41">
-        <f>IF($I232&lt;=0,0,$S231*(Rate_1*MAX(0,MIN($O232,R1_To)-MAX($O231,R1_From))+Rate_2*MAX(0,MIN($O232,R2_To)-MAX($O231,R2_From))+Rate_3*MAX(0,MIN($O232,R3_To)-MAX($O231,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I232&lt;=0,0,$S231*('Engine'!$B$8*MAX(0,MIN($O232,'Engine'!$B$3)-MAX($O231,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O232,'Engine'!$B$5)-MAX($O231,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O232,'Engine'!$B$7)-MAX($O231,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K232" s="41">
@@ -12135,7 +12118,7 @@
         <v/>
       </c>
       <c r="N232" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O232&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O232&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O232" s="25">
@@ -12166,7 +12149,7 @@
         <v/>
       </c>
       <c r="H233" s="42">
-        <f>IF($I233&lt;=0,"",(Rate_1*MAX(0,MIN($O233,R1_To)-MAX($O232,R1_From))+Rate_2*MAX(0,MIN($O233,R2_To)-MAX($O232,R2_From))+Rate_3*MAX(0,MIN($O233,R3_To)-MAX($O232,R3_From)))/100/Day_Basis/$I233*Day_Basis*100)</f>
+        <f>IF($I233&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O233,'Engine'!$B$3)-MAX($O232,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O233,'Engine'!$B$5)-MAX($O232,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O233,'Engine'!$B$7)-MAX($O232,'Engine'!$B$6)))/100/$H$8/$I233*$H$8*100)</f>
         <v/>
       </c>
       <c r="I233" s="43">
@@ -12174,7 +12157,7 @@
         <v/>
       </c>
       <c r="J233" s="41">
-        <f>IF($I233&lt;=0,0,$S232*(Rate_1*MAX(0,MIN($O233,R1_To)-MAX($O232,R1_From))+Rate_2*MAX(0,MIN($O233,R2_To)-MAX($O232,R2_From))+Rate_3*MAX(0,MIN($O233,R3_To)-MAX($O232,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I233&lt;=0,0,$S232*('Engine'!$B$8*MAX(0,MIN($O233,'Engine'!$B$3)-MAX($O232,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O233,'Engine'!$B$5)-MAX($O232,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O233,'Engine'!$B$7)-MAX($O232,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K233" s="41">
@@ -12187,7 +12170,7 @@
         <v/>
       </c>
       <c r="N233" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O233&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O233&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O233" s="25">
@@ -12228,7 +12211,7 @@
         <v/>
       </c>
       <c r="H234" s="51">
-        <f>IF($I234&lt;=0,"",(Rate_1*MAX(0,MIN($O234,R1_To)-MAX($O233,R1_From))+Rate_2*MAX(0,MIN($O234,R2_To)-MAX($O233,R2_From))+Rate_3*MAX(0,MIN($O234,R3_To)-MAX($O233,R3_From)))/100/Day_Basis/$I234*Day_Basis*100)</f>
+        <f>IF($I234&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O234,'Engine'!$B$3)-MAX($O233,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O234,'Engine'!$B$5)-MAX($O233,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O234,'Engine'!$B$7)-MAX($O233,'Engine'!$B$6)))/100/$H$8/$I234*$H$8*100)</f>
         <v/>
       </c>
       <c r="I234" s="52">
@@ -12236,7 +12219,7 @@
         <v/>
       </c>
       <c r="J234" s="53">
-        <f>IF($I234&lt;=0,0,$S233*(Rate_1*MAX(0,MIN($O234,R1_To)-MAX($O233,R1_From))+Rate_2*MAX(0,MIN($O234,R2_To)-MAX($O233,R2_From))+Rate_3*MAX(0,MIN($O234,R3_To)-MAX($O233,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I234&lt;=0,0,$S233*('Engine'!$B$8*MAX(0,MIN($O234,'Engine'!$B$3)-MAX($O233,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O234,'Engine'!$B$5)-MAX($O233,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O234,'Engine'!$B$7)-MAX($O233,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K234" s="53" t="n">
@@ -12248,7 +12231,7 @@
         <v/>
       </c>
       <c r="N234" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O234&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O234&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O234" s="25">
@@ -12265,7 +12248,7 @@
     </row>
     <row r="235" ht="18" customHeight="1">
       <c r="A235" s="24">
-        <f>IF($P$235=0,"QUARTER 18          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 18          "&amp;TEXT($P$235,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$235,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$235&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$235)</f>
+        <f>IF($P$235=0,"QUARTER 18          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 18          "&amp;TEXT($P$235,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$235,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$235&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$235)</f>
         <v/>
       </c>
       <c r="O235" s="25">
@@ -12323,7 +12306,7 @@
         <v/>
       </c>
       <c r="N236" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$236&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$236&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O236" s="25">
@@ -12353,7 +12336,7 @@
         <v/>
       </c>
       <c r="H237" s="42">
-        <f>IF($I237&lt;=0,"",(Rate_1*MAX(0,MIN($O237,R1_To)-MAX($O236,R1_From))+Rate_2*MAX(0,MIN($O237,R2_To)-MAX($O236,R2_From))+Rate_3*MAX(0,MIN($O237,R3_To)-MAX($O236,R3_From)))/100/Day_Basis/$I237*Day_Basis*100)</f>
+        <f>IF($I237&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O237,'Engine'!$B$3)-MAX($O236,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O237,'Engine'!$B$5)-MAX($O236,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O237,'Engine'!$B$7)-MAX($O236,'Engine'!$B$6)))/100/$H$8/$I237*$H$8*100)</f>
         <v/>
       </c>
       <c r="I237" s="43">
@@ -12361,7 +12344,7 @@
         <v/>
       </c>
       <c r="J237" s="41">
-        <f>IF($I237&lt;=0,0,$S236*(Rate_1*MAX(0,MIN($O237,R1_To)-MAX($O236,R1_From))+Rate_2*MAX(0,MIN($O237,R2_To)-MAX($O236,R2_From))+Rate_3*MAX(0,MIN($O237,R3_To)-MAX($O236,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I237&lt;=0,0,$S236*('Engine'!$B$8*MAX(0,MIN($O237,'Engine'!$B$3)-MAX($O236,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O237,'Engine'!$B$5)-MAX($O236,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O237,'Engine'!$B$7)-MAX($O236,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K237" s="41">
@@ -12374,7 +12357,7 @@
         <v/>
       </c>
       <c r="N237" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O237&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O237&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O237" s="25">
@@ -12405,7 +12388,7 @@
         <v/>
       </c>
       <c r="H238" s="42">
-        <f>IF($I238&lt;=0,"",(Rate_1*MAX(0,MIN($O238,R1_To)-MAX($O237,R1_From))+Rate_2*MAX(0,MIN($O238,R2_To)-MAX($O237,R2_From))+Rate_3*MAX(0,MIN($O238,R3_To)-MAX($O237,R3_From)))/100/Day_Basis/$I238*Day_Basis*100)</f>
+        <f>IF($I238&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O238,'Engine'!$B$3)-MAX($O237,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O238,'Engine'!$B$5)-MAX($O237,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O238,'Engine'!$B$7)-MAX($O237,'Engine'!$B$6)))/100/$H$8/$I238*$H$8*100)</f>
         <v/>
       </c>
       <c r="I238" s="43">
@@ -12413,7 +12396,7 @@
         <v/>
       </c>
       <c r="J238" s="41">
-        <f>IF($I238&lt;=0,0,$S237*(Rate_1*MAX(0,MIN($O238,R1_To)-MAX($O237,R1_From))+Rate_2*MAX(0,MIN($O238,R2_To)-MAX($O237,R2_From))+Rate_3*MAX(0,MIN($O238,R3_To)-MAX($O237,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I238&lt;=0,0,$S237*('Engine'!$B$8*MAX(0,MIN($O238,'Engine'!$B$3)-MAX($O237,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O238,'Engine'!$B$5)-MAX($O237,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O238,'Engine'!$B$7)-MAX($O237,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K238" s="41">
@@ -12426,7 +12409,7 @@
         <v/>
       </c>
       <c r="N238" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O238&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O238&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O238" s="25">
@@ -12457,7 +12440,7 @@
         <v/>
       </c>
       <c r="H239" s="42">
-        <f>IF($I239&lt;=0,"",(Rate_1*MAX(0,MIN($O239,R1_To)-MAX($O238,R1_From))+Rate_2*MAX(0,MIN($O239,R2_To)-MAX($O238,R2_From))+Rate_3*MAX(0,MIN($O239,R3_To)-MAX($O238,R3_From)))/100/Day_Basis/$I239*Day_Basis*100)</f>
+        <f>IF($I239&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O239,'Engine'!$B$3)-MAX($O238,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O239,'Engine'!$B$5)-MAX($O238,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O239,'Engine'!$B$7)-MAX($O238,'Engine'!$B$6)))/100/$H$8/$I239*$H$8*100)</f>
         <v/>
       </c>
       <c r="I239" s="43">
@@ -12465,7 +12448,7 @@
         <v/>
       </c>
       <c r="J239" s="41">
-        <f>IF($I239&lt;=0,0,$S238*(Rate_1*MAX(0,MIN($O239,R1_To)-MAX($O238,R1_From))+Rate_2*MAX(0,MIN($O239,R2_To)-MAX($O238,R2_From))+Rate_3*MAX(0,MIN($O239,R3_To)-MAX($O238,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I239&lt;=0,0,$S238*('Engine'!$B$8*MAX(0,MIN($O239,'Engine'!$B$3)-MAX($O238,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O239,'Engine'!$B$5)-MAX($O238,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O239,'Engine'!$B$7)-MAX($O238,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K239" s="41">
@@ -12478,7 +12461,7 @@
         <v/>
       </c>
       <c r="N239" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O239&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O239&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O239" s="25">
@@ -12509,7 +12492,7 @@
         <v/>
       </c>
       <c r="H240" s="42">
-        <f>IF($I240&lt;=0,"",(Rate_1*MAX(0,MIN($O240,R1_To)-MAX($O239,R1_From))+Rate_2*MAX(0,MIN($O240,R2_To)-MAX($O239,R2_From))+Rate_3*MAX(0,MIN($O240,R3_To)-MAX($O239,R3_From)))/100/Day_Basis/$I240*Day_Basis*100)</f>
+        <f>IF($I240&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O240,'Engine'!$B$3)-MAX($O239,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O240,'Engine'!$B$5)-MAX($O239,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O240,'Engine'!$B$7)-MAX($O239,'Engine'!$B$6)))/100/$H$8/$I240*$H$8*100)</f>
         <v/>
       </c>
       <c r="I240" s="43">
@@ -12517,7 +12500,7 @@
         <v/>
       </c>
       <c r="J240" s="41">
-        <f>IF($I240&lt;=0,0,$S239*(Rate_1*MAX(0,MIN($O240,R1_To)-MAX($O239,R1_From))+Rate_2*MAX(0,MIN($O240,R2_To)-MAX($O239,R2_From))+Rate_3*MAX(0,MIN($O240,R3_To)-MAX($O239,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I240&lt;=0,0,$S239*('Engine'!$B$8*MAX(0,MIN($O240,'Engine'!$B$3)-MAX($O239,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O240,'Engine'!$B$5)-MAX($O239,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O240,'Engine'!$B$7)-MAX($O239,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K240" s="41">
@@ -12530,7 +12513,7 @@
         <v/>
       </c>
       <c r="N240" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O240&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O240&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O240" s="25">
@@ -12561,7 +12544,7 @@
         <v/>
       </c>
       <c r="H241" s="42">
-        <f>IF($I241&lt;=0,"",(Rate_1*MAX(0,MIN($O241,R1_To)-MAX($O240,R1_From))+Rate_2*MAX(0,MIN($O241,R2_To)-MAX($O240,R2_From))+Rate_3*MAX(0,MIN($O241,R3_To)-MAX($O240,R3_From)))/100/Day_Basis/$I241*Day_Basis*100)</f>
+        <f>IF($I241&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O241,'Engine'!$B$3)-MAX($O240,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O241,'Engine'!$B$5)-MAX($O240,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O241,'Engine'!$B$7)-MAX($O240,'Engine'!$B$6)))/100/$H$8/$I241*$H$8*100)</f>
         <v/>
       </c>
       <c r="I241" s="43">
@@ -12569,7 +12552,7 @@
         <v/>
       </c>
       <c r="J241" s="41">
-        <f>IF($I241&lt;=0,0,$S240*(Rate_1*MAX(0,MIN($O241,R1_To)-MAX($O240,R1_From))+Rate_2*MAX(0,MIN($O241,R2_To)-MAX($O240,R2_From))+Rate_3*MAX(0,MIN($O241,R3_To)-MAX($O240,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I241&lt;=0,0,$S240*('Engine'!$B$8*MAX(0,MIN($O241,'Engine'!$B$3)-MAX($O240,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O241,'Engine'!$B$5)-MAX($O240,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O241,'Engine'!$B$7)-MAX($O240,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K241" s="41">
@@ -12582,7 +12565,7 @@
         <v/>
       </c>
       <c r="N241" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O241&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O241&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O241" s="25">
@@ -12613,7 +12596,7 @@
         <v/>
       </c>
       <c r="H242" s="42">
-        <f>IF($I242&lt;=0,"",(Rate_1*MAX(0,MIN($O242,R1_To)-MAX($O241,R1_From))+Rate_2*MAX(0,MIN($O242,R2_To)-MAX($O241,R2_From))+Rate_3*MAX(0,MIN($O242,R3_To)-MAX($O241,R3_From)))/100/Day_Basis/$I242*Day_Basis*100)</f>
+        <f>IF($I242&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O242,'Engine'!$B$3)-MAX($O241,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O242,'Engine'!$B$5)-MAX($O241,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O242,'Engine'!$B$7)-MAX($O241,'Engine'!$B$6)))/100/$H$8/$I242*$H$8*100)</f>
         <v/>
       </c>
       <c r="I242" s="43">
@@ -12621,7 +12604,7 @@
         <v/>
       </c>
       <c r="J242" s="41">
-        <f>IF($I242&lt;=0,0,$S241*(Rate_1*MAX(0,MIN($O242,R1_To)-MAX($O241,R1_From))+Rate_2*MAX(0,MIN($O242,R2_To)-MAX($O241,R2_From))+Rate_3*MAX(0,MIN($O242,R3_To)-MAX($O241,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I242&lt;=0,0,$S241*('Engine'!$B$8*MAX(0,MIN($O242,'Engine'!$B$3)-MAX($O241,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O242,'Engine'!$B$5)-MAX($O241,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O242,'Engine'!$B$7)-MAX($O241,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K242" s="41">
@@ -12634,7 +12617,7 @@
         <v/>
       </c>
       <c r="N242" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O242&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O242&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O242" s="25">
@@ -12665,7 +12648,7 @@
         <v/>
       </c>
       <c r="H243" s="42">
-        <f>IF($I243&lt;=0,"",(Rate_1*MAX(0,MIN($O243,R1_To)-MAX($O242,R1_From))+Rate_2*MAX(0,MIN($O243,R2_To)-MAX($O242,R2_From))+Rate_3*MAX(0,MIN($O243,R3_To)-MAX($O242,R3_From)))/100/Day_Basis/$I243*Day_Basis*100)</f>
+        <f>IF($I243&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O243,'Engine'!$B$3)-MAX($O242,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O243,'Engine'!$B$5)-MAX($O242,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O243,'Engine'!$B$7)-MAX($O242,'Engine'!$B$6)))/100/$H$8/$I243*$H$8*100)</f>
         <v/>
       </c>
       <c r="I243" s="43">
@@ -12673,7 +12656,7 @@
         <v/>
       </c>
       <c r="J243" s="41">
-        <f>IF($I243&lt;=0,0,$S242*(Rate_1*MAX(0,MIN($O243,R1_To)-MAX($O242,R1_From))+Rate_2*MAX(0,MIN($O243,R2_To)-MAX($O242,R2_From))+Rate_3*MAX(0,MIN($O243,R3_To)-MAX($O242,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I243&lt;=0,0,$S242*('Engine'!$B$8*MAX(0,MIN($O243,'Engine'!$B$3)-MAX($O242,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O243,'Engine'!$B$5)-MAX($O242,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O243,'Engine'!$B$7)-MAX($O242,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K243" s="41">
@@ -12686,7 +12669,7 @@
         <v/>
       </c>
       <c r="N243" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O243&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O243&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O243" s="25">
@@ -12717,7 +12700,7 @@
         <v/>
       </c>
       <c r="H244" s="42">
-        <f>IF($I244&lt;=0,"",(Rate_1*MAX(0,MIN($O244,R1_To)-MAX($O243,R1_From))+Rate_2*MAX(0,MIN($O244,R2_To)-MAX($O243,R2_From))+Rate_3*MAX(0,MIN($O244,R3_To)-MAX($O243,R3_From)))/100/Day_Basis/$I244*Day_Basis*100)</f>
+        <f>IF($I244&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O244,'Engine'!$B$3)-MAX($O243,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O244,'Engine'!$B$5)-MAX($O243,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O244,'Engine'!$B$7)-MAX($O243,'Engine'!$B$6)))/100/$H$8/$I244*$H$8*100)</f>
         <v/>
       </c>
       <c r="I244" s="43">
@@ -12725,7 +12708,7 @@
         <v/>
       </c>
       <c r="J244" s="41">
-        <f>IF($I244&lt;=0,0,$S243*(Rate_1*MAX(0,MIN($O244,R1_To)-MAX($O243,R1_From))+Rate_2*MAX(0,MIN($O244,R2_To)-MAX($O243,R2_From))+Rate_3*MAX(0,MIN($O244,R3_To)-MAX($O243,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I244&lt;=0,0,$S243*('Engine'!$B$8*MAX(0,MIN($O244,'Engine'!$B$3)-MAX($O243,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O244,'Engine'!$B$5)-MAX($O243,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O244,'Engine'!$B$7)-MAX($O243,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K244" s="41">
@@ -12738,7 +12721,7 @@
         <v/>
       </c>
       <c r="N244" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O244&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O244&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O244" s="25">
@@ -12769,7 +12752,7 @@
         <v/>
       </c>
       <c r="H245" s="42">
-        <f>IF($I245&lt;=0,"",(Rate_1*MAX(0,MIN($O245,R1_To)-MAX($O244,R1_From))+Rate_2*MAX(0,MIN($O245,R2_To)-MAX($O244,R2_From))+Rate_3*MAX(0,MIN($O245,R3_To)-MAX($O244,R3_From)))/100/Day_Basis/$I245*Day_Basis*100)</f>
+        <f>IF($I245&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O245,'Engine'!$B$3)-MAX($O244,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O245,'Engine'!$B$5)-MAX($O244,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O245,'Engine'!$B$7)-MAX($O244,'Engine'!$B$6)))/100/$H$8/$I245*$H$8*100)</f>
         <v/>
       </c>
       <c r="I245" s="43">
@@ -12777,7 +12760,7 @@
         <v/>
       </c>
       <c r="J245" s="41">
-        <f>IF($I245&lt;=0,0,$S244*(Rate_1*MAX(0,MIN($O245,R1_To)-MAX($O244,R1_From))+Rate_2*MAX(0,MIN($O245,R2_To)-MAX($O244,R2_From))+Rate_3*MAX(0,MIN($O245,R3_To)-MAX($O244,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I245&lt;=0,0,$S244*('Engine'!$B$8*MAX(0,MIN($O245,'Engine'!$B$3)-MAX($O244,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O245,'Engine'!$B$5)-MAX($O244,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O245,'Engine'!$B$7)-MAX($O244,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K245" s="41">
@@ -12790,7 +12773,7 @@
         <v/>
       </c>
       <c r="N245" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O245&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O245&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O245" s="25">
@@ -12821,7 +12804,7 @@
         <v/>
       </c>
       <c r="H246" s="42">
-        <f>IF($I246&lt;=0,"",(Rate_1*MAX(0,MIN($O246,R1_To)-MAX($O245,R1_From))+Rate_2*MAX(0,MIN($O246,R2_To)-MAX($O245,R2_From))+Rate_3*MAX(0,MIN($O246,R3_To)-MAX($O245,R3_From)))/100/Day_Basis/$I246*Day_Basis*100)</f>
+        <f>IF($I246&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O246,'Engine'!$B$3)-MAX($O245,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O246,'Engine'!$B$5)-MAX($O245,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O246,'Engine'!$B$7)-MAX($O245,'Engine'!$B$6)))/100/$H$8/$I246*$H$8*100)</f>
         <v/>
       </c>
       <c r="I246" s="43">
@@ -12829,7 +12812,7 @@
         <v/>
       </c>
       <c r="J246" s="41">
-        <f>IF($I246&lt;=0,0,$S245*(Rate_1*MAX(0,MIN($O246,R1_To)-MAX($O245,R1_From))+Rate_2*MAX(0,MIN($O246,R2_To)-MAX($O245,R2_From))+Rate_3*MAX(0,MIN($O246,R3_To)-MAX($O245,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I246&lt;=0,0,$S245*('Engine'!$B$8*MAX(0,MIN($O246,'Engine'!$B$3)-MAX($O245,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O246,'Engine'!$B$5)-MAX($O245,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O246,'Engine'!$B$7)-MAX($O245,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K246" s="41">
@@ -12842,7 +12825,7 @@
         <v/>
       </c>
       <c r="N246" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O246&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O246&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O246" s="25">
@@ -12883,7 +12866,7 @@
         <v/>
       </c>
       <c r="H247" s="51">
-        <f>IF($I247&lt;=0,"",(Rate_1*MAX(0,MIN($O247,R1_To)-MAX($O246,R1_From))+Rate_2*MAX(0,MIN($O247,R2_To)-MAX($O246,R2_From))+Rate_3*MAX(0,MIN($O247,R3_To)-MAX($O246,R3_From)))/100/Day_Basis/$I247*Day_Basis*100)</f>
+        <f>IF($I247&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O247,'Engine'!$B$3)-MAX($O246,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O247,'Engine'!$B$5)-MAX($O246,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O247,'Engine'!$B$7)-MAX($O246,'Engine'!$B$6)))/100/$H$8/$I247*$H$8*100)</f>
         <v/>
       </c>
       <c r="I247" s="52">
@@ -12891,7 +12874,7 @@
         <v/>
       </c>
       <c r="J247" s="53">
-        <f>IF($I247&lt;=0,0,$S246*(Rate_1*MAX(0,MIN($O247,R1_To)-MAX($O246,R1_From))+Rate_2*MAX(0,MIN($O247,R2_To)-MAX($O246,R2_From))+Rate_3*MAX(0,MIN($O247,R3_To)-MAX($O246,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I247&lt;=0,0,$S246*('Engine'!$B$8*MAX(0,MIN($O247,'Engine'!$B$3)-MAX($O246,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O247,'Engine'!$B$5)-MAX($O246,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O247,'Engine'!$B$7)-MAX($O246,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K247" s="53" t="n">
@@ -12903,7 +12886,7 @@
         <v/>
       </c>
       <c r="N247" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O247&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O247&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O247" s="25">
@@ -12920,7 +12903,7 @@
     </row>
     <row r="248" ht="18" customHeight="1">
       <c r="A248" s="24">
-        <f>IF($P$248=0,"QUARTER 19          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 19          "&amp;TEXT($P$248,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$248,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$248&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$248)</f>
+        <f>IF($P$248=0,"QUARTER 19          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 19          "&amp;TEXT($P$248,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$248,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$248&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$248)</f>
         <v/>
       </c>
       <c r="O248" s="25">
@@ -12978,7 +12961,7 @@
         <v/>
       </c>
       <c r="N249" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$249&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$249&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O249" s="25">
@@ -13008,7 +12991,7 @@
         <v/>
       </c>
       <c r="H250" s="42">
-        <f>IF($I250&lt;=0,"",(Rate_1*MAX(0,MIN($O250,R1_To)-MAX($O249,R1_From))+Rate_2*MAX(0,MIN($O250,R2_To)-MAX($O249,R2_From))+Rate_3*MAX(0,MIN($O250,R3_To)-MAX($O249,R3_From)))/100/Day_Basis/$I250*Day_Basis*100)</f>
+        <f>IF($I250&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O250,'Engine'!$B$3)-MAX($O249,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O250,'Engine'!$B$5)-MAX($O249,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O250,'Engine'!$B$7)-MAX($O249,'Engine'!$B$6)))/100/$H$8/$I250*$H$8*100)</f>
         <v/>
       </c>
       <c r="I250" s="43">
@@ -13016,7 +12999,7 @@
         <v/>
       </c>
       <c r="J250" s="41">
-        <f>IF($I250&lt;=0,0,$S249*(Rate_1*MAX(0,MIN($O250,R1_To)-MAX($O249,R1_From))+Rate_2*MAX(0,MIN($O250,R2_To)-MAX($O249,R2_From))+Rate_3*MAX(0,MIN($O250,R3_To)-MAX($O249,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I250&lt;=0,0,$S249*('Engine'!$B$8*MAX(0,MIN($O250,'Engine'!$B$3)-MAX($O249,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O250,'Engine'!$B$5)-MAX($O249,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O250,'Engine'!$B$7)-MAX($O249,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K250" s="41">
@@ -13029,7 +13012,7 @@
         <v/>
       </c>
       <c r="N250" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O250&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O250&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O250" s="25">
@@ -13060,7 +13043,7 @@
         <v/>
       </c>
       <c r="H251" s="42">
-        <f>IF($I251&lt;=0,"",(Rate_1*MAX(0,MIN($O251,R1_To)-MAX($O250,R1_From))+Rate_2*MAX(0,MIN($O251,R2_To)-MAX($O250,R2_From))+Rate_3*MAX(0,MIN($O251,R3_To)-MAX($O250,R3_From)))/100/Day_Basis/$I251*Day_Basis*100)</f>
+        <f>IF($I251&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O251,'Engine'!$B$3)-MAX($O250,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O251,'Engine'!$B$5)-MAX($O250,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O251,'Engine'!$B$7)-MAX($O250,'Engine'!$B$6)))/100/$H$8/$I251*$H$8*100)</f>
         <v/>
       </c>
       <c r="I251" s="43">
@@ -13068,7 +13051,7 @@
         <v/>
       </c>
       <c r="J251" s="41">
-        <f>IF($I251&lt;=0,0,$S250*(Rate_1*MAX(0,MIN($O251,R1_To)-MAX($O250,R1_From))+Rate_2*MAX(0,MIN($O251,R2_To)-MAX($O250,R2_From))+Rate_3*MAX(0,MIN($O251,R3_To)-MAX($O250,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I251&lt;=0,0,$S250*('Engine'!$B$8*MAX(0,MIN($O251,'Engine'!$B$3)-MAX($O250,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O251,'Engine'!$B$5)-MAX($O250,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O251,'Engine'!$B$7)-MAX($O250,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K251" s="41">
@@ -13081,7 +13064,7 @@
         <v/>
       </c>
       <c r="N251" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O251&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O251&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O251" s="25">
@@ -13112,7 +13095,7 @@
         <v/>
       </c>
       <c r="H252" s="42">
-        <f>IF($I252&lt;=0,"",(Rate_1*MAX(0,MIN($O252,R1_To)-MAX($O251,R1_From))+Rate_2*MAX(0,MIN($O252,R2_To)-MAX($O251,R2_From))+Rate_3*MAX(0,MIN($O252,R3_To)-MAX($O251,R3_From)))/100/Day_Basis/$I252*Day_Basis*100)</f>
+        <f>IF($I252&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O252,'Engine'!$B$3)-MAX($O251,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O252,'Engine'!$B$5)-MAX($O251,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O252,'Engine'!$B$7)-MAX($O251,'Engine'!$B$6)))/100/$H$8/$I252*$H$8*100)</f>
         <v/>
       </c>
       <c r="I252" s="43">
@@ -13120,7 +13103,7 @@
         <v/>
       </c>
       <c r="J252" s="41">
-        <f>IF($I252&lt;=0,0,$S251*(Rate_1*MAX(0,MIN($O252,R1_To)-MAX($O251,R1_From))+Rate_2*MAX(0,MIN($O252,R2_To)-MAX($O251,R2_From))+Rate_3*MAX(0,MIN($O252,R3_To)-MAX($O251,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I252&lt;=0,0,$S251*('Engine'!$B$8*MAX(0,MIN($O252,'Engine'!$B$3)-MAX($O251,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O252,'Engine'!$B$5)-MAX($O251,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O252,'Engine'!$B$7)-MAX($O251,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K252" s="41">
@@ -13133,7 +13116,7 @@
         <v/>
       </c>
       <c r="N252" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O252&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O252&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O252" s="25">
@@ -13164,7 +13147,7 @@
         <v/>
       </c>
       <c r="H253" s="42">
-        <f>IF($I253&lt;=0,"",(Rate_1*MAX(0,MIN($O253,R1_To)-MAX($O252,R1_From))+Rate_2*MAX(0,MIN($O253,R2_To)-MAX($O252,R2_From))+Rate_3*MAX(0,MIN($O253,R3_To)-MAX($O252,R3_From)))/100/Day_Basis/$I253*Day_Basis*100)</f>
+        <f>IF($I253&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O253,'Engine'!$B$3)-MAX($O252,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O253,'Engine'!$B$5)-MAX($O252,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O253,'Engine'!$B$7)-MAX($O252,'Engine'!$B$6)))/100/$H$8/$I253*$H$8*100)</f>
         <v/>
       </c>
       <c r="I253" s="43">
@@ -13172,7 +13155,7 @@
         <v/>
       </c>
       <c r="J253" s="41">
-        <f>IF($I253&lt;=0,0,$S252*(Rate_1*MAX(0,MIN($O253,R1_To)-MAX($O252,R1_From))+Rate_2*MAX(0,MIN($O253,R2_To)-MAX($O252,R2_From))+Rate_3*MAX(0,MIN($O253,R3_To)-MAX($O252,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I253&lt;=0,0,$S252*('Engine'!$B$8*MAX(0,MIN($O253,'Engine'!$B$3)-MAX($O252,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O253,'Engine'!$B$5)-MAX($O252,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O253,'Engine'!$B$7)-MAX($O252,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K253" s="41">
@@ -13185,7 +13168,7 @@
         <v/>
       </c>
       <c r="N253" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O253&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O253&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O253" s="25">
@@ -13216,7 +13199,7 @@
         <v/>
       </c>
       <c r="H254" s="42">
-        <f>IF($I254&lt;=0,"",(Rate_1*MAX(0,MIN($O254,R1_To)-MAX($O253,R1_From))+Rate_2*MAX(0,MIN($O254,R2_To)-MAX($O253,R2_From))+Rate_3*MAX(0,MIN($O254,R3_To)-MAX($O253,R3_From)))/100/Day_Basis/$I254*Day_Basis*100)</f>
+        <f>IF($I254&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O254,'Engine'!$B$3)-MAX($O253,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O254,'Engine'!$B$5)-MAX($O253,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O254,'Engine'!$B$7)-MAX($O253,'Engine'!$B$6)))/100/$H$8/$I254*$H$8*100)</f>
         <v/>
       </c>
       <c r="I254" s="43">
@@ -13224,7 +13207,7 @@
         <v/>
       </c>
       <c r="J254" s="41">
-        <f>IF($I254&lt;=0,0,$S253*(Rate_1*MAX(0,MIN($O254,R1_To)-MAX($O253,R1_From))+Rate_2*MAX(0,MIN($O254,R2_To)-MAX($O253,R2_From))+Rate_3*MAX(0,MIN($O254,R3_To)-MAX($O253,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I254&lt;=0,0,$S253*('Engine'!$B$8*MAX(0,MIN($O254,'Engine'!$B$3)-MAX($O253,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O254,'Engine'!$B$5)-MAX($O253,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O254,'Engine'!$B$7)-MAX($O253,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K254" s="41">
@@ -13237,7 +13220,7 @@
         <v/>
       </c>
       <c r="N254" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O254&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O254&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O254" s="25">
@@ -13268,7 +13251,7 @@
         <v/>
       </c>
       <c r="H255" s="42">
-        <f>IF($I255&lt;=0,"",(Rate_1*MAX(0,MIN($O255,R1_To)-MAX($O254,R1_From))+Rate_2*MAX(0,MIN($O255,R2_To)-MAX($O254,R2_From))+Rate_3*MAX(0,MIN($O255,R3_To)-MAX($O254,R3_From)))/100/Day_Basis/$I255*Day_Basis*100)</f>
+        <f>IF($I255&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O255,'Engine'!$B$3)-MAX($O254,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O255,'Engine'!$B$5)-MAX($O254,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O255,'Engine'!$B$7)-MAX($O254,'Engine'!$B$6)))/100/$H$8/$I255*$H$8*100)</f>
         <v/>
       </c>
       <c r="I255" s="43">
@@ -13276,7 +13259,7 @@
         <v/>
       </c>
       <c r="J255" s="41">
-        <f>IF($I255&lt;=0,0,$S254*(Rate_1*MAX(0,MIN($O255,R1_To)-MAX($O254,R1_From))+Rate_2*MAX(0,MIN($O255,R2_To)-MAX($O254,R2_From))+Rate_3*MAX(0,MIN($O255,R3_To)-MAX($O254,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I255&lt;=0,0,$S254*('Engine'!$B$8*MAX(0,MIN($O255,'Engine'!$B$3)-MAX($O254,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O255,'Engine'!$B$5)-MAX($O254,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O255,'Engine'!$B$7)-MAX($O254,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K255" s="41">
@@ -13289,7 +13272,7 @@
         <v/>
       </c>
       <c r="N255" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O255&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O255&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O255" s="25">
@@ -13320,7 +13303,7 @@
         <v/>
       </c>
       <c r="H256" s="42">
-        <f>IF($I256&lt;=0,"",(Rate_1*MAX(0,MIN($O256,R1_To)-MAX($O255,R1_From))+Rate_2*MAX(0,MIN($O256,R2_To)-MAX($O255,R2_From))+Rate_3*MAX(0,MIN($O256,R3_To)-MAX($O255,R3_From)))/100/Day_Basis/$I256*Day_Basis*100)</f>
+        <f>IF($I256&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O256,'Engine'!$B$3)-MAX($O255,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O256,'Engine'!$B$5)-MAX($O255,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O256,'Engine'!$B$7)-MAX($O255,'Engine'!$B$6)))/100/$H$8/$I256*$H$8*100)</f>
         <v/>
       </c>
       <c r="I256" s="43">
@@ -13328,7 +13311,7 @@
         <v/>
       </c>
       <c r="J256" s="41">
-        <f>IF($I256&lt;=0,0,$S255*(Rate_1*MAX(0,MIN($O256,R1_To)-MAX($O255,R1_From))+Rate_2*MAX(0,MIN($O256,R2_To)-MAX($O255,R2_From))+Rate_3*MAX(0,MIN($O256,R3_To)-MAX($O255,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I256&lt;=0,0,$S255*('Engine'!$B$8*MAX(0,MIN($O256,'Engine'!$B$3)-MAX($O255,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O256,'Engine'!$B$5)-MAX($O255,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O256,'Engine'!$B$7)-MAX($O255,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K256" s="41">
@@ -13341,7 +13324,7 @@
         <v/>
       </c>
       <c r="N256" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O256&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O256&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O256" s="25">
@@ -13372,7 +13355,7 @@
         <v/>
       </c>
       <c r="H257" s="42">
-        <f>IF($I257&lt;=0,"",(Rate_1*MAX(0,MIN($O257,R1_To)-MAX($O256,R1_From))+Rate_2*MAX(0,MIN($O257,R2_To)-MAX($O256,R2_From))+Rate_3*MAX(0,MIN($O257,R3_To)-MAX($O256,R3_From)))/100/Day_Basis/$I257*Day_Basis*100)</f>
+        <f>IF($I257&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O257,'Engine'!$B$3)-MAX($O256,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O257,'Engine'!$B$5)-MAX($O256,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O257,'Engine'!$B$7)-MAX($O256,'Engine'!$B$6)))/100/$H$8/$I257*$H$8*100)</f>
         <v/>
       </c>
       <c r="I257" s="43">
@@ -13380,7 +13363,7 @@
         <v/>
       </c>
       <c r="J257" s="41">
-        <f>IF($I257&lt;=0,0,$S256*(Rate_1*MAX(0,MIN($O257,R1_To)-MAX($O256,R1_From))+Rate_2*MAX(0,MIN($O257,R2_To)-MAX($O256,R2_From))+Rate_3*MAX(0,MIN($O257,R3_To)-MAX($O256,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I257&lt;=0,0,$S256*('Engine'!$B$8*MAX(0,MIN($O257,'Engine'!$B$3)-MAX($O256,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O257,'Engine'!$B$5)-MAX($O256,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O257,'Engine'!$B$7)-MAX($O256,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K257" s="41">
@@ -13393,7 +13376,7 @@
         <v/>
       </c>
       <c r="N257" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O257&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O257&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O257" s="25">
@@ -13424,7 +13407,7 @@
         <v/>
       </c>
       <c r="H258" s="42">
-        <f>IF($I258&lt;=0,"",(Rate_1*MAX(0,MIN($O258,R1_To)-MAX($O257,R1_From))+Rate_2*MAX(0,MIN($O258,R2_To)-MAX($O257,R2_From))+Rate_3*MAX(0,MIN($O258,R3_To)-MAX($O257,R3_From)))/100/Day_Basis/$I258*Day_Basis*100)</f>
+        <f>IF($I258&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O258,'Engine'!$B$3)-MAX($O257,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O258,'Engine'!$B$5)-MAX($O257,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O258,'Engine'!$B$7)-MAX($O257,'Engine'!$B$6)))/100/$H$8/$I258*$H$8*100)</f>
         <v/>
       </c>
       <c r="I258" s="43">
@@ -13432,7 +13415,7 @@
         <v/>
       </c>
       <c r="J258" s="41">
-        <f>IF($I258&lt;=0,0,$S257*(Rate_1*MAX(0,MIN($O258,R1_To)-MAX($O257,R1_From))+Rate_2*MAX(0,MIN($O258,R2_To)-MAX($O257,R2_From))+Rate_3*MAX(0,MIN($O258,R3_To)-MAX($O257,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I258&lt;=0,0,$S257*('Engine'!$B$8*MAX(0,MIN($O258,'Engine'!$B$3)-MAX($O257,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O258,'Engine'!$B$5)-MAX($O257,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O258,'Engine'!$B$7)-MAX($O257,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K258" s="41">
@@ -13445,7 +13428,7 @@
         <v/>
       </c>
       <c r="N258" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O258&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O258&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O258" s="25">
@@ -13476,7 +13459,7 @@
         <v/>
       </c>
       <c r="H259" s="42">
-        <f>IF($I259&lt;=0,"",(Rate_1*MAX(0,MIN($O259,R1_To)-MAX($O258,R1_From))+Rate_2*MAX(0,MIN($O259,R2_To)-MAX($O258,R2_From))+Rate_3*MAX(0,MIN($O259,R3_To)-MAX($O258,R3_From)))/100/Day_Basis/$I259*Day_Basis*100)</f>
+        <f>IF($I259&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O259,'Engine'!$B$3)-MAX($O258,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O259,'Engine'!$B$5)-MAX($O258,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O259,'Engine'!$B$7)-MAX($O258,'Engine'!$B$6)))/100/$H$8/$I259*$H$8*100)</f>
         <v/>
       </c>
       <c r="I259" s="43">
@@ -13484,7 +13467,7 @@
         <v/>
       </c>
       <c r="J259" s="41">
-        <f>IF($I259&lt;=0,0,$S258*(Rate_1*MAX(0,MIN($O259,R1_To)-MAX($O258,R1_From))+Rate_2*MAX(0,MIN($O259,R2_To)-MAX($O258,R2_From))+Rate_3*MAX(0,MIN($O259,R3_To)-MAX($O258,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I259&lt;=0,0,$S258*('Engine'!$B$8*MAX(0,MIN($O259,'Engine'!$B$3)-MAX($O258,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O259,'Engine'!$B$5)-MAX($O258,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O259,'Engine'!$B$7)-MAX($O258,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K259" s="41">
@@ -13497,7 +13480,7 @@
         <v/>
       </c>
       <c r="N259" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O259&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O259&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O259" s="25">
@@ -13538,7 +13521,7 @@
         <v/>
       </c>
       <c r="H260" s="51">
-        <f>IF($I260&lt;=0,"",(Rate_1*MAX(0,MIN($O260,R1_To)-MAX($O259,R1_From))+Rate_2*MAX(0,MIN($O260,R2_To)-MAX($O259,R2_From))+Rate_3*MAX(0,MIN($O260,R3_To)-MAX($O259,R3_From)))/100/Day_Basis/$I260*Day_Basis*100)</f>
+        <f>IF($I260&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O260,'Engine'!$B$3)-MAX($O259,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O260,'Engine'!$B$5)-MAX($O259,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O260,'Engine'!$B$7)-MAX($O259,'Engine'!$B$6)))/100/$H$8/$I260*$H$8*100)</f>
         <v/>
       </c>
       <c r="I260" s="52">
@@ -13546,7 +13529,7 @@
         <v/>
       </c>
       <c r="J260" s="53">
-        <f>IF($I260&lt;=0,0,$S259*(Rate_1*MAX(0,MIN($O260,R1_To)-MAX($O259,R1_From))+Rate_2*MAX(0,MIN($O260,R2_To)-MAX($O259,R2_From))+Rate_3*MAX(0,MIN($O260,R3_To)-MAX($O259,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I260&lt;=0,0,$S259*('Engine'!$B$8*MAX(0,MIN($O260,'Engine'!$B$3)-MAX($O259,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O260,'Engine'!$B$5)-MAX($O259,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O260,'Engine'!$B$7)-MAX($O259,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K260" s="53" t="n">
@@ -13558,7 +13541,7 @@
         <v/>
       </c>
       <c r="N260" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O260&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O260&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O260" s="25">
@@ -13575,7 +13558,7 @@
     </row>
     <row r="261" ht="18" customHeight="1">
       <c r="A261" s="24">
-        <f>IF($P$261=0,"QUARTER 20          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 20          "&amp;TEXT($P$261,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$261,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$261&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$261)</f>
+        <f>IF($P$261=0,"QUARTER 20          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 20          "&amp;TEXT($P$261,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$261,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$261&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$261)</f>
         <v/>
       </c>
       <c r="O261" s="25">
@@ -13633,7 +13616,7 @@
         <v/>
       </c>
       <c r="N262" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$262&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$262&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O262" s="25">
@@ -13663,7 +13646,7 @@
         <v/>
       </c>
       <c r="H263" s="42">
-        <f>IF($I263&lt;=0,"",(Rate_1*MAX(0,MIN($O263,R1_To)-MAX($O262,R1_From))+Rate_2*MAX(0,MIN($O263,R2_To)-MAX($O262,R2_From))+Rate_3*MAX(0,MIN($O263,R3_To)-MAX($O262,R3_From)))/100/Day_Basis/$I263*Day_Basis*100)</f>
+        <f>IF($I263&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O263,'Engine'!$B$3)-MAX($O262,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O263,'Engine'!$B$5)-MAX($O262,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O263,'Engine'!$B$7)-MAX($O262,'Engine'!$B$6)))/100/$H$8/$I263*$H$8*100)</f>
         <v/>
       </c>
       <c r="I263" s="43">
@@ -13671,7 +13654,7 @@
         <v/>
       </c>
       <c r="J263" s="41">
-        <f>IF($I263&lt;=0,0,$S262*(Rate_1*MAX(0,MIN($O263,R1_To)-MAX($O262,R1_From))+Rate_2*MAX(0,MIN($O263,R2_To)-MAX($O262,R2_From))+Rate_3*MAX(0,MIN($O263,R3_To)-MAX($O262,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I263&lt;=0,0,$S262*('Engine'!$B$8*MAX(0,MIN($O263,'Engine'!$B$3)-MAX($O262,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O263,'Engine'!$B$5)-MAX($O262,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O263,'Engine'!$B$7)-MAX($O262,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K263" s="41">
@@ -13684,7 +13667,7 @@
         <v/>
       </c>
       <c r="N263" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O263&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O263&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O263" s="25">
@@ -13715,7 +13698,7 @@
         <v/>
       </c>
       <c r="H264" s="42">
-        <f>IF($I264&lt;=0,"",(Rate_1*MAX(0,MIN($O264,R1_To)-MAX($O263,R1_From))+Rate_2*MAX(0,MIN($O264,R2_To)-MAX($O263,R2_From))+Rate_3*MAX(0,MIN($O264,R3_To)-MAX($O263,R3_From)))/100/Day_Basis/$I264*Day_Basis*100)</f>
+        <f>IF($I264&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O264,'Engine'!$B$3)-MAX($O263,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O264,'Engine'!$B$5)-MAX($O263,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O264,'Engine'!$B$7)-MAX($O263,'Engine'!$B$6)))/100/$H$8/$I264*$H$8*100)</f>
         <v/>
       </c>
       <c r="I264" s="43">
@@ -13723,7 +13706,7 @@
         <v/>
       </c>
       <c r="J264" s="41">
-        <f>IF($I264&lt;=0,0,$S263*(Rate_1*MAX(0,MIN($O264,R1_To)-MAX($O263,R1_From))+Rate_2*MAX(0,MIN($O264,R2_To)-MAX($O263,R2_From))+Rate_3*MAX(0,MIN($O264,R3_To)-MAX($O263,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I264&lt;=0,0,$S263*('Engine'!$B$8*MAX(0,MIN($O264,'Engine'!$B$3)-MAX($O263,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O264,'Engine'!$B$5)-MAX($O263,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O264,'Engine'!$B$7)-MAX($O263,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K264" s="41">
@@ -13736,7 +13719,7 @@
         <v/>
       </c>
       <c r="N264" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O264&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O264&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O264" s="25">
@@ -13767,7 +13750,7 @@
         <v/>
       </c>
       <c r="H265" s="42">
-        <f>IF($I265&lt;=0,"",(Rate_1*MAX(0,MIN($O265,R1_To)-MAX($O264,R1_From))+Rate_2*MAX(0,MIN($O265,R2_To)-MAX($O264,R2_From))+Rate_3*MAX(0,MIN($O265,R3_To)-MAX($O264,R3_From)))/100/Day_Basis/$I265*Day_Basis*100)</f>
+        <f>IF($I265&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O265,'Engine'!$B$3)-MAX($O264,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O265,'Engine'!$B$5)-MAX($O264,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O265,'Engine'!$B$7)-MAX($O264,'Engine'!$B$6)))/100/$H$8/$I265*$H$8*100)</f>
         <v/>
       </c>
       <c r="I265" s="43">
@@ -13775,7 +13758,7 @@
         <v/>
       </c>
       <c r="J265" s="41">
-        <f>IF($I265&lt;=0,0,$S264*(Rate_1*MAX(0,MIN($O265,R1_To)-MAX($O264,R1_From))+Rate_2*MAX(0,MIN($O265,R2_To)-MAX($O264,R2_From))+Rate_3*MAX(0,MIN($O265,R3_To)-MAX($O264,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I265&lt;=0,0,$S264*('Engine'!$B$8*MAX(0,MIN($O265,'Engine'!$B$3)-MAX($O264,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O265,'Engine'!$B$5)-MAX($O264,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O265,'Engine'!$B$7)-MAX($O264,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K265" s="41">
@@ -13788,7 +13771,7 @@
         <v/>
       </c>
       <c r="N265" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O265&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O265&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O265" s="25">
@@ -13819,7 +13802,7 @@
         <v/>
       </c>
       <c r="H266" s="42">
-        <f>IF($I266&lt;=0,"",(Rate_1*MAX(0,MIN($O266,R1_To)-MAX($O265,R1_From))+Rate_2*MAX(0,MIN($O266,R2_To)-MAX($O265,R2_From))+Rate_3*MAX(0,MIN($O266,R3_To)-MAX($O265,R3_From)))/100/Day_Basis/$I266*Day_Basis*100)</f>
+        <f>IF($I266&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O266,'Engine'!$B$3)-MAX($O265,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O266,'Engine'!$B$5)-MAX($O265,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O266,'Engine'!$B$7)-MAX($O265,'Engine'!$B$6)))/100/$H$8/$I266*$H$8*100)</f>
         <v/>
       </c>
       <c r="I266" s="43">
@@ -13827,7 +13810,7 @@
         <v/>
       </c>
       <c r="J266" s="41">
-        <f>IF($I266&lt;=0,0,$S265*(Rate_1*MAX(0,MIN($O266,R1_To)-MAX($O265,R1_From))+Rate_2*MAX(0,MIN($O266,R2_To)-MAX($O265,R2_From))+Rate_3*MAX(0,MIN($O266,R3_To)-MAX($O265,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I266&lt;=0,0,$S265*('Engine'!$B$8*MAX(0,MIN($O266,'Engine'!$B$3)-MAX($O265,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O266,'Engine'!$B$5)-MAX($O265,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O266,'Engine'!$B$7)-MAX($O265,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K266" s="41">
@@ -13840,7 +13823,7 @@
         <v/>
       </c>
       <c r="N266" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O266&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O266&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O266" s="25">
@@ -13871,7 +13854,7 @@
         <v/>
       </c>
       <c r="H267" s="42">
-        <f>IF($I267&lt;=0,"",(Rate_1*MAX(0,MIN($O267,R1_To)-MAX($O266,R1_From))+Rate_2*MAX(0,MIN($O267,R2_To)-MAX($O266,R2_From))+Rate_3*MAX(0,MIN($O267,R3_To)-MAX($O266,R3_From)))/100/Day_Basis/$I267*Day_Basis*100)</f>
+        <f>IF($I267&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O267,'Engine'!$B$3)-MAX($O266,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O267,'Engine'!$B$5)-MAX($O266,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O267,'Engine'!$B$7)-MAX($O266,'Engine'!$B$6)))/100/$H$8/$I267*$H$8*100)</f>
         <v/>
       </c>
       <c r="I267" s="43">
@@ -13879,7 +13862,7 @@
         <v/>
       </c>
       <c r="J267" s="41">
-        <f>IF($I267&lt;=0,0,$S266*(Rate_1*MAX(0,MIN($O267,R1_To)-MAX($O266,R1_From))+Rate_2*MAX(0,MIN($O267,R2_To)-MAX($O266,R2_From))+Rate_3*MAX(0,MIN($O267,R3_To)-MAX($O266,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I267&lt;=0,0,$S266*('Engine'!$B$8*MAX(0,MIN($O267,'Engine'!$B$3)-MAX($O266,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O267,'Engine'!$B$5)-MAX($O266,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O267,'Engine'!$B$7)-MAX($O266,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K267" s="41">
@@ -13892,7 +13875,7 @@
         <v/>
       </c>
       <c r="N267" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O267&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O267&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O267" s="25">
@@ -13923,7 +13906,7 @@
         <v/>
       </c>
       <c r="H268" s="42">
-        <f>IF($I268&lt;=0,"",(Rate_1*MAX(0,MIN($O268,R1_To)-MAX($O267,R1_From))+Rate_2*MAX(0,MIN($O268,R2_To)-MAX($O267,R2_From))+Rate_3*MAX(0,MIN($O268,R3_To)-MAX($O267,R3_From)))/100/Day_Basis/$I268*Day_Basis*100)</f>
+        <f>IF($I268&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O268,'Engine'!$B$3)-MAX($O267,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O268,'Engine'!$B$5)-MAX($O267,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O268,'Engine'!$B$7)-MAX($O267,'Engine'!$B$6)))/100/$H$8/$I268*$H$8*100)</f>
         <v/>
       </c>
       <c r="I268" s="43">
@@ -13931,7 +13914,7 @@
         <v/>
       </c>
       <c r="J268" s="41">
-        <f>IF($I268&lt;=0,0,$S267*(Rate_1*MAX(0,MIN($O268,R1_To)-MAX($O267,R1_From))+Rate_2*MAX(0,MIN($O268,R2_To)-MAX($O267,R2_From))+Rate_3*MAX(0,MIN($O268,R3_To)-MAX($O267,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I268&lt;=0,0,$S267*('Engine'!$B$8*MAX(0,MIN($O268,'Engine'!$B$3)-MAX($O267,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O268,'Engine'!$B$5)-MAX($O267,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O268,'Engine'!$B$7)-MAX($O267,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K268" s="41">
@@ -13944,7 +13927,7 @@
         <v/>
       </c>
       <c r="N268" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O268&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O268&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O268" s="25">
@@ -13975,7 +13958,7 @@
         <v/>
       </c>
       <c r="H269" s="42">
-        <f>IF($I269&lt;=0,"",(Rate_1*MAX(0,MIN($O269,R1_To)-MAX($O268,R1_From))+Rate_2*MAX(0,MIN($O269,R2_To)-MAX($O268,R2_From))+Rate_3*MAX(0,MIN($O269,R3_To)-MAX($O268,R3_From)))/100/Day_Basis/$I269*Day_Basis*100)</f>
+        <f>IF($I269&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O269,'Engine'!$B$3)-MAX($O268,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O269,'Engine'!$B$5)-MAX($O268,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O269,'Engine'!$B$7)-MAX($O268,'Engine'!$B$6)))/100/$H$8/$I269*$H$8*100)</f>
         <v/>
       </c>
       <c r="I269" s="43">
@@ -13983,7 +13966,7 @@
         <v/>
       </c>
       <c r="J269" s="41">
-        <f>IF($I269&lt;=0,0,$S268*(Rate_1*MAX(0,MIN($O269,R1_To)-MAX($O268,R1_From))+Rate_2*MAX(0,MIN($O269,R2_To)-MAX($O268,R2_From))+Rate_3*MAX(0,MIN($O269,R3_To)-MAX($O268,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I269&lt;=0,0,$S268*('Engine'!$B$8*MAX(0,MIN($O269,'Engine'!$B$3)-MAX($O268,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O269,'Engine'!$B$5)-MAX($O268,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O269,'Engine'!$B$7)-MAX($O268,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K269" s="41">
@@ -13996,7 +13979,7 @@
         <v/>
       </c>
       <c r="N269" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O269&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O269&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O269" s="25">
@@ -14027,7 +14010,7 @@
         <v/>
       </c>
       <c r="H270" s="42">
-        <f>IF($I270&lt;=0,"",(Rate_1*MAX(0,MIN($O270,R1_To)-MAX($O269,R1_From))+Rate_2*MAX(0,MIN($O270,R2_To)-MAX($O269,R2_From))+Rate_3*MAX(0,MIN($O270,R3_To)-MAX($O269,R3_From)))/100/Day_Basis/$I270*Day_Basis*100)</f>
+        <f>IF($I270&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O270,'Engine'!$B$3)-MAX($O269,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O270,'Engine'!$B$5)-MAX($O269,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O270,'Engine'!$B$7)-MAX($O269,'Engine'!$B$6)))/100/$H$8/$I270*$H$8*100)</f>
         <v/>
       </c>
       <c r="I270" s="43">
@@ -14035,7 +14018,7 @@
         <v/>
       </c>
       <c r="J270" s="41">
-        <f>IF($I270&lt;=0,0,$S269*(Rate_1*MAX(0,MIN($O270,R1_To)-MAX($O269,R1_From))+Rate_2*MAX(0,MIN($O270,R2_To)-MAX($O269,R2_From))+Rate_3*MAX(0,MIN($O270,R3_To)-MAX($O269,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I270&lt;=0,0,$S269*('Engine'!$B$8*MAX(0,MIN($O270,'Engine'!$B$3)-MAX($O269,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O270,'Engine'!$B$5)-MAX($O269,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O270,'Engine'!$B$7)-MAX($O269,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K270" s="41">
@@ -14048,7 +14031,7 @@
         <v/>
       </c>
       <c r="N270" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O270&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O270&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O270" s="25">
@@ -14079,7 +14062,7 @@
         <v/>
       </c>
       <c r="H271" s="42">
-        <f>IF($I271&lt;=0,"",(Rate_1*MAX(0,MIN($O271,R1_To)-MAX($O270,R1_From))+Rate_2*MAX(0,MIN($O271,R2_To)-MAX($O270,R2_From))+Rate_3*MAX(0,MIN($O271,R3_To)-MAX($O270,R3_From)))/100/Day_Basis/$I271*Day_Basis*100)</f>
+        <f>IF($I271&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O271,'Engine'!$B$3)-MAX($O270,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O271,'Engine'!$B$5)-MAX($O270,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O271,'Engine'!$B$7)-MAX($O270,'Engine'!$B$6)))/100/$H$8/$I271*$H$8*100)</f>
         <v/>
       </c>
       <c r="I271" s="43">
@@ -14087,7 +14070,7 @@
         <v/>
       </c>
       <c r="J271" s="41">
-        <f>IF($I271&lt;=0,0,$S270*(Rate_1*MAX(0,MIN($O271,R1_To)-MAX($O270,R1_From))+Rate_2*MAX(0,MIN($O271,R2_To)-MAX($O270,R2_From))+Rate_3*MAX(0,MIN($O271,R3_To)-MAX($O270,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I271&lt;=0,0,$S270*('Engine'!$B$8*MAX(0,MIN($O271,'Engine'!$B$3)-MAX($O270,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O271,'Engine'!$B$5)-MAX($O270,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O271,'Engine'!$B$7)-MAX($O270,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K271" s="41">
@@ -14100,7 +14083,7 @@
         <v/>
       </c>
       <c r="N271" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O271&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O271&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O271" s="25">
@@ -14131,7 +14114,7 @@
         <v/>
       </c>
       <c r="H272" s="42">
-        <f>IF($I272&lt;=0,"",(Rate_1*MAX(0,MIN($O272,R1_To)-MAX($O271,R1_From))+Rate_2*MAX(0,MIN($O272,R2_To)-MAX($O271,R2_From))+Rate_3*MAX(0,MIN($O272,R3_To)-MAX($O271,R3_From)))/100/Day_Basis/$I272*Day_Basis*100)</f>
+        <f>IF($I272&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O272,'Engine'!$B$3)-MAX($O271,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O272,'Engine'!$B$5)-MAX($O271,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O272,'Engine'!$B$7)-MAX($O271,'Engine'!$B$6)))/100/$H$8/$I272*$H$8*100)</f>
         <v/>
       </c>
       <c r="I272" s="43">
@@ -14139,7 +14122,7 @@
         <v/>
       </c>
       <c r="J272" s="41">
-        <f>IF($I272&lt;=0,0,$S271*(Rate_1*MAX(0,MIN($O272,R1_To)-MAX($O271,R1_From))+Rate_2*MAX(0,MIN($O272,R2_To)-MAX($O271,R2_From))+Rate_3*MAX(0,MIN($O272,R3_To)-MAX($O271,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I272&lt;=0,0,$S271*('Engine'!$B$8*MAX(0,MIN($O272,'Engine'!$B$3)-MAX($O271,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O272,'Engine'!$B$5)-MAX($O271,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O272,'Engine'!$B$7)-MAX($O271,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K272" s="41">
@@ -14152,7 +14135,7 @@
         <v/>
       </c>
       <c r="N272" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O272&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O272&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O272" s="25">
@@ -14193,7 +14176,7 @@
         <v/>
       </c>
       <c r="H273" s="51">
-        <f>IF($I273&lt;=0,"",(Rate_1*MAX(0,MIN($O273,R1_To)-MAX($O272,R1_From))+Rate_2*MAX(0,MIN($O273,R2_To)-MAX($O272,R2_From))+Rate_3*MAX(0,MIN($O273,R3_To)-MAX($O272,R3_From)))/100/Day_Basis/$I273*Day_Basis*100)</f>
+        <f>IF($I273&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O273,'Engine'!$B$3)-MAX($O272,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O273,'Engine'!$B$5)-MAX($O272,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O273,'Engine'!$B$7)-MAX($O272,'Engine'!$B$6)))/100/$H$8/$I273*$H$8*100)</f>
         <v/>
       </c>
       <c r="I273" s="52">
@@ -14201,7 +14184,7 @@
         <v/>
       </c>
       <c r="J273" s="53">
-        <f>IF($I273&lt;=0,0,$S272*(Rate_1*MAX(0,MIN($O273,R1_To)-MAX($O272,R1_From))+Rate_2*MAX(0,MIN($O273,R2_To)-MAX($O272,R2_From))+Rate_3*MAX(0,MIN($O273,R3_To)-MAX($O272,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I273&lt;=0,0,$S272*('Engine'!$B$8*MAX(0,MIN($O273,'Engine'!$B$3)-MAX($O272,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O273,'Engine'!$B$5)-MAX($O272,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O273,'Engine'!$B$7)-MAX($O272,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K273" s="53" t="n">
@@ -14213,7 +14196,7 @@
         <v/>
       </c>
       <c r="N273" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O273&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O273&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O273" s="25">
@@ -14230,7 +14213,7 @@
     </row>
     <row r="274" ht="18" customHeight="1">
       <c r="A274" s="24">
-        <f>IF($P$274=0,"QUARTER 21          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 21          "&amp;TEXT($P$274,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$274,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$274&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$274)</f>
+        <f>IF($P$274=0,"QUARTER 21          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 21          "&amp;TEXT($P$274,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$274,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$274&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$274)</f>
         <v/>
       </c>
       <c r="O274" s="25">
@@ -14288,7 +14271,7 @@
         <v/>
       </c>
       <c r="N275" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$275&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$275&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O275" s="25">
@@ -14318,7 +14301,7 @@
         <v/>
       </c>
       <c r="H276" s="42">
-        <f>IF($I276&lt;=0,"",(Rate_1*MAX(0,MIN($O276,R1_To)-MAX($O275,R1_From))+Rate_2*MAX(0,MIN($O276,R2_To)-MAX($O275,R2_From))+Rate_3*MAX(0,MIN($O276,R3_To)-MAX($O275,R3_From)))/100/Day_Basis/$I276*Day_Basis*100)</f>
+        <f>IF($I276&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O276,'Engine'!$B$3)-MAX($O275,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O276,'Engine'!$B$5)-MAX($O275,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O276,'Engine'!$B$7)-MAX($O275,'Engine'!$B$6)))/100/$H$8/$I276*$H$8*100)</f>
         <v/>
       </c>
       <c r="I276" s="43">
@@ -14326,7 +14309,7 @@
         <v/>
       </c>
       <c r="J276" s="41">
-        <f>IF($I276&lt;=0,0,$S275*(Rate_1*MAX(0,MIN($O276,R1_To)-MAX($O275,R1_From))+Rate_2*MAX(0,MIN($O276,R2_To)-MAX($O275,R2_From))+Rate_3*MAX(0,MIN($O276,R3_To)-MAX($O275,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I276&lt;=0,0,$S275*('Engine'!$B$8*MAX(0,MIN($O276,'Engine'!$B$3)-MAX($O275,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O276,'Engine'!$B$5)-MAX($O275,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O276,'Engine'!$B$7)-MAX($O275,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K276" s="41">
@@ -14339,7 +14322,7 @@
         <v/>
       </c>
       <c r="N276" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O276&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O276&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O276" s="25">
@@ -14370,7 +14353,7 @@
         <v/>
       </c>
       <c r="H277" s="42">
-        <f>IF($I277&lt;=0,"",(Rate_1*MAX(0,MIN($O277,R1_To)-MAX($O276,R1_From))+Rate_2*MAX(0,MIN($O277,R2_To)-MAX($O276,R2_From))+Rate_3*MAX(0,MIN($O277,R3_To)-MAX($O276,R3_From)))/100/Day_Basis/$I277*Day_Basis*100)</f>
+        <f>IF($I277&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O277,'Engine'!$B$3)-MAX($O276,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O277,'Engine'!$B$5)-MAX($O276,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O277,'Engine'!$B$7)-MAX($O276,'Engine'!$B$6)))/100/$H$8/$I277*$H$8*100)</f>
         <v/>
       </c>
       <c r="I277" s="43">
@@ -14378,7 +14361,7 @@
         <v/>
       </c>
       <c r="J277" s="41">
-        <f>IF($I277&lt;=0,0,$S276*(Rate_1*MAX(0,MIN($O277,R1_To)-MAX($O276,R1_From))+Rate_2*MAX(0,MIN($O277,R2_To)-MAX($O276,R2_From))+Rate_3*MAX(0,MIN($O277,R3_To)-MAX($O276,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I277&lt;=0,0,$S276*('Engine'!$B$8*MAX(0,MIN($O277,'Engine'!$B$3)-MAX($O276,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O277,'Engine'!$B$5)-MAX($O276,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O277,'Engine'!$B$7)-MAX($O276,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K277" s="41">
@@ -14391,7 +14374,7 @@
         <v/>
       </c>
       <c r="N277" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O277&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O277&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O277" s="25">
@@ -14422,7 +14405,7 @@
         <v/>
       </c>
       <c r="H278" s="42">
-        <f>IF($I278&lt;=0,"",(Rate_1*MAX(0,MIN($O278,R1_To)-MAX($O277,R1_From))+Rate_2*MAX(0,MIN($O278,R2_To)-MAX($O277,R2_From))+Rate_3*MAX(0,MIN($O278,R3_To)-MAX($O277,R3_From)))/100/Day_Basis/$I278*Day_Basis*100)</f>
+        <f>IF($I278&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O278,'Engine'!$B$3)-MAX($O277,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O278,'Engine'!$B$5)-MAX($O277,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O278,'Engine'!$B$7)-MAX($O277,'Engine'!$B$6)))/100/$H$8/$I278*$H$8*100)</f>
         <v/>
       </c>
       <c r="I278" s="43">
@@ -14430,7 +14413,7 @@
         <v/>
       </c>
       <c r="J278" s="41">
-        <f>IF($I278&lt;=0,0,$S277*(Rate_1*MAX(0,MIN($O278,R1_To)-MAX($O277,R1_From))+Rate_2*MAX(0,MIN($O278,R2_To)-MAX($O277,R2_From))+Rate_3*MAX(0,MIN($O278,R3_To)-MAX($O277,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I278&lt;=0,0,$S277*('Engine'!$B$8*MAX(0,MIN($O278,'Engine'!$B$3)-MAX($O277,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O278,'Engine'!$B$5)-MAX($O277,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O278,'Engine'!$B$7)-MAX($O277,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K278" s="41">
@@ -14443,7 +14426,7 @@
         <v/>
       </c>
       <c r="N278" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O278&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O278&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O278" s="25">
@@ -14474,7 +14457,7 @@
         <v/>
       </c>
       <c r="H279" s="42">
-        <f>IF($I279&lt;=0,"",(Rate_1*MAX(0,MIN($O279,R1_To)-MAX($O278,R1_From))+Rate_2*MAX(0,MIN($O279,R2_To)-MAX($O278,R2_From))+Rate_3*MAX(0,MIN($O279,R3_To)-MAX($O278,R3_From)))/100/Day_Basis/$I279*Day_Basis*100)</f>
+        <f>IF($I279&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O279,'Engine'!$B$3)-MAX($O278,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O279,'Engine'!$B$5)-MAX($O278,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O279,'Engine'!$B$7)-MAX($O278,'Engine'!$B$6)))/100/$H$8/$I279*$H$8*100)</f>
         <v/>
       </c>
       <c r="I279" s="43">
@@ -14482,7 +14465,7 @@
         <v/>
       </c>
       <c r="J279" s="41">
-        <f>IF($I279&lt;=0,0,$S278*(Rate_1*MAX(0,MIN($O279,R1_To)-MAX($O278,R1_From))+Rate_2*MAX(0,MIN($O279,R2_To)-MAX($O278,R2_From))+Rate_3*MAX(0,MIN($O279,R3_To)-MAX($O278,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I279&lt;=0,0,$S278*('Engine'!$B$8*MAX(0,MIN($O279,'Engine'!$B$3)-MAX($O278,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O279,'Engine'!$B$5)-MAX($O278,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O279,'Engine'!$B$7)-MAX($O278,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K279" s="41">
@@ -14495,7 +14478,7 @@
         <v/>
       </c>
       <c r="N279" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O279&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O279&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O279" s="25">
@@ -14526,7 +14509,7 @@
         <v/>
       </c>
       <c r="H280" s="42">
-        <f>IF($I280&lt;=0,"",(Rate_1*MAX(0,MIN($O280,R1_To)-MAX($O279,R1_From))+Rate_2*MAX(0,MIN($O280,R2_To)-MAX($O279,R2_From))+Rate_3*MAX(0,MIN($O280,R3_To)-MAX($O279,R3_From)))/100/Day_Basis/$I280*Day_Basis*100)</f>
+        <f>IF($I280&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O280,'Engine'!$B$3)-MAX($O279,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O280,'Engine'!$B$5)-MAX($O279,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O280,'Engine'!$B$7)-MAX($O279,'Engine'!$B$6)))/100/$H$8/$I280*$H$8*100)</f>
         <v/>
       </c>
       <c r="I280" s="43">
@@ -14534,7 +14517,7 @@
         <v/>
       </c>
       <c r="J280" s="41">
-        <f>IF($I280&lt;=0,0,$S279*(Rate_1*MAX(0,MIN($O280,R1_To)-MAX($O279,R1_From))+Rate_2*MAX(0,MIN($O280,R2_To)-MAX($O279,R2_From))+Rate_3*MAX(0,MIN($O280,R3_To)-MAX($O279,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I280&lt;=0,0,$S279*('Engine'!$B$8*MAX(0,MIN($O280,'Engine'!$B$3)-MAX($O279,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O280,'Engine'!$B$5)-MAX($O279,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O280,'Engine'!$B$7)-MAX($O279,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K280" s="41">
@@ -14547,7 +14530,7 @@
         <v/>
       </c>
       <c r="N280" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O280&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O280&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O280" s="25">
@@ -14578,7 +14561,7 @@
         <v/>
       </c>
       <c r="H281" s="42">
-        <f>IF($I281&lt;=0,"",(Rate_1*MAX(0,MIN($O281,R1_To)-MAX($O280,R1_From))+Rate_2*MAX(0,MIN($O281,R2_To)-MAX($O280,R2_From))+Rate_3*MAX(0,MIN($O281,R3_To)-MAX($O280,R3_From)))/100/Day_Basis/$I281*Day_Basis*100)</f>
+        <f>IF($I281&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O281,'Engine'!$B$3)-MAX($O280,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O281,'Engine'!$B$5)-MAX($O280,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O281,'Engine'!$B$7)-MAX($O280,'Engine'!$B$6)))/100/$H$8/$I281*$H$8*100)</f>
         <v/>
       </c>
       <c r="I281" s="43">
@@ -14586,7 +14569,7 @@
         <v/>
       </c>
       <c r="J281" s="41">
-        <f>IF($I281&lt;=0,0,$S280*(Rate_1*MAX(0,MIN($O281,R1_To)-MAX($O280,R1_From))+Rate_2*MAX(0,MIN($O281,R2_To)-MAX($O280,R2_From))+Rate_3*MAX(0,MIN($O281,R3_To)-MAX($O280,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I281&lt;=0,0,$S280*('Engine'!$B$8*MAX(0,MIN($O281,'Engine'!$B$3)-MAX($O280,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O281,'Engine'!$B$5)-MAX($O280,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O281,'Engine'!$B$7)-MAX($O280,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K281" s="41">
@@ -14599,7 +14582,7 @@
         <v/>
       </c>
       <c r="N281" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O281&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O281&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O281" s="25">
@@ -14630,7 +14613,7 @@
         <v/>
       </c>
       <c r="H282" s="42">
-        <f>IF($I282&lt;=0,"",(Rate_1*MAX(0,MIN($O282,R1_To)-MAX($O281,R1_From))+Rate_2*MAX(0,MIN($O282,R2_To)-MAX($O281,R2_From))+Rate_3*MAX(0,MIN($O282,R3_To)-MAX($O281,R3_From)))/100/Day_Basis/$I282*Day_Basis*100)</f>
+        <f>IF($I282&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O282,'Engine'!$B$3)-MAX($O281,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O282,'Engine'!$B$5)-MAX($O281,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O282,'Engine'!$B$7)-MAX($O281,'Engine'!$B$6)))/100/$H$8/$I282*$H$8*100)</f>
         <v/>
       </c>
       <c r="I282" s="43">
@@ -14638,7 +14621,7 @@
         <v/>
       </c>
       <c r="J282" s="41">
-        <f>IF($I282&lt;=0,0,$S281*(Rate_1*MAX(0,MIN($O282,R1_To)-MAX($O281,R1_From))+Rate_2*MAX(0,MIN($O282,R2_To)-MAX($O281,R2_From))+Rate_3*MAX(0,MIN($O282,R3_To)-MAX($O281,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I282&lt;=0,0,$S281*('Engine'!$B$8*MAX(0,MIN($O282,'Engine'!$B$3)-MAX($O281,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O282,'Engine'!$B$5)-MAX($O281,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O282,'Engine'!$B$7)-MAX($O281,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K282" s="41">
@@ -14651,7 +14634,7 @@
         <v/>
       </c>
       <c r="N282" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O282&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O282&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O282" s="25">
@@ -14682,7 +14665,7 @@
         <v/>
       </c>
       <c r="H283" s="42">
-        <f>IF($I283&lt;=0,"",(Rate_1*MAX(0,MIN($O283,R1_To)-MAX($O282,R1_From))+Rate_2*MAX(0,MIN($O283,R2_To)-MAX($O282,R2_From))+Rate_3*MAX(0,MIN($O283,R3_To)-MAX($O282,R3_From)))/100/Day_Basis/$I283*Day_Basis*100)</f>
+        <f>IF($I283&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O283,'Engine'!$B$3)-MAX($O282,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O283,'Engine'!$B$5)-MAX($O282,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O283,'Engine'!$B$7)-MAX($O282,'Engine'!$B$6)))/100/$H$8/$I283*$H$8*100)</f>
         <v/>
       </c>
       <c r="I283" s="43">
@@ -14690,7 +14673,7 @@
         <v/>
       </c>
       <c r="J283" s="41">
-        <f>IF($I283&lt;=0,0,$S282*(Rate_1*MAX(0,MIN($O283,R1_To)-MAX($O282,R1_From))+Rate_2*MAX(0,MIN($O283,R2_To)-MAX($O282,R2_From))+Rate_3*MAX(0,MIN($O283,R3_To)-MAX($O282,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I283&lt;=0,0,$S282*('Engine'!$B$8*MAX(0,MIN($O283,'Engine'!$B$3)-MAX($O282,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O283,'Engine'!$B$5)-MAX($O282,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O283,'Engine'!$B$7)-MAX($O282,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K283" s="41">
@@ -14703,7 +14686,7 @@
         <v/>
       </c>
       <c r="N283" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O283&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O283&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O283" s="25">
@@ -14734,7 +14717,7 @@
         <v/>
       </c>
       <c r="H284" s="42">
-        <f>IF($I284&lt;=0,"",(Rate_1*MAX(0,MIN($O284,R1_To)-MAX($O283,R1_From))+Rate_2*MAX(0,MIN($O284,R2_To)-MAX($O283,R2_From))+Rate_3*MAX(0,MIN($O284,R3_To)-MAX($O283,R3_From)))/100/Day_Basis/$I284*Day_Basis*100)</f>
+        <f>IF($I284&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O284,'Engine'!$B$3)-MAX($O283,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O284,'Engine'!$B$5)-MAX($O283,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O284,'Engine'!$B$7)-MAX($O283,'Engine'!$B$6)))/100/$H$8/$I284*$H$8*100)</f>
         <v/>
       </c>
       <c r="I284" s="43">
@@ -14742,7 +14725,7 @@
         <v/>
       </c>
       <c r="J284" s="41">
-        <f>IF($I284&lt;=0,0,$S283*(Rate_1*MAX(0,MIN($O284,R1_To)-MAX($O283,R1_From))+Rate_2*MAX(0,MIN($O284,R2_To)-MAX($O283,R2_From))+Rate_3*MAX(0,MIN($O284,R3_To)-MAX($O283,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I284&lt;=0,0,$S283*('Engine'!$B$8*MAX(0,MIN($O284,'Engine'!$B$3)-MAX($O283,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O284,'Engine'!$B$5)-MAX($O283,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O284,'Engine'!$B$7)-MAX($O283,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K284" s="41">
@@ -14755,7 +14738,7 @@
         <v/>
       </c>
       <c r="N284" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O284&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O284&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O284" s="25">
@@ -14786,7 +14769,7 @@
         <v/>
       </c>
       <c r="H285" s="42">
-        <f>IF($I285&lt;=0,"",(Rate_1*MAX(0,MIN($O285,R1_To)-MAX($O284,R1_From))+Rate_2*MAX(0,MIN($O285,R2_To)-MAX($O284,R2_From))+Rate_3*MAX(0,MIN($O285,R3_To)-MAX($O284,R3_From)))/100/Day_Basis/$I285*Day_Basis*100)</f>
+        <f>IF($I285&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O285,'Engine'!$B$3)-MAX($O284,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O285,'Engine'!$B$5)-MAX($O284,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O285,'Engine'!$B$7)-MAX($O284,'Engine'!$B$6)))/100/$H$8/$I285*$H$8*100)</f>
         <v/>
       </c>
       <c r="I285" s="43">
@@ -14794,7 +14777,7 @@
         <v/>
       </c>
       <c r="J285" s="41">
-        <f>IF($I285&lt;=0,0,$S284*(Rate_1*MAX(0,MIN($O285,R1_To)-MAX($O284,R1_From))+Rate_2*MAX(0,MIN($O285,R2_To)-MAX($O284,R2_From))+Rate_3*MAX(0,MIN($O285,R3_To)-MAX($O284,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I285&lt;=0,0,$S284*('Engine'!$B$8*MAX(0,MIN($O285,'Engine'!$B$3)-MAX($O284,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O285,'Engine'!$B$5)-MAX($O284,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O285,'Engine'!$B$7)-MAX($O284,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K285" s="41">
@@ -14807,7 +14790,7 @@
         <v/>
       </c>
       <c r="N285" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O285&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O285&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O285" s="25">
@@ -14848,7 +14831,7 @@
         <v/>
       </c>
       <c r="H286" s="51">
-        <f>IF($I286&lt;=0,"",(Rate_1*MAX(0,MIN($O286,R1_To)-MAX($O285,R1_From))+Rate_2*MAX(0,MIN($O286,R2_To)-MAX($O285,R2_From))+Rate_3*MAX(0,MIN($O286,R3_To)-MAX($O285,R3_From)))/100/Day_Basis/$I286*Day_Basis*100)</f>
+        <f>IF($I286&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O286,'Engine'!$B$3)-MAX($O285,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O286,'Engine'!$B$5)-MAX($O285,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O286,'Engine'!$B$7)-MAX($O285,'Engine'!$B$6)))/100/$H$8/$I286*$H$8*100)</f>
         <v/>
       </c>
       <c r="I286" s="52">
@@ -14856,7 +14839,7 @@
         <v/>
       </c>
       <c r="J286" s="53">
-        <f>IF($I286&lt;=0,0,$S285*(Rate_1*MAX(0,MIN($O286,R1_To)-MAX($O285,R1_From))+Rate_2*MAX(0,MIN($O286,R2_To)-MAX($O285,R2_From))+Rate_3*MAX(0,MIN($O286,R3_To)-MAX($O285,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I286&lt;=0,0,$S285*('Engine'!$B$8*MAX(0,MIN($O286,'Engine'!$B$3)-MAX($O285,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O286,'Engine'!$B$5)-MAX($O285,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O286,'Engine'!$B$7)-MAX($O285,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K286" s="53" t="n">
@@ -14868,7 +14851,7 @@
         <v/>
       </c>
       <c r="N286" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O286&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O286&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O286" s="25">
@@ -14885,7 +14868,7 @@
     </row>
     <row r="287" ht="18" customHeight="1">
       <c r="A287" s="24">
-        <f>IF($P$287=0,"QUARTER 22          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 22          "&amp;TEXT($P$287,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$287,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$287&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$287)</f>
+        <f>IF($P$287=0,"QUARTER 22          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 22          "&amp;TEXT($P$287,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$287,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$287&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$287)</f>
         <v/>
       </c>
       <c r="O287" s="25">
@@ -14943,7 +14926,7 @@
         <v/>
       </c>
       <c r="N288" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$288&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$288&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O288" s="25">
@@ -14973,7 +14956,7 @@
         <v/>
       </c>
       <c r="H289" s="42">
-        <f>IF($I289&lt;=0,"",(Rate_1*MAX(0,MIN($O289,R1_To)-MAX($O288,R1_From))+Rate_2*MAX(0,MIN($O289,R2_To)-MAX($O288,R2_From))+Rate_3*MAX(0,MIN($O289,R3_To)-MAX($O288,R3_From)))/100/Day_Basis/$I289*Day_Basis*100)</f>
+        <f>IF($I289&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O289,'Engine'!$B$3)-MAX($O288,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O289,'Engine'!$B$5)-MAX($O288,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O289,'Engine'!$B$7)-MAX($O288,'Engine'!$B$6)))/100/$H$8/$I289*$H$8*100)</f>
         <v/>
       </c>
       <c r="I289" s="43">
@@ -14981,7 +14964,7 @@
         <v/>
       </c>
       <c r="J289" s="41">
-        <f>IF($I289&lt;=0,0,$S288*(Rate_1*MAX(0,MIN($O289,R1_To)-MAX($O288,R1_From))+Rate_2*MAX(0,MIN($O289,R2_To)-MAX($O288,R2_From))+Rate_3*MAX(0,MIN($O289,R3_To)-MAX($O288,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I289&lt;=0,0,$S288*('Engine'!$B$8*MAX(0,MIN($O289,'Engine'!$B$3)-MAX($O288,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O289,'Engine'!$B$5)-MAX($O288,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O289,'Engine'!$B$7)-MAX($O288,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K289" s="41">
@@ -14994,7 +14977,7 @@
         <v/>
       </c>
       <c r="N289" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O289&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O289&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O289" s="25">
@@ -15025,7 +15008,7 @@
         <v/>
       </c>
       <c r="H290" s="42">
-        <f>IF($I290&lt;=0,"",(Rate_1*MAX(0,MIN($O290,R1_To)-MAX($O289,R1_From))+Rate_2*MAX(0,MIN($O290,R2_To)-MAX($O289,R2_From))+Rate_3*MAX(0,MIN($O290,R3_To)-MAX($O289,R3_From)))/100/Day_Basis/$I290*Day_Basis*100)</f>
+        <f>IF($I290&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O290,'Engine'!$B$3)-MAX($O289,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O290,'Engine'!$B$5)-MAX($O289,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O290,'Engine'!$B$7)-MAX($O289,'Engine'!$B$6)))/100/$H$8/$I290*$H$8*100)</f>
         <v/>
       </c>
       <c r="I290" s="43">
@@ -15033,7 +15016,7 @@
         <v/>
       </c>
       <c r="J290" s="41">
-        <f>IF($I290&lt;=0,0,$S289*(Rate_1*MAX(0,MIN($O290,R1_To)-MAX($O289,R1_From))+Rate_2*MAX(0,MIN($O290,R2_To)-MAX($O289,R2_From))+Rate_3*MAX(0,MIN($O290,R3_To)-MAX($O289,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I290&lt;=0,0,$S289*('Engine'!$B$8*MAX(0,MIN($O290,'Engine'!$B$3)-MAX($O289,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O290,'Engine'!$B$5)-MAX($O289,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O290,'Engine'!$B$7)-MAX($O289,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K290" s="41">
@@ -15046,7 +15029,7 @@
         <v/>
       </c>
       <c r="N290" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O290&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O290&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O290" s="25">
@@ -15077,7 +15060,7 @@
         <v/>
       </c>
       <c r="H291" s="42">
-        <f>IF($I291&lt;=0,"",(Rate_1*MAX(0,MIN($O291,R1_To)-MAX($O290,R1_From))+Rate_2*MAX(0,MIN($O291,R2_To)-MAX($O290,R2_From))+Rate_3*MAX(0,MIN($O291,R3_To)-MAX($O290,R3_From)))/100/Day_Basis/$I291*Day_Basis*100)</f>
+        <f>IF($I291&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O291,'Engine'!$B$3)-MAX($O290,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O291,'Engine'!$B$5)-MAX($O290,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O291,'Engine'!$B$7)-MAX($O290,'Engine'!$B$6)))/100/$H$8/$I291*$H$8*100)</f>
         <v/>
       </c>
       <c r="I291" s="43">
@@ -15085,7 +15068,7 @@
         <v/>
       </c>
       <c r="J291" s="41">
-        <f>IF($I291&lt;=0,0,$S290*(Rate_1*MAX(0,MIN($O291,R1_To)-MAX($O290,R1_From))+Rate_2*MAX(0,MIN($O291,R2_To)-MAX($O290,R2_From))+Rate_3*MAX(0,MIN($O291,R3_To)-MAX($O290,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I291&lt;=0,0,$S290*('Engine'!$B$8*MAX(0,MIN($O291,'Engine'!$B$3)-MAX($O290,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O291,'Engine'!$B$5)-MAX($O290,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O291,'Engine'!$B$7)-MAX($O290,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K291" s="41">
@@ -15098,7 +15081,7 @@
         <v/>
       </c>
       <c r="N291" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O291&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O291&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O291" s="25">
@@ -15129,7 +15112,7 @@
         <v/>
       </c>
       <c r="H292" s="42">
-        <f>IF($I292&lt;=0,"",(Rate_1*MAX(0,MIN($O292,R1_To)-MAX($O291,R1_From))+Rate_2*MAX(0,MIN($O292,R2_To)-MAX($O291,R2_From))+Rate_3*MAX(0,MIN($O292,R3_To)-MAX($O291,R3_From)))/100/Day_Basis/$I292*Day_Basis*100)</f>
+        <f>IF($I292&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O292,'Engine'!$B$3)-MAX($O291,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O292,'Engine'!$B$5)-MAX($O291,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O292,'Engine'!$B$7)-MAX($O291,'Engine'!$B$6)))/100/$H$8/$I292*$H$8*100)</f>
         <v/>
       </c>
       <c r="I292" s="43">
@@ -15137,7 +15120,7 @@
         <v/>
       </c>
       <c r="J292" s="41">
-        <f>IF($I292&lt;=0,0,$S291*(Rate_1*MAX(0,MIN($O292,R1_To)-MAX($O291,R1_From))+Rate_2*MAX(0,MIN($O292,R2_To)-MAX($O291,R2_From))+Rate_3*MAX(0,MIN($O292,R3_To)-MAX($O291,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I292&lt;=0,0,$S291*('Engine'!$B$8*MAX(0,MIN($O292,'Engine'!$B$3)-MAX($O291,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O292,'Engine'!$B$5)-MAX($O291,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O292,'Engine'!$B$7)-MAX($O291,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K292" s="41">
@@ -15150,7 +15133,7 @@
         <v/>
       </c>
       <c r="N292" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O292&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O292&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O292" s="25">
@@ -15181,7 +15164,7 @@
         <v/>
       </c>
       <c r="H293" s="42">
-        <f>IF($I293&lt;=0,"",(Rate_1*MAX(0,MIN($O293,R1_To)-MAX($O292,R1_From))+Rate_2*MAX(0,MIN($O293,R2_To)-MAX($O292,R2_From))+Rate_3*MAX(0,MIN($O293,R3_To)-MAX($O292,R3_From)))/100/Day_Basis/$I293*Day_Basis*100)</f>
+        <f>IF($I293&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O293,'Engine'!$B$3)-MAX($O292,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O293,'Engine'!$B$5)-MAX($O292,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O293,'Engine'!$B$7)-MAX($O292,'Engine'!$B$6)))/100/$H$8/$I293*$H$8*100)</f>
         <v/>
       </c>
       <c r="I293" s="43">
@@ -15189,7 +15172,7 @@
         <v/>
       </c>
       <c r="J293" s="41">
-        <f>IF($I293&lt;=0,0,$S292*(Rate_1*MAX(0,MIN($O293,R1_To)-MAX($O292,R1_From))+Rate_2*MAX(0,MIN($O293,R2_To)-MAX($O292,R2_From))+Rate_3*MAX(0,MIN($O293,R3_To)-MAX($O292,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I293&lt;=0,0,$S292*('Engine'!$B$8*MAX(0,MIN($O293,'Engine'!$B$3)-MAX($O292,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O293,'Engine'!$B$5)-MAX($O292,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O293,'Engine'!$B$7)-MAX($O292,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K293" s="41">
@@ -15202,7 +15185,7 @@
         <v/>
       </c>
       <c r="N293" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O293&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O293&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O293" s="25">
@@ -15233,7 +15216,7 @@
         <v/>
       </c>
       <c r="H294" s="42">
-        <f>IF($I294&lt;=0,"",(Rate_1*MAX(0,MIN($O294,R1_To)-MAX($O293,R1_From))+Rate_2*MAX(0,MIN($O294,R2_To)-MAX($O293,R2_From))+Rate_3*MAX(0,MIN($O294,R3_To)-MAX($O293,R3_From)))/100/Day_Basis/$I294*Day_Basis*100)</f>
+        <f>IF($I294&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O294,'Engine'!$B$3)-MAX($O293,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O294,'Engine'!$B$5)-MAX($O293,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O294,'Engine'!$B$7)-MAX($O293,'Engine'!$B$6)))/100/$H$8/$I294*$H$8*100)</f>
         <v/>
       </c>
       <c r="I294" s="43">
@@ -15241,7 +15224,7 @@
         <v/>
       </c>
       <c r="J294" s="41">
-        <f>IF($I294&lt;=0,0,$S293*(Rate_1*MAX(0,MIN($O294,R1_To)-MAX($O293,R1_From))+Rate_2*MAX(0,MIN($O294,R2_To)-MAX($O293,R2_From))+Rate_3*MAX(0,MIN($O294,R3_To)-MAX($O293,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I294&lt;=0,0,$S293*('Engine'!$B$8*MAX(0,MIN($O294,'Engine'!$B$3)-MAX($O293,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O294,'Engine'!$B$5)-MAX($O293,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O294,'Engine'!$B$7)-MAX($O293,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K294" s="41">
@@ -15254,7 +15237,7 @@
         <v/>
       </c>
       <c r="N294" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O294&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O294&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O294" s="25">
@@ -15285,7 +15268,7 @@
         <v/>
       </c>
       <c r="H295" s="42">
-        <f>IF($I295&lt;=0,"",(Rate_1*MAX(0,MIN($O295,R1_To)-MAX($O294,R1_From))+Rate_2*MAX(0,MIN($O295,R2_To)-MAX($O294,R2_From))+Rate_3*MAX(0,MIN($O295,R3_To)-MAX($O294,R3_From)))/100/Day_Basis/$I295*Day_Basis*100)</f>
+        <f>IF($I295&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O295,'Engine'!$B$3)-MAX($O294,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O295,'Engine'!$B$5)-MAX($O294,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O295,'Engine'!$B$7)-MAX($O294,'Engine'!$B$6)))/100/$H$8/$I295*$H$8*100)</f>
         <v/>
       </c>
       <c r="I295" s="43">
@@ -15293,7 +15276,7 @@
         <v/>
       </c>
       <c r="J295" s="41">
-        <f>IF($I295&lt;=0,0,$S294*(Rate_1*MAX(0,MIN($O295,R1_To)-MAX($O294,R1_From))+Rate_2*MAX(0,MIN($O295,R2_To)-MAX($O294,R2_From))+Rate_3*MAX(0,MIN($O295,R3_To)-MAX($O294,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I295&lt;=0,0,$S294*('Engine'!$B$8*MAX(0,MIN($O295,'Engine'!$B$3)-MAX($O294,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O295,'Engine'!$B$5)-MAX($O294,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O295,'Engine'!$B$7)-MAX($O294,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K295" s="41">
@@ -15306,7 +15289,7 @@
         <v/>
       </c>
       <c r="N295" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O295&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O295&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O295" s="25">
@@ -15337,7 +15320,7 @@
         <v/>
       </c>
       <c r="H296" s="42">
-        <f>IF($I296&lt;=0,"",(Rate_1*MAX(0,MIN($O296,R1_To)-MAX($O295,R1_From))+Rate_2*MAX(0,MIN($O296,R2_To)-MAX($O295,R2_From))+Rate_3*MAX(0,MIN($O296,R3_To)-MAX($O295,R3_From)))/100/Day_Basis/$I296*Day_Basis*100)</f>
+        <f>IF($I296&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O296,'Engine'!$B$3)-MAX($O295,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O296,'Engine'!$B$5)-MAX($O295,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O296,'Engine'!$B$7)-MAX($O295,'Engine'!$B$6)))/100/$H$8/$I296*$H$8*100)</f>
         <v/>
       </c>
       <c r="I296" s="43">
@@ -15345,7 +15328,7 @@
         <v/>
       </c>
       <c r="J296" s="41">
-        <f>IF($I296&lt;=0,0,$S295*(Rate_1*MAX(0,MIN($O296,R1_To)-MAX($O295,R1_From))+Rate_2*MAX(0,MIN($O296,R2_To)-MAX($O295,R2_From))+Rate_3*MAX(0,MIN($O296,R3_To)-MAX($O295,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I296&lt;=0,0,$S295*('Engine'!$B$8*MAX(0,MIN($O296,'Engine'!$B$3)-MAX($O295,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O296,'Engine'!$B$5)-MAX($O295,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O296,'Engine'!$B$7)-MAX($O295,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K296" s="41">
@@ -15358,7 +15341,7 @@
         <v/>
       </c>
       <c r="N296" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O296&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O296&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O296" s="25">
@@ -15389,7 +15372,7 @@
         <v/>
       </c>
       <c r="H297" s="42">
-        <f>IF($I297&lt;=0,"",(Rate_1*MAX(0,MIN($O297,R1_To)-MAX($O296,R1_From))+Rate_2*MAX(0,MIN($O297,R2_To)-MAX($O296,R2_From))+Rate_3*MAX(0,MIN($O297,R3_To)-MAX($O296,R3_From)))/100/Day_Basis/$I297*Day_Basis*100)</f>
+        <f>IF($I297&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O297,'Engine'!$B$3)-MAX($O296,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O297,'Engine'!$B$5)-MAX($O296,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O297,'Engine'!$B$7)-MAX($O296,'Engine'!$B$6)))/100/$H$8/$I297*$H$8*100)</f>
         <v/>
       </c>
       <c r="I297" s="43">
@@ -15397,7 +15380,7 @@
         <v/>
       </c>
       <c r="J297" s="41">
-        <f>IF($I297&lt;=0,0,$S296*(Rate_1*MAX(0,MIN($O297,R1_To)-MAX($O296,R1_From))+Rate_2*MAX(0,MIN($O297,R2_To)-MAX($O296,R2_From))+Rate_3*MAX(0,MIN($O297,R3_To)-MAX($O296,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I297&lt;=0,0,$S296*('Engine'!$B$8*MAX(0,MIN($O297,'Engine'!$B$3)-MAX($O296,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O297,'Engine'!$B$5)-MAX($O296,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O297,'Engine'!$B$7)-MAX($O296,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K297" s="41">
@@ -15410,7 +15393,7 @@
         <v/>
       </c>
       <c r="N297" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O297&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O297&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O297" s="25">
@@ -15441,7 +15424,7 @@
         <v/>
       </c>
       <c r="H298" s="42">
-        <f>IF($I298&lt;=0,"",(Rate_1*MAX(0,MIN($O298,R1_To)-MAX($O297,R1_From))+Rate_2*MAX(0,MIN($O298,R2_To)-MAX($O297,R2_From))+Rate_3*MAX(0,MIN($O298,R3_To)-MAX($O297,R3_From)))/100/Day_Basis/$I298*Day_Basis*100)</f>
+        <f>IF($I298&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O298,'Engine'!$B$3)-MAX($O297,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O298,'Engine'!$B$5)-MAX($O297,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O298,'Engine'!$B$7)-MAX($O297,'Engine'!$B$6)))/100/$H$8/$I298*$H$8*100)</f>
         <v/>
       </c>
       <c r="I298" s="43">
@@ -15449,7 +15432,7 @@
         <v/>
       </c>
       <c r="J298" s="41">
-        <f>IF($I298&lt;=0,0,$S297*(Rate_1*MAX(0,MIN($O298,R1_To)-MAX($O297,R1_From))+Rate_2*MAX(0,MIN($O298,R2_To)-MAX($O297,R2_From))+Rate_3*MAX(0,MIN($O298,R3_To)-MAX($O297,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I298&lt;=0,0,$S297*('Engine'!$B$8*MAX(0,MIN($O298,'Engine'!$B$3)-MAX($O297,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O298,'Engine'!$B$5)-MAX($O297,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O298,'Engine'!$B$7)-MAX($O297,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K298" s="41">
@@ -15462,7 +15445,7 @@
         <v/>
       </c>
       <c r="N298" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O298&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O298&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O298" s="25">
@@ -15503,7 +15486,7 @@
         <v/>
       </c>
       <c r="H299" s="51">
-        <f>IF($I299&lt;=0,"",(Rate_1*MAX(0,MIN($O299,R1_To)-MAX($O298,R1_From))+Rate_2*MAX(0,MIN($O299,R2_To)-MAX($O298,R2_From))+Rate_3*MAX(0,MIN($O299,R3_To)-MAX($O298,R3_From)))/100/Day_Basis/$I299*Day_Basis*100)</f>
+        <f>IF($I299&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O299,'Engine'!$B$3)-MAX($O298,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O299,'Engine'!$B$5)-MAX($O298,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O299,'Engine'!$B$7)-MAX($O298,'Engine'!$B$6)))/100/$H$8/$I299*$H$8*100)</f>
         <v/>
       </c>
       <c r="I299" s="52">
@@ -15511,7 +15494,7 @@
         <v/>
       </c>
       <c r="J299" s="53">
-        <f>IF($I299&lt;=0,0,$S298*(Rate_1*MAX(0,MIN($O299,R1_To)-MAX($O298,R1_From))+Rate_2*MAX(0,MIN($O299,R2_To)-MAX($O298,R2_From))+Rate_3*MAX(0,MIN($O299,R3_To)-MAX($O298,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I299&lt;=0,0,$S298*('Engine'!$B$8*MAX(0,MIN($O299,'Engine'!$B$3)-MAX($O298,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O299,'Engine'!$B$5)-MAX($O298,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O299,'Engine'!$B$7)-MAX($O298,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K299" s="53" t="n">
@@ -15523,7 +15506,7 @@
         <v/>
       </c>
       <c r="N299" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O299&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O299&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O299" s="25">
@@ -15540,7 +15523,7 @@
     </row>
     <row r="300" ht="18" customHeight="1">
       <c r="A300" s="24">
-        <f>IF($P$300=0,"QUARTER 23          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 23          "&amp;TEXT($P$300,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$300,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$300&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$300)</f>
+        <f>IF($P$300=0,"QUARTER 23          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 23          "&amp;TEXT($P$300,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$300,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$300&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$300)</f>
         <v/>
       </c>
       <c r="O300" s="25">
@@ -15598,7 +15581,7 @@
         <v/>
       </c>
       <c r="N301" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$301&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$301&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O301" s="25">
@@ -15628,7 +15611,7 @@
         <v/>
       </c>
       <c r="H302" s="42">
-        <f>IF($I302&lt;=0,"",(Rate_1*MAX(0,MIN($O302,R1_To)-MAX($O301,R1_From))+Rate_2*MAX(0,MIN($O302,R2_To)-MAX($O301,R2_From))+Rate_3*MAX(0,MIN($O302,R3_To)-MAX($O301,R3_From)))/100/Day_Basis/$I302*Day_Basis*100)</f>
+        <f>IF($I302&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O302,'Engine'!$B$3)-MAX($O301,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O302,'Engine'!$B$5)-MAX($O301,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O302,'Engine'!$B$7)-MAX($O301,'Engine'!$B$6)))/100/$H$8/$I302*$H$8*100)</f>
         <v/>
       </c>
       <c r="I302" s="43">
@@ -15636,7 +15619,7 @@
         <v/>
       </c>
       <c r="J302" s="41">
-        <f>IF($I302&lt;=0,0,$S301*(Rate_1*MAX(0,MIN($O302,R1_To)-MAX($O301,R1_From))+Rate_2*MAX(0,MIN($O302,R2_To)-MAX($O301,R2_From))+Rate_3*MAX(0,MIN($O302,R3_To)-MAX($O301,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I302&lt;=0,0,$S301*('Engine'!$B$8*MAX(0,MIN($O302,'Engine'!$B$3)-MAX($O301,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O302,'Engine'!$B$5)-MAX($O301,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O302,'Engine'!$B$7)-MAX($O301,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K302" s="41">
@@ -15649,7 +15632,7 @@
         <v/>
       </c>
       <c r="N302" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O302&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O302&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O302" s="25">
@@ -15680,7 +15663,7 @@
         <v/>
       </c>
       <c r="H303" s="42">
-        <f>IF($I303&lt;=0,"",(Rate_1*MAX(0,MIN($O303,R1_To)-MAX($O302,R1_From))+Rate_2*MAX(0,MIN($O303,R2_To)-MAX($O302,R2_From))+Rate_3*MAX(0,MIN($O303,R3_To)-MAX($O302,R3_From)))/100/Day_Basis/$I303*Day_Basis*100)</f>
+        <f>IF($I303&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O303,'Engine'!$B$3)-MAX($O302,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O303,'Engine'!$B$5)-MAX($O302,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O303,'Engine'!$B$7)-MAX($O302,'Engine'!$B$6)))/100/$H$8/$I303*$H$8*100)</f>
         <v/>
       </c>
       <c r="I303" s="43">
@@ -15688,7 +15671,7 @@
         <v/>
       </c>
       <c r="J303" s="41">
-        <f>IF($I303&lt;=0,0,$S302*(Rate_1*MAX(0,MIN($O303,R1_To)-MAX($O302,R1_From))+Rate_2*MAX(0,MIN($O303,R2_To)-MAX($O302,R2_From))+Rate_3*MAX(0,MIN($O303,R3_To)-MAX($O302,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I303&lt;=0,0,$S302*('Engine'!$B$8*MAX(0,MIN($O303,'Engine'!$B$3)-MAX($O302,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O303,'Engine'!$B$5)-MAX($O302,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O303,'Engine'!$B$7)-MAX($O302,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K303" s="41">
@@ -15701,7 +15684,7 @@
         <v/>
       </c>
       <c r="N303" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O303&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O303&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O303" s="25">
@@ -15732,7 +15715,7 @@
         <v/>
       </c>
       <c r="H304" s="42">
-        <f>IF($I304&lt;=0,"",(Rate_1*MAX(0,MIN($O304,R1_To)-MAX($O303,R1_From))+Rate_2*MAX(0,MIN($O304,R2_To)-MAX($O303,R2_From))+Rate_3*MAX(0,MIN($O304,R3_To)-MAX($O303,R3_From)))/100/Day_Basis/$I304*Day_Basis*100)</f>
+        <f>IF($I304&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O304,'Engine'!$B$3)-MAX($O303,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O304,'Engine'!$B$5)-MAX($O303,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O304,'Engine'!$B$7)-MAX($O303,'Engine'!$B$6)))/100/$H$8/$I304*$H$8*100)</f>
         <v/>
       </c>
       <c r="I304" s="43">
@@ -15740,7 +15723,7 @@
         <v/>
       </c>
       <c r="J304" s="41">
-        <f>IF($I304&lt;=0,0,$S303*(Rate_1*MAX(0,MIN($O304,R1_To)-MAX($O303,R1_From))+Rate_2*MAX(0,MIN($O304,R2_To)-MAX($O303,R2_From))+Rate_3*MAX(0,MIN($O304,R3_To)-MAX($O303,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I304&lt;=0,0,$S303*('Engine'!$B$8*MAX(0,MIN($O304,'Engine'!$B$3)-MAX($O303,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O304,'Engine'!$B$5)-MAX($O303,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O304,'Engine'!$B$7)-MAX($O303,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K304" s="41">
@@ -15753,7 +15736,7 @@
         <v/>
       </c>
       <c r="N304" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O304&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O304&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O304" s="25">
@@ -15784,7 +15767,7 @@
         <v/>
       </c>
       <c r="H305" s="42">
-        <f>IF($I305&lt;=0,"",(Rate_1*MAX(0,MIN($O305,R1_To)-MAX($O304,R1_From))+Rate_2*MAX(0,MIN($O305,R2_To)-MAX($O304,R2_From))+Rate_3*MAX(0,MIN($O305,R3_To)-MAX($O304,R3_From)))/100/Day_Basis/$I305*Day_Basis*100)</f>
+        <f>IF($I305&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O305,'Engine'!$B$3)-MAX($O304,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O305,'Engine'!$B$5)-MAX($O304,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O305,'Engine'!$B$7)-MAX($O304,'Engine'!$B$6)))/100/$H$8/$I305*$H$8*100)</f>
         <v/>
       </c>
       <c r="I305" s="43">
@@ -15792,7 +15775,7 @@
         <v/>
       </c>
       <c r="J305" s="41">
-        <f>IF($I305&lt;=0,0,$S304*(Rate_1*MAX(0,MIN($O305,R1_To)-MAX($O304,R1_From))+Rate_2*MAX(0,MIN($O305,R2_To)-MAX($O304,R2_From))+Rate_3*MAX(0,MIN($O305,R3_To)-MAX($O304,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I305&lt;=0,0,$S304*('Engine'!$B$8*MAX(0,MIN($O305,'Engine'!$B$3)-MAX($O304,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O305,'Engine'!$B$5)-MAX($O304,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O305,'Engine'!$B$7)-MAX($O304,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K305" s="41">
@@ -15805,7 +15788,7 @@
         <v/>
       </c>
       <c r="N305" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O305&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O305&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O305" s="25">
@@ -15836,7 +15819,7 @@
         <v/>
       </c>
       <c r="H306" s="42">
-        <f>IF($I306&lt;=0,"",(Rate_1*MAX(0,MIN($O306,R1_To)-MAX($O305,R1_From))+Rate_2*MAX(0,MIN($O306,R2_To)-MAX($O305,R2_From))+Rate_3*MAX(0,MIN($O306,R3_To)-MAX($O305,R3_From)))/100/Day_Basis/$I306*Day_Basis*100)</f>
+        <f>IF($I306&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O306,'Engine'!$B$3)-MAX($O305,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O306,'Engine'!$B$5)-MAX($O305,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O306,'Engine'!$B$7)-MAX($O305,'Engine'!$B$6)))/100/$H$8/$I306*$H$8*100)</f>
         <v/>
       </c>
       <c r="I306" s="43">
@@ -15844,7 +15827,7 @@
         <v/>
       </c>
       <c r="J306" s="41">
-        <f>IF($I306&lt;=0,0,$S305*(Rate_1*MAX(0,MIN($O306,R1_To)-MAX($O305,R1_From))+Rate_2*MAX(0,MIN($O306,R2_To)-MAX($O305,R2_From))+Rate_3*MAX(0,MIN($O306,R3_To)-MAX($O305,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I306&lt;=0,0,$S305*('Engine'!$B$8*MAX(0,MIN($O306,'Engine'!$B$3)-MAX($O305,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O306,'Engine'!$B$5)-MAX($O305,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O306,'Engine'!$B$7)-MAX($O305,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K306" s="41">
@@ -15857,7 +15840,7 @@
         <v/>
       </c>
       <c r="N306" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O306&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O306&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O306" s="25">
@@ -15888,7 +15871,7 @@
         <v/>
       </c>
       <c r="H307" s="42">
-        <f>IF($I307&lt;=0,"",(Rate_1*MAX(0,MIN($O307,R1_To)-MAX($O306,R1_From))+Rate_2*MAX(0,MIN($O307,R2_To)-MAX($O306,R2_From))+Rate_3*MAX(0,MIN($O307,R3_To)-MAX($O306,R3_From)))/100/Day_Basis/$I307*Day_Basis*100)</f>
+        <f>IF($I307&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O307,'Engine'!$B$3)-MAX($O306,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O307,'Engine'!$B$5)-MAX($O306,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O307,'Engine'!$B$7)-MAX($O306,'Engine'!$B$6)))/100/$H$8/$I307*$H$8*100)</f>
         <v/>
       </c>
       <c r="I307" s="43">
@@ -15896,7 +15879,7 @@
         <v/>
       </c>
       <c r="J307" s="41">
-        <f>IF($I307&lt;=0,0,$S306*(Rate_1*MAX(0,MIN($O307,R1_To)-MAX($O306,R1_From))+Rate_2*MAX(0,MIN($O307,R2_To)-MAX($O306,R2_From))+Rate_3*MAX(0,MIN($O307,R3_To)-MAX($O306,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I307&lt;=0,0,$S306*('Engine'!$B$8*MAX(0,MIN($O307,'Engine'!$B$3)-MAX($O306,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O307,'Engine'!$B$5)-MAX($O306,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O307,'Engine'!$B$7)-MAX($O306,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K307" s="41">
@@ -15909,7 +15892,7 @@
         <v/>
       </c>
       <c r="N307" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O307&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O307&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O307" s="25">
@@ -15940,7 +15923,7 @@
         <v/>
       </c>
       <c r="H308" s="42">
-        <f>IF($I308&lt;=0,"",(Rate_1*MAX(0,MIN($O308,R1_To)-MAX($O307,R1_From))+Rate_2*MAX(0,MIN($O308,R2_To)-MAX($O307,R2_From))+Rate_3*MAX(0,MIN($O308,R3_To)-MAX($O307,R3_From)))/100/Day_Basis/$I308*Day_Basis*100)</f>
+        <f>IF($I308&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O308,'Engine'!$B$3)-MAX($O307,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O308,'Engine'!$B$5)-MAX($O307,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O308,'Engine'!$B$7)-MAX($O307,'Engine'!$B$6)))/100/$H$8/$I308*$H$8*100)</f>
         <v/>
       </c>
       <c r="I308" s="43">
@@ -15948,7 +15931,7 @@
         <v/>
       </c>
       <c r="J308" s="41">
-        <f>IF($I308&lt;=0,0,$S307*(Rate_1*MAX(0,MIN($O308,R1_To)-MAX($O307,R1_From))+Rate_2*MAX(0,MIN($O308,R2_To)-MAX($O307,R2_From))+Rate_3*MAX(0,MIN($O308,R3_To)-MAX($O307,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I308&lt;=0,0,$S307*('Engine'!$B$8*MAX(0,MIN($O308,'Engine'!$B$3)-MAX($O307,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O308,'Engine'!$B$5)-MAX($O307,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O308,'Engine'!$B$7)-MAX($O307,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K308" s="41">
@@ -15961,7 +15944,7 @@
         <v/>
       </c>
       <c r="N308" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O308&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O308&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O308" s="25">
@@ -15992,7 +15975,7 @@
         <v/>
       </c>
       <c r="H309" s="42">
-        <f>IF($I309&lt;=0,"",(Rate_1*MAX(0,MIN($O309,R1_To)-MAX($O308,R1_From))+Rate_2*MAX(0,MIN($O309,R2_To)-MAX($O308,R2_From))+Rate_3*MAX(0,MIN($O309,R3_To)-MAX($O308,R3_From)))/100/Day_Basis/$I309*Day_Basis*100)</f>
+        <f>IF($I309&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O309,'Engine'!$B$3)-MAX($O308,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O309,'Engine'!$B$5)-MAX($O308,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O309,'Engine'!$B$7)-MAX($O308,'Engine'!$B$6)))/100/$H$8/$I309*$H$8*100)</f>
         <v/>
       </c>
       <c r="I309" s="43">
@@ -16000,7 +15983,7 @@
         <v/>
       </c>
       <c r="J309" s="41">
-        <f>IF($I309&lt;=0,0,$S308*(Rate_1*MAX(0,MIN($O309,R1_To)-MAX($O308,R1_From))+Rate_2*MAX(0,MIN($O309,R2_To)-MAX($O308,R2_From))+Rate_3*MAX(0,MIN($O309,R3_To)-MAX($O308,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I309&lt;=0,0,$S308*('Engine'!$B$8*MAX(0,MIN($O309,'Engine'!$B$3)-MAX($O308,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O309,'Engine'!$B$5)-MAX($O308,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O309,'Engine'!$B$7)-MAX($O308,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K309" s="41">
@@ -16013,7 +15996,7 @@
         <v/>
       </c>
       <c r="N309" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O309&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O309&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O309" s="25">
@@ -16044,7 +16027,7 @@
         <v/>
       </c>
       <c r="H310" s="42">
-        <f>IF($I310&lt;=0,"",(Rate_1*MAX(0,MIN($O310,R1_To)-MAX($O309,R1_From))+Rate_2*MAX(0,MIN($O310,R2_To)-MAX($O309,R2_From))+Rate_3*MAX(0,MIN($O310,R3_To)-MAX($O309,R3_From)))/100/Day_Basis/$I310*Day_Basis*100)</f>
+        <f>IF($I310&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O310,'Engine'!$B$3)-MAX($O309,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O310,'Engine'!$B$5)-MAX($O309,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O310,'Engine'!$B$7)-MAX($O309,'Engine'!$B$6)))/100/$H$8/$I310*$H$8*100)</f>
         <v/>
       </c>
       <c r="I310" s="43">
@@ -16052,7 +16035,7 @@
         <v/>
       </c>
       <c r="J310" s="41">
-        <f>IF($I310&lt;=0,0,$S309*(Rate_1*MAX(0,MIN($O310,R1_To)-MAX($O309,R1_From))+Rate_2*MAX(0,MIN($O310,R2_To)-MAX($O309,R2_From))+Rate_3*MAX(0,MIN($O310,R3_To)-MAX($O309,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I310&lt;=0,0,$S309*('Engine'!$B$8*MAX(0,MIN($O310,'Engine'!$B$3)-MAX($O309,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O310,'Engine'!$B$5)-MAX($O309,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O310,'Engine'!$B$7)-MAX($O309,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K310" s="41">
@@ -16065,7 +16048,7 @@
         <v/>
       </c>
       <c r="N310" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O310&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O310&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O310" s="25">
@@ -16096,7 +16079,7 @@
         <v/>
       </c>
       <c r="H311" s="42">
-        <f>IF($I311&lt;=0,"",(Rate_1*MAX(0,MIN($O311,R1_To)-MAX($O310,R1_From))+Rate_2*MAX(0,MIN($O311,R2_To)-MAX($O310,R2_From))+Rate_3*MAX(0,MIN($O311,R3_To)-MAX($O310,R3_From)))/100/Day_Basis/$I311*Day_Basis*100)</f>
+        <f>IF($I311&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O311,'Engine'!$B$3)-MAX($O310,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O311,'Engine'!$B$5)-MAX($O310,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O311,'Engine'!$B$7)-MAX($O310,'Engine'!$B$6)))/100/$H$8/$I311*$H$8*100)</f>
         <v/>
       </c>
       <c r="I311" s="43">
@@ -16104,7 +16087,7 @@
         <v/>
       </c>
       <c r="J311" s="41">
-        <f>IF($I311&lt;=0,0,$S310*(Rate_1*MAX(0,MIN($O311,R1_To)-MAX($O310,R1_From))+Rate_2*MAX(0,MIN($O311,R2_To)-MAX($O310,R2_From))+Rate_3*MAX(0,MIN($O311,R3_To)-MAX($O310,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I311&lt;=0,0,$S310*('Engine'!$B$8*MAX(0,MIN($O311,'Engine'!$B$3)-MAX($O310,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O311,'Engine'!$B$5)-MAX($O310,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O311,'Engine'!$B$7)-MAX($O310,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K311" s="41">
@@ -16117,7 +16100,7 @@
         <v/>
       </c>
       <c r="N311" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O311&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O311&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O311" s="25">
@@ -16158,7 +16141,7 @@
         <v/>
       </c>
       <c r="H312" s="51">
-        <f>IF($I312&lt;=0,"",(Rate_1*MAX(0,MIN($O312,R1_To)-MAX($O311,R1_From))+Rate_2*MAX(0,MIN($O312,R2_To)-MAX($O311,R2_From))+Rate_3*MAX(0,MIN($O312,R3_To)-MAX($O311,R3_From)))/100/Day_Basis/$I312*Day_Basis*100)</f>
+        <f>IF($I312&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O312,'Engine'!$B$3)-MAX($O311,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O312,'Engine'!$B$5)-MAX($O311,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O312,'Engine'!$B$7)-MAX($O311,'Engine'!$B$6)))/100/$H$8/$I312*$H$8*100)</f>
         <v/>
       </c>
       <c r="I312" s="52">
@@ -16166,7 +16149,7 @@
         <v/>
       </c>
       <c r="J312" s="53">
-        <f>IF($I312&lt;=0,0,$S311*(Rate_1*MAX(0,MIN($O312,R1_To)-MAX($O311,R1_From))+Rate_2*MAX(0,MIN($O312,R2_To)-MAX($O311,R2_From))+Rate_3*MAX(0,MIN($O312,R3_To)-MAX($O311,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I312&lt;=0,0,$S311*('Engine'!$B$8*MAX(0,MIN($O312,'Engine'!$B$3)-MAX($O311,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O312,'Engine'!$B$5)-MAX($O311,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O312,'Engine'!$B$7)-MAX($O311,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K312" s="53" t="n">
@@ -16178,7 +16161,7 @@
         <v/>
       </c>
       <c r="N312" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O312&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O312&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O312" s="25">
@@ -16195,7 +16178,7 @@
     </row>
     <row r="313" ht="18" customHeight="1">
       <c r="A313" s="24">
-        <f>IF($P$313=0,"QUARTER 24          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 24          "&amp;TEXT($P$313,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$313,"DD-MM-YYYY")&amp;"          "&amp;IF(AND(Locked_To&lt;&gt;"",$Q$313&lt;=Locked_To),"🔒 LOCKED – reconciled, no entry allowed","▶ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$313)</f>
+        <f>IF($P$313=0,"QUARTER 24          –  enter the Balance B/F date above to activate this quarter  –","QUARTER 24          "&amp;TEXT($P$313,"DD-MM-YYYY")&amp;"   to   "&amp;TEXT($Q$313,"DD-MM-YYYY")&amp;"          "&amp;IF(AND($H$10&lt;&gt;"",$Q$313&lt;=$H$10),"■ LOCKED – reconciled, no entry allowed","▷ OPEN for entry")&amp;"          RATE(S) APPLIED :  "&amp;$R$313)</f>
         <v/>
       </c>
       <c r="O313" s="25">
@@ -16253,7 +16236,7 @@
         <v/>
       </c>
       <c r="N314" s="37">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O$314&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O$314&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O314" s="25">
@@ -16283,7 +16266,7 @@
         <v/>
       </c>
       <c r="H315" s="42">
-        <f>IF($I315&lt;=0,"",(Rate_1*MAX(0,MIN($O315,R1_To)-MAX($O314,R1_From))+Rate_2*MAX(0,MIN($O315,R2_To)-MAX($O314,R2_From))+Rate_3*MAX(0,MIN($O315,R3_To)-MAX($O314,R3_From)))/100/Day_Basis/$I315*Day_Basis*100)</f>
+        <f>IF($I315&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O315,'Engine'!$B$3)-MAX($O314,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O315,'Engine'!$B$5)-MAX($O314,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O315,'Engine'!$B$7)-MAX($O314,'Engine'!$B$6)))/100/$H$8/$I315*$H$8*100)</f>
         <v/>
       </c>
       <c r="I315" s="43">
@@ -16291,7 +16274,7 @@
         <v/>
       </c>
       <c r="J315" s="41">
-        <f>IF($I315&lt;=0,0,$S314*(Rate_1*MAX(0,MIN($O315,R1_To)-MAX($O314,R1_From))+Rate_2*MAX(0,MIN($O315,R2_To)-MAX($O314,R2_From))+Rate_3*MAX(0,MIN($O315,R3_To)-MAX($O314,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I315&lt;=0,0,$S314*('Engine'!$B$8*MAX(0,MIN($O315,'Engine'!$B$3)-MAX($O314,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O315,'Engine'!$B$5)-MAX($O314,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O315,'Engine'!$B$7)-MAX($O314,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K315" s="41">
@@ -16304,7 +16287,7 @@
         <v/>
       </c>
       <c r="N315" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O315&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O315&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O315" s="25">
@@ -16335,7 +16318,7 @@
         <v/>
       </c>
       <c r="H316" s="42">
-        <f>IF($I316&lt;=0,"",(Rate_1*MAX(0,MIN($O316,R1_To)-MAX($O315,R1_From))+Rate_2*MAX(0,MIN($O316,R2_To)-MAX($O315,R2_From))+Rate_3*MAX(0,MIN($O316,R3_To)-MAX($O315,R3_From)))/100/Day_Basis/$I316*Day_Basis*100)</f>
+        <f>IF($I316&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O316,'Engine'!$B$3)-MAX($O315,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O316,'Engine'!$B$5)-MAX($O315,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O316,'Engine'!$B$7)-MAX($O315,'Engine'!$B$6)))/100/$H$8/$I316*$H$8*100)</f>
         <v/>
       </c>
       <c r="I316" s="43">
@@ -16343,7 +16326,7 @@
         <v/>
       </c>
       <c r="J316" s="41">
-        <f>IF($I316&lt;=0,0,$S315*(Rate_1*MAX(0,MIN($O316,R1_To)-MAX($O315,R1_From))+Rate_2*MAX(0,MIN($O316,R2_To)-MAX($O315,R2_From))+Rate_3*MAX(0,MIN($O316,R3_To)-MAX($O315,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I316&lt;=0,0,$S315*('Engine'!$B$8*MAX(0,MIN($O316,'Engine'!$B$3)-MAX($O315,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O316,'Engine'!$B$5)-MAX($O315,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O316,'Engine'!$B$7)-MAX($O315,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K316" s="41">
@@ -16356,7 +16339,7 @@
         <v/>
       </c>
       <c r="N316" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O316&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O316&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O316" s="25">
@@ -16387,7 +16370,7 @@
         <v/>
       </c>
       <c r="H317" s="42">
-        <f>IF($I317&lt;=0,"",(Rate_1*MAX(0,MIN($O317,R1_To)-MAX($O316,R1_From))+Rate_2*MAX(0,MIN($O317,R2_To)-MAX($O316,R2_From))+Rate_3*MAX(0,MIN($O317,R3_To)-MAX($O316,R3_From)))/100/Day_Basis/$I317*Day_Basis*100)</f>
+        <f>IF($I317&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O317,'Engine'!$B$3)-MAX($O316,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O317,'Engine'!$B$5)-MAX($O316,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O317,'Engine'!$B$7)-MAX($O316,'Engine'!$B$6)))/100/$H$8/$I317*$H$8*100)</f>
         <v/>
       </c>
       <c r="I317" s="43">
@@ -16395,7 +16378,7 @@
         <v/>
       </c>
       <c r="J317" s="41">
-        <f>IF($I317&lt;=0,0,$S316*(Rate_1*MAX(0,MIN($O317,R1_To)-MAX($O316,R1_From))+Rate_2*MAX(0,MIN($O317,R2_To)-MAX($O316,R2_From))+Rate_3*MAX(0,MIN($O317,R3_To)-MAX($O316,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I317&lt;=0,0,$S316*('Engine'!$B$8*MAX(0,MIN($O317,'Engine'!$B$3)-MAX($O316,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O317,'Engine'!$B$5)-MAX($O316,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O317,'Engine'!$B$7)-MAX($O316,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K317" s="41">
@@ -16408,7 +16391,7 @@
         <v/>
       </c>
       <c r="N317" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O317&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O317&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O317" s="25">
@@ -16439,7 +16422,7 @@
         <v/>
       </c>
       <c r="H318" s="42">
-        <f>IF($I318&lt;=0,"",(Rate_1*MAX(0,MIN($O318,R1_To)-MAX($O317,R1_From))+Rate_2*MAX(0,MIN($O318,R2_To)-MAX($O317,R2_From))+Rate_3*MAX(0,MIN($O318,R3_To)-MAX($O317,R3_From)))/100/Day_Basis/$I318*Day_Basis*100)</f>
+        <f>IF($I318&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O318,'Engine'!$B$3)-MAX($O317,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O318,'Engine'!$B$5)-MAX($O317,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O318,'Engine'!$B$7)-MAX($O317,'Engine'!$B$6)))/100/$H$8/$I318*$H$8*100)</f>
         <v/>
       </c>
       <c r="I318" s="43">
@@ -16447,7 +16430,7 @@
         <v/>
       </c>
       <c r="J318" s="41">
-        <f>IF($I318&lt;=0,0,$S317*(Rate_1*MAX(0,MIN($O318,R1_To)-MAX($O317,R1_From))+Rate_2*MAX(0,MIN($O318,R2_To)-MAX($O317,R2_From))+Rate_3*MAX(0,MIN($O318,R3_To)-MAX($O317,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I318&lt;=0,0,$S317*('Engine'!$B$8*MAX(0,MIN($O318,'Engine'!$B$3)-MAX($O317,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O318,'Engine'!$B$5)-MAX($O317,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O318,'Engine'!$B$7)-MAX($O317,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K318" s="41">
@@ -16460,7 +16443,7 @@
         <v/>
       </c>
       <c r="N318" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O318&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O318&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O318" s="25">
@@ -16491,7 +16474,7 @@
         <v/>
       </c>
       <c r="H319" s="42">
-        <f>IF($I319&lt;=0,"",(Rate_1*MAX(0,MIN($O319,R1_To)-MAX($O318,R1_From))+Rate_2*MAX(0,MIN($O319,R2_To)-MAX($O318,R2_From))+Rate_3*MAX(0,MIN($O319,R3_To)-MAX($O318,R3_From)))/100/Day_Basis/$I319*Day_Basis*100)</f>
+        <f>IF($I319&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O319,'Engine'!$B$3)-MAX($O318,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O319,'Engine'!$B$5)-MAX($O318,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O319,'Engine'!$B$7)-MAX($O318,'Engine'!$B$6)))/100/$H$8/$I319*$H$8*100)</f>
         <v/>
       </c>
       <c r="I319" s="43">
@@ -16499,7 +16482,7 @@
         <v/>
       </c>
       <c r="J319" s="41">
-        <f>IF($I319&lt;=0,0,$S318*(Rate_1*MAX(0,MIN($O319,R1_To)-MAX($O318,R1_From))+Rate_2*MAX(0,MIN($O319,R2_To)-MAX($O318,R2_From))+Rate_3*MAX(0,MIN($O319,R3_To)-MAX($O318,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I319&lt;=0,0,$S318*('Engine'!$B$8*MAX(0,MIN($O319,'Engine'!$B$3)-MAX($O318,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O319,'Engine'!$B$5)-MAX($O318,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O319,'Engine'!$B$7)-MAX($O318,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K319" s="41">
@@ -16512,7 +16495,7 @@
         <v/>
       </c>
       <c r="N319" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O319&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O319&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O319" s="25">
@@ -16543,7 +16526,7 @@
         <v/>
       </c>
       <c r="H320" s="42">
-        <f>IF($I320&lt;=0,"",(Rate_1*MAX(0,MIN($O320,R1_To)-MAX($O319,R1_From))+Rate_2*MAX(0,MIN($O320,R2_To)-MAX($O319,R2_From))+Rate_3*MAX(0,MIN($O320,R3_To)-MAX($O319,R3_From)))/100/Day_Basis/$I320*Day_Basis*100)</f>
+        <f>IF($I320&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O320,'Engine'!$B$3)-MAX($O319,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O320,'Engine'!$B$5)-MAX($O319,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O320,'Engine'!$B$7)-MAX($O319,'Engine'!$B$6)))/100/$H$8/$I320*$H$8*100)</f>
         <v/>
       </c>
       <c r="I320" s="43">
@@ -16551,7 +16534,7 @@
         <v/>
       </c>
       <c r="J320" s="41">
-        <f>IF($I320&lt;=0,0,$S319*(Rate_1*MAX(0,MIN($O320,R1_To)-MAX($O319,R1_From))+Rate_2*MAX(0,MIN($O320,R2_To)-MAX($O319,R2_From))+Rate_3*MAX(0,MIN($O320,R3_To)-MAX($O319,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I320&lt;=0,0,$S319*('Engine'!$B$8*MAX(0,MIN($O320,'Engine'!$B$3)-MAX($O319,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O320,'Engine'!$B$5)-MAX($O319,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O320,'Engine'!$B$7)-MAX($O319,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K320" s="41">
@@ -16564,7 +16547,7 @@
         <v/>
       </c>
       <c r="N320" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O320&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O320&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O320" s="25">
@@ -16595,7 +16578,7 @@
         <v/>
       </c>
       <c r="H321" s="42">
-        <f>IF($I321&lt;=0,"",(Rate_1*MAX(0,MIN($O321,R1_To)-MAX($O320,R1_From))+Rate_2*MAX(0,MIN($O321,R2_To)-MAX($O320,R2_From))+Rate_3*MAX(0,MIN($O321,R3_To)-MAX($O320,R3_From)))/100/Day_Basis/$I321*Day_Basis*100)</f>
+        <f>IF($I321&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O321,'Engine'!$B$3)-MAX($O320,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O321,'Engine'!$B$5)-MAX($O320,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O321,'Engine'!$B$7)-MAX($O320,'Engine'!$B$6)))/100/$H$8/$I321*$H$8*100)</f>
         <v/>
       </c>
       <c r="I321" s="43">
@@ -16603,7 +16586,7 @@
         <v/>
       </c>
       <c r="J321" s="41">
-        <f>IF($I321&lt;=0,0,$S320*(Rate_1*MAX(0,MIN($O321,R1_To)-MAX($O320,R1_From))+Rate_2*MAX(0,MIN($O321,R2_To)-MAX($O320,R2_From))+Rate_3*MAX(0,MIN($O321,R3_To)-MAX($O320,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I321&lt;=0,0,$S320*('Engine'!$B$8*MAX(0,MIN($O321,'Engine'!$B$3)-MAX($O320,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O321,'Engine'!$B$5)-MAX($O320,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O321,'Engine'!$B$7)-MAX($O320,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K321" s="41">
@@ -16616,7 +16599,7 @@
         <v/>
       </c>
       <c r="N321" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O321&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O321&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O321" s="25">
@@ -16647,7 +16630,7 @@
         <v/>
       </c>
       <c r="H322" s="42">
-        <f>IF($I322&lt;=0,"",(Rate_1*MAX(0,MIN($O322,R1_To)-MAX($O321,R1_From))+Rate_2*MAX(0,MIN($O322,R2_To)-MAX($O321,R2_From))+Rate_3*MAX(0,MIN($O322,R3_To)-MAX($O321,R3_From)))/100/Day_Basis/$I322*Day_Basis*100)</f>
+        <f>IF($I322&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O322,'Engine'!$B$3)-MAX($O321,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O322,'Engine'!$B$5)-MAX($O321,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O322,'Engine'!$B$7)-MAX($O321,'Engine'!$B$6)))/100/$H$8/$I322*$H$8*100)</f>
         <v/>
       </c>
       <c r="I322" s="43">
@@ -16655,7 +16638,7 @@
         <v/>
       </c>
       <c r="J322" s="41">
-        <f>IF($I322&lt;=0,0,$S321*(Rate_1*MAX(0,MIN($O322,R1_To)-MAX($O321,R1_From))+Rate_2*MAX(0,MIN($O322,R2_To)-MAX($O321,R2_From))+Rate_3*MAX(0,MIN($O322,R3_To)-MAX($O321,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I322&lt;=0,0,$S321*('Engine'!$B$8*MAX(0,MIN($O322,'Engine'!$B$3)-MAX($O321,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O322,'Engine'!$B$5)-MAX($O321,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O322,'Engine'!$B$7)-MAX($O321,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K322" s="41">
@@ -16668,7 +16651,7 @@
         <v/>
       </c>
       <c r="N322" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O322&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O322&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O322" s="25">
@@ -16699,7 +16682,7 @@
         <v/>
       </c>
       <c r="H323" s="42">
-        <f>IF($I323&lt;=0,"",(Rate_1*MAX(0,MIN($O323,R1_To)-MAX($O322,R1_From))+Rate_2*MAX(0,MIN($O323,R2_To)-MAX($O322,R2_From))+Rate_3*MAX(0,MIN($O323,R3_To)-MAX($O322,R3_From)))/100/Day_Basis/$I323*Day_Basis*100)</f>
+        <f>IF($I323&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O323,'Engine'!$B$3)-MAX($O322,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O323,'Engine'!$B$5)-MAX($O322,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O323,'Engine'!$B$7)-MAX($O322,'Engine'!$B$6)))/100/$H$8/$I323*$H$8*100)</f>
         <v/>
       </c>
       <c r="I323" s="43">
@@ -16707,7 +16690,7 @@
         <v/>
       </c>
       <c r="J323" s="41">
-        <f>IF($I323&lt;=0,0,$S322*(Rate_1*MAX(0,MIN($O323,R1_To)-MAX($O322,R1_From))+Rate_2*MAX(0,MIN($O323,R2_To)-MAX($O322,R2_From))+Rate_3*MAX(0,MIN($O323,R3_To)-MAX($O322,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I323&lt;=0,0,$S322*('Engine'!$B$8*MAX(0,MIN($O323,'Engine'!$B$3)-MAX($O322,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O323,'Engine'!$B$5)-MAX($O322,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O323,'Engine'!$B$7)-MAX($O322,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K323" s="41">
@@ -16720,7 +16703,7 @@
         <v/>
       </c>
       <c r="N323" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O323&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O323&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O323" s="25">
@@ -16751,7 +16734,7 @@
         <v/>
       </c>
       <c r="H324" s="42">
-        <f>IF($I324&lt;=0,"",(Rate_1*MAX(0,MIN($O324,R1_To)-MAX($O323,R1_From))+Rate_2*MAX(0,MIN($O324,R2_To)-MAX($O323,R2_From))+Rate_3*MAX(0,MIN($O324,R3_To)-MAX($O323,R3_From)))/100/Day_Basis/$I324*Day_Basis*100)</f>
+        <f>IF($I324&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O324,'Engine'!$B$3)-MAX($O323,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O324,'Engine'!$B$5)-MAX($O323,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O324,'Engine'!$B$7)-MAX($O323,'Engine'!$B$6)))/100/$H$8/$I324*$H$8*100)</f>
         <v/>
       </c>
       <c r="I324" s="43">
@@ -16759,7 +16742,7 @@
         <v/>
       </c>
       <c r="J324" s="41">
-        <f>IF($I324&lt;=0,0,$S323*(Rate_1*MAX(0,MIN($O324,R1_To)-MAX($O323,R1_From))+Rate_2*MAX(0,MIN($O324,R2_To)-MAX($O323,R2_From))+Rate_3*MAX(0,MIN($O324,R3_To)-MAX($O323,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I324&lt;=0,0,$S323*('Engine'!$B$8*MAX(0,MIN($O324,'Engine'!$B$3)-MAX($O323,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O324,'Engine'!$B$5)-MAX($O323,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O324,'Engine'!$B$7)-MAX($O323,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K324" s="41">
@@ -16772,7 +16755,7 @@
         <v/>
       </c>
       <c r="N324" s="44">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O324&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O324&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O324" s="25">
@@ -16813,7 +16796,7 @@
         <v/>
       </c>
       <c r="H325" s="51">
-        <f>IF($I325&lt;=0,"",(Rate_1*MAX(0,MIN($O325,R1_To)-MAX($O324,R1_From))+Rate_2*MAX(0,MIN($O325,R2_To)-MAX($O324,R2_From))+Rate_3*MAX(0,MIN($O325,R3_To)-MAX($O324,R3_From)))/100/Day_Basis/$I325*Day_Basis*100)</f>
+        <f>IF($I325&lt;=0,"",('Engine'!$B$8*MAX(0,MIN($O325,'Engine'!$B$3)-MAX($O324,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O325,'Engine'!$B$5)-MAX($O324,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O325,'Engine'!$B$7)-MAX($O324,'Engine'!$B$6)))/100/$H$8/$I325*$H$8*100)</f>
         <v/>
       </c>
       <c r="I325" s="52">
@@ -16821,7 +16804,7 @@
         <v/>
       </c>
       <c r="J325" s="53">
-        <f>IF($I325&lt;=0,0,$S324*(Rate_1*MAX(0,MIN($O325,R1_To)-MAX($O324,R1_From))+Rate_2*MAX(0,MIN($O325,R2_To)-MAX($O324,R2_From))+Rate_3*MAX(0,MIN($O325,R3_To)-MAX($O324,R3_From)))/100/Day_Basis)</f>
+        <f>IF($I325&lt;=0,0,$S324*('Engine'!$B$8*MAX(0,MIN($O325,'Engine'!$B$3)-MAX($O324,'Engine'!$B$2))+'Engine'!$B$9*MAX(0,MIN($O325,'Engine'!$B$5)-MAX($O324,'Engine'!$B$4))+'Engine'!$B$10*MAX(0,MIN($O325,'Engine'!$B$7)-MAX($O324,'Engine'!$B$6)))/100/$H$8)</f>
         <v/>
       </c>
       <c r="K325" s="53" t="n">
@@ -16833,7 +16816,7 @@
         <v/>
       </c>
       <c r="N325" s="54">
-        <f>IF(AND(Locked_To&lt;&gt;"",$O325&lt;=Locked_To),"LOCKED","OPEN")</f>
+        <f>IF(AND($H$10&lt;&gt;"",$O325&lt;=$H$10),"LOCKED","OPEN")</f>
         <v/>
       </c>
       <c r="O325" s="25">
@@ -16963,20 +16946,20 @@
       <formula1>"Calendar quarter-ends,3 months from B/F date"</formula1>
     </dataValidation>
     <dataValidation sqref="H10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid lock date" error="The lock date must be a real date, on/after the B/F date and not in the future. It can only be moved forward as you reconcile with the bank." promptTitle="Locked / reconciled up to" prompt="Everything dated on or before this date is frozen: no entries, no rate revisions." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER(H10),H10&gt;=BF_Date,H10&lt;=TODAY())</formula1>
+      <formula1>AND(ISNUMBER(H10),H10&gt;=$H$6,H10&lt;=TODAY())</formula1>
     </dataValidation>
     <dataValidation sqref="L7:L9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Rate out of range" error="Enter the annual rate in percent, e.g. 9.5 for 9.50% p.a." promptTitle="Interest rate % p.a." prompt="Annual rate in percent, e.g. 9.5" type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
     <dataValidation sqref="K8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Revision cannot be back-dated" error="A revised rate must take effect AFTER the B/F date, AFTER the ‘Locked / reconciled up to’ date, and before the next revision. Periods already calculated at the earlier rate stay untouched." promptTitle="1st revision effective from" prompt="Date the revised rate starts. Must be later than the locked-up-to date." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER(K8),K8&gt;BF_Date,K8&gt;Locked_To,OR(K9="",K8&lt;K9))</formula1>
+      <formula1>AND(ISNUMBER(K8),K8&gt;$H$6,K8&gt;$H$10,OR(K9="",K8&lt;K9))</formula1>
     </dataValidation>
     <dataValidation sqref="K9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Revision cannot be back-dated" error="Fill slot 2 first. The 2nd revision must take effect after the 1st revision and after the ‘Locked / reconciled up to’ date." promptTitle="2nd revision effective from" prompt="Date the second revised rate starts." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER(K9),K9&gt;Locked_To,K8&lt;&gt;"",K9&gt;K8)</formula1>
+      <formula1>AND(ISNUMBER(K9),K9&gt;$H$10,K8&lt;&gt;"",K9&gt;K8)</formula1>
     </dataValidation>
     <dataValidation sqref="B16:B25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B16),$B16&gt;=$O15,$B16&lt;=$Q$14,$B16&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B16),$B16&gt;=$O15,$B16&lt;=$Q$14,$B16&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F16:F25" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F16),$F16&gt;0,ISNUMBER($B16))</formula1>
@@ -16985,7 +16968,7 @@
       <formula1>ISNUMBER($L15)</formula1>
     </dataValidation>
     <dataValidation sqref="B29:B38" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B29),$B29&gt;=$O28,$B29&lt;=$Q$27,$B29&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B29),$B29&gt;=$O28,$B29&lt;=$Q$27,$B29&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F29:F38" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F29),$F29&gt;0,ISNUMBER($B29))</formula1>
@@ -16994,7 +16977,7 @@
       <formula1>ISNUMBER($L28)</formula1>
     </dataValidation>
     <dataValidation sqref="B42:B51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B42),$B42&gt;=$O41,$B42&lt;=$Q$40,$B42&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B42),$B42&gt;=$O41,$B42&lt;=$Q$40,$B42&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F42:F51" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F42),$F42&gt;0,ISNUMBER($B42))</formula1>
@@ -17003,7 +16986,7 @@
       <formula1>ISNUMBER($L41)</formula1>
     </dataValidation>
     <dataValidation sqref="B55:B64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B55),$B55&gt;=$O54,$B55&lt;=$Q$53,$B55&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B55),$B55&gt;=$O54,$B55&lt;=$Q$53,$B55&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F55:F64" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F55),$F55&gt;0,ISNUMBER($B55))</formula1>
@@ -17012,7 +16995,7 @@
       <formula1>ISNUMBER($L54)</formula1>
     </dataValidation>
     <dataValidation sqref="B68:B77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B68),$B68&gt;=$O67,$B68&lt;=$Q$66,$B68&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B68),$B68&gt;=$O67,$B68&lt;=$Q$66,$B68&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F68:F77" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F68),$F68&gt;0,ISNUMBER($B68))</formula1>
@@ -17021,7 +17004,7 @@
       <formula1>ISNUMBER($L67)</formula1>
     </dataValidation>
     <dataValidation sqref="B81:B90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B81),$B81&gt;=$O80,$B81&lt;=$Q$79,$B81&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B81),$B81&gt;=$O80,$B81&lt;=$Q$79,$B81&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F81:F90" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F81),$F81&gt;0,ISNUMBER($B81))</formula1>
@@ -17030,7 +17013,7 @@
       <formula1>ISNUMBER($L80)</formula1>
     </dataValidation>
     <dataValidation sqref="B94:B103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B94),$B94&gt;=$O93,$B94&lt;=$Q$92,$B94&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B94),$B94&gt;=$O93,$B94&lt;=$Q$92,$B94&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F94:F103" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F94),$F94&gt;0,ISNUMBER($B94))</formula1>
@@ -17039,7 +17022,7 @@
       <formula1>ISNUMBER($L93)</formula1>
     </dataValidation>
     <dataValidation sqref="B107:B116" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B107),$B107&gt;=$O106,$B107&lt;=$Q$105,$B107&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B107),$B107&gt;=$O106,$B107&lt;=$Q$105,$B107&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F107:F116" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F107),$F107&gt;0,ISNUMBER($B107))</formula1>
@@ -17048,7 +17031,7 @@
       <formula1>ISNUMBER($L106)</formula1>
     </dataValidation>
     <dataValidation sqref="B120:B129" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B120),$B120&gt;=$O119,$B120&lt;=$Q$118,$B120&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B120),$B120&gt;=$O119,$B120&lt;=$Q$118,$B120&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F120:F129" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F120),$F120&gt;0,ISNUMBER($B120))</formula1>
@@ -17057,7 +17040,7 @@
       <formula1>ISNUMBER($L119)</formula1>
     </dataValidation>
     <dataValidation sqref="B133:B142" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B133),$B133&gt;=$O132,$B133&lt;=$Q$131,$B133&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B133),$B133&gt;=$O132,$B133&lt;=$Q$131,$B133&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F133:F142" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F133),$F133&gt;0,ISNUMBER($B133))</formula1>
@@ -17066,7 +17049,7 @@
       <formula1>ISNUMBER($L132)</formula1>
     </dataValidation>
     <dataValidation sqref="B146:B155" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B146),$B146&gt;=$O145,$B146&lt;=$Q$144,$B146&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B146),$B146&gt;=$O145,$B146&lt;=$Q$144,$B146&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F146:F155" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F146),$F146&gt;0,ISNUMBER($B146))</formula1>
@@ -17075,7 +17058,7 @@
       <formula1>ISNUMBER($L145)</formula1>
     </dataValidation>
     <dataValidation sqref="B159:B168" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B159),$B159&gt;=$O158,$B159&lt;=$Q$157,$B159&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B159),$B159&gt;=$O158,$B159&lt;=$Q$157,$B159&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F159:F168" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F159),$F159&gt;0,ISNUMBER($B159))</formula1>
@@ -17084,7 +17067,7 @@
       <formula1>ISNUMBER($L158)</formula1>
     </dataValidation>
     <dataValidation sqref="B172:B181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B172),$B172&gt;=$O171,$B172&lt;=$Q$170,$B172&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B172),$B172&gt;=$O171,$B172&lt;=$Q$170,$B172&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F172:F181" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F172),$F172&gt;0,ISNUMBER($B172))</formula1>
@@ -17093,7 +17076,7 @@
       <formula1>ISNUMBER($L171)</formula1>
     </dataValidation>
     <dataValidation sqref="B185:B194" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B185),$B185&gt;=$O184,$B185&lt;=$Q$183,$B185&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B185),$B185&gt;=$O184,$B185&lt;=$Q$183,$B185&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F185:F194" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F185),$F185&gt;0,ISNUMBER($B185))</formula1>
@@ -17102,7 +17085,7 @@
       <formula1>ISNUMBER($L184)</formula1>
     </dataValidation>
     <dataValidation sqref="B198:B207" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B198),$B198&gt;=$O197,$B198&lt;=$Q$196,$B198&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B198),$B198&gt;=$O197,$B198&lt;=$Q$196,$B198&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F198:F207" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F198),$F198&gt;0,ISNUMBER($B198))</formula1>
@@ -17111,7 +17094,7 @@
       <formula1>ISNUMBER($L197)</formula1>
     </dataValidation>
     <dataValidation sqref="B211:B220" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B211),$B211&gt;=$O210,$B211&lt;=$Q$209,$B211&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B211),$B211&gt;=$O210,$B211&lt;=$Q$209,$B211&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F211:F220" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F211),$F211&gt;0,ISNUMBER($B211))</formula1>
@@ -17120,7 +17103,7 @@
       <formula1>ISNUMBER($L210)</formula1>
     </dataValidation>
     <dataValidation sqref="B224:B233" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B224),$B224&gt;=$O223,$B224&lt;=$Q$222,$B224&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B224),$B224&gt;=$O223,$B224&lt;=$Q$222,$B224&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F224:F233" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F224),$F224&gt;0,ISNUMBER($B224))</formula1>
@@ -17129,7 +17112,7 @@
       <formula1>ISNUMBER($L223)</formula1>
     </dataValidation>
     <dataValidation sqref="B237:B246" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B237),$B237&gt;=$O236,$B237&lt;=$Q$235,$B237&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B237),$B237&gt;=$O236,$B237&lt;=$Q$235,$B237&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F237:F246" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F237),$F237&gt;0,ISNUMBER($B237))</formula1>
@@ -17138,7 +17121,7 @@
       <formula1>ISNUMBER($L236)</formula1>
     </dataValidation>
     <dataValidation sqref="B250:B259" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B250),$B250&gt;=$O249,$B250&lt;=$Q$248,$B250&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B250),$B250&gt;=$O249,$B250&lt;=$Q$248,$B250&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F250:F259" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F250),$F250&gt;0,ISNUMBER($B250))</formula1>
@@ -17147,7 +17130,7 @@
       <formula1>ISNUMBER($L249)</formula1>
     </dataValidation>
     <dataValidation sqref="B263:B272" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B263),$B263&gt;=$O262,$B263&lt;=$Q$261,$B263&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B263),$B263&gt;=$O262,$B263&lt;=$Q$261,$B263&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F263:F272" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F263),$F263&gt;0,ISNUMBER($B263))</formula1>
@@ -17156,7 +17139,7 @@
       <formula1>ISNUMBER($L262)</formula1>
     </dataValidation>
     <dataValidation sqref="B276:B285" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B276),$B276&gt;=$O275,$B276&lt;=$Q$274,$B276&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B276),$B276&gt;=$O275,$B276&lt;=$Q$274,$B276&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F276:F285" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F276),$F276&gt;0,ISNUMBER($B276))</formula1>
@@ -17165,7 +17148,7 @@
       <formula1>ISNUMBER($L275)</formula1>
     </dataValidation>
     <dataValidation sqref="B289:B298" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B289),$B289&gt;=$O288,$B289&lt;=$Q$287,$B289&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B289),$B289&gt;=$O288,$B289&lt;=$Q$287,$B289&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F289:F298" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F289),$F289&gt;0,ISNUMBER($B289))</formula1>
@@ -17174,7 +17157,7 @@
       <formula1>ISNUMBER($L288)</formula1>
     </dataValidation>
     <dataValidation sqref="B302:B311" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B302),$B302&gt;=$O301,$B302&lt;=$Q$300,$B302&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B302),$B302&gt;=$O301,$B302&lt;=$Q$300,$B302&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F302:F311" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F302),$F302&gt;0,ISNUMBER($B302))</formula1>
@@ -17183,7 +17166,7 @@
       <formula1>ISNUMBER($L301)</formula1>
     </dataValidation>
     <dataValidation sqref="B315:B324" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date not allowed in this quarter" error="The date must fall inside the quarter shown in the blue bar above this block, must not be earlier than the entry above it, and must be after the ‘Locked / reconciled up to’ date. Use the block of the correct quarter." promptTitle="Repayment date" prompt="Value date of the repayment (must sit inside this quarter)." type="custom" errorStyle="stop">
-      <formula1>AND(ISNUMBER($B315),$B315&gt;=$O314,$B315&lt;=$Q$313,$B315&gt;Locked_To)</formula1>
+      <formula1>AND(ISNUMBER($B315),$B315&gt;=$O314,$B315&lt;=$Q$313,$B315&gt;$H$10)</formula1>
     </dataValidation>
     <dataValidation sqref="F315:F324" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Enter the date first" error="Type the repayment date in the Date column first, then a positive amount." promptTitle="Repayment amount" prompt="Amount credited to the loan on that date." type="custom" errorStyle="stop">
       <formula1>AND(ISNUMBER($F315),$F315&gt;0,ISNUMBER($B315))</formula1>
@@ -17192,8 +17175,27 @@
       <formula1>ISNUMBER($L314)</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" gridLines="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.55" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 Bank loan account – quarterly compound interest statement&amp;R&amp;8 Printed &amp;D</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;F&amp;C&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <rowBreaks count="8" manualBreakCount="8">
+    <brk id="39" min="0" max="16383" man="1"/>
+    <brk id="78" min="0" max="16383" man="1"/>
+    <brk id="117" min="0" max="16383" man="1"/>
+    <brk id="156" min="0" max="16383" man="1"/>
+    <brk id="195" min="0" max="16383" man="1"/>
+    <brk id="234" min="0" max="16383" man="1"/>
+    <brk id="273" min="0" max="16383" man="1"/>
+    <brk id="312" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -17206,18 +17208,18 @@
   <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="5" max="5"/>
+    <col width="13.5" customWidth="1" min="6" max="6"/>
+    <col width="14.5" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="13.5" customWidth="1" min="9" max="9"/>
+    <col width="10.5" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -18596,8 +18598,17 @@
       <formula>$K5="LOCKED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" gridLines="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.55" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 Bank loan account – quarter-by-quarter summary&amp;R&amp;8 Printed &amp;D</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;F&amp;C&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -18605,13 +18616,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="93" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -18628,7 +18639,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="66" t="inlineStr">
         <is>
           <t>This workbook keeps a bank loan account on the same layout as a bank statement and charges interest the way the bank does: interest accrues on the daily outstanding balance and is added to the balance (capitalised) at every quarter-end, so the next quarter earns interest on interest – quarterly compounding.</t>
@@ -18666,7 +18677,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18678,7 +18689,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
+    <row r="11" ht="60" customHeight="1">
       <c r="A11" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18752,7 +18763,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18764,7 +18775,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="45" customHeight="1">
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18776,7 +18787,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18819,7 +18830,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18831,7 +18842,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18843,7 +18854,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18874,7 +18885,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18886,7 +18897,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
+    <row r="34" ht="30" customHeight="1">
       <c r="A34" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18898,7 +18909,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="67" t="inlineStr">
         <is>
           <t>•</t>
@@ -18906,12 +18917,24 @@
       </c>
       <c r="B35" s="66" t="inlineStr">
         <is>
+          <t>Printing is set up for A4. The statement and the summary print landscape, scaled to one page wide, with the column headings repeated on every page, each quarter kept whole on a page, and ‘Page n of m’ in the footer. This guide prints A4 portrait. Just press Ctrl+P – no page setup needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="67" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B36" s="66" t="inlineStr">
+        <is>
           <t>Sheet/workbook password: MMS-loan-2026 – keep it with the file owner. You only need it to change the structure (for example to add more repayment rows or quarters).</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="68" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="68" t="inlineStr">
         <is>
           <t>Ask for a rebuilt file if you need more than 3 rate slots, more rows per quarter, a longer tenure, or repayments split between interest and principal instead of quarter-end capitalisation.</t>
         </is>
@@ -18922,7 +18945,7 @@
   <mergeCells count="9">
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A18:B18"/>
@@ -18930,7 +18953,17 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1" gridLines="0"/>
+  <pageMargins left="0.3" right="0.3" top="0.55" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 Bank loan – quarterly compound interest file · user guide&amp;R&amp;8 Printed &amp;D</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;F&amp;C&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -18988,15 +19021,15 @@
         <v>1</v>
       </c>
       <c r="E2" s="70">
-        <f>IF(BF_Date="",0,BF_Date)</f>
+        <f>IF('Loan Statement'!$H$6="",0,'Loan Statement'!$H$6)</f>
         <v/>
       </c>
       <c r="F2" s="70">
-        <f>IF(BF_Date="",0,IF(Qtr_Mode="Calendar quarter-ends",IF(EOMONTH(BF_Date,MOD(3-MOD(MONTH(BF_Date),3),3))=BF_Date,EOMONTH(BF_Date,3),EOMONTH(BF_Date,MOD(3-MOD(MONTH(BF_Date),3),3))),EDATE(BF_Date,3)))</f>
+        <f>IF('Loan Statement'!$H$6="",0,IF('Loan Statement'!$H$9="Calendar quarter-ends",IF(EOMONTH('Loan Statement'!$H$6,MOD(3-MOD(MONTH('Loan Statement'!$H$6),3),3))='Loan Statement'!$H$6,EOMONTH('Loan Statement'!$H$6,3),EOMONTH('Loan Statement'!$H$6,MOD(3-MOD(MONTH('Loan Statement'!$H$6),3),3))),EDATE('Loan Statement'!$H$6,3)))</f>
         <v/>
       </c>
       <c r="G2">
-        <f>TRIM(IF(MAX(0,MIN($F$2,R1_To)-MAX($E$2,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$2,R1_To)-MAX($E$2,R1_From))&amp;IF(MAX(0,MIN($F$2,R1_To)-MAX($E$2,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$2,R2_To)-MAX($E$2,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$2,R2_To)-MAX($E$2,R2_From))&amp;IF(MAX(0,MIN($F$2,R2_To)-MAX($E$2,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$2,R3_To)-MAX($E$2,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$2,R3_To)-MAX($E$2,R3_From))&amp;IF(MAX(0,MIN($F$2,R3_To)-MAX($E$2,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$2,$B$3)-MAX($E$2,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$2,$B$3)-MAX($E$2,$B$2))&amp;IF(MAX(0,MIN($F$2,$B$3)-MAX($E$2,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$2,$B$5)-MAX($E$2,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$2,$B$5)-MAX($E$2,$B$4))&amp;IF(MAX(0,MIN($F$2,$B$5)-MAX($E$2,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$2,$B$7)-MAX($E$2,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$2,$B$7)-MAX($E$2,$B$6))&amp;IF(MAX(0,MIN($F$2,$B$7)-MAX($E$2,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19007,7 +19040,7 @@
         </is>
       </c>
       <c r="B3">
-        <f>IF('Loan Statement'!$K$8="",Big_Date,'Loan Statement'!$K$8)</f>
+        <f>IF('Loan Statement'!$K$8="",$B$1,'Loan Statement'!$K$8)</f>
         <v/>
       </c>
       <c r="D3" t="n">
@@ -19018,11 +19051,11 @@
         <v/>
       </c>
       <c r="F3" s="70">
-        <f>IF($F$2=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$2,3),EDATE($F$2,3)))</f>
+        <f>IF($F$2=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$2,3),EDATE($F$2,3)))</f>
         <v/>
       </c>
       <c r="G3">
-        <f>TRIM(IF(MAX(0,MIN($F$3,R1_To)-MAX($E$3,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$3,R1_To)-MAX($E$3,R1_From))&amp;IF(MAX(0,MIN($F$3,R1_To)-MAX($E$3,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$3,R2_To)-MAX($E$3,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$3,R2_To)-MAX($E$3,R2_From))&amp;IF(MAX(0,MIN($F$3,R2_To)-MAX($E$3,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$3,R3_To)-MAX($E$3,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$3,R3_To)-MAX($E$3,R3_From))&amp;IF(MAX(0,MIN($F$3,R3_To)-MAX($E$3,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$3,$B$3)-MAX($E$3,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$3,$B$3)-MAX($E$3,$B$2))&amp;IF(MAX(0,MIN($F$3,$B$3)-MAX($E$3,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$3,$B$5)-MAX($E$3,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$3,$B$5)-MAX($E$3,$B$4))&amp;IF(MAX(0,MIN($F$3,$B$5)-MAX($E$3,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$3,$B$7)-MAX($E$3,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$3,$B$7)-MAX($E$3,$B$6))&amp;IF(MAX(0,MIN($F$3,$B$7)-MAX($E$3,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19033,7 +19066,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>IF('Loan Statement'!$K$8="",Big_Date,'Loan Statement'!$K$8)</f>
+        <f>IF('Loan Statement'!$K$8="",$B$1,'Loan Statement'!$K$8)</f>
         <v/>
       </c>
       <c r="D4" t="n">
@@ -19044,11 +19077,11 @@
         <v/>
       </c>
       <c r="F4" s="70">
-        <f>IF($F$3=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$3,3),EDATE($F$3,3)))</f>
+        <f>IF($F$3=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$3,3),EDATE($F$3,3)))</f>
         <v/>
       </c>
       <c r="G4">
-        <f>TRIM(IF(MAX(0,MIN($F$4,R1_To)-MAX($E$4,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$4,R1_To)-MAX($E$4,R1_From))&amp;IF(MAX(0,MIN($F$4,R1_To)-MAX($E$4,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$4,R2_To)-MAX($E$4,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$4,R2_To)-MAX($E$4,R2_From))&amp;IF(MAX(0,MIN($F$4,R2_To)-MAX($E$4,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$4,R3_To)-MAX($E$4,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$4,R3_To)-MAX($E$4,R3_From))&amp;IF(MAX(0,MIN($F$4,R3_To)-MAX($E$4,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$4,$B$3)-MAX($E$4,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$4,$B$3)-MAX($E$4,$B$2))&amp;IF(MAX(0,MIN($F$4,$B$3)-MAX($E$4,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$4,$B$5)-MAX($E$4,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$4,$B$5)-MAX($E$4,$B$4))&amp;IF(MAX(0,MIN($F$4,$B$5)-MAX($E$4,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$4,$B$7)-MAX($E$4,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$4,$B$7)-MAX($E$4,$B$6))&amp;IF(MAX(0,MIN($F$4,$B$7)-MAX($E$4,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19059,7 +19092,7 @@
         </is>
       </c>
       <c r="B5">
-        <f>IF('Loan Statement'!$K$9="",Big_Date,'Loan Statement'!$K$9)</f>
+        <f>IF('Loan Statement'!$K$9="",$B$1,'Loan Statement'!$K$9)</f>
         <v/>
       </c>
       <c r="D5" t="n">
@@ -19070,11 +19103,11 @@
         <v/>
       </c>
       <c r="F5" s="70">
-        <f>IF($F$4=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$4,3),EDATE($F$4,3)))</f>
+        <f>IF($F$4=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$4,3),EDATE($F$4,3)))</f>
         <v/>
       </c>
       <c r="G5">
-        <f>TRIM(IF(MAX(0,MIN($F$5,R1_To)-MAX($E$5,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$5,R1_To)-MAX($E$5,R1_From))&amp;IF(MAX(0,MIN($F$5,R1_To)-MAX($E$5,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$5,R2_To)-MAX($E$5,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$5,R2_To)-MAX($E$5,R2_From))&amp;IF(MAX(0,MIN($F$5,R2_To)-MAX($E$5,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$5,R3_To)-MAX($E$5,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$5,R3_To)-MAX($E$5,R3_From))&amp;IF(MAX(0,MIN($F$5,R3_To)-MAX($E$5,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$5,$B$3)-MAX($E$5,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$5,$B$3)-MAX($E$5,$B$2))&amp;IF(MAX(0,MIN($F$5,$B$3)-MAX($E$5,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$5,$B$5)-MAX($E$5,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$5,$B$5)-MAX($E$5,$B$4))&amp;IF(MAX(0,MIN($F$5,$B$5)-MAX($E$5,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$5,$B$7)-MAX($E$5,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$5,$B$7)-MAX($E$5,$B$6))&amp;IF(MAX(0,MIN($F$5,$B$7)-MAX($E$5,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19085,7 +19118,7 @@
         </is>
       </c>
       <c r="B6">
-        <f>IF('Loan Statement'!$K$9="",Big_Date,'Loan Statement'!$K$9)</f>
+        <f>IF('Loan Statement'!$K$9="",$B$1,'Loan Statement'!$K$9)</f>
         <v/>
       </c>
       <c r="D6" t="n">
@@ -19096,11 +19129,11 @@
         <v/>
       </c>
       <c r="F6" s="70">
-        <f>IF($F$5=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$5,3),EDATE($F$5,3)))</f>
+        <f>IF($F$5=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$5,3),EDATE($F$5,3)))</f>
         <v/>
       </c>
       <c r="G6">
-        <f>TRIM(IF(MAX(0,MIN($F$6,R1_To)-MAX($E$6,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$6,R1_To)-MAX($E$6,R1_From))&amp;IF(MAX(0,MIN($F$6,R1_To)-MAX($E$6,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$6,R2_To)-MAX($E$6,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$6,R2_To)-MAX($E$6,R2_From))&amp;IF(MAX(0,MIN($F$6,R2_To)-MAX($E$6,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$6,R3_To)-MAX($E$6,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$6,R3_To)-MAX($E$6,R3_From))&amp;IF(MAX(0,MIN($F$6,R3_To)-MAX($E$6,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$6,$B$3)-MAX($E$6,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$6,$B$3)-MAX($E$6,$B$2))&amp;IF(MAX(0,MIN($F$6,$B$3)-MAX($E$6,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$6,$B$5)-MAX($E$6,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$6,$B$5)-MAX($E$6,$B$4))&amp;IF(MAX(0,MIN($F$6,$B$5)-MAX($E$6,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$6,$B$7)-MAX($E$6,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$6,$B$7)-MAX($E$6,$B$6))&amp;IF(MAX(0,MIN($F$6,$B$7)-MAX($E$6,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19111,7 +19144,7 @@
         </is>
       </c>
       <c r="B7">
-        <f>Big_Date</f>
+        <f>$B$1</f>
         <v/>
       </c>
       <c r="D7" t="n">
@@ -19122,11 +19155,11 @@
         <v/>
       </c>
       <c r="F7" s="70">
-        <f>IF($F$6=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$6,3),EDATE($F$6,3)))</f>
+        <f>IF($F$6=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$6,3),EDATE($F$6,3)))</f>
         <v/>
       </c>
       <c r="G7">
-        <f>TRIM(IF(MAX(0,MIN($F$7,R1_To)-MAX($E$7,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$7,R1_To)-MAX($E$7,R1_From))&amp;IF(MAX(0,MIN($F$7,R1_To)-MAX($E$7,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$7,R2_To)-MAX($E$7,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$7,R2_To)-MAX($E$7,R2_From))&amp;IF(MAX(0,MIN($F$7,R2_To)-MAX($E$7,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$7,R3_To)-MAX($E$7,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$7,R3_To)-MAX($E$7,R3_From))&amp;IF(MAX(0,MIN($F$7,R3_To)-MAX($E$7,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$7,$B$3)-MAX($E$7,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$7,$B$3)-MAX($E$7,$B$2))&amp;IF(MAX(0,MIN($F$7,$B$3)-MAX($E$7,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$7,$B$5)-MAX($E$7,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$7,$B$5)-MAX($E$7,$B$4))&amp;IF(MAX(0,MIN($F$7,$B$5)-MAX($E$7,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$7,$B$7)-MAX($E$7,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$7,$B$7)-MAX($E$7,$B$6))&amp;IF(MAX(0,MIN($F$7,$B$7)-MAX($E$7,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19148,11 +19181,11 @@
         <v/>
       </c>
       <c r="F8" s="70">
-        <f>IF($F$7=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$7,3),EDATE($F$7,3)))</f>
+        <f>IF($F$7=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$7,3),EDATE($F$7,3)))</f>
         <v/>
       </c>
       <c r="G8">
-        <f>TRIM(IF(MAX(0,MIN($F$8,R1_To)-MAX($E$8,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$8,R1_To)-MAX($E$8,R1_From))&amp;IF(MAX(0,MIN($F$8,R1_To)-MAX($E$8,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$8,R2_To)-MAX($E$8,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$8,R2_To)-MAX($E$8,R2_From))&amp;IF(MAX(0,MIN($F$8,R2_To)-MAX($E$8,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$8,R3_To)-MAX($E$8,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$8,R3_To)-MAX($E$8,R3_From))&amp;IF(MAX(0,MIN($F$8,R3_To)-MAX($E$8,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$8,$B$3)-MAX($E$8,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$8,$B$3)-MAX($E$8,$B$2))&amp;IF(MAX(0,MIN($F$8,$B$3)-MAX($E$8,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$8,$B$5)-MAX($E$8,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$8,$B$5)-MAX($E$8,$B$4))&amp;IF(MAX(0,MIN($F$8,$B$5)-MAX($E$8,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$8,$B$7)-MAX($E$8,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$8,$B$7)-MAX($E$8,$B$6))&amp;IF(MAX(0,MIN($F$8,$B$7)-MAX($E$8,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19174,11 +19207,11 @@
         <v/>
       </c>
       <c r="F9" s="70">
-        <f>IF($F$8=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$8,3),EDATE($F$8,3)))</f>
+        <f>IF($F$8=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$8,3),EDATE($F$8,3)))</f>
         <v/>
       </c>
       <c r="G9">
-        <f>TRIM(IF(MAX(0,MIN($F$9,R1_To)-MAX($E$9,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$9,R1_To)-MAX($E$9,R1_From))&amp;IF(MAX(0,MIN($F$9,R1_To)-MAX($E$9,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$9,R2_To)-MAX($E$9,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$9,R2_To)-MAX($E$9,R2_From))&amp;IF(MAX(0,MIN($F$9,R2_To)-MAX($E$9,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$9,R3_To)-MAX($E$9,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$9,R3_To)-MAX($E$9,R3_From))&amp;IF(MAX(0,MIN($F$9,R3_To)-MAX($E$9,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$9,$B$3)-MAX($E$9,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$9,$B$3)-MAX($E$9,$B$2))&amp;IF(MAX(0,MIN($F$9,$B$3)-MAX($E$9,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$9,$B$5)-MAX($E$9,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$9,$B$5)-MAX($E$9,$B$4))&amp;IF(MAX(0,MIN($F$9,$B$5)-MAX($E$9,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$9,$B$7)-MAX($E$9,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$9,$B$7)-MAX($E$9,$B$6))&amp;IF(MAX(0,MIN($F$9,$B$7)-MAX($E$9,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19200,11 +19233,11 @@
         <v/>
       </c>
       <c r="F10" s="70">
-        <f>IF($F$9=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$9,3),EDATE($F$9,3)))</f>
+        <f>IF($F$9=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$9,3),EDATE($F$9,3)))</f>
         <v/>
       </c>
       <c r="G10">
-        <f>TRIM(IF(MAX(0,MIN($F$10,R1_To)-MAX($E$10,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$10,R1_To)-MAX($E$10,R1_From))&amp;IF(MAX(0,MIN($F$10,R1_To)-MAX($E$10,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$10,R2_To)-MAX($E$10,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$10,R2_To)-MAX($E$10,R2_From))&amp;IF(MAX(0,MIN($F$10,R2_To)-MAX($E$10,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$10,R3_To)-MAX($E$10,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$10,R3_To)-MAX($E$10,R3_From))&amp;IF(MAX(0,MIN($F$10,R3_To)-MAX($E$10,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$10,$B$3)-MAX($E$10,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$10,$B$3)-MAX($E$10,$B$2))&amp;IF(MAX(0,MIN($F$10,$B$3)-MAX($E$10,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$10,$B$5)-MAX($E$10,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$10,$B$5)-MAX($E$10,$B$4))&amp;IF(MAX(0,MIN($F$10,$B$5)-MAX($E$10,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$10,$B$7)-MAX($E$10,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$10,$B$7)-MAX($E$10,$B$6))&amp;IF(MAX(0,MIN($F$10,$B$7)-MAX($E$10,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19217,11 +19250,11 @@
         <v/>
       </c>
       <c r="F11" s="70">
-        <f>IF($F$10=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$10,3),EDATE($F$10,3)))</f>
+        <f>IF($F$10=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$10,3),EDATE($F$10,3)))</f>
         <v/>
       </c>
       <c r="G11">
-        <f>TRIM(IF(MAX(0,MIN($F$11,R1_To)-MAX($E$11,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$11,R1_To)-MAX($E$11,R1_From))&amp;IF(MAX(0,MIN($F$11,R1_To)-MAX($E$11,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$11,R2_To)-MAX($E$11,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$11,R2_To)-MAX($E$11,R2_From))&amp;IF(MAX(0,MIN($F$11,R2_To)-MAX($E$11,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$11,R3_To)-MAX($E$11,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$11,R3_To)-MAX($E$11,R3_From))&amp;IF(MAX(0,MIN($F$11,R3_To)-MAX($E$11,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$11,$B$3)-MAX($E$11,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$11,$B$3)-MAX($E$11,$B$2))&amp;IF(MAX(0,MIN($F$11,$B$3)-MAX($E$11,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$11,$B$5)-MAX($E$11,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$11,$B$5)-MAX($E$11,$B$4))&amp;IF(MAX(0,MIN($F$11,$B$5)-MAX($E$11,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$11,$B$7)-MAX($E$11,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$11,$B$7)-MAX($E$11,$B$6))&amp;IF(MAX(0,MIN($F$11,$B$7)-MAX($E$11,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19232,7 +19265,7 @@
         </is>
       </c>
       <c r="B12">
-        <f>IFERROR(LOOKUP(TODAY(),Eff_Dates,Bal_Col),BF_Amount)</f>
+        <f>IFERROR(LOOKUP(TODAY(),'Loan Statement'!$O$14:$O$325,'Loan Statement'!$S$14:$S$325),'Loan Statement'!$H$7)</f>
         <v/>
       </c>
       <c r="D12" t="n">
@@ -19243,11 +19276,11 @@
         <v/>
       </c>
       <c r="F12" s="70">
-        <f>IF($F$11=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$11,3),EDATE($F$11,3)))</f>
+        <f>IF($F$11=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$11,3),EDATE($F$11,3)))</f>
         <v/>
       </c>
       <c r="G12">
-        <f>TRIM(IF(MAX(0,MIN($F$12,R1_To)-MAX($E$12,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$12,R1_To)-MAX($E$12,R1_From))&amp;IF(MAX(0,MIN($F$12,R1_To)-MAX($E$12,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$12,R2_To)-MAX($E$12,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$12,R2_To)-MAX($E$12,R2_From))&amp;IF(MAX(0,MIN($F$12,R2_To)-MAX($E$12,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$12,R3_To)-MAX($E$12,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$12,R3_To)-MAX($E$12,R3_From))&amp;IF(MAX(0,MIN($F$12,R3_To)-MAX($E$12,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$12,$B$3)-MAX($E$12,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$12,$B$3)-MAX($E$12,$B$2))&amp;IF(MAX(0,MIN($F$12,$B$3)-MAX($E$12,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$12,$B$5)-MAX($E$12,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$12,$B$5)-MAX($E$12,$B$4))&amp;IF(MAX(0,MIN($F$12,$B$5)-MAX($E$12,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$12,$B$7)-MAX($E$12,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$12,$B$7)-MAX($E$12,$B$6))&amp;IF(MAX(0,MIN($F$12,$B$7)-MAX($E$12,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19258,7 +19291,7 @@
         </is>
       </c>
       <c r="B13">
-        <f>IFERROR(LOOKUP(TODAY(),Eff_Dates,Eff_Dates),BF_Date)</f>
+        <f>IFERROR(LOOKUP(TODAY(),'Loan Statement'!$O$14:$O$325,'Loan Statement'!$O$14:$O$325),'Loan Statement'!$H$6)</f>
         <v/>
       </c>
       <c r="D13" t="n">
@@ -19269,11 +19302,11 @@
         <v/>
       </c>
       <c r="F13" s="70">
-        <f>IF($F$12=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$12,3),EDATE($F$12,3)))</f>
+        <f>IF($F$12=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$12,3),EDATE($F$12,3)))</f>
         <v/>
       </c>
       <c r="G13">
-        <f>TRIM(IF(MAX(0,MIN($F$13,R1_To)-MAX($E$13,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$13,R1_To)-MAX($E$13,R1_From))&amp;IF(MAX(0,MIN($F$13,R1_To)-MAX($E$13,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$13,R2_To)-MAX($E$13,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$13,R2_To)-MAX($E$13,R2_From))&amp;IF(MAX(0,MIN($F$13,R2_To)-MAX($E$13,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$13,R3_To)-MAX($E$13,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$13,R3_To)-MAX($E$13,R3_From))&amp;IF(MAX(0,MIN($F$13,R3_To)-MAX($E$13,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$13,$B$3)-MAX($E$13,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$13,$B$3)-MAX($E$13,$B$2))&amp;IF(MAX(0,MIN($F$13,$B$3)-MAX($E$13,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$13,$B$5)-MAX($E$13,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$13,$B$5)-MAX($E$13,$B$4))&amp;IF(MAX(0,MIN($F$13,$B$5)-MAX($E$13,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$13,$B$7)-MAX($E$13,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$13,$B$7)-MAX($E$13,$B$6))&amp;IF(MAX(0,MIN($F$13,$B$7)-MAX($E$13,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19284,7 +19317,7 @@
         </is>
       </c>
       <c r="B14">
-        <f>IF(OR(Day_Basis=0,Day_Basis=""),0,IFERROR(LOOKUP(TODAY(),Eff_Dates,Accr_Col),0)+$B$12*(Rate_1*MAX(0,MIN(TODAY(),R1_To)-MAX($B$13,R1_From))+Rate_2*MAX(0,MIN(TODAY(),R2_To)-MAX($B$13,R2_From))+Rate_3*MAX(0,MIN(TODAY(),R3_To)-MAX($B$13,R3_From)))/100/Day_Basis)</f>
+        <f>IF(OR('Loan Statement'!$H$8=0,'Loan Statement'!$H$8=""),0,IFERROR(LOOKUP(TODAY(),'Loan Statement'!$O$14:$O$325,'Loan Statement'!$T$14:$T$325),0)+$B$12*($B$8*MAX(0,MIN(TODAY(),$B$3)-MAX($B$13,$B$2))+$B$9*MAX(0,MIN(TODAY(),$B$5)-MAX($B$13,$B$4))+$B$10*MAX(0,MIN(TODAY(),$B$7)-MAX($B$13,$B$6)))/100/'Loan Statement'!$H$8)</f>
         <v/>
       </c>
       <c r="D14" t="n">
@@ -19295,11 +19328,11 @@
         <v/>
       </c>
       <c r="F14" s="70">
-        <f>IF($F$13=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$13,3),EDATE($F$13,3)))</f>
+        <f>IF($F$13=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$13,3),EDATE($F$13,3)))</f>
         <v/>
       </c>
       <c r="G14">
-        <f>TRIM(IF(MAX(0,MIN($F$14,R1_To)-MAX($E$14,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$14,R1_To)-MAX($E$14,R1_From))&amp;IF(MAX(0,MIN($F$14,R1_To)-MAX($E$14,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$14,R2_To)-MAX($E$14,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$14,R2_To)-MAX($E$14,R2_From))&amp;IF(MAX(0,MIN($F$14,R2_To)-MAX($E$14,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$14,R3_To)-MAX($E$14,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$14,R3_To)-MAX($E$14,R3_From))&amp;IF(MAX(0,MIN($F$14,R3_To)-MAX($E$14,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$14,$B$3)-MAX($E$14,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$14,$B$3)-MAX($E$14,$B$2))&amp;IF(MAX(0,MIN($F$14,$B$3)-MAX($E$14,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$14,$B$5)-MAX($E$14,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$14,$B$5)-MAX($E$14,$B$4))&amp;IF(MAX(0,MIN($F$14,$B$5)-MAX($E$14,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$14,$B$7)-MAX($E$14,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$14,$B$7)-MAX($E$14,$B$6))&amp;IF(MAX(0,MIN($F$14,$B$7)-MAX($E$14,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19321,11 +19354,11 @@
         <v/>
       </c>
       <c r="F15" s="70">
-        <f>IF($F$14=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$14,3),EDATE($F$14,3)))</f>
+        <f>IF($F$14=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$14,3),EDATE($F$14,3)))</f>
         <v/>
       </c>
       <c r="G15">
-        <f>TRIM(IF(MAX(0,MIN($F$15,R1_To)-MAX($E$15,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$15,R1_To)-MAX($E$15,R1_From))&amp;IF(MAX(0,MIN($F$15,R1_To)-MAX($E$15,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$15,R2_To)-MAX($E$15,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$15,R2_To)-MAX($E$15,R2_From))&amp;IF(MAX(0,MIN($F$15,R2_To)-MAX($E$15,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$15,R3_To)-MAX($E$15,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$15,R3_To)-MAX($E$15,R3_From))&amp;IF(MAX(0,MIN($F$15,R3_To)-MAX($E$15,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$15,$B$3)-MAX($E$15,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$15,$B$3)-MAX($E$15,$B$2))&amp;IF(MAX(0,MIN($F$15,$B$3)-MAX($E$15,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$15,$B$5)-MAX($E$15,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$15,$B$5)-MAX($E$15,$B$4))&amp;IF(MAX(0,MIN($F$15,$B$5)-MAX($E$15,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$15,$B$7)-MAX($E$15,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$15,$B$7)-MAX($E$15,$B$6))&amp;IF(MAX(0,MIN($F$15,$B$7)-MAX($E$15,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19347,11 +19380,11 @@
         <v/>
       </c>
       <c r="F16" s="70">
-        <f>IF($F$15=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$15,3),EDATE($F$15,3)))</f>
+        <f>IF($F$15=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$15,3),EDATE($F$15,3)))</f>
         <v/>
       </c>
       <c r="G16">
-        <f>TRIM(IF(MAX(0,MIN($F$16,R1_To)-MAX($E$16,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$16,R1_To)-MAX($E$16,R1_From))&amp;IF(MAX(0,MIN($F$16,R1_To)-MAX($E$16,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$16,R2_To)-MAX($E$16,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$16,R2_To)-MAX($E$16,R2_From))&amp;IF(MAX(0,MIN($F$16,R2_To)-MAX($E$16,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$16,R3_To)-MAX($E$16,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$16,R3_To)-MAX($E$16,R3_From))&amp;IF(MAX(0,MIN($F$16,R3_To)-MAX($E$16,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$16,$B$3)-MAX($E$16,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$16,$B$3)-MAX($E$16,$B$2))&amp;IF(MAX(0,MIN($F$16,$B$3)-MAX($E$16,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$16,$B$5)-MAX($E$16,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$16,$B$5)-MAX($E$16,$B$4))&amp;IF(MAX(0,MIN($F$16,$B$5)-MAX($E$16,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$16,$B$7)-MAX($E$16,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$16,$B$7)-MAX($E$16,$B$6))&amp;IF(MAX(0,MIN($F$16,$B$7)-MAX($E$16,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19373,11 +19406,11 @@
         <v/>
       </c>
       <c r="F17" s="70">
-        <f>IF($F$16=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$16,3),EDATE($F$16,3)))</f>
+        <f>IF($F$16=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$16,3),EDATE($F$16,3)))</f>
         <v/>
       </c>
       <c r="G17">
-        <f>TRIM(IF(MAX(0,MIN($F$17,R1_To)-MAX($E$17,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$17,R1_To)-MAX($E$17,R1_From))&amp;IF(MAX(0,MIN($F$17,R1_To)-MAX($E$17,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$17,R2_To)-MAX($E$17,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$17,R2_To)-MAX($E$17,R2_From))&amp;IF(MAX(0,MIN($F$17,R2_To)-MAX($E$17,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$17,R3_To)-MAX($E$17,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$17,R3_To)-MAX($E$17,R3_From))&amp;IF(MAX(0,MIN($F$17,R3_To)-MAX($E$17,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$17,$B$3)-MAX($E$17,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$17,$B$3)-MAX($E$17,$B$2))&amp;IF(MAX(0,MIN($F$17,$B$3)-MAX($E$17,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$17,$B$5)-MAX($E$17,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$17,$B$5)-MAX($E$17,$B$4))&amp;IF(MAX(0,MIN($F$17,$B$5)-MAX($E$17,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$17,$B$7)-MAX($E$17,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$17,$B$7)-MAX($E$17,$B$6))&amp;IF(MAX(0,MIN($F$17,$B$7)-MAX($E$17,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19399,11 +19432,11 @@
         <v/>
       </c>
       <c r="F18" s="70">
-        <f>IF($F$17=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$17,3),EDATE($F$17,3)))</f>
+        <f>IF($F$17=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$17,3),EDATE($F$17,3)))</f>
         <v/>
       </c>
       <c r="G18">
-        <f>TRIM(IF(MAX(0,MIN($F$18,R1_To)-MAX($E$18,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$18,R1_To)-MAX($E$18,R1_From))&amp;IF(MAX(0,MIN($F$18,R1_To)-MAX($E$18,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$18,R2_To)-MAX($E$18,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$18,R2_To)-MAX($E$18,R2_From))&amp;IF(MAX(0,MIN($F$18,R2_To)-MAX($E$18,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$18,R3_To)-MAX($E$18,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$18,R3_To)-MAX($E$18,R3_From))&amp;IF(MAX(0,MIN($F$18,R3_To)-MAX($E$18,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$18,$B$3)-MAX($E$18,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$18,$B$3)-MAX($E$18,$B$2))&amp;IF(MAX(0,MIN($F$18,$B$3)-MAX($E$18,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$18,$B$5)-MAX($E$18,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$18,$B$5)-MAX($E$18,$B$4))&amp;IF(MAX(0,MIN($F$18,$B$5)-MAX($E$18,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$18,$B$7)-MAX($E$18,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$18,$B$7)-MAX($E$18,$B$6))&amp;IF(MAX(0,MIN($F$18,$B$7)-MAX($E$18,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19416,11 +19449,11 @@
         <v/>
       </c>
       <c r="F19" s="70">
-        <f>IF($F$18=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$18,3),EDATE($F$18,3)))</f>
+        <f>IF($F$18=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$18,3),EDATE($F$18,3)))</f>
         <v/>
       </c>
       <c r="G19">
-        <f>TRIM(IF(MAX(0,MIN($F$19,R1_To)-MAX($E$19,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$19,R1_To)-MAX($E$19,R1_From))&amp;IF(MAX(0,MIN($F$19,R1_To)-MAX($E$19,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$19,R2_To)-MAX($E$19,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$19,R2_To)-MAX($E$19,R2_From))&amp;IF(MAX(0,MIN($F$19,R2_To)-MAX($E$19,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$19,R3_To)-MAX($E$19,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$19,R3_To)-MAX($E$19,R3_From))&amp;IF(MAX(0,MIN($F$19,R3_To)-MAX($E$19,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$19,$B$3)-MAX($E$19,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$19,$B$3)-MAX($E$19,$B$2))&amp;IF(MAX(0,MIN($F$19,$B$3)-MAX($E$19,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$19,$B$5)-MAX($E$19,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$19,$B$5)-MAX($E$19,$B$4))&amp;IF(MAX(0,MIN($F$19,$B$5)-MAX($E$19,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$19,$B$7)-MAX($E$19,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$19,$B$7)-MAX($E$19,$B$6))&amp;IF(MAX(0,MIN($F$19,$B$7)-MAX($E$19,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19433,11 +19466,11 @@
         <v/>
       </c>
       <c r="F20" s="70">
-        <f>IF($F$19=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$19,3),EDATE($F$19,3)))</f>
+        <f>IF($F$19=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$19,3),EDATE($F$19,3)))</f>
         <v/>
       </c>
       <c r="G20">
-        <f>TRIM(IF(MAX(0,MIN($F$20,R1_To)-MAX($E$20,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$20,R1_To)-MAX($E$20,R1_From))&amp;IF(MAX(0,MIN($F$20,R1_To)-MAX($E$20,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$20,R2_To)-MAX($E$20,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$20,R2_To)-MAX($E$20,R2_From))&amp;IF(MAX(0,MIN($F$20,R2_To)-MAX($E$20,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$20,R3_To)-MAX($E$20,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$20,R3_To)-MAX($E$20,R3_From))&amp;IF(MAX(0,MIN($F$20,R3_To)-MAX($E$20,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$20,$B$3)-MAX($E$20,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$20,$B$3)-MAX($E$20,$B$2))&amp;IF(MAX(0,MIN($F$20,$B$3)-MAX($E$20,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$20,$B$5)-MAX($E$20,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$20,$B$5)-MAX($E$20,$B$4))&amp;IF(MAX(0,MIN($F$20,$B$5)-MAX($E$20,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$20,$B$7)-MAX($E$20,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$20,$B$7)-MAX($E$20,$B$6))&amp;IF(MAX(0,MIN($F$20,$B$7)-MAX($E$20,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19450,11 +19483,11 @@
         <v/>
       </c>
       <c r="F21" s="70">
-        <f>IF($F$20=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$20,3),EDATE($F$20,3)))</f>
+        <f>IF($F$20=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$20,3),EDATE($F$20,3)))</f>
         <v/>
       </c>
       <c r="G21">
-        <f>TRIM(IF(MAX(0,MIN($F$21,R1_To)-MAX($E$21,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$21,R1_To)-MAX($E$21,R1_From))&amp;IF(MAX(0,MIN($F$21,R1_To)-MAX($E$21,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$21,R2_To)-MAX($E$21,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$21,R2_To)-MAX($E$21,R2_From))&amp;IF(MAX(0,MIN($F$21,R2_To)-MAX($E$21,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$21,R3_To)-MAX($E$21,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$21,R3_To)-MAX($E$21,R3_From))&amp;IF(MAX(0,MIN($F$21,R3_To)-MAX($E$21,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$21,$B$3)-MAX($E$21,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$21,$B$3)-MAX($E$21,$B$2))&amp;IF(MAX(0,MIN($F$21,$B$3)-MAX($E$21,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$21,$B$5)-MAX($E$21,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$21,$B$5)-MAX($E$21,$B$4))&amp;IF(MAX(0,MIN($F$21,$B$5)-MAX($E$21,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$21,$B$7)-MAX($E$21,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$21,$B$7)-MAX($E$21,$B$6))&amp;IF(MAX(0,MIN($F$21,$B$7)-MAX($E$21,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19467,11 +19500,11 @@
         <v/>
       </c>
       <c r="F22" s="70">
-        <f>IF($F$21=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$21,3),EDATE($F$21,3)))</f>
+        <f>IF($F$21=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$21,3),EDATE($F$21,3)))</f>
         <v/>
       </c>
       <c r="G22">
-        <f>TRIM(IF(MAX(0,MIN($F$22,R1_To)-MAX($E$22,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$22,R1_To)-MAX($E$22,R1_From))&amp;IF(MAX(0,MIN($F$22,R1_To)-MAX($E$22,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$22,R2_To)-MAX($E$22,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$22,R2_To)-MAX($E$22,R2_From))&amp;IF(MAX(0,MIN($F$22,R2_To)-MAX($E$22,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$22,R3_To)-MAX($E$22,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$22,R3_To)-MAX($E$22,R3_From))&amp;IF(MAX(0,MIN($F$22,R3_To)-MAX($E$22,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$22,$B$3)-MAX($E$22,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$22,$B$3)-MAX($E$22,$B$2))&amp;IF(MAX(0,MIN($F$22,$B$3)-MAX($E$22,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$22,$B$5)-MAX($E$22,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$22,$B$5)-MAX($E$22,$B$4))&amp;IF(MAX(0,MIN($F$22,$B$5)-MAX($E$22,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$22,$B$7)-MAX($E$22,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$22,$B$7)-MAX($E$22,$B$6))&amp;IF(MAX(0,MIN($F$22,$B$7)-MAX($E$22,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19484,11 +19517,11 @@
         <v/>
       </c>
       <c r="F23" s="70">
-        <f>IF($F$22=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$22,3),EDATE($F$22,3)))</f>
+        <f>IF($F$22=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$22,3),EDATE($F$22,3)))</f>
         <v/>
       </c>
       <c r="G23">
-        <f>TRIM(IF(MAX(0,MIN($F$23,R1_To)-MAX($E$23,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$23,R1_To)-MAX($E$23,R1_From))&amp;IF(MAX(0,MIN($F$23,R1_To)-MAX($E$23,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$23,R2_To)-MAX($E$23,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$23,R2_To)-MAX($E$23,R2_From))&amp;IF(MAX(0,MIN($F$23,R2_To)-MAX($E$23,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$23,R3_To)-MAX($E$23,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$23,R3_To)-MAX($E$23,R3_From))&amp;IF(MAX(0,MIN($F$23,R3_To)-MAX($E$23,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$23,$B$3)-MAX($E$23,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$23,$B$3)-MAX($E$23,$B$2))&amp;IF(MAX(0,MIN($F$23,$B$3)-MAX($E$23,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$23,$B$5)-MAX($E$23,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$23,$B$5)-MAX($E$23,$B$4))&amp;IF(MAX(0,MIN($F$23,$B$5)-MAX($E$23,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$23,$B$7)-MAX($E$23,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$23,$B$7)-MAX($E$23,$B$6))&amp;IF(MAX(0,MIN($F$23,$B$7)-MAX($E$23,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19501,11 +19534,11 @@
         <v/>
       </c>
       <c r="F24" s="70">
-        <f>IF($F$23=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$23,3),EDATE($F$23,3)))</f>
+        <f>IF($F$23=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$23,3),EDATE($F$23,3)))</f>
         <v/>
       </c>
       <c r="G24">
-        <f>TRIM(IF(MAX(0,MIN($F$24,R1_To)-MAX($E$24,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$24,R1_To)-MAX($E$24,R1_From))&amp;IF(MAX(0,MIN($F$24,R1_To)-MAX($E$24,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$24,R2_To)-MAX($E$24,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$24,R2_To)-MAX($E$24,R2_From))&amp;IF(MAX(0,MIN($F$24,R2_To)-MAX($E$24,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$24,R3_To)-MAX($E$24,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$24,R3_To)-MAX($E$24,R3_From))&amp;IF(MAX(0,MIN($F$24,R3_To)-MAX($E$24,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$24,$B$3)-MAX($E$24,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$24,$B$3)-MAX($E$24,$B$2))&amp;IF(MAX(0,MIN($F$24,$B$3)-MAX($E$24,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$24,$B$5)-MAX($E$24,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$24,$B$5)-MAX($E$24,$B$4))&amp;IF(MAX(0,MIN($F$24,$B$5)-MAX($E$24,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$24,$B$7)-MAX($E$24,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$24,$B$7)-MAX($E$24,$B$6))&amp;IF(MAX(0,MIN($F$24,$B$7)-MAX($E$24,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
@@ -19518,11 +19551,11 @@
         <v/>
       </c>
       <c r="F25" s="70">
-        <f>IF($F$24=0,0,IF(Qtr_Mode="Calendar quarter-ends",EOMONTH($F$24,3),EDATE($F$24,3)))</f>
+        <f>IF($F$24=0,0,IF('Loan Statement'!$H$9="Calendar quarter-ends",EOMONTH($F$24,3),EDATE($F$24,3)))</f>
         <v/>
       </c>
       <c r="G25">
-        <f>TRIM(IF(MAX(0,MIN($F$25,R1_To)-MAX($E$25,R1_From))&gt;0,TEXT(Rate_1,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$25,R1_To)-MAX($E$25,R1_From))&amp;IF(MAX(0,MIN($F$25,R1_To)-MAX($E$25,R1_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$25,R2_To)-MAX($E$25,R2_From))&gt;0,TEXT(Rate_2,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$25,R2_To)-MAX($E$25,R2_From))&amp;IF(MAX(0,MIN($F$25,R2_To)-MAX($E$25,R2_From))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$25,R3_To)-MAX($E$25,R3_From))&gt;0,TEXT(Rate_3,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$25,R3_To)-MAX($E$25,R3_From))&amp;IF(MAX(0,MIN($F$25,R3_To)-MAX($E$25,R3_From))=1," day   "," days   "),""))</f>
+        <f>TRIM(IF(MAX(0,MIN($F$25,$B$3)-MAX($E$25,$B$2))&gt;0,TEXT($B$8,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$25,$B$3)-MAX($E$25,$B$2))&amp;IF(MAX(0,MIN($F$25,$B$3)-MAX($E$25,$B$2))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$25,$B$5)-MAX($E$25,$B$4))&gt;0,TEXT($B$9,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$25,$B$5)-MAX($E$25,$B$4))&amp;IF(MAX(0,MIN($F$25,$B$5)-MAX($E$25,$B$4))=1," day   "," days   "),"")&amp;IF(MAX(0,MIN($F$25,$B$7)-MAX($E$25,$B$6))&gt;0,TEXT($B$10,"0.00")&amp;"% for "&amp;MAX(0,MIN($F$25,$B$7)-MAX($E$25,$B$6))&amp;IF(MAX(0,MIN($F$25,$B$7)-MAX($E$25,$B$6))=1," day   "," days   "),""))</f>
         <v/>
       </c>
     </row>
